--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erjav\Desktop\TeideThermal\TeideThermal\teidecode_v1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD164C9-77A6-4CFC-992C-5C08B12207BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B651987-C95F-4C5A-A3C2-50B235221F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes properties" sheetId="1" r:id="rId1"/>
@@ -50,6 +50,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Thermal capacitance
@@ -64,6 +65,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Thermal conductivity
@@ -78,6 +80,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Young Modulus
@@ -92,6 +95,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Distancia entre los centros de cada nodo (distancia recorrida por el flujo del calor)
@@ -109,6 +113,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Superficie que queda expuesta a la luz solar.
@@ -126,6 +131,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Vector normal a la superficie (para la incidencia solar)
@@ -143,6 +149,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Emisividad en infrarrojo
@@ -160,6 +167,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>absortividad (en solar)
@@ -177,6 +185,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>nodos con los que esta conectado el nodo en cuestión. El nodo 0 es el espacio exterior
@@ -191,6 +200,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Calor generado
@@ -205,6 +215,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>======
@@ -223,6 +234,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Thermal capacitance
@@ -237,6 +249,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Superficie que queda expuesta a la luz solar.
@@ -254,6 +267,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Vector normal a la superficie (para la incidencia solar)
@@ -271,6 +285,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Emisividad en infrarrojo
@@ -288,6 +303,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>absortividad (en solar)
@@ -305,6 +321,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>nodos con los que esta conectado el nodo en cuestión. El nodo 0 es el espacio exterior
@@ -319,6 +336,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Calor generado
@@ -333,6 +351,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Thermal conductivity
@@ -347,6 +366,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Distancia entre los centros de cada nodo (distancia recorrida por el flujo del calor)
@@ -364,6 +384,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>======
@@ -397,6 +418,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Interpolated values
@@ -411,6 +433,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>======
@@ -1093,17 +1116,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1114,23 +1140,27 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="17">
@@ -1847,10 +1877,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6981825" cy="4943475"/>
     <xdr:pic>
@@ -1872,7 +1902,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14106525" y="6353175"/>
+          <a:off x="14382750" y="6943725"/>
           <a:ext cx="6981825" cy="4943475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2190,7 +2220,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AD995"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="31.28515625" customWidth="1"/>
@@ -9056,7 +9086,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD990"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
     <col min="2" max="10" width="7" customWidth="1"/>
@@ -43010,7 +43040,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I127"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>

--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B651987-C95F-4C5A-A3C2-50B235221F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1566D7CD-A537-433B-AEF4-67918B0F3E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes properties" sheetId="1" r:id="rId1"/>
     <sheet name="Conductances_between_nodes" sheetId="2" r:id="rId2"/>
     <sheet name="Conductances determination" sheetId="3" r:id="rId3"/>
+    <sheet name="Nodes thermal properties" sheetId="4" r:id="rId4"/>
+    <sheet name="Operation" sheetId="5" r:id="rId5"/>
+    <sheet name="Modes" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -453,7 +456,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="263">
   <si>
     <t>Esta tabla representado el struct con todos los datos de entrada que uso para el satélite,¿que le falta? pues el coeficiente Cp (specific heat capacity ) esta bastamente aproximado y habría que mirar material por material, puede que algo de info útil pueda ser encontrada en la tabla de mecánica</t>
   </si>
@@ -1094,6 +1097,156 @@
   <si>
     <t>1 &amp; 1</t>
   </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Frame 1, +X</t>
+  </si>
+  <si>
+    <t>Frame 2, -X</t>
+  </si>
+  <si>
+    <t>Beam -Y +Z</t>
+  </si>
+  <si>
+    <t>Beam +Y +Z</t>
+  </si>
+  <si>
+    <t>Beam +Y -Z</t>
+  </si>
+  <si>
+    <t>Beam -Y -Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">panel +Z, payload plate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED 1 </t>
+  </si>
+  <si>
+    <t>LED 2</t>
+  </si>
+  <si>
+    <t>LED 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED 4 </t>
+  </si>
+  <si>
+    <t>Node 12, BMS</t>
+  </si>
+  <si>
+    <t>Node 13, Batteries Isolation</t>
+  </si>
+  <si>
+    <t>Node 14, LiFePo4 1</t>
+  </si>
+  <si>
+    <t>Node 15, LiFePo4 3</t>
+  </si>
+  <si>
+    <t>Node 16, LiFePo4 2</t>
+  </si>
+  <si>
+    <t>Node 17, LiFePo4 4</t>
+  </si>
+  <si>
+    <t>Node 18, Cell Litio 1</t>
+  </si>
+  <si>
+    <t>Node 19, Cell Litio 2</t>
+  </si>
+  <si>
+    <t>Node 20, LoMo</t>
+  </si>
+  <si>
+    <t>Node 21, Transceiver(Tx-Rx)</t>
+  </si>
+  <si>
+    <t>Node 22, Antena module</t>
+  </si>
+  <si>
+    <t>Node 23, OBC</t>
+  </si>
+  <si>
+    <t>Node 24, Solar Panel (Y)</t>
+  </si>
+  <si>
+    <t>Node 25, Solar Panel (-Y)</t>
+  </si>
+  <si>
+    <t>Node 26, Solar Panel (X)</t>
+  </si>
+  <si>
+    <t>Node 27, Solar Panel (-X)RBF</t>
+  </si>
+  <si>
+    <t>Node 28, Solar Panel (-Z(antenna))</t>
+  </si>
+  <si>
+    <t>Node 29, EPS de alta</t>
+  </si>
+  <si>
+    <t>Emisivity</t>
+  </si>
+  <si>
+    <t>Absorptivity</t>
+  </si>
+  <si>
+    <t>Mass (kg)</t>
+  </si>
+  <si>
+    <t>Specific Heat (J/(kg*K))</t>
+  </si>
+  <si>
+    <t>Radiative area (m2)</t>
+  </si>
+  <si>
+    <t>Thermal conductivity (W/(mK))</t>
+  </si>
+  <si>
+    <t>Norm x</t>
+  </si>
+  <si>
+    <t>Norm y</t>
+  </si>
+  <si>
+    <t>Norm z</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>Minutes</t>
+  </si>
+  <si>
+    <t>Seconds</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>High Power</t>
+  </si>
+  <si>
+    <t>Low Power</t>
+  </si>
+  <si>
+    <t>Off</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>Radiates? 1=Yes, 0=No</t>
+  </si>
 </sst>
 </file>
 
@@ -1105,11 +1258,18 @@
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1163,7 +1323,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1260,8 +1420,38 @@
         <bgColor rgb="FFCCCCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -1567,163 +1757,735 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="46" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="43" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="54" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -43066,10 +43828,10 @@
         <v>149</v>
       </c>
       <c r="G2" s="32"/>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="130" t="s">
         <v>150</v>
       </c>
-      <c r="I2" s="81"/>
+      <c r="I2" s="131"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="33" t="s">
@@ -44068,4 +44830,2280 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4985A03E-5096-4337-92A3-24224C69AEFA}">
+  <dimension ref="B1:M32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:13" ht="30" customHeight="1" thickBot="1">
+      <c r="B2" s="139" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="140" t="s">
+        <v>245</v>
+      </c>
+      <c r="D2" s="141" t="s">
+        <v>246</v>
+      </c>
+      <c r="E2" s="141" t="s">
+        <v>248</v>
+      </c>
+      <c r="F2" s="141" t="s">
+        <v>247</v>
+      </c>
+      <c r="G2" s="141" t="s">
+        <v>243</v>
+      </c>
+      <c r="H2" s="141" t="s">
+        <v>244</v>
+      </c>
+      <c r="I2" s="141" t="s">
+        <v>249</v>
+      </c>
+      <c r="J2" s="141" t="s">
+        <v>250</v>
+      </c>
+      <c r="K2" s="141" t="s">
+        <v>251</v>
+      </c>
+      <c r="L2" s="141" t="s">
+        <v>262</v>
+      </c>
+      <c r="M2" s="142" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13">
+      <c r="B3" s="143" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="136">
+        <v>4.0280000000000003E-2</v>
+      </c>
+      <c r="D3" s="134">
+        <v>800</v>
+      </c>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="G3" s="134">
+        <v>0.8</v>
+      </c>
+      <c r="H3" s="134">
+        <v>0.8</v>
+      </c>
+      <c r="I3" s="134">
+        <v>1</v>
+      </c>
+      <c r="J3" s="134">
+        <v>0</v>
+      </c>
+      <c r="K3" s="134">
+        <v>0</v>
+      </c>
+      <c r="L3" s="134">
+        <v>1</v>
+      </c>
+      <c r="M3" s="135"/>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" s="144" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="137">
+        <v>4.0280000000000003E-2</v>
+      </c>
+      <c r="D4" s="114">
+        <v>800</v>
+      </c>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="G4" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H4" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I4" s="114">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="114">
+        <v>0</v>
+      </c>
+      <c r="K4" s="114">
+        <v>0</v>
+      </c>
+      <c r="L4" s="114">
+        <v>1</v>
+      </c>
+      <c r="M4" s="132"/>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="144" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="137">
+        <v>7.2909999999999997E-3</v>
+      </c>
+      <c r="D5" s="114">
+        <v>800</v>
+      </c>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="G5" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H5" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I5" s="114">
+        <v>0</v>
+      </c>
+      <c r="J5" s="114">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="114">
+        <v>1</v>
+      </c>
+      <c r="L5" s="114">
+        <v>1</v>
+      </c>
+      <c r="M5" s="132"/>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="144" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="137">
+        <v>7.2909999999999997E-3</v>
+      </c>
+      <c r="D6" s="114">
+        <v>800</v>
+      </c>
+      <c r="E6" s="114"/>
+      <c r="F6" s="114">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="G6" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I6" s="114">
+        <v>0</v>
+      </c>
+      <c r="J6" s="114">
+        <v>1</v>
+      </c>
+      <c r="K6" s="114">
+        <v>1</v>
+      </c>
+      <c r="L6" s="114">
+        <v>1</v>
+      </c>
+      <c r="M6" s="132"/>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="144" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="137">
+        <v>6.4250000000000002E-3</v>
+      </c>
+      <c r="D7" s="114">
+        <v>800</v>
+      </c>
+      <c r="E7" s="114"/>
+      <c r="F7" s="114">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="G7" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H7" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I7" s="114">
+        <v>0</v>
+      </c>
+      <c r="J7" s="114">
+        <v>1</v>
+      </c>
+      <c r="K7" s="114">
+        <v>-1</v>
+      </c>
+      <c r="L7" s="114">
+        <v>1</v>
+      </c>
+      <c r="M7" s="132"/>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="144" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="137">
+        <v>6.4250000000000002E-3</v>
+      </c>
+      <c r="D8" s="114">
+        <v>800</v>
+      </c>
+      <c r="E8" s="114"/>
+      <c r="F8" s="114">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="G8" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H8" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I8" s="114">
+        <v>0</v>
+      </c>
+      <c r="J8" s="114">
+        <v>-1</v>
+      </c>
+      <c r="K8" s="114">
+        <v>-1</v>
+      </c>
+      <c r="L8" s="114">
+        <v>1</v>
+      </c>
+      <c r="M8" s="132"/>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="144" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="137">
+        <v>2.1919999999999999E-2</v>
+      </c>
+      <c r="D9" s="114">
+        <v>800</v>
+      </c>
+      <c r="E9" s="114"/>
+      <c r="F9" s="114">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="G9" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H9" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I9" s="114">
+        <v>0</v>
+      </c>
+      <c r="J9" s="114">
+        <v>0</v>
+      </c>
+      <c r="K9" s="114">
+        <v>1</v>
+      </c>
+      <c r="L9" s="114">
+        <v>1</v>
+      </c>
+      <c r="M9" s="132"/>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="144" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="137">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D10" s="114">
+        <v>800</v>
+      </c>
+      <c r="E10" s="114"/>
+      <c r="F10" s="114">
+        <v>5.7600000000000001E-4</v>
+      </c>
+      <c r="G10" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H10" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I10" s="114">
+        <v>0</v>
+      </c>
+      <c r="J10" s="114">
+        <v>0</v>
+      </c>
+      <c r="K10" s="114">
+        <v>1</v>
+      </c>
+      <c r="L10" s="114">
+        <v>1</v>
+      </c>
+      <c r="M10" s="132"/>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="144" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="137">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D11" s="114">
+        <v>800</v>
+      </c>
+      <c r="E11" s="114"/>
+      <c r="F11" s="114">
+        <v>5.7600000000000001E-4</v>
+      </c>
+      <c r="G11" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I11" s="114">
+        <v>0</v>
+      </c>
+      <c r="J11" s="114">
+        <v>0</v>
+      </c>
+      <c r="K11" s="114">
+        <v>1</v>
+      </c>
+      <c r="L11" s="114">
+        <v>1</v>
+      </c>
+      <c r="M11" s="132"/>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" s="144" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="137">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D12" s="114">
+        <v>800</v>
+      </c>
+      <c r="E12" s="114"/>
+      <c r="F12" s="114">
+        <v>5.7600000000000001E-4</v>
+      </c>
+      <c r="G12" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H12" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I12" s="114">
+        <v>0</v>
+      </c>
+      <c r="J12" s="114">
+        <v>0</v>
+      </c>
+      <c r="K12" s="114">
+        <v>1</v>
+      </c>
+      <c r="L12" s="114">
+        <v>1</v>
+      </c>
+      <c r="M12" s="132"/>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="144" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="137">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D13" s="114">
+        <v>800</v>
+      </c>
+      <c r="E13" s="114"/>
+      <c r="F13" s="114">
+        <v>5.7600000000000001E-4</v>
+      </c>
+      <c r="G13" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H13" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I13" s="114">
+        <v>0</v>
+      </c>
+      <c r="J13" s="114">
+        <v>0</v>
+      </c>
+      <c r="K13" s="114">
+        <v>1</v>
+      </c>
+      <c r="L13" s="114">
+        <v>1</v>
+      </c>
+      <c r="M13" s="132"/>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14" s="144" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="137">
+        <v>2.375E-2</v>
+      </c>
+      <c r="D14" s="114">
+        <v>600</v>
+      </c>
+      <c r="E14" s="114"/>
+      <c r="F14" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="114"/>
+      <c r="L14" s="114">
+        <v>0</v>
+      </c>
+      <c r="M14" s="132"/>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15" s="144" t="s">
+        <v>226</v>
+      </c>
+      <c r="C15" s="137">
+        <v>0.125</v>
+      </c>
+      <c r="D15" s="114">
+        <v>800</v>
+      </c>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="114"/>
+      <c r="L15" s="114">
+        <v>0</v>
+      </c>
+      <c r="M15" s="132"/>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16" s="144" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="137">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D16" s="114">
+        <v>600</v>
+      </c>
+      <c r="E16" s="114"/>
+      <c r="F16" s="114">
+        <v>0.01</v>
+      </c>
+      <c r="G16" s="114"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="114"/>
+      <c r="L16" s="114">
+        <v>0</v>
+      </c>
+      <c r="M16" s="132"/>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="B17" s="144" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="137">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D17" s="114">
+        <v>600</v>
+      </c>
+      <c r="E17" s="114"/>
+      <c r="F17" s="114">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="114"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="114">
+        <v>0</v>
+      </c>
+      <c r="M17" s="132"/>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" s="144" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" s="137">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D18" s="114">
+        <v>600</v>
+      </c>
+      <c r="E18" s="114"/>
+      <c r="F18" s="114">
+        <v>0.1</v>
+      </c>
+      <c r="G18" s="114"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="114"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114"/>
+      <c r="L18" s="114">
+        <v>0</v>
+      </c>
+      <c r="M18" s="132"/>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" s="144" t="s">
+        <v>230</v>
+      </c>
+      <c r="C19" s="137">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D19" s="114">
+        <v>600</v>
+      </c>
+      <c r="E19" s="114"/>
+      <c r="F19" s="114">
+        <v>0.1</v>
+      </c>
+      <c r="G19" s="114"/>
+      <c r="H19" s="114"/>
+      <c r="I19" s="114"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="114"/>
+      <c r="L19" s="114">
+        <v>0</v>
+      </c>
+      <c r="M19" s="132"/>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="144" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" s="137">
+        <v>0.05</v>
+      </c>
+      <c r="D20" s="114">
+        <v>600</v>
+      </c>
+      <c r="E20" s="114"/>
+      <c r="F20" s="114">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="114"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="114"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="114"/>
+      <c r="L20" s="114">
+        <v>0</v>
+      </c>
+      <c r="M20" s="132"/>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="144" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" s="137">
+        <v>0.05</v>
+      </c>
+      <c r="D21" s="114">
+        <v>600</v>
+      </c>
+      <c r="E21" s="114"/>
+      <c r="F21" s="114">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="114"/>
+      <c r="H21" s="114"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="114">
+        <v>0</v>
+      </c>
+      <c r="M21" s="132"/>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="B22" s="144" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" s="137">
+        <v>3.8490000000000003E-2</v>
+      </c>
+      <c r="D22" s="114">
+        <v>600</v>
+      </c>
+      <c r="E22" s="114"/>
+      <c r="F22" s="114">
+        <v>8.6E-3</v>
+      </c>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="114">
+        <v>0</v>
+      </c>
+      <c r="M22" s="132"/>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="B23" s="144" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="137">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="D23" s="114">
+        <v>600</v>
+      </c>
+      <c r="E23" s="114"/>
+      <c r="F23" s="114">
+        <v>8.6E-3</v>
+      </c>
+      <c r="G23" s="114"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="114">
+        <v>0</v>
+      </c>
+      <c r="M23" s="132"/>
+    </row>
+    <row r="24" spans="2:13">
+      <c r="B24" s="144" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="137">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="D24" s="114">
+        <v>600</v>
+      </c>
+      <c r="E24" s="114">
+        <v>15</v>
+      </c>
+      <c r="F24" s="114">
+        <v>0.08</v>
+      </c>
+      <c r="G24" s="114"/>
+      <c r="H24" s="114"/>
+      <c r="I24" s="114"/>
+      <c r="J24" s="114"/>
+      <c r="K24" s="114"/>
+      <c r="L24" s="114">
+        <v>0</v>
+      </c>
+      <c r="M24" s="132">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="B25" s="144" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="137">
+        <v>2.4E-2</v>
+      </c>
+      <c r="D25" s="114">
+        <v>600</v>
+      </c>
+      <c r="E25" s="114"/>
+      <c r="F25" s="114">
+        <v>0.33</v>
+      </c>
+      <c r="G25" s="114"/>
+      <c r="H25" s="114"/>
+      <c r="I25" s="114"/>
+      <c r="J25" s="114"/>
+      <c r="K25" s="114"/>
+      <c r="L25" s="114">
+        <v>0</v>
+      </c>
+      <c r="M25" s="132"/>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="B26" s="144" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="137">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="D26" s="114">
+        <v>600</v>
+      </c>
+      <c r="E26" s="114">
+        <v>15</v>
+      </c>
+      <c r="F26" s="114">
+        <v>8.0940000000000005E-3</v>
+      </c>
+      <c r="G26" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H26" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I26" s="114">
+        <v>0</v>
+      </c>
+      <c r="J26" s="114">
+        <v>1</v>
+      </c>
+      <c r="K26" s="114">
+        <v>0</v>
+      </c>
+      <c r="L26" s="114">
+        <v>1</v>
+      </c>
+      <c r="M26" s="132">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="B27" s="144" t="s">
+        <v>238</v>
+      </c>
+      <c r="C27" s="137">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="D27" s="114">
+        <v>600</v>
+      </c>
+      <c r="E27" s="114">
+        <v>15</v>
+      </c>
+      <c r="F27" s="114">
+        <v>8.0940000000000005E-3</v>
+      </c>
+      <c r="G27" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H27" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I27" s="114">
+        <v>0</v>
+      </c>
+      <c r="J27" s="114">
+        <v>-1</v>
+      </c>
+      <c r="K27" s="114">
+        <v>0</v>
+      </c>
+      <c r="L27" s="114">
+        <v>1</v>
+      </c>
+      <c r="M27" s="132">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="B28" s="144" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="137">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D28" s="114">
+        <v>600</v>
+      </c>
+      <c r="E28" s="114">
+        <v>15</v>
+      </c>
+      <c r="F28" s="114">
+        <v>8.0940000000000005E-3</v>
+      </c>
+      <c r="G28" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H28" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I28" s="114">
+        <v>1</v>
+      </c>
+      <c r="J28" s="114">
+        <v>0</v>
+      </c>
+      <c r="K28" s="114">
+        <v>0</v>
+      </c>
+      <c r="L28" s="114">
+        <v>1</v>
+      </c>
+      <c r="M28" s="132">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
+      <c r="B29" s="144" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="137">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="D29" s="114">
+        <v>600</v>
+      </c>
+      <c r="E29" s="114">
+        <v>15</v>
+      </c>
+      <c r="F29" s="114">
+        <v>8.0940000000000005E-3</v>
+      </c>
+      <c r="G29" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H29" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I29" s="114">
+        <v>-1</v>
+      </c>
+      <c r="J29" s="114">
+        <v>0</v>
+      </c>
+      <c r="K29" s="114">
+        <v>0</v>
+      </c>
+      <c r="L29" s="114">
+        <v>1</v>
+      </c>
+      <c r="M29" s="132">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="B30" s="144" t="s">
+        <v>241</v>
+      </c>
+      <c r="C30" s="137">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="D30" s="114">
+        <v>600</v>
+      </c>
+      <c r="E30" s="114">
+        <v>15</v>
+      </c>
+      <c r="F30" s="114">
+        <v>8.4469999999999996E-3</v>
+      </c>
+      <c r="G30" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="H30" s="114">
+        <v>0.8</v>
+      </c>
+      <c r="I30" s="114">
+        <v>0</v>
+      </c>
+      <c r="J30" s="114">
+        <v>0</v>
+      </c>
+      <c r="K30" s="114">
+        <v>-1</v>
+      </c>
+      <c r="L30" s="114">
+        <v>1</v>
+      </c>
+      <c r="M30" s="132">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B31" s="145" t="s">
+        <v>242</v>
+      </c>
+      <c r="C31" s="138">
+        <v>0.04</v>
+      </c>
+      <c r="D31" s="117">
+        <v>600</v>
+      </c>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117">
+        <v>0.01</v>
+      </c>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="117">
+        <v>0</v>
+      </c>
+      <c r="M31" s="133"/>
+    </row>
+    <row r="32" spans="2:13">
+      <c r="B32" s="80"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4723E147-5D28-48F2-9A19-B61306348D73}">
+  <dimension ref="A1:N37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.75" thickBot="1"/>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1">
+      <c r="B2" s="96" t="s">
+        <v>257</v>
+      </c>
+      <c r="C2" s="88" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" s="87" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="87" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="97" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2" s="101"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="B3" s="91" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="94">
+        <f>C4+C5*60+C6*3600+C7*3600*24</f>
+        <v>3600</v>
+      </c>
+      <c r="D3" s="95">
+        <f>C3+D4+D5*60+D6*3600+D7*3600*24</f>
+        <v>3720</v>
+      </c>
+      <c r="E3" s="95">
+        <f t="shared" ref="E3" si="0">D3+E4+E5*60+E6*3600+E7*3600*24</f>
+        <v>10920</v>
+      </c>
+      <c r="F3" s="98">
+        <f>E3+F4+F5*60+F6*3600+F7*3600*24</f>
+        <v>18120</v>
+      </c>
+      <c r="G3" s="101"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="B4" s="92" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="89"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="101"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="B5" s="92" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="89"/>
+      <c r="D5" s="84">
+        <v>2</v>
+      </c>
+      <c r="E5" s="83"/>
+      <c r="F5" s="99">
+        <v>0</v>
+      </c>
+      <c r="G5" s="101"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="92" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="89">
+        <v>1</v>
+      </c>
+      <c r="D6" s="84"/>
+      <c r="E6" s="83">
+        <v>2</v>
+      </c>
+      <c r="F6" s="99">
+        <v>2</v>
+      </c>
+      <c r="G6" s="101"/>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" thickBot="1">
+      <c r="B7" s="93" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="90"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="101"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="82">
+        <v>1</v>
+      </c>
+      <c r="B8" s="102" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A8+1)</f>
+        <v>Frame 1, +X</v>
+      </c>
+      <c r="C8" s="103">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="104">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="104">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="105">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="101"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="82">
+        <v>2</v>
+      </c>
+      <c r="B9" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A9+1)</f>
+        <v>Frame 2, -X</v>
+      </c>
+      <c r="C9" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="101"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="82">
+        <v>3</v>
+      </c>
+      <c r="B10" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A10+1)</f>
+        <v>Beam -Y +Z</v>
+      </c>
+      <c r="C10" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="101"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="82">
+        <v>4</v>
+      </c>
+      <c r="B11" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A11+1)</f>
+        <v>Beam +Y +Z</v>
+      </c>
+      <c r="C11" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="101"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="82">
+        <v>5</v>
+      </c>
+      <c r="B12" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A12+1)</f>
+        <v>Beam +Y -Z</v>
+      </c>
+      <c r="C12" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="101"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="82">
+        <v>6</v>
+      </c>
+      <c r="B13" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A13+1)</f>
+        <v>Beam -Y -Z</v>
+      </c>
+      <c r="C13" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="101"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="82">
+        <v>7</v>
+      </c>
+      <c r="B14" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A14+1)</f>
+        <v xml:space="preserve">panel +Z, payload plate </v>
+      </c>
+      <c r="C14" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="101"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="82">
+        <v>8</v>
+      </c>
+      <c r="B15" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A15+1)</f>
+        <v xml:space="preserve">LED 1 </v>
+      </c>
+      <c r="C15" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A15+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A15+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="E15" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A15+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A15+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G15" s="101"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="82">
+        <v>9</v>
+      </c>
+      <c r="B16" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A16+1)</f>
+        <v>LED 2</v>
+      </c>
+      <c r="C16" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A16+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A16+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="E16" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A16+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A16+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G16" s="101"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="82">
+        <v>10</v>
+      </c>
+      <c r="B17" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A17+1)</f>
+        <v>LED 3</v>
+      </c>
+      <c r="C17" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A17+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A17+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="E17" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A17+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A17+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G17" s="101"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="82">
+        <v>11</v>
+      </c>
+      <c r="B18" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A18+1)</f>
+        <v xml:space="preserve">LED 4 </v>
+      </c>
+      <c r="C18" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A18+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A18+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="E18" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A18+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A18+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G18" s="101"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="82">
+        <v>12</v>
+      </c>
+      <c r="B19" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A19+1)</f>
+        <v>Node 12, BMS</v>
+      </c>
+      <c r="C19" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="101"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="82">
+        <v>13</v>
+      </c>
+      <c r="B20" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A20+1)</f>
+        <v>Node 13, Batteries Isolation</v>
+      </c>
+      <c r="C20" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="101"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="82">
+        <v>14</v>
+      </c>
+      <c r="B21" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A21+1)</f>
+        <v>Node 14, LiFePo4 1</v>
+      </c>
+      <c r="C21" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="101"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="82">
+        <v>15</v>
+      </c>
+      <c r="B22" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A22+1)</f>
+        <v>Node 15, LiFePo4 3</v>
+      </c>
+      <c r="C22" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="101"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="82">
+        <v>16</v>
+      </c>
+      <c r="B23" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A23+1)</f>
+        <v>Node 16, LiFePo4 2</v>
+      </c>
+      <c r="C23" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="101"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="82">
+        <v>17</v>
+      </c>
+      <c r="B24" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A24+1)</f>
+        <v>Node 17, LiFePo4 4</v>
+      </c>
+      <c r="C24" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="101"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="82">
+        <v>18</v>
+      </c>
+      <c r="B25" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A25+1)</f>
+        <v>Node 18, Cell Litio 1</v>
+      </c>
+      <c r="C25" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="101"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="82">
+        <v>19</v>
+      </c>
+      <c r="B26" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A26+1)</f>
+        <v>Node 19, Cell Litio 2</v>
+      </c>
+      <c r="C26" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="101"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="82">
+        <v>20</v>
+      </c>
+      <c r="B27" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A27+1)</f>
+        <v>Node 20, LoMo</v>
+      </c>
+      <c r="C27" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="101"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="82">
+        <v>21</v>
+      </c>
+      <c r="B28" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A28+1)</f>
+        <v>Node 21, Transceiver(Tx-Rx)</v>
+      </c>
+      <c r="C28" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="101"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="82">
+        <v>22</v>
+      </c>
+      <c r="B29" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A29+1)</f>
+        <v>Node 22, Antena module</v>
+      </c>
+      <c r="C29" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="101"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="82">
+        <v>23</v>
+      </c>
+      <c r="B30" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A30+1)</f>
+        <v>Node 23, OBC</v>
+      </c>
+      <c r="C30" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="101"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="82">
+        <v>24</v>
+      </c>
+      <c r="B31" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A31+1)</f>
+        <v>Node 24, Solar Panel (Y)</v>
+      </c>
+      <c r="C31" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="101"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="82">
+        <v>25</v>
+      </c>
+      <c r="B32" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A32+1)</f>
+        <v>Node 25, Solar Panel (-Y)</v>
+      </c>
+      <c r="C32" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="101"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="82">
+        <v>26</v>
+      </c>
+      <c r="B33" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A33+1)</f>
+        <v>Node 26, Solar Panel (X)</v>
+      </c>
+      <c r="C33" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="101"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="82">
+        <v>27</v>
+      </c>
+      <c r="B34" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A34+1)</f>
+        <v>Node 27, Solar Panel (-X)RBF</v>
+      </c>
+      <c r="C34" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="101"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="82">
+        <v>28</v>
+      </c>
+      <c r="B35" s="106" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A35+1)</f>
+        <v>Node 28, Solar Panel (-Z(antenna))</v>
+      </c>
+      <c r="C35" s="107">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="108">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="108">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="109">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="101"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A36" s="82">
+        <v>29</v>
+      </c>
+      <c r="B36" s="110" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A36+1)</f>
+        <v>Node 29, EPS de alta</v>
+      </c>
+      <c r="C36" s="111">
+        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="112">
+        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="112">
+        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="113">
+        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="101"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="B37" s="80"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B005E130-2D16-4A0C-8BB3-2172273CEA1D}">
+  <dimension ref="B1:F31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:6" ht="15.75" thickBot="1">
+      <c r="B2" s="126" t="s">
+        <v>257</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" s="118" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="122" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" s="101"/>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="B3" s="127" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="119">
+        <v>0</v>
+      </c>
+      <c r="D3" s="120">
+        <v>0</v>
+      </c>
+      <c r="E3" s="123">
+        <v>0</v>
+      </c>
+      <c r="F3" s="101"/>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="128" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="115">
+        <v>0</v>
+      </c>
+      <c r="D4" s="114">
+        <v>0</v>
+      </c>
+      <c r="E4" s="124">
+        <v>0</v>
+      </c>
+      <c r="F4" s="101"/>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="128" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="115">
+        <v>0</v>
+      </c>
+      <c r="D5" s="114">
+        <v>0</v>
+      </c>
+      <c r="E5" s="124">
+        <v>0</v>
+      </c>
+      <c r="F5" s="101"/>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="128" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="115">
+        <v>0</v>
+      </c>
+      <c r="D6" s="114">
+        <v>0</v>
+      </c>
+      <c r="E6" s="124">
+        <v>0</v>
+      </c>
+      <c r="F6" s="101"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="128" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="115">
+        <v>0</v>
+      </c>
+      <c r="D7" s="114">
+        <v>0</v>
+      </c>
+      <c r="E7" s="124">
+        <v>0</v>
+      </c>
+      <c r="F7" s="101"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="128" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="115">
+        <v>0</v>
+      </c>
+      <c r="D8" s="114">
+        <v>0</v>
+      </c>
+      <c r="E8" s="124">
+        <v>0</v>
+      </c>
+      <c r="F8" s="101"/>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="128" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="115">
+        <v>0</v>
+      </c>
+      <c r="D9" s="114">
+        <v>0</v>
+      </c>
+      <c r="E9" s="124">
+        <v>0</v>
+      </c>
+      <c r="F9" s="101"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="128" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="115">
+        <v>0</v>
+      </c>
+      <c r="D10" s="114">
+        <v>200</v>
+      </c>
+      <c r="E10" s="124">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F10" s="101"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="128" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="115">
+        <v>0</v>
+      </c>
+      <c r="D11" s="114">
+        <v>200</v>
+      </c>
+      <c r="E11" s="124">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F11" s="101"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="128" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="115">
+        <v>0</v>
+      </c>
+      <c r="D12" s="114">
+        <v>200</v>
+      </c>
+      <c r="E12" s="124">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F12" s="101"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="128" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="115">
+        <v>0</v>
+      </c>
+      <c r="D13" s="114">
+        <v>200</v>
+      </c>
+      <c r="E13" s="124">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F13" s="101"/>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="128" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="115">
+        <v>0</v>
+      </c>
+      <c r="D14" s="114">
+        <v>0</v>
+      </c>
+      <c r="E14" s="124">
+        <v>0</v>
+      </c>
+      <c r="F14" s="101"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="128" t="s">
+        <v>226</v>
+      </c>
+      <c r="C15" s="115">
+        <v>0</v>
+      </c>
+      <c r="D15" s="114">
+        <v>0</v>
+      </c>
+      <c r="E15" s="124">
+        <v>0</v>
+      </c>
+      <c r="F15" s="101"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="128" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="115">
+        <v>0</v>
+      </c>
+      <c r="D16" s="114">
+        <v>0</v>
+      </c>
+      <c r="E16" s="124">
+        <v>0</v>
+      </c>
+      <c r="F16" s="101"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="128" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="115">
+        <v>0</v>
+      </c>
+      <c r="D17" s="114">
+        <v>0</v>
+      </c>
+      <c r="E17" s="124">
+        <v>0</v>
+      </c>
+      <c r="F17" s="101"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="128" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" s="115">
+        <v>0</v>
+      </c>
+      <c r="D18" s="114">
+        <v>0</v>
+      </c>
+      <c r="E18" s="124">
+        <v>0</v>
+      </c>
+      <c r="F18" s="101"/>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="128" t="s">
+        <v>230</v>
+      </c>
+      <c r="C19" s="115">
+        <v>0</v>
+      </c>
+      <c r="D19" s="114">
+        <v>0</v>
+      </c>
+      <c r="E19" s="124">
+        <v>0</v>
+      </c>
+      <c r="F19" s="101"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="128" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" s="115">
+        <v>0</v>
+      </c>
+      <c r="D20" s="114">
+        <v>0</v>
+      </c>
+      <c r="E20" s="124">
+        <v>0</v>
+      </c>
+      <c r="F20" s="101"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="128" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" s="115">
+        <v>0</v>
+      </c>
+      <c r="D21" s="114">
+        <v>0</v>
+      </c>
+      <c r="E21" s="124">
+        <v>0</v>
+      </c>
+      <c r="F21" s="101"/>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="128" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" s="115">
+        <v>0</v>
+      </c>
+      <c r="D22" s="114">
+        <v>0</v>
+      </c>
+      <c r="E22" s="124">
+        <v>0</v>
+      </c>
+      <c r="F22" s="101"/>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="128" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="115">
+        <v>0</v>
+      </c>
+      <c r="D23" s="114">
+        <v>0</v>
+      </c>
+      <c r="E23" s="124">
+        <v>0</v>
+      </c>
+      <c r="F23" s="101"/>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="128" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="115">
+        <v>0</v>
+      </c>
+      <c r="D24" s="114">
+        <v>0</v>
+      </c>
+      <c r="E24" s="124">
+        <v>0</v>
+      </c>
+      <c r="F24" s="101"/>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="128" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="115">
+        <v>0</v>
+      </c>
+      <c r="D25" s="114">
+        <v>0</v>
+      </c>
+      <c r="E25" s="124">
+        <v>0</v>
+      </c>
+      <c r="F25" s="101"/>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="128" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="115">
+        <v>0</v>
+      </c>
+      <c r="D26" s="114">
+        <v>0</v>
+      </c>
+      <c r="E26" s="124">
+        <v>0</v>
+      </c>
+      <c r="F26" s="101"/>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="128" t="s">
+        <v>238</v>
+      </c>
+      <c r="C27" s="115">
+        <v>0</v>
+      </c>
+      <c r="D27" s="114">
+        <v>0</v>
+      </c>
+      <c r="E27" s="124">
+        <v>0</v>
+      </c>
+      <c r="F27" s="101"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="128" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="115">
+        <v>0</v>
+      </c>
+      <c r="D28" s="114">
+        <v>0</v>
+      </c>
+      <c r="E28" s="124">
+        <v>0</v>
+      </c>
+      <c r="F28" s="101"/>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="128" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="115">
+        <v>0</v>
+      </c>
+      <c r="D29" s="114">
+        <v>0</v>
+      </c>
+      <c r="E29" s="124">
+        <v>0</v>
+      </c>
+      <c r="F29" s="101"/>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="128" t="s">
+        <v>241</v>
+      </c>
+      <c r="C30" s="115">
+        <v>0</v>
+      </c>
+      <c r="D30" s="114">
+        <v>0</v>
+      </c>
+      <c r="E30" s="124">
+        <v>0</v>
+      </c>
+      <c r="F30" s="101"/>
+    </row>
+    <row r="31" spans="2:6" ht="15.75" thickBot="1">
+      <c r="B31" s="129" t="s">
+        <v>242</v>
+      </c>
+      <c r="C31" s="116">
+        <v>0</v>
+      </c>
+      <c r="D31" s="117">
+        <v>0</v>
+      </c>
+      <c r="E31" s="125">
+        <v>0</v>
+      </c>
+      <c r="F31" s="101"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1566D7CD-A537-433B-AEF4-67918B0F3E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DA363B-02D6-471C-A546-574AA58E41CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes properties" sheetId="1" r:id="rId1"/>
-    <sheet name="Conductances_between_nodes" sheetId="2" r:id="rId2"/>
-    <sheet name="Conductances determination" sheetId="3" r:id="rId3"/>
-    <sheet name="Nodes thermal properties" sheetId="4" r:id="rId4"/>
-    <sheet name="Operation" sheetId="5" r:id="rId5"/>
-    <sheet name="Modes" sheetId="6" r:id="rId6"/>
+    <sheet name="Conductances determination" sheetId="3" r:id="rId2"/>
+    <sheet name="Startup Parameters" sheetId="7" r:id="rId3"/>
+    <sheet name="Operation" sheetId="5" r:id="rId4"/>
+    <sheet name="Modes" sheetId="6" r:id="rId5"/>
+    <sheet name="Nodes thermal properties" sheetId="4" r:id="rId6"/>
+    <sheet name="Conductances_between_nodes" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataSignature="AMtx7mjKFLR0Am3JTZ+8bb0VcOSu/VdiBw=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataSignature="AMtx7mjKFLR0Am3JTZ+8bb0VcOSu/VdiBw=="/>
     </ext>
   </extLst>
 </workbook>
@@ -456,7 +457,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="268">
   <si>
     <t>Esta tabla representado el struct con todos los datos de entrada que uso para el satélite,¿que le falta? pues el coeficiente Cp (specific heat capacity ) esta bastamente aproximado y habría que mirar material por material, puede que algo de info útil pueda ser encontrada en la tabla de mecánica</t>
   </si>
@@ -1247,6 +1248,21 @@
   <si>
     <t>Radiates? 1=Yes, 0=No</t>
   </si>
+  <si>
+    <t>dt (s)</t>
+  </si>
+  <si>
+    <t>Starting temperature (K)</t>
+  </si>
+  <si>
+    <t>Vacuum temperature (K)</t>
+  </si>
+  <si>
+    <t>Solar radiation and albedo (1=Yes, 0=No)</t>
+  </si>
+  <si>
+    <t>Radiation to enviroment (1=Yes, 0=No)</t>
+  </si>
 </sst>
 </file>
 
@@ -1258,11 +1274,18 @@
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1428,19 +1451,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1450,8 +1461,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="55">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -2014,19 +2037,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -2035,19 +2045,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2085,17 +2082,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2193,167 +2179,280 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2362,130 +2461,157 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="41" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="58" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="46" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="43" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="54" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2564,6 +2690,45 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>771525</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6981825" cy="4943475"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image3.png" title="Imagen">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2667,45 +2832,6 @@
           <a:off x="14382750" y="6943725"/>
           <a:ext cx="6981825" cy="4943475"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>771525</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6981825" cy="4943475"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image3.png" title="Imagen">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -9846,6 +9972,3772 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:I127"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="25.28515625" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="6" max="6" width="21.28515625" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" s="29"/>
+      <c r="I1" s="30"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="32"/>
+      <c r="H2" s="118" t="s">
+        <v>150</v>
+      </c>
+      <c r="I2" s="119"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="35">
+        <v>1.57</v>
+      </c>
+      <c r="I3" s="36">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="38">
+        <v>2.5</v>
+      </c>
+      <c r="H4" s="39">
+        <v>15.17</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="42">
+        <v>2.8</v>
+      </c>
+      <c r="H5" s="43">
+        <v>12.6</v>
+      </c>
+      <c r="I5" s="44" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="G6" s="38">
+        <v>3</v>
+      </c>
+      <c r="H6" s="39">
+        <f>((H5-H7)/(G5-G7))*(G6-G7)+H7</f>
+        <v>10.888571428571428</v>
+      </c>
+      <c r="I6" s="40">
+        <f>((I7-I8)/(G7-G8))*(G6-G7)+I7</f>
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="G7" s="42">
+        <v>3.5</v>
+      </c>
+      <c r="H7" s="43">
+        <v>6.61</v>
+      </c>
+      <c r="I7" s="44">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="47">
+        <v>4.2</v>
+      </c>
+      <c r="H8" s="48">
+        <v>4.5</v>
+      </c>
+      <c r="I8" s="49">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="54">
+        <v>7.762E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="53">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B16" s="55">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="57">
+        <f>1/B16</f>
+        <v>0.37037037037037035</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="59">
+        <f>B12*B17</f>
+        <v>0.37037037037037035</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="60" t="s">
+        <v>161</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="54">
+        <v>4.8523999999999998E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="55">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="62" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" s="63">
+        <f>B24*B23</f>
+        <v>0.24262</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" s="46" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="54">
+        <v>1.302E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B31" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B33" s="53" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="53">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" s="55">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" s="64">
+        <f>1/B35</f>
+        <v>9.1827364554637275E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B37" s="59">
+        <f>B31*B36</f>
+        <v>0.3673094582185491</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="F38" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" s="46" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B40" s="51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="53" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="54">
+        <v>3.9569999999999996E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="53" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="B46" s="53">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B47" s="55">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B48" s="64">
+        <f>1/B47</f>
+        <v>9.1827364554637275E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B49" s="59">
+        <f>B43*B48</f>
+        <v>0.18365472910927455</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" s="46" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B52" s="51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" s="53" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="54">
+        <v>1.6140000000000002E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B55" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" s="53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" s="53" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="B58" s="53">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B59" s="55">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B60" s="57">
+        <f>1/B59</f>
+        <v>9.1827364554637275E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B61" s="59">
+        <f>B55*B60</f>
+        <v>0.18365472910927455</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" s="46" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B64" s="51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B65" s="53" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" s="54" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B67" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B68" s="53" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B69" s="53" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="B70" s="53">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B71" s="55">
+        <v>15.17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B72" s="57">
+        <f>1/B71</f>
+        <v>6.5919578114700061E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B73" s="59">
+        <f>B67*B72</f>
+        <v>0.26367831245880025</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B75" s="66" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="B76" s="68" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B77" s="53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="54">
+        <v>5.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B79" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B80" s="53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81" s="53" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="B82" s="53">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B83" s="55">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B84" s="53">
+        <f>1/B83</f>
+        <v>9.1827364554637275E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="B85" s="55">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B86" s="59">
+        <f>B79*B84+B85*B78</f>
+        <v>5.6836547291092749</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="B88" s="46" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B89" s="51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B90" s="53" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B91" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B92" s="53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B93" s="53">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="B94" s="53">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B95" s="55">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B96" s="57">
+        <f>1/B95</f>
+        <v>9.1827364554637275E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B97" s="59">
+        <f>B91*B96</f>
+        <v>0.3673094582185491</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="B99" s="46" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B100" s="51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B101" s="53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B102" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B103" s="53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B104" s="53" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="B105" s="53">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B106" s="55">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B107" s="57">
+        <f>1/B106</f>
+        <v>9.1827364554637275E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B108" s="59">
+        <f>B102*B107</f>
+        <v>0.18365472910927455</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="65" t="s">
+        <v>206</v>
+      </c>
+      <c r="B110" s="66" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="69" t="s">
+        <v>161</v>
+      </c>
+      <c r="B111" s="70" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B112" s="53" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B113" s="54">
+        <v>3.7569999999999999E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="B114" s="55">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B115" s="59">
+        <f>B114*B113</f>
+        <v>37.57</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="B117" s="46" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B118" s="51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B119" s="53" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B120" s="54" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="B121" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="B122" s="53" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B123" s="53" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="B124" s="53">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B125" s="55">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="B126" s="57">
+        <f>1/B125</f>
+        <v>9.1827364554637275E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B127" s="59">
+        <f>B121*B126</f>
+        <v>0.3673094582185491</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFF58F4-2122-4D7A-8536-BCD5250BA286}">
+  <dimension ref="B1:F3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:6" ht="45">
+      <c r="B2" s="146" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="147" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2" s="147" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" s="147" t="s">
+        <v>264</v>
+      </c>
+      <c r="F2" s="148" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="15.75" thickBot="1">
+      <c r="B3" s="136">
+        <v>1</v>
+      </c>
+      <c r="C3" s="85">
+        <v>1</v>
+      </c>
+      <c r="D3" s="85">
+        <v>0</v>
+      </c>
+      <c r="E3" s="85">
+        <v>0</v>
+      </c>
+      <c r="F3" s="137">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4723E147-5D28-48F2-9A19-B61306348D73}">
+  <dimension ref="A1:N37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.75" thickBot="1"/>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1">
+      <c r="B2" s="141" t="s">
+        <v>257</v>
+      </c>
+      <c r="C2" s="87" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="125" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="93" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2" s="126"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="B3" s="89" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="91">
+        <f>C4+C5*60+C6*3600+C7*3600*24</f>
+        <v>3600</v>
+      </c>
+      <c r="D3" s="92">
+        <f>C3+D4+D5*60+D6*3600+D7*3600*24</f>
+        <v>3720</v>
+      </c>
+      <c r="E3" s="92">
+        <f t="shared" ref="E3" si="0">D3+E4+E5*60+E6*3600+E7*3600*24</f>
+        <v>10920</v>
+      </c>
+      <c r="F3" s="94">
+        <f>E3+F4+F5*60+F6*3600+F7*3600*24</f>
+        <v>18120</v>
+      </c>
+      <c r="G3" s="96"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="B4" s="90" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="88"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="96"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="B5" s="90" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="88"/>
+      <c r="D5" s="84">
+        <v>2</v>
+      </c>
+      <c r="E5" s="83"/>
+      <c r="F5" s="95">
+        <v>0</v>
+      </c>
+      <c r="G5" s="96"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="90" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="88">
+        <v>1</v>
+      </c>
+      <c r="D6" s="84"/>
+      <c r="E6" s="83">
+        <v>2</v>
+      </c>
+      <c r="F6" s="95">
+        <v>2</v>
+      </c>
+      <c r="G6" s="96"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7" s="120" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="121"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="96"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="82">
+        <v>1</v>
+      </c>
+      <c r="B8" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A8+1)</f>
+        <v>Frame 1, +X</v>
+      </c>
+      <c r="C8" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="100"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="100"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="82">
+        <v>2</v>
+      </c>
+      <c r="B9" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A9+1)</f>
+        <v>Frame 2, -X</v>
+      </c>
+      <c r="C9" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="100"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="82">
+        <v>3</v>
+      </c>
+      <c r="B10" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A10+1)</f>
+        <v>Beam -Y +Z</v>
+      </c>
+      <c r="C10" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="100"/>
+      <c r="H10" s="100"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="82">
+        <v>4</v>
+      </c>
+      <c r="B11" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A11+1)</f>
+        <v>Beam +Y +Z</v>
+      </c>
+      <c r="C11" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="82">
+        <v>5</v>
+      </c>
+      <c r="B12" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A12+1)</f>
+        <v>Beam +Y -Z</v>
+      </c>
+      <c r="C12" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="100"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="82">
+        <v>6</v>
+      </c>
+      <c r="B13" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A13+1)</f>
+        <v>Beam -Y -Z</v>
+      </c>
+      <c r="C13" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="82">
+        <v>7</v>
+      </c>
+      <c r="B14" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A14+1)</f>
+        <v xml:space="preserve">panel +Z, payload plate </v>
+      </c>
+      <c r="C14" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="100"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="100"/>
+      <c r="K14" s="100"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="82">
+        <v>8</v>
+      </c>
+      <c r="B15" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A15+1)</f>
+        <v xml:space="preserve">LED 1 </v>
+      </c>
+      <c r="C15" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="E15" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G15" s="100"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="100"/>
+      <c r="K15" s="100"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="82">
+        <v>9</v>
+      </c>
+      <c r="B16" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A16+1)</f>
+        <v>LED 2</v>
+      </c>
+      <c r="C16" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="E16" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="100"/>
+      <c r="J16" s="100"/>
+      <c r="K16" s="100"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="82">
+        <v>10</v>
+      </c>
+      <c r="B17" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A17+1)</f>
+        <v>LED 3</v>
+      </c>
+      <c r="C17" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="E17" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="82">
+        <v>11</v>
+      </c>
+      <c r="B18" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A18+1)</f>
+        <v xml:space="preserve">LED 4 </v>
+      </c>
+      <c r="C18" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="E18" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="82">
+        <v>12</v>
+      </c>
+      <c r="B19" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A19+1)</f>
+        <v>Node 12, BMS</v>
+      </c>
+      <c r="C19" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="100"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="82">
+        <v>13</v>
+      </c>
+      <c r="B20" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A20+1)</f>
+        <v>Node 13, Batteries Isolation</v>
+      </c>
+      <c r="C20" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="82">
+        <v>14</v>
+      </c>
+      <c r="B21" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A21+1)</f>
+        <v>Node 14, LiFePo4 1</v>
+      </c>
+      <c r="C21" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="100"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="100"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="82">
+        <v>15</v>
+      </c>
+      <c r="B22" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A22+1)</f>
+        <v>Node 15, LiFePo4 3</v>
+      </c>
+      <c r="C22" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="100"/>
+      <c r="H22" s="100"/>
+      <c r="I22" s="100"/>
+      <c r="J22" s="100"/>
+      <c r="K22" s="100"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="82">
+        <v>16</v>
+      </c>
+      <c r="B23" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A23+1)</f>
+        <v>Node 16, LiFePo4 2</v>
+      </c>
+      <c r="C23" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="100"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="82">
+        <v>17</v>
+      </c>
+      <c r="B24" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A24+1)</f>
+        <v>Node 17, LiFePo4 4</v>
+      </c>
+      <c r="C24" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="100"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="82">
+        <v>18</v>
+      </c>
+      <c r="B25" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A25+1)</f>
+        <v>Node 18, Cell Litio 1</v>
+      </c>
+      <c r="C25" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="100"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="100"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="82">
+        <v>19</v>
+      </c>
+      <c r="B26" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A26+1)</f>
+        <v>Node 19, Cell Litio 2</v>
+      </c>
+      <c r="C26" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="100"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="100"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="100"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="82">
+        <v>20</v>
+      </c>
+      <c r="B27" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A27+1)</f>
+        <v>Node 20, LoMo</v>
+      </c>
+      <c r="C27" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="100"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="100"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="100"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="82">
+        <v>21</v>
+      </c>
+      <c r="B28" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A28+1)</f>
+        <v>Node 21, Transceiver(Tx-Rx)</v>
+      </c>
+      <c r="C28" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="100"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="100"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="100"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="82">
+        <v>22</v>
+      </c>
+      <c r="B29" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A29+1)</f>
+        <v>Node 22, Antena module</v>
+      </c>
+      <c r="C29" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="100"/>
+      <c r="H29" s="100"/>
+      <c r="I29" s="100"/>
+      <c r="J29" s="100"/>
+      <c r="K29" s="100"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="82">
+        <v>23</v>
+      </c>
+      <c r="B30" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A30+1)</f>
+        <v>Node 23, OBC</v>
+      </c>
+      <c r="C30" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="100"/>
+      <c r="H30" s="100"/>
+      <c r="I30" s="100"/>
+      <c r="J30" s="100"/>
+      <c r="K30" s="100"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="82">
+        <v>24</v>
+      </c>
+      <c r="B31" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A31+1)</f>
+        <v>Node 24, Solar Panel (Y)</v>
+      </c>
+      <c r="C31" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="100"/>
+      <c r="H31" s="100"/>
+      <c r="I31" s="100"/>
+      <c r="J31" s="100"/>
+      <c r="K31" s="100"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="82">
+        <v>25</v>
+      </c>
+      <c r="B32" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A32+1)</f>
+        <v>Node 25, Solar Panel (-Y)</v>
+      </c>
+      <c r="C32" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="100"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="100"/>
+      <c r="J32" s="100"/>
+      <c r="K32" s="100"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="82">
+        <v>26</v>
+      </c>
+      <c r="B33" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A33+1)</f>
+        <v>Node 26, Solar Panel (X)</v>
+      </c>
+      <c r="C33" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="100"/>
+      <c r="H33" s="100"/>
+      <c r="I33" s="100"/>
+      <c r="J33" s="100"/>
+      <c r="K33" s="100"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="82">
+        <v>27</v>
+      </c>
+      <c r="B34" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A34+1)</f>
+        <v>Node 27, Solar Panel (-X)RBF</v>
+      </c>
+      <c r="C34" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="100"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="100"/>
+      <c r="J34" s="100"/>
+      <c r="K34" s="100"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="82">
+        <v>28</v>
+      </c>
+      <c r="B35" s="97" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A35+1)</f>
+        <v>Node 28, Solar Panel (-Z(antenna))</v>
+      </c>
+      <c r="C35" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="100"/>
+      <c r="H35" s="100"/>
+      <c r="I35" s="100"/>
+      <c r="J35" s="100"/>
+      <c r="K35" s="100"/>
+    </row>
+    <row r="36" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A36" s="82">
+        <v>29</v>
+      </c>
+      <c r="B36" s="101" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A36+1)</f>
+        <v>Node 29, EPS de alta</v>
+      </c>
+      <c r="C36" s="98">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="99">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="99">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="100">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="100"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="B37" s="80"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B005E130-2D16-4A0C-8BB3-2172273CEA1D}">
+  <dimension ref="B1:O32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:15" ht="15.75" thickBot="1">
+      <c r="B2" s="142" t="s">
+        <v>257</v>
+      </c>
+      <c r="C2" s="127" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" s="128" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="128" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="130"/>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3" s="143" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="131">
+        <v>0</v>
+      </c>
+      <c r="D3" s="132">
+        <v>0</v>
+      </c>
+      <c r="E3" s="132">
+        <v>0</v>
+      </c>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="132"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="132"/>
+      <c r="L3" s="132"/>
+      <c r="M3" s="132"/>
+      <c r="N3" s="132"/>
+      <c r="O3" s="133"/>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="B4" s="144" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="134">
+        <v>0</v>
+      </c>
+      <c r="D4" s="84">
+        <v>0</v>
+      </c>
+      <c r="E4" s="84">
+        <v>0</v>
+      </c>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="84"/>
+      <c r="O4" s="135"/>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="B5" s="144" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="134">
+        <v>0</v>
+      </c>
+      <c r="D5" s="84">
+        <v>0</v>
+      </c>
+      <c r="E5" s="84">
+        <v>0</v>
+      </c>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="135"/>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="B6" s="144" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="134">
+        <v>0</v>
+      </c>
+      <c r="D6" s="84">
+        <v>0</v>
+      </c>
+      <c r="E6" s="84">
+        <v>0</v>
+      </c>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="84"/>
+      <c r="O6" s="135"/>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="B7" s="144" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="134">
+        <v>0</v>
+      </c>
+      <c r="D7" s="84">
+        <v>0</v>
+      </c>
+      <c r="E7" s="84">
+        <v>0</v>
+      </c>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="84"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="84"/>
+      <c r="O7" s="135"/>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="B8" s="144" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="134">
+        <v>0</v>
+      </c>
+      <c r="D8" s="84">
+        <v>0</v>
+      </c>
+      <c r="E8" s="84">
+        <v>0</v>
+      </c>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="84"/>
+      <c r="J8" s="84"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="84"/>
+      <c r="O8" s="135"/>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="B9" s="144" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="134">
+        <v>0</v>
+      </c>
+      <c r="D9" s="84">
+        <v>0</v>
+      </c>
+      <c r="E9" s="84">
+        <v>0</v>
+      </c>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="84"/>
+      <c r="K9" s="84"/>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="84"/>
+      <c r="O9" s="135"/>
+    </row>
+    <row r="10" spans="2:15">
+      <c r="B10" s="144" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="134">
+        <v>0</v>
+      </c>
+      <c r="D10" s="84">
+        <v>200</v>
+      </c>
+      <c r="E10" s="84">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="84"/>
+      <c r="M10" s="84"/>
+      <c r="N10" s="84"/>
+      <c r="O10" s="135"/>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="B11" s="144" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="134">
+        <v>0</v>
+      </c>
+      <c r="D11" s="84">
+        <v>200</v>
+      </c>
+      <c r="E11" s="84">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="84"/>
+      <c r="O11" s="135"/>
+    </row>
+    <row r="12" spans="2:15">
+      <c r="B12" s="144" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="134">
+        <v>0</v>
+      </c>
+      <c r="D12" s="84">
+        <v>200</v>
+      </c>
+      <c r="E12" s="84">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84"/>
+      <c r="O12" s="135"/>
+    </row>
+    <row r="13" spans="2:15">
+      <c r="B13" s="144" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="134">
+        <v>0</v>
+      </c>
+      <c r="D13" s="84">
+        <v>200</v>
+      </c>
+      <c r="E13" s="84">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="135"/>
+    </row>
+    <row r="14" spans="2:15">
+      <c r="B14" s="144" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="134">
+        <v>0</v>
+      </c>
+      <c r="D14" s="84">
+        <v>0</v>
+      </c>
+      <c r="E14" s="84">
+        <v>0</v>
+      </c>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="84"/>
+      <c r="O14" s="135"/>
+    </row>
+    <row r="15" spans="2:15">
+      <c r="B15" s="144" t="s">
+        <v>226</v>
+      </c>
+      <c r="C15" s="134">
+        <v>0</v>
+      </c>
+      <c r="D15" s="84">
+        <v>0</v>
+      </c>
+      <c r="E15" s="84">
+        <v>0</v>
+      </c>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="135"/>
+    </row>
+    <row r="16" spans="2:15">
+      <c r="B16" s="144" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="134">
+        <v>0</v>
+      </c>
+      <c r="D16" s="84">
+        <v>0</v>
+      </c>
+      <c r="E16" s="84">
+        <v>0</v>
+      </c>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="135"/>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17" s="144" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="134">
+        <v>0</v>
+      </c>
+      <c r="D17" s="84">
+        <v>0</v>
+      </c>
+      <c r="E17" s="84">
+        <v>0</v>
+      </c>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="84"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="135"/>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="B18" s="144" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" s="134">
+        <v>0</v>
+      </c>
+      <c r="D18" s="84">
+        <v>0</v>
+      </c>
+      <c r="E18" s="84">
+        <v>0</v>
+      </c>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="135"/>
+    </row>
+    <row r="19" spans="2:15">
+      <c r="B19" s="144" t="s">
+        <v>230</v>
+      </c>
+      <c r="C19" s="134">
+        <v>0</v>
+      </c>
+      <c r="D19" s="84">
+        <v>0</v>
+      </c>
+      <c r="E19" s="84">
+        <v>0</v>
+      </c>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="135"/>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20" s="144" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" s="134">
+        <v>0</v>
+      </c>
+      <c r="D20" s="84">
+        <v>0</v>
+      </c>
+      <c r="E20" s="84">
+        <v>0</v>
+      </c>
+      <c r="F20" s="84"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="135"/>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21" s="144" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" s="134">
+        <v>0</v>
+      </c>
+      <c r="D21" s="84">
+        <v>0</v>
+      </c>
+      <c r="E21" s="84">
+        <v>0</v>
+      </c>
+      <c r="F21" s="84"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="135"/>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22" s="144" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" s="134">
+        <v>0</v>
+      </c>
+      <c r="D22" s="84">
+        <v>0</v>
+      </c>
+      <c r="E22" s="84">
+        <v>0</v>
+      </c>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="135"/>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23" s="144" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="134">
+        <v>0</v>
+      </c>
+      <c r="D23" s="84">
+        <v>0</v>
+      </c>
+      <c r="E23" s="84">
+        <v>0</v>
+      </c>
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="135"/>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="B24" s="144" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="134">
+        <v>0</v>
+      </c>
+      <c r="D24" s="84">
+        <v>0</v>
+      </c>
+      <c r="E24" s="84">
+        <v>0</v>
+      </c>
+      <c r="F24" s="84"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="84"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="135"/>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="B25" s="144" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="134">
+        <v>0</v>
+      </c>
+      <c r="D25" s="84">
+        <v>0</v>
+      </c>
+      <c r="E25" s="84">
+        <v>0</v>
+      </c>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="135"/>
+    </row>
+    <row r="26" spans="2:15">
+      <c r="B26" s="144" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="134">
+        <v>0</v>
+      </c>
+      <c r="D26" s="84">
+        <v>0</v>
+      </c>
+      <c r="E26" s="84">
+        <v>0</v>
+      </c>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="135"/>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="B27" s="144" t="s">
+        <v>238</v>
+      </c>
+      <c r="C27" s="134">
+        <v>0</v>
+      </c>
+      <c r="D27" s="84">
+        <v>0</v>
+      </c>
+      <c r="E27" s="84">
+        <v>0</v>
+      </c>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="135"/>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="B28" s="144" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="134">
+        <v>0</v>
+      </c>
+      <c r="D28" s="84">
+        <v>0</v>
+      </c>
+      <c r="E28" s="84">
+        <v>0</v>
+      </c>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="135"/>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="B29" s="144" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="134">
+        <v>0</v>
+      </c>
+      <c r="D29" s="84">
+        <v>0</v>
+      </c>
+      <c r="E29" s="84">
+        <v>0</v>
+      </c>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="135"/>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="B30" s="144" t="s">
+        <v>241</v>
+      </c>
+      <c r="C30" s="134">
+        <v>0</v>
+      </c>
+      <c r="D30" s="84">
+        <v>0</v>
+      </c>
+      <c r="E30" s="84">
+        <v>0</v>
+      </c>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="135"/>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="B31" s="145" t="s">
+        <v>242</v>
+      </c>
+      <c r="C31" s="138">
+        <v>0</v>
+      </c>
+      <c r="D31" s="122">
+        <v>0</v>
+      </c>
+      <c r="E31" s="122">
+        <v>0</v>
+      </c>
+      <c r="F31" s="122"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="122"/>
+      <c r="I31" s="122"/>
+      <c r="J31" s="122"/>
+      <c r="K31" s="122"/>
+      <c r="L31" s="122"/>
+      <c r="M31" s="122"/>
+      <c r="N31" s="122"/>
+      <c r="O31" s="139"/>
+    </row>
+    <row r="32" spans="2:15">
+      <c r="B32" s="96"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="96"/>
+      <c r="H32" s="96"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="96"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="96"/>
+      <c r="O32" s="96"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4985A03E-5096-4337-92A3-24224C69AEFA}">
+  <dimension ref="B1:M32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:13" ht="30" customHeight="1" thickBot="1">
+      <c r="B2" s="111" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="112" t="s">
+        <v>245</v>
+      </c>
+      <c r="D2" s="113" t="s">
+        <v>246</v>
+      </c>
+      <c r="E2" s="113" t="s">
+        <v>248</v>
+      </c>
+      <c r="F2" s="113" t="s">
+        <v>247</v>
+      </c>
+      <c r="G2" s="113" t="s">
+        <v>243</v>
+      </c>
+      <c r="H2" s="113" t="s">
+        <v>244</v>
+      </c>
+      <c r="I2" s="113" t="s">
+        <v>249</v>
+      </c>
+      <c r="J2" s="113" t="s">
+        <v>250</v>
+      </c>
+      <c r="K2" s="113" t="s">
+        <v>251</v>
+      </c>
+      <c r="L2" s="140" t="s">
+        <v>262</v>
+      </c>
+      <c r="M2" s="114" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13">
+      <c r="B3" s="115" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="108">
+        <v>4.0280000000000003E-2</v>
+      </c>
+      <c r="D3" s="106">
+        <v>800</v>
+      </c>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="G3" s="106">
+        <v>0.8</v>
+      </c>
+      <c r="H3" s="106">
+        <v>0.8</v>
+      </c>
+      <c r="I3" s="106">
+        <v>1</v>
+      </c>
+      <c r="J3" s="106">
+        <v>0</v>
+      </c>
+      <c r="K3" s="106">
+        <v>0</v>
+      </c>
+      <c r="L3" s="106">
+        <v>1</v>
+      </c>
+      <c r="M3" s="107"/>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" s="116" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="109">
+        <v>4.0280000000000003E-2</v>
+      </c>
+      <c r="D4" s="102">
+        <v>800</v>
+      </c>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="G4" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H4" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I4" s="102">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="102">
+        <v>0</v>
+      </c>
+      <c r="K4" s="102">
+        <v>0</v>
+      </c>
+      <c r="L4" s="102">
+        <v>1</v>
+      </c>
+      <c r="M4" s="104"/>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="116" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="109">
+        <v>7.2909999999999997E-3</v>
+      </c>
+      <c r="D5" s="102">
+        <v>800</v>
+      </c>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="G5" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H5" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I5" s="102">
+        <v>0</v>
+      </c>
+      <c r="J5" s="102">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="102">
+        <v>1</v>
+      </c>
+      <c r="L5" s="102">
+        <v>1</v>
+      </c>
+      <c r="M5" s="104"/>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="116" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="109">
+        <v>7.2909999999999997E-3</v>
+      </c>
+      <c r="D6" s="102">
+        <v>800</v>
+      </c>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="G6" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I6" s="102">
+        <v>0</v>
+      </c>
+      <c r="J6" s="102">
+        <v>1</v>
+      </c>
+      <c r="K6" s="102">
+        <v>1</v>
+      </c>
+      <c r="L6" s="102">
+        <v>1</v>
+      </c>
+      <c r="M6" s="104"/>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="116" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="109">
+        <v>6.4250000000000002E-3</v>
+      </c>
+      <c r="D7" s="102">
+        <v>800</v>
+      </c>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="G7" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H7" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I7" s="102">
+        <v>0</v>
+      </c>
+      <c r="J7" s="102">
+        <v>1</v>
+      </c>
+      <c r="K7" s="102">
+        <v>-1</v>
+      </c>
+      <c r="L7" s="102">
+        <v>1</v>
+      </c>
+      <c r="M7" s="104"/>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="116" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="109">
+        <v>6.4250000000000002E-3</v>
+      </c>
+      <c r="D8" s="102">
+        <v>800</v>
+      </c>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="G8" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H8" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I8" s="102">
+        <v>0</v>
+      </c>
+      <c r="J8" s="102">
+        <v>-1</v>
+      </c>
+      <c r="K8" s="102">
+        <v>-1</v>
+      </c>
+      <c r="L8" s="102">
+        <v>1</v>
+      </c>
+      <c r="M8" s="104"/>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="116" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="109">
+        <v>2.1919999999999999E-2</v>
+      </c>
+      <c r="D9" s="102">
+        <v>800</v>
+      </c>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="G9" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H9" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I9" s="102">
+        <v>0</v>
+      </c>
+      <c r="J9" s="102">
+        <v>0</v>
+      </c>
+      <c r="K9" s="102">
+        <v>1</v>
+      </c>
+      <c r="L9" s="102">
+        <v>1</v>
+      </c>
+      <c r="M9" s="104"/>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="116" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="109">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D10" s="102">
+        <v>800</v>
+      </c>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102">
+        <v>5.7600000000000001E-4</v>
+      </c>
+      <c r="G10" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H10" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I10" s="102">
+        <v>0</v>
+      </c>
+      <c r="J10" s="102">
+        <v>0</v>
+      </c>
+      <c r="K10" s="102">
+        <v>1</v>
+      </c>
+      <c r="L10" s="102">
+        <v>1</v>
+      </c>
+      <c r="M10" s="104"/>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="116" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="109">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D11" s="102">
+        <v>800</v>
+      </c>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102">
+        <v>5.7600000000000001E-4</v>
+      </c>
+      <c r="G11" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I11" s="102">
+        <v>0</v>
+      </c>
+      <c r="J11" s="102">
+        <v>0</v>
+      </c>
+      <c r="K11" s="102">
+        <v>1</v>
+      </c>
+      <c r="L11" s="102">
+        <v>1</v>
+      </c>
+      <c r="M11" s="104"/>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" s="116" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="109">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D12" s="102">
+        <v>800</v>
+      </c>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102">
+        <v>5.7600000000000001E-4</v>
+      </c>
+      <c r="G12" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H12" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I12" s="102">
+        <v>0</v>
+      </c>
+      <c r="J12" s="102">
+        <v>0</v>
+      </c>
+      <c r="K12" s="102">
+        <v>1</v>
+      </c>
+      <c r="L12" s="102">
+        <v>1</v>
+      </c>
+      <c r="M12" s="104"/>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="116" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="109">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D13" s="102">
+        <v>800</v>
+      </c>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102">
+        <v>5.7600000000000001E-4</v>
+      </c>
+      <c r="G13" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H13" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I13" s="102">
+        <v>0</v>
+      </c>
+      <c r="J13" s="102">
+        <v>0</v>
+      </c>
+      <c r="K13" s="102">
+        <v>1</v>
+      </c>
+      <c r="L13" s="102">
+        <v>1</v>
+      </c>
+      <c r="M13" s="104"/>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14" s="116" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="109">
+        <v>2.375E-2</v>
+      </c>
+      <c r="D14" s="102">
+        <v>600</v>
+      </c>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102">
+        <v>0.01</v>
+      </c>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="102">
+        <v>0</v>
+      </c>
+      <c r="M14" s="104"/>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15" s="116" t="s">
+        <v>226</v>
+      </c>
+      <c r="C15" s="109">
+        <v>0.125</v>
+      </c>
+      <c r="D15" s="102">
+        <v>800</v>
+      </c>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102">
+        <v>0.01</v>
+      </c>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="102"/>
+      <c r="L15" s="102">
+        <v>0</v>
+      </c>
+      <c r="M15" s="104"/>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16" s="116" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="109">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D16" s="102">
+        <v>600</v>
+      </c>
+      <c r="E16" s="102"/>
+      <c r="F16" s="102">
+        <v>0.01</v>
+      </c>
+      <c r="G16" s="102"/>
+      <c r="H16" s="102"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="102"/>
+      <c r="K16" s="102"/>
+      <c r="L16" s="102">
+        <v>0</v>
+      </c>
+      <c r="M16" s="104"/>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="B17" s="116" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="109">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D17" s="102">
+        <v>600</v>
+      </c>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="102"/>
+      <c r="H17" s="102"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="102"/>
+      <c r="K17" s="102"/>
+      <c r="L17" s="102">
+        <v>0</v>
+      </c>
+      <c r="M17" s="104"/>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" s="116" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" s="109">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D18" s="102">
+        <v>600</v>
+      </c>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102">
+        <v>0.1</v>
+      </c>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="102"/>
+      <c r="L18" s="102">
+        <v>0</v>
+      </c>
+      <c r="M18" s="104"/>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" s="116" t="s">
+        <v>230</v>
+      </c>
+      <c r="C19" s="109">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D19" s="102">
+        <v>600</v>
+      </c>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102">
+        <v>0.1</v>
+      </c>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="102"/>
+      <c r="L19" s="102">
+        <v>0</v>
+      </c>
+      <c r="M19" s="104"/>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="116" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" s="109">
+        <v>0.05</v>
+      </c>
+      <c r="D20" s="102">
+        <v>600</v>
+      </c>
+      <c r="E20" s="102"/>
+      <c r="F20" s="102">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="102"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="102"/>
+      <c r="L20" s="102">
+        <v>0</v>
+      </c>
+      <c r="M20" s="104"/>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="116" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" s="109">
+        <v>0.05</v>
+      </c>
+      <c r="D21" s="102">
+        <v>600</v>
+      </c>
+      <c r="E21" s="102"/>
+      <c r="F21" s="102">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="102"/>
+      <c r="H21" s="102"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="102"/>
+      <c r="K21" s="102"/>
+      <c r="L21" s="102">
+        <v>0</v>
+      </c>
+      <c r="M21" s="104"/>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="B22" s="116" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" s="109">
+        <v>3.8490000000000003E-2</v>
+      </c>
+      <c r="D22" s="102">
+        <v>600</v>
+      </c>
+      <c r="E22" s="102"/>
+      <c r="F22" s="102">
+        <v>8.6E-3</v>
+      </c>
+      <c r="G22" s="102"/>
+      <c r="H22" s="102"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="102"/>
+      <c r="K22" s="102"/>
+      <c r="L22" s="102">
+        <v>0</v>
+      </c>
+      <c r="M22" s="104"/>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="B23" s="116" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="109">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="D23" s="102">
+        <v>600</v>
+      </c>
+      <c r="E23" s="102"/>
+      <c r="F23" s="102">
+        <v>8.6E-3</v>
+      </c>
+      <c r="G23" s="102"/>
+      <c r="H23" s="102"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="102"/>
+      <c r="L23" s="102">
+        <v>0</v>
+      </c>
+      <c r="M23" s="104"/>
+    </row>
+    <row r="24" spans="2:13">
+      <c r="B24" s="116" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="109">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="D24" s="102">
+        <v>600</v>
+      </c>
+      <c r="E24" s="102">
+        <v>15</v>
+      </c>
+      <c r="F24" s="102">
+        <v>0.08</v>
+      </c>
+      <c r="G24" s="102"/>
+      <c r="H24" s="102"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="102"/>
+      <c r="L24" s="102">
+        <v>0</v>
+      </c>
+      <c r="M24" s="104">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="B25" s="116" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="109">
+        <v>2.4E-2</v>
+      </c>
+      <c r="D25" s="102">
+        <v>600</v>
+      </c>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102">
+        <v>0.33</v>
+      </c>
+      <c r="G25" s="102"/>
+      <c r="H25" s="102"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="102"/>
+      <c r="L25" s="102">
+        <v>0</v>
+      </c>
+      <c r="M25" s="104"/>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="B26" s="116" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="109">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="D26" s="102">
+        <v>600</v>
+      </c>
+      <c r="E26" s="102">
+        <v>15</v>
+      </c>
+      <c r="F26" s="102">
+        <v>8.0940000000000005E-3</v>
+      </c>
+      <c r="G26" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H26" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I26" s="102">
+        <v>0</v>
+      </c>
+      <c r="J26" s="102">
+        <v>1</v>
+      </c>
+      <c r="K26" s="102">
+        <v>0</v>
+      </c>
+      <c r="L26" s="102">
+        <v>1</v>
+      </c>
+      <c r="M26" s="104">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="B27" s="116" t="s">
+        <v>238</v>
+      </c>
+      <c r="C27" s="109">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="D27" s="102">
+        <v>600</v>
+      </c>
+      <c r="E27" s="102">
+        <v>15</v>
+      </c>
+      <c r="F27" s="102">
+        <v>8.0940000000000005E-3</v>
+      </c>
+      <c r="G27" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H27" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I27" s="102">
+        <v>0</v>
+      </c>
+      <c r="J27" s="102">
+        <v>-1</v>
+      </c>
+      <c r="K27" s="102">
+        <v>0</v>
+      </c>
+      <c r="L27" s="102">
+        <v>1</v>
+      </c>
+      <c r="M27" s="104">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="B28" s="116" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="109">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D28" s="102">
+        <v>600</v>
+      </c>
+      <c r="E28" s="102">
+        <v>15</v>
+      </c>
+      <c r="F28" s="102">
+        <v>8.0940000000000005E-3</v>
+      </c>
+      <c r="G28" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H28" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I28" s="102">
+        <v>1</v>
+      </c>
+      <c r="J28" s="102">
+        <v>0</v>
+      </c>
+      <c r="K28" s="102">
+        <v>0</v>
+      </c>
+      <c r="L28" s="102">
+        <v>1</v>
+      </c>
+      <c r="M28" s="104">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
+      <c r="B29" s="116" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="109">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="D29" s="102">
+        <v>600</v>
+      </c>
+      <c r="E29" s="102">
+        <v>15</v>
+      </c>
+      <c r="F29" s="102">
+        <v>8.0940000000000005E-3</v>
+      </c>
+      <c r="G29" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H29" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I29" s="102">
+        <v>-1</v>
+      </c>
+      <c r="J29" s="102">
+        <v>0</v>
+      </c>
+      <c r="K29" s="102">
+        <v>0</v>
+      </c>
+      <c r="L29" s="102">
+        <v>1</v>
+      </c>
+      <c r="M29" s="104">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="B30" s="116" t="s">
+        <v>241</v>
+      </c>
+      <c r="C30" s="109">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="D30" s="102">
+        <v>600</v>
+      </c>
+      <c r="E30" s="102">
+        <v>15</v>
+      </c>
+      <c r="F30" s="102">
+        <v>8.4469999999999996E-3</v>
+      </c>
+      <c r="G30" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="H30" s="102">
+        <v>0.8</v>
+      </c>
+      <c r="I30" s="102">
+        <v>0</v>
+      </c>
+      <c r="J30" s="102">
+        <v>0</v>
+      </c>
+      <c r="K30" s="102">
+        <v>-1</v>
+      </c>
+      <c r="L30" s="102">
+        <v>1</v>
+      </c>
+      <c r="M30" s="104">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B31" s="117" t="s">
+        <v>242</v>
+      </c>
+      <c r="C31" s="110">
+        <v>0.04</v>
+      </c>
+      <c r="D31" s="103">
+        <v>600</v>
+      </c>
+      <c r="E31" s="103"/>
+      <c r="F31" s="103">
+        <v>0.01</v>
+      </c>
+      <c r="G31" s="103"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="103"/>
+      <c r="J31" s="103"/>
+      <c r="K31" s="103"/>
+      <c r="L31" s="103">
+        <v>0</v>
+      </c>
+      <c r="M31" s="105"/>
+    </row>
+    <row r="32" spans="2:13">
+      <c r="B32" s="80"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD990"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -43794,3316 +47686,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:I127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="25.28515625" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="130" t="s">
-        <v>150</v>
-      </c>
-      <c r="I2" s="131"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="H3" s="35">
-        <v>1.57</v>
-      </c>
-      <c r="I3" s="36">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G4" s="38">
-        <v>2.5</v>
-      </c>
-      <c r="H4" s="39">
-        <v>15.17</v>
-      </c>
-      <c r="I4" s="40" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G5" s="42">
-        <v>2.8</v>
-      </c>
-      <c r="H5" s="43">
-        <v>12.6</v>
-      </c>
-      <c r="I5" s="44" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="G6" s="38">
-        <v>3</v>
-      </c>
-      <c r="H6" s="39">
-        <f>((H5-H7)/(G5-G7))*(G6-G7)+H7</f>
-        <v>10.888571428571428</v>
-      </c>
-      <c r="I6" s="40">
-        <f>((I7-I8)/(G7-G8))*(G6-G7)+I7</f>
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="G7" s="42">
-        <v>3.5</v>
-      </c>
-      <c r="H7" s="43">
-        <v>6.61</v>
-      </c>
-      <c r="I7" s="44">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="G8" s="47">
-        <v>4.2</v>
-      </c>
-      <c r="H8" s="48">
-        <v>4.5</v>
-      </c>
-      <c r="I8" s="49">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B10" s="53" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="54">
-        <v>7.762E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B13" s="53" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="B14" s="53" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B15" s="53">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="B16" s="55">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="56" t="s">
-        <v>171</v>
-      </c>
-      <c r="B17" s="57">
-        <f>1/B16</f>
-        <v>0.37037037037037035</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B18" s="59">
-        <f>B12*B17</f>
-        <v>0.37037037037037035</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="B20" s="46" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="60" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="61" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B22" s="53" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="54">
-        <v>4.8523999999999998E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="B24" s="55">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="B25" s="63">
-        <f>B24*B23</f>
-        <v>0.24262</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="45" t="s">
-        <v>177</v>
-      </c>
-      <c r="B27" s="46" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B29" s="53" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="54">
-        <v>1.302E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="B31" s="53">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B32" s="53" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="B33" s="53" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B34" s="53">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="B35" s="55">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B36" s="64">
-        <f>1/B35</f>
-        <v>9.1827364554637275E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B37" s="59">
-        <f>B31*B36</f>
-        <v>0.3673094582185491</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="F38" s="7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="B39" s="46" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B40" s="51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B41" s="53" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B42" s="54">
-        <v>3.9569999999999996E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="B43" s="53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B44" s="53" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="B45" s="53" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B46" s="53">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="B47" s="55">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B48" s="64">
-        <f>1/B47</f>
-        <v>9.1827364554637275E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B49" s="59">
-        <f>B43*B48</f>
-        <v>0.18365472910927455</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="B51" s="46" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B52" s="51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B53" s="53" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B54" s="54">
-        <v>1.6140000000000002E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="B55" s="53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B56" s="53" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="B57" s="53" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B58" s="53">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="B59" s="55">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B60" s="57">
-        <f>1/B59</f>
-        <v>9.1827364554637275E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B61" s="59">
-        <f>B55*B60</f>
-        <v>0.18365472910927455</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="B63" s="46" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B64" s="51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B65" s="53" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="54" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="B67" s="53">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B68" s="53" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="B69" s="53" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B70" s="53">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="B71" s="55">
-        <v>15.17</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B72" s="57">
-        <f>1/B71</f>
-        <v>6.5919578114700061E-2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B73" s="59">
-        <f>B67*B72</f>
-        <v>0.26367831245880025</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="65" t="s">
-        <v>194</v>
-      </c>
-      <c r="B75" s="66" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="67" t="s">
-        <v>161</v>
-      </c>
-      <c r="B76" s="68" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B77" s="53" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" s="54">
-        <v>5.4999999999999997E-3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="B79" s="53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B80" s="53" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="B81" s="53" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B82" s="53">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="B83" s="55">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B84" s="53">
-        <f>1/B83</f>
-        <v>9.1827364554637275E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="B85" s="55">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B86" s="59">
-        <f>B79*B84+B85*B78</f>
-        <v>5.6836547291092749</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="45" t="s">
-        <v>199</v>
-      </c>
-      <c r="B88" s="46" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B89" s="51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B90" s="53" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="B91" s="53">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B92" s="53" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="B93" s="53">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B94" s="53">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="B95" s="55">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B96" s="57">
-        <f>1/B95</f>
-        <v>9.1827364554637275E-2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B97" s="59">
-        <f>B91*B96</f>
-        <v>0.3673094582185491</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="B99" s="46" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B100" s="51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B101" s="53" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="B102" s="53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B103" s="53" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="B104" s="53" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B105" s="53">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="B106" s="55">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B107" s="57">
-        <f>1/B106</f>
-        <v>9.1827364554637275E-2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B108" s="59">
-        <f>B102*B107</f>
-        <v>0.18365472910927455</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="65" t="s">
-        <v>206</v>
-      </c>
-      <c r="B110" s="66" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="69" t="s">
-        <v>161</v>
-      </c>
-      <c r="B111" s="70" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B112" s="53" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B113" s="54">
-        <v>3.7569999999999999E-2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="B114" s="55">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B115" s="59">
-        <f>B114*B113</f>
-        <v>37.57</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="B117" s="46" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B118" s="51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="B119" s="53" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B120" s="54" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="B121" s="53">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="52" t="s">
-        <v>165</v>
-      </c>
-      <c r="B122" s="53" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="B123" s="53" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B124" s="53">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="B125" s="55">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="56" t="s">
-        <v>171</v>
-      </c>
-      <c r="B126" s="57">
-        <f>1/B125</f>
-        <v>9.1827364554637275E-2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="58" t="s">
-        <v>172</v>
-      </c>
-      <c r="B127" s="59">
-        <f>B121*B126</f>
-        <v>0.3673094582185491</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H2:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4985A03E-5096-4337-92A3-24224C69AEFA}">
-  <dimension ref="B1:M32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:13" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:13" ht="30" customHeight="1" thickBot="1">
-      <c r="B2" s="139" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="140" t="s">
-        <v>245</v>
-      </c>
-      <c r="D2" s="141" t="s">
-        <v>246</v>
-      </c>
-      <c r="E2" s="141" t="s">
-        <v>248</v>
-      </c>
-      <c r="F2" s="141" t="s">
-        <v>247</v>
-      </c>
-      <c r="G2" s="141" t="s">
-        <v>243</v>
-      </c>
-      <c r="H2" s="141" t="s">
-        <v>244</v>
-      </c>
-      <c r="I2" s="141" t="s">
-        <v>249</v>
-      </c>
-      <c r="J2" s="141" t="s">
-        <v>250</v>
-      </c>
-      <c r="K2" s="141" t="s">
-        <v>251</v>
-      </c>
-      <c r="L2" s="141" t="s">
-        <v>262</v>
-      </c>
-      <c r="M2" s="142" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13">
-      <c r="B3" s="143" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" s="136">
-        <v>4.0280000000000003E-2</v>
-      </c>
-      <c r="D3" s="134">
-        <v>800</v>
-      </c>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134">
-        <v>5.1999999999999998E-3</v>
-      </c>
-      <c r="G3" s="134">
-        <v>0.8</v>
-      </c>
-      <c r="H3" s="134">
-        <v>0.8</v>
-      </c>
-      <c r="I3" s="134">
-        <v>1</v>
-      </c>
-      <c r="J3" s="134">
-        <v>0</v>
-      </c>
-      <c r="K3" s="134">
-        <v>0</v>
-      </c>
-      <c r="L3" s="134">
-        <v>1</v>
-      </c>
-      <c r="M3" s="135"/>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="B4" s="144" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="137">
-        <v>4.0280000000000003E-2</v>
-      </c>
-      <c r="D4" s="114">
-        <v>800</v>
-      </c>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114">
-        <v>5.1999999999999998E-3</v>
-      </c>
-      <c r="G4" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H4" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I4" s="114">
-        <v>-1</v>
-      </c>
-      <c r="J4" s="114">
-        <v>0</v>
-      </c>
-      <c r="K4" s="114">
-        <v>0</v>
-      </c>
-      <c r="L4" s="114">
-        <v>1</v>
-      </c>
-      <c r="M4" s="132"/>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="144" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="137">
-        <v>7.2909999999999997E-3</v>
-      </c>
-      <c r="D5" s="114">
-        <v>800</v>
-      </c>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="G5" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H5" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I5" s="114">
-        <v>0</v>
-      </c>
-      <c r="J5" s="114">
-        <v>-1</v>
-      </c>
-      <c r="K5" s="114">
-        <v>1</v>
-      </c>
-      <c r="L5" s="114">
-        <v>1</v>
-      </c>
-      <c r="M5" s="132"/>
-    </row>
-    <row r="6" spans="2:13">
-      <c r="B6" s="144" t="s">
-        <v>217</v>
-      </c>
-      <c r="C6" s="137">
-        <v>7.2909999999999997E-3</v>
-      </c>
-      <c r="D6" s="114">
-        <v>800</v>
-      </c>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="G6" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H6" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I6" s="114">
-        <v>0</v>
-      </c>
-      <c r="J6" s="114">
-        <v>1</v>
-      </c>
-      <c r="K6" s="114">
-        <v>1</v>
-      </c>
-      <c r="L6" s="114">
-        <v>1</v>
-      </c>
-      <c r="M6" s="132"/>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="144" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="137">
-        <v>6.4250000000000002E-3</v>
-      </c>
-      <c r="D7" s="114">
-        <v>800</v>
-      </c>
-      <c r="E7" s="114"/>
-      <c r="F7" s="114">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="G7" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H7" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I7" s="114">
-        <v>0</v>
-      </c>
-      <c r="J7" s="114">
-        <v>1</v>
-      </c>
-      <c r="K7" s="114">
-        <v>-1</v>
-      </c>
-      <c r="L7" s="114">
-        <v>1</v>
-      </c>
-      <c r="M7" s="132"/>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="144" t="s">
-        <v>219</v>
-      </c>
-      <c r="C8" s="137">
-        <v>6.4250000000000002E-3</v>
-      </c>
-      <c r="D8" s="114">
-        <v>800</v>
-      </c>
-      <c r="E8" s="114"/>
-      <c r="F8" s="114">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="G8" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H8" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I8" s="114">
-        <v>0</v>
-      </c>
-      <c r="J8" s="114">
-        <v>-1</v>
-      </c>
-      <c r="K8" s="114">
-        <v>-1</v>
-      </c>
-      <c r="L8" s="114">
-        <v>1</v>
-      </c>
-      <c r="M8" s="132"/>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="144" t="s">
-        <v>220</v>
-      </c>
-      <c r="C9" s="137">
-        <v>2.1919999999999999E-2</v>
-      </c>
-      <c r="D9" s="114">
-        <v>800</v>
-      </c>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114">
-        <v>9.5999999999999992E-3</v>
-      </c>
-      <c r="G9" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H9" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I9" s="114">
-        <v>0</v>
-      </c>
-      <c r="J9" s="114">
-        <v>0</v>
-      </c>
-      <c r="K9" s="114">
-        <v>1</v>
-      </c>
-      <c r="L9" s="114">
-        <v>1</v>
-      </c>
-      <c r="M9" s="132"/>
-    </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="144" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="137">
-        <v>1.8E-3</v>
-      </c>
-      <c r="D10" s="114">
-        <v>800</v>
-      </c>
-      <c r="E10" s="114"/>
-      <c r="F10" s="114">
-        <v>5.7600000000000001E-4</v>
-      </c>
-      <c r="G10" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H10" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I10" s="114">
-        <v>0</v>
-      </c>
-      <c r="J10" s="114">
-        <v>0</v>
-      </c>
-      <c r="K10" s="114">
-        <v>1</v>
-      </c>
-      <c r="L10" s="114">
-        <v>1</v>
-      </c>
-      <c r="M10" s="132"/>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="144" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="137">
-        <v>1.8E-3</v>
-      </c>
-      <c r="D11" s="114">
-        <v>800</v>
-      </c>
-      <c r="E11" s="114"/>
-      <c r="F11" s="114">
-        <v>5.7600000000000001E-4</v>
-      </c>
-      <c r="G11" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H11" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I11" s="114">
-        <v>0</v>
-      </c>
-      <c r="J11" s="114">
-        <v>0</v>
-      </c>
-      <c r="K11" s="114">
-        <v>1</v>
-      </c>
-      <c r="L11" s="114">
-        <v>1</v>
-      </c>
-      <c r="M11" s="132"/>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="B12" s="144" t="s">
-        <v>223</v>
-      </c>
-      <c r="C12" s="137">
-        <v>1.8E-3</v>
-      </c>
-      <c r="D12" s="114">
-        <v>800</v>
-      </c>
-      <c r="E12" s="114"/>
-      <c r="F12" s="114">
-        <v>5.7600000000000001E-4</v>
-      </c>
-      <c r="G12" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H12" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I12" s="114">
-        <v>0</v>
-      </c>
-      <c r="J12" s="114">
-        <v>0</v>
-      </c>
-      <c r="K12" s="114">
-        <v>1</v>
-      </c>
-      <c r="L12" s="114">
-        <v>1</v>
-      </c>
-      <c r="M12" s="132"/>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="144" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" s="137">
-        <v>1.8E-3</v>
-      </c>
-      <c r="D13" s="114">
-        <v>800</v>
-      </c>
-      <c r="E13" s="114"/>
-      <c r="F13" s="114">
-        <v>5.7600000000000001E-4</v>
-      </c>
-      <c r="G13" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H13" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I13" s="114">
-        <v>0</v>
-      </c>
-      <c r="J13" s="114">
-        <v>0</v>
-      </c>
-      <c r="K13" s="114">
-        <v>1</v>
-      </c>
-      <c r="L13" s="114">
-        <v>1</v>
-      </c>
-      <c r="M13" s="132"/>
-    </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="144" t="s">
-        <v>225</v>
-      </c>
-      <c r="C14" s="137">
-        <v>2.375E-2</v>
-      </c>
-      <c r="D14" s="114">
-        <v>600</v>
-      </c>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114">
-        <v>0.01</v>
-      </c>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="114"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="114">
-        <v>0</v>
-      </c>
-      <c r="M14" s="132"/>
-    </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="144" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" s="137">
-        <v>0.125</v>
-      </c>
-      <c r="D15" s="114">
-        <v>800</v>
-      </c>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114">
-        <v>0.01</v>
-      </c>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="114">
-        <v>0</v>
-      </c>
-      <c r="M15" s="132"/>
-    </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="144" t="s">
-        <v>227</v>
-      </c>
-      <c r="C16" s="137">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D16" s="114">
-        <v>600</v>
-      </c>
-      <c r="E16" s="114"/>
-      <c r="F16" s="114">
-        <v>0.01</v>
-      </c>
-      <c r="G16" s="114"/>
-      <c r="H16" s="114"/>
-      <c r="I16" s="114"/>
-      <c r="J16" s="114"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="114">
-        <v>0</v>
-      </c>
-      <c r="M16" s="132"/>
-    </row>
-    <row r="17" spans="2:13">
-      <c r="B17" s="144" t="s">
-        <v>228</v>
-      </c>
-      <c r="C17" s="137">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D17" s="114">
-        <v>600</v>
-      </c>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114">
-        <v>0.1</v>
-      </c>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="114"/>
-      <c r="K17" s="114"/>
-      <c r="L17" s="114">
-        <v>0</v>
-      </c>
-      <c r="M17" s="132"/>
-    </row>
-    <row r="18" spans="2:13">
-      <c r="B18" s="144" t="s">
-        <v>229</v>
-      </c>
-      <c r="C18" s="137">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D18" s="114">
-        <v>600</v>
-      </c>
-      <c r="E18" s="114"/>
-      <c r="F18" s="114">
-        <v>0.1</v>
-      </c>
-      <c r="G18" s="114"/>
-      <c r="H18" s="114"/>
-      <c r="I18" s="114"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="114"/>
-      <c r="L18" s="114">
-        <v>0</v>
-      </c>
-      <c r="M18" s="132"/>
-    </row>
-    <row r="19" spans="2:13">
-      <c r="B19" s="144" t="s">
-        <v>230</v>
-      </c>
-      <c r="C19" s="137">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D19" s="114">
-        <v>600</v>
-      </c>
-      <c r="E19" s="114"/>
-      <c r="F19" s="114">
-        <v>0.1</v>
-      </c>
-      <c r="G19" s="114"/>
-      <c r="H19" s="114"/>
-      <c r="I19" s="114"/>
-      <c r="J19" s="114"/>
-      <c r="K19" s="114"/>
-      <c r="L19" s="114">
-        <v>0</v>
-      </c>
-      <c r="M19" s="132"/>
-    </row>
-    <row r="20" spans="2:13">
-      <c r="B20" s="144" t="s">
-        <v>231</v>
-      </c>
-      <c r="C20" s="137">
-        <v>0.05</v>
-      </c>
-      <c r="D20" s="114">
-        <v>600</v>
-      </c>
-      <c r="E20" s="114"/>
-      <c r="F20" s="114">
-        <v>0.1</v>
-      </c>
-      <c r="G20" s="114"/>
-      <c r="H20" s="114"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="114">
-        <v>0</v>
-      </c>
-      <c r="M20" s="132"/>
-    </row>
-    <row r="21" spans="2:13">
-      <c r="B21" s="144" t="s">
-        <v>232</v>
-      </c>
-      <c r="C21" s="137">
-        <v>0.05</v>
-      </c>
-      <c r="D21" s="114">
-        <v>600</v>
-      </c>
-      <c r="E21" s="114"/>
-      <c r="F21" s="114">
-        <v>0.1</v>
-      </c>
-      <c r="G21" s="114"/>
-      <c r="H21" s="114"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="114"/>
-      <c r="L21" s="114">
-        <v>0</v>
-      </c>
-      <c r="M21" s="132"/>
-    </row>
-    <row r="22" spans="2:13">
-      <c r="B22" s="144" t="s">
-        <v>233</v>
-      </c>
-      <c r="C22" s="137">
-        <v>3.8490000000000003E-2</v>
-      </c>
-      <c r="D22" s="114">
-        <v>600</v>
-      </c>
-      <c r="E22" s="114"/>
-      <c r="F22" s="114">
-        <v>8.6E-3</v>
-      </c>
-      <c r="G22" s="114"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="114"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="114"/>
-      <c r="L22" s="114">
-        <v>0</v>
-      </c>
-      <c r="M22" s="132"/>
-    </row>
-    <row r="23" spans="2:13">
-      <c r="B23" s="144" t="s">
-        <v>234</v>
-      </c>
-      <c r="C23" s="137">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="D23" s="114">
-        <v>600</v>
-      </c>
-      <c r="E23" s="114"/>
-      <c r="F23" s="114">
-        <v>8.6E-3</v>
-      </c>
-      <c r="G23" s="114"/>
-      <c r="H23" s="114"/>
-      <c r="I23" s="114"/>
-      <c r="J23" s="114"/>
-      <c r="K23" s="114"/>
-      <c r="L23" s="114">
-        <v>0</v>
-      </c>
-      <c r="M23" s="132"/>
-    </row>
-    <row r="24" spans="2:13">
-      <c r="B24" s="144" t="s">
-        <v>235</v>
-      </c>
-      <c r="C24" s="137">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="D24" s="114">
-        <v>600</v>
-      </c>
-      <c r="E24" s="114">
-        <v>15</v>
-      </c>
-      <c r="F24" s="114">
-        <v>0.08</v>
-      </c>
-      <c r="G24" s="114"/>
-      <c r="H24" s="114"/>
-      <c r="I24" s="114"/>
-      <c r="J24" s="114"/>
-      <c r="K24" s="114"/>
-      <c r="L24" s="114">
-        <v>0</v>
-      </c>
-      <c r="M24" s="132">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13">
-      <c r="B25" s="144" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="137">
-        <v>2.4E-2</v>
-      </c>
-      <c r="D25" s="114">
-        <v>600</v>
-      </c>
-      <c r="E25" s="114"/>
-      <c r="F25" s="114">
-        <v>0.33</v>
-      </c>
-      <c r="G25" s="114"/>
-      <c r="H25" s="114"/>
-      <c r="I25" s="114"/>
-      <c r="J25" s="114"/>
-      <c r="K25" s="114"/>
-      <c r="L25" s="114">
-        <v>0</v>
-      </c>
-      <c r="M25" s="132"/>
-    </row>
-    <row r="26" spans="2:13">
-      <c r="B26" s="144" t="s">
-        <v>237</v>
-      </c>
-      <c r="C26" s="137">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="D26" s="114">
-        <v>600</v>
-      </c>
-      <c r="E26" s="114">
-        <v>15</v>
-      </c>
-      <c r="F26" s="114">
-        <v>8.0940000000000005E-3</v>
-      </c>
-      <c r="G26" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H26" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I26" s="114">
-        <v>0</v>
-      </c>
-      <c r="J26" s="114">
-        <v>1</v>
-      </c>
-      <c r="K26" s="114">
-        <v>0</v>
-      </c>
-      <c r="L26" s="114">
-        <v>1</v>
-      </c>
-      <c r="M26" s="132">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13">
-      <c r="B27" s="144" t="s">
-        <v>238</v>
-      </c>
-      <c r="C27" s="137">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="D27" s="114">
-        <v>600</v>
-      </c>
-      <c r="E27" s="114">
-        <v>15</v>
-      </c>
-      <c r="F27" s="114">
-        <v>8.0940000000000005E-3</v>
-      </c>
-      <c r="G27" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H27" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I27" s="114">
-        <v>0</v>
-      </c>
-      <c r="J27" s="114">
-        <v>-1</v>
-      </c>
-      <c r="K27" s="114">
-        <v>0</v>
-      </c>
-      <c r="L27" s="114">
-        <v>1</v>
-      </c>
-      <c r="M27" s="132">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13">
-      <c r="B28" s="144" t="s">
-        <v>239</v>
-      </c>
-      <c r="C28" s="137">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="D28" s="114">
-        <v>600</v>
-      </c>
-      <c r="E28" s="114">
-        <v>15</v>
-      </c>
-      <c r="F28" s="114">
-        <v>8.0940000000000005E-3</v>
-      </c>
-      <c r="G28" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H28" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I28" s="114">
-        <v>1</v>
-      </c>
-      <c r="J28" s="114">
-        <v>0</v>
-      </c>
-      <c r="K28" s="114">
-        <v>0</v>
-      </c>
-      <c r="L28" s="114">
-        <v>1</v>
-      </c>
-      <c r="M28" s="132">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13">
-      <c r="B29" s="144" t="s">
-        <v>240</v>
-      </c>
-      <c r="C29" s="137">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="D29" s="114">
-        <v>600</v>
-      </c>
-      <c r="E29" s="114">
-        <v>15</v>
-      </c>
-      <c r="F29" s="114">
-        <v>8.0940000000000005E-3</v>
-      </c>
-      <c r="G29" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H29" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I29" s="114">
-        <v>-1</v>
-      </c>
-      <c r="J29" s="114">
-        <v>0</v>
-      </c>
-      <c r="K29" s="114">
-        <v>0</v>
-      </c>
-      <c r="L29" s="114">
-        <v>1</v>
-      </c>
-      <c r="M29" s="132">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13">
-      <c r="B30" s="144" t="s">
-        <v>241</v>
-      </c>
-      <c r="C30" s="137">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="D30" s="114">
-        <v>600</v>
-      </c>
-      <c r="E30" s="114">
-        <v>15</v>
-      </c>
-      <c r="F30" s="114">
-        <v>8.4469999999999996E-3</v>
-      </c>
-      <c r="G30" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="H30" s="114">
-        <v>0.8</v>
-      </c>
-      <c r="I30" s="114">
-        <v>0</v>
-      </c>
-      <c r="J30" s="114">
-        <v>0</v>
-      </c>
-      <c r="K30" s="114">
-        <v>-1</v>
-      </c>
-      <c r="L30" s="114">
-        <v>1</v>
-      </c>
-      <c r="M30" s="132">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B31" s="145" t="s">
-        <v>242</v>
-      </c>
-      <c r="C31" s="138">
-        <v>0.04</v>
-      </c>
-      <c r="D31" s="117">
-        <v>600</v>
-      </c>
-      <c r="E31" s="117"/>
-      <c r="F31" s="117">
-        <v>0.01</v>
-      </c>
-      <c r="G31" s="117"/>
-      <c r="H31" s="117"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="117">
-        <v>0</v>
-      </c>
-      <c r="M31" s="133"/>
-    </row>
-    <row r="32" spans="2:13">
-      <c r="B32" s="80"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4723E147-5D28-48F2-9A19-B61306348D73}">
-  <dimension ref="A1:N37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1"/>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1">
-      <c r="B2" s="96" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" s="88" t="s">
-        <v>260</v>
-      </c>
-      <c r="D2" s="87" t="s">
-        <v>258</v>
-      </c>
-      <c r="E2" s="87" t="s">
-        <v>260</v>
-      </c>
-      <c r="F2" s="97" t="s">
-        <v>259</v>
-      </c>
-      <c r="G2" s="101"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="B3" s="91" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="94">
-        <f>C4+C5*60+C6*3600+C7*3600*24</f>
-        <v>3600</v>
-      </c>
-      <c r="D3" s="95">
-        <f>C3+D4+D5*60+D6*3600+D7*3600*24</f>
-        <v>3720</v>
-      </c>
-      <c r="E3" s="95">
-        <f t="shared" ref="E3" si="0">D3+E4+E5*60+E6*3600+E7*3600*24</f>
-        <v>10920</v>
-      </c>
-      <c r="F3" s="98">
-        <f>E3+F4+F5*60+F6*3600+F7*3600*24</f>
-        <v>18120</v>
-      </c>
-      <c r="G3" s="101"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="B4" s="92" t="s">
-        <v>256</v>
-      </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="101"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="B5" s="92" t="s">
-        <v>255</v>
-      </c>
-      <c r="C5" s="89"/>
-      <c r="D5" s="84">
-        <v>2</v>
-      </c>
-      <c r="E5" s="83"/>
-      <c r="F5" s="99">
-        <v>0</v>
-      </c>
-      <c r="G5" s="101"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="B6" s="92" t="s">
-        <v>254</v>
-      </c>
-      <c r="C6" s="89">
-        <v>1</v>
-      </c>
-      <c r="D6" s="84"/>
-      <c r="E6" s="83">
-        <v>2</v>
-      </c>
-      <c r="F6" s="99">
-        <v>2</v>
-      </c>
-      <c r="G6" s="101"/>
-    </row>
-    <row r="7" spans="1:14" ht="15.75" thickBot="1">
-      <c r="B7" s="93" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="90"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="101"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="82">
-        <v>1</v>
-      </c>
-      <c r="B8" s="102" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A8+1)</f>
-        <v>Frame 1, +X</v>
-      </c>
-      <c r="C8" s="103">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A8+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="104">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A8+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="104">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A8+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="105">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A8+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="101"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="82">
-        <v>2</v>
-      </c>
-      <c r="B9" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A9+1)</f>
-        <v>Frame 2, -X</v>
-      </c>
-      <c r="C9" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A9+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A9+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A9+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A9+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="101"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="82">
-        <v>3</v>
-      </c>
-      <c r="B10" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A10+1)</f>
-        <v>Beam -Y +Z</v>
-      </c>
-      <c r="C10" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A10+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A10+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A10+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A10+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="101"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="82">
-        <v>4</v>
-      </c>
-      <c r="B11" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A11+1)</f>
-        <v>Beam +Y +Z</v>
-      </c>
-      <c r="C11" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A11+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A11+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A11+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A11+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="101"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="82">
-        <v>5</v>
-      </c>
-      <c r="B12" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A12+1)</f>
-        <v>Beam +Y -Z</v>
-      </c>
-      <c r="C12" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A12+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A12+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A12+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A12+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="101"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="82">
-        <v>6</v>
-      </c>
-      <c r="B13" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A13+1)</f>
-        <v>Beam -Y -Z</v>
-      </c>
-      <c r="C13" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A13+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A13+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A13+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A13+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="101"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="82">
-        <v>7</v>
-      </c>
-      <c r="B14" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A14+1)</f>
-        <v xml:space="preserve">panel +Z, payload plate </v>
-      </c>
-      <c r="C14" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A14+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A14+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A14+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A14+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="101"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="82">
-        <v>8</v>
-      </c>
-      <c r="B15" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A15+1)</f>
-        <v xml:space="preserve">LED 1 </v>
-      </c>
-      <c r="C15" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A15+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A15+1,FALSE)</f>
-        <v>200</v>
-      </c>
-      <c r="E15" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A15+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A15+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G15" s="101"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="82">
-        <v>9</v>
-      </c>
-      <c r="B16" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A16+1)</f>
-        <v>LED 2</v>
-      </c>
-      <c r="C16" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A16+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A16+1,FALSE)</f>
-        <v>200</v>
-      </c>
-      <c r="E16" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A16+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A16+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G16" s="101"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="82">
-        <v>10</v>
-      </c>
-      <c r="B17" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A17+1)</f>
-        <v>LED 3</v>
-      </c>
-      <c r="C17" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A17+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A17+1,FALSE)</f>
-        <v>200</v>
-      </c>
-      <c r="E17" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A17+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A17+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G17" s="101"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="82">
-        <v>11</v>
-      </c>
-      <c r="B18" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A18+1)</f>
-        <v xml:space="preserve">LED 4 </v>
-      </c>
-      <c r="C18" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A18+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A18+1,FALSE)</f>
-        <v>200</v>
-      </c>
-      <c r="E18" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A18+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A18+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G18" s="101"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="82">
-        <v>12</v>
-      </c>
-      <c r="B19" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A19+1)</f>
-        <v>Node 12, BMS</v>
-      </c>
-      <c r="C19" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A19+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A19+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A19+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A19+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="101"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="82">
-        <v>13</v>
-      </c>
-      <c r="B20" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A20+1)</f>
-        <v>Node 13, Batteries Isolation</v>
-      </c>
-      <c r="C20" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A20+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A20+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A20+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A20+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="101"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="82">
-        <v>14</v>
-      </c>
-      <c r="B21" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A21+1)</f>
-        <v>Node 14, LiFePo4 1</v>
-      </c>
-      <c r="C21" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A21+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A21+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A21+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A21+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="101"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="82">
-        <v>15</v>
-      </c>
-      <c r="B22" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A22+1)</f>
-        <v>Node 15, LiFePo4 3</v>
-      </c>
-      <c r="C22" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A22+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A22+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A22+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A22+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="101"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="82">
-        <v>16</v>
-      </c>
-      <c r="B23" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A23+1)</f>
-        <v>Node 16, LiFePo4 2</v>
-      </c>
-      <c r="C23" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A23+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A23+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A23+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A23+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="101"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="82">
-        <v>17</v>
-      </c>
-      <c r="B24" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A24+1)</f>
-        <v>Node 17, LiFePo4 4</v>
-      </c>
-      <c r="C24" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A24+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A24+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A24+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A24+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="101"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="82">
-        <v>18</v>
-      </c>
-      <c r="B25" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A25+1)</f>
-        <v>Node 18, Cell Litio 1</v>
-      </c>
-      <c r="C25" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A25+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A25+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A25+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A25+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="101"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="82">
-        <v>19</v>
-      </c>
-      <c r="B26" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A26+1)</f>
-        <v>Node 19, Cell Litio 2</v>
-      </c>
-      <c r="C26" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A26+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A26+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A26+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A26+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="101"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="82">
-        <v>20</v>
-      </c>
-      <c r="B27" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A27+1)</f>
-        <v>Node 20, LoMo</v>
-      </c>
-      <c r="C27" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A27+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A27+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A27+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A27+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="101"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="82">
-        <v>21</v>
-      </c>
-      <c r="B28" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A28+1)</f>
-        <v>Node 21, Transceiver(Tx-Rx)</v>
-      </c>
-      <c r="C28" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A28+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A28+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A28+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A28+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="101"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="82">
-        <v>22</v>
-      </c>
-      <c r="B29" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A29+1)</f>
-        <v>Node 22, Antena module</v>
-      </c>
-      <c r="C29" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A29+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A29+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A29+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A29+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="101"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="82">
-        <v>23</v>
-      </c>
-      <c r="B30" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A30+1)</f>
-        <v>Node 23, OBC</v>
-      </c>
-      <c r="C30" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A30+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A30+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A30+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A30+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="101"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="82">
-        <v>24</v>
-      </c>
-      <c r="B31" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A31+1)</f>
-        <v>Node 24, Solar Panel (Y)</v>
-      </c>
-      <c r="C31" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A31+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A31+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A31+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A31+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="101"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="82">
-        <v>25</v>
-      </c>
-      <c r="B32" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A32+1)</f>
-        <v>Node 25, Solar Panel (-Y)</v>
-      </c>
-      <c r="C32" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A32+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A32+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A32+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A32+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G32" s="101"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="82">
-        <v>26</v>
-      </c>
-      <c r="B33" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A33+1)</f>
-        <v>Node 26, Solar Panel (X)</v>
-      </c>
-      <c r="C33" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A33+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A33+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A33+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A33+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="101"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="82">
-        <v>27</v>
-      </c>
-      <c r="B34" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A34+1)</f>
-        <v>Node 27, Solar Panel (-X)RBF</v>
-      </c>
-      <c r="C34" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A34+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A34+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A34+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A34+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="101"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="82">
-        <v>28</v>
-      </c>
-      <c r="B35" s="106" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A35+1)</f>
-        <v>Node 28, Solar Panel (-Z(antenna))</v>
-      </c>
-      <c r="C35" s="107">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A35+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D35" s="108">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A35+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="108">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A35+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="109">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A35+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="101"/>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A36" s="82">
-        <v>29</v>
-      </c>
-      <c r="B36" s="110" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A36+1)</f>
-        <v>Node 29, EPS de alta</v>
-      </c>
-      <c r="C36" s="111">
-        <f>HLOOKUP(C$2,Modes!$B$2:$E$31,$A36+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="112">
-        <f>HLOOKUP(D$2,Modes!$B$2:$E$31,$A36+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="112">
-        <f>HLOOKUP(E$2,Modes!$B$2:$E$31,$A36+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="113">
-        <f>HLOOKUP(F$2,Modes!$B$2:$E$31,$A36+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="101"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="B37" s="80"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B005E130-2D16-4A0C-8BB3-2172273CEA1D}">
-  <dimension ref="B1:F31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B2" s="126" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" s="121" t="s">
-        <v>260</v>
-      </c>
-      <c r="D2" s="118" t="s">
-        <v>258</v>
-      </c>
-      <c r="E2" s="122" t="s">
-        <v>259</v>
-      </c>
-      <c r="F2" s="101"/>
-    </row>
-    <row r="3" spans="2:6">
-      <c r="B3" s="127" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" s="119">
-        <v>0</v>
-      </c>
-      <c r="D3" s="120">
-        <v>0</v>
-      </c>
-      <c r="E3" s="123">
-        <v>0</v>
-      </c>
-      <c r="F3" s="101"/>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="128" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="115">
-        <v>0</v>
-      </c>
-      <c r="D4" s="114">
-        <v>0</v>
-      </c>
-      <c r="E4" s="124">
-        <v>0</v>
-      </c>
-      <c r="F4" s="101"/>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="128" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="115">
-        <v>0</v>
-      </c>
-      <c r="D5" s="114">
-        <v>0</v>
-      </c>
-      <c r="E5" s="124">
-        <v>0</v>
-      </c>
-      <c r="F5" s="101"/>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="128" t="s">
-        <v>217</v>
-      </c>
-      <c r="C6" s="115">
-        <v>0</v>
-      </c>
-      <c r="D6" s="114">
-        <v>0</v>
-      </c>
-      <c r="E6" s="124">
-        <v>0</v>
-      </c>
-      <c r="F6" s="101"/>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="128" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="115">
-        <v>0</v>
-      </c>
-      <c r="D7" s="114">
-        <v>0</v>
-      </c>
-      <c r="E7" s="124">
-        <v>0</v>
-      </c>
-      <c r="F7" s="101"/>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="128" t="s">
-        <v>219</v>
-      </c>
-      <c r="C8" s="115">
-        <v>0</v>
-      </c>
-      <c r="D8" s="114">
-        <v>0</v>
-      </c>
-      <c r="E8" s="124">
-        <v>0</v>
-      </c>
-      <c r="F8" s="101"/>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="128" t="s">
-        <v>220</v>
-      </c>
-      <c r="C9" s="115">
-        <v>0</v>
-      </c>
-      <c r="D9" s="114">
-        <v>0</v>
-      </c>
-      <c r="E9" s="124">
-        <v>0</v>
-      </c>
-      <c r="F9" s="101"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="128" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="115">
-        <v>0</v>
-      </c>
-      <c r="D10" s="114">
-        <v>200</v>
-      </c>
-      <c r="E10" s="124">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F10" s="101"/>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="128" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="115">
-        <v>0</v>
-      </c>
-      <c r="D11" s="114">
-        <v>200</v>
-      </c>
-      <c r="E11" s="124">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F11" s="101"/>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="128" t="s">
-        <v>223</v>
-      </c>
-      <c r="C12" s="115">
-        <v>0</v>
-      </c>
-      <c r="D12" s="114">
-        <v>200</v>
-      </c>
-      <c r="E12" s="124">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F12" s="101"/>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="128" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" s="115">
-        <v>0</v>
-      </c>
-      <c r="D13" s="114">
-        <v>200</v>
-      </c>
-      <c r="E13" s="124">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F13" s="101"/>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="128" t="s">
-        <v>225</v>
-      </c>
-      <c r="C14" s="115">
-        <v>0</v>
-      </c>
-      <c r="D14" s="114">
-        <v>0</v>
-      </c>
-      <c r="E14" s="124">
-        <v>0</v>
-      </c>
-      <c r="F14" s="101"/>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="128" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" s="115">
-        <v>0</v>
-      </c>
-      <c r="D15" s="114">
-        <v>0</v>
-      </c>
-      <c r="E15" s="124">
-        <v>0</v>
-      </c>
-      <c r="F15" s="101"/>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="128" t="s">
-        <v>227</v>
-      </c>
-      <c r="C16" s="115">
-        <v>0</v>
-      </c>
-      <c r="D16" s="114">
-        <v>0</v>
-      </c>
-      <c r="E16" s="124">
-        <v>0</v>
-      </c>
-      <c r="F16" s="101"/>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="128" t="s">
-        <v>228</v>
-      </c>
-      <c r="C17" s="115">
-        <v>0</v>
-      </c>
-      <c r="D17" s="114">
-        <v>0</v>
-      </c>
-      <c r="E17" s="124">
-        <v>0</v>
-      </c>
-      <c r="F17" s="101"/>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="128" t="s">
-        <v>229</v>
-      </c>
-      <c r="C18" s="115">
-        <v>0</v>
-      </c>
-      <c r="D18" s="114">
-        <v>0</v>
-      </c>
-      <c r="E18" s="124">
-        <v>0</v>
-      </c>
-      <c r="F18" s="101"/>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="128" t="s">
-        <v>230</v>
-      </c>
-      <c r="C19" s="115">
-        <v>0</v>
-      </c>
-      <c r="D19" s="114">
-        <v>0</v>
-      </c>
-      <c r="E19" s="124">
-        <v>0</v>
-      </c>
-      <c r="F19" s="101"/>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="128" t="s">
-        <v>231</v>
-      </c>
-      <c r="C20" s="115">
-        <v>0</v>
-      </c>
-      <c r="D20" s="114">
-        <v>0</v>
-      </c>
-      <c r="E20" s="124">
-        <v>0</v>
-      </c>
-      <c r="F20" s="101"/>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="128" t="s">
-        <v>232</v>
-      </c>
-      <c r="C21" s="115">
-        <v>0</v>
-      </c>
-      <c r="D21" s="114">
-        <v>0</v>
-      </c>
-      <c r="E21" s="124">
-        <v>0</v>
-      </c>
-      <c r="F21" s="101"/>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" s="128" t="s">
-        <v>233</v>
-      </c>
-      <c r="C22" s="115">
-        <v>0</v>
-      </c>
-      <c r="D22" s="114">
-        <v>0</v>
-      </c>
-      <c r="E22" s="124">
-        <v>0</v>
-      </c>
-      <c r="F22" s="101"/>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" s="128" t="s">
-        <v>234</v>
-      </c>
-      <c r="C23" s="115">
-        <v>0</v>
-      </c>
-      <c r="D23" s="114">
-        <v>0</v>
-      </c>
-      <c r="E23" s="124">
-        <v>0</v>
-      </c>
-      <c r="F23" s="101"/>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" s="128" t="s">
-        <v>235</v>
-      </c>
-      <c r="C24" s="115">
-        <v>0</v>
-      </c>
-      <c r="D24" s="114">
-        <v>0</v>
-      </c>
-      <c r="E24" s="124">
-        <v>0</v>
-      </c>
-      <c r="F24" s="101"/>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="128" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="115">
-        <v>0</v>
-      </c>
-      <c r="D25" s="114">
-        <v>0</v>
-      </c>
-      <c r="E25" s="124">
-        <v>0</v>
-      </c>
-      <c r="F25" s="101"/>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="128" t="s">
-        <v>237</v>
-      </c>
-      <c r="C26" s="115">
-        <v>0</v>
-      </c>
-      <c r="D26" s="114">
-        <v>0</v>
-      </c>
-      <c r="E26" s="124">
-        <v>0</v>
-      </c>
-      <c r="F26" s="101"/>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27" s="128" t="s">
-        <v>238</v>
-      </c>
-      <c r="C27" s="115">
-        <v>0</v>
-      </c>
-      <c r="D27" s="114">
-        <v>0</v>
-      </c>
-      <c r="E27" s="124">
-        <v>0</v>
-      </c>
-      <c r="F27" s="101"/>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28" s="128" t="s">
-        <v>239</v>
-      </c>
-      <c r="C28" s="115">
-        <v>0</v>
-      </c>
-      <c r="D28" s="114">
-        <v>0</v>
-      </c>
-      <c r="E28" s="124">
-        <v>0</v>
-      </c>
-      <c r="F28" s="101"/>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="128" t="s">
-        <v>240</v>
-      </c>
-      <c r="C29" s="115">
-        <v>0</v>
-      </c>
-      <c r="D29" s="114">
-        <v>0</v>
-      </c>
-      <c r="E29" s="124">
-        <v>0</v>
-      </c>
-      <c r="F29" s="101"/>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" s="128" t="s">
-        <v>241</v>
-      </c>
-      <c r="C30" s="115">
-        <v>0</v>
-      </c>
-      <c r="D30" s="114">
-        <v>0</v>
-      </c>
-      <c r="E30" s="124">
-        <v>0</v>
-      </c>
-      <c r="F30" s="101"/>
-    </row>
-    <row r="31" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B31" s="129" t="s">
-        <v>242</v>
-      </c>
-      <c r="C31" s="116">
-        <v>0</v>
-      </c>
-      <c r="D31" s="117">
-        <v>0</v>
-      </c>
-      <c r="E31" s="125">
-        <v>0</v>
-      </c>
-      <c r="F31" s="101"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DA363B-02D6-471C-A546-574AA58E41CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF56F914-63FC-4545-8856-CE21525E64FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF56F914-63FC-4545-8856-CE21525E64FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9328060-3922-4B4F-9519-0E5D671A65AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2531,10 +2531,6 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2612,6 +2608,10 @@
     <xf numFmtId="0" fontId="1" fillId="21" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10003,10 +10003,10 @@
         <v>149</v>
       </c>
       <c r="G2" s="32"/>
-      <c r="H2" s="118" t="s">
+      <c r="H2" s="147" t="s">
         <v>150</v>
       </c>
-      <c r="I2" s="119"/>
+      <c r="I2" s="148"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="33" t="s">
@@ -11021,24 +11021,24 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:6" ht="45">
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="144" t="s">
         <v>266</v>
       </c>
-      <c r="C2" s="147" t="s">
+      <c r="C2" s="145" t="s">
         <v>267</v>
       </c>
-      <c r="D2" s="147" t="s">
+      <c r="D2" s="145" t="s">
         <v>265</v>
       </c>
-      <c r="E2" s="147" t="s">
+      <c r="E2" s="145" t="s">
         <v>264</v>
       </c>
-      <c r="F2" s="148" t="s">
+      <c r="F2" s="146" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B3" s="136">
+      <c r="B3" s="134">
         <v>1</v>
       </c>
       <c r="C3" s="85">
@@ -11048,9 +11048,9 @@
         <v>0</v>
       </c>
       <c r="E3" s="85">
-        <v>0</v>
-      </c>
-      <c r="F3" s="137">
+        <v>300</v>
+      </c>
+      <c r="F3" s="135">
         <v>1</v>
       </c>
     </row>
@@ -11069,7 +11069,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1">
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="139" t="s">
         <v>257</v>
       </c>
       <c r="C2" s="87" t="s">
@@ -11078,13 +11078,13 @@
       <c r="D2" s="86" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="125" t="s">
+      <c r="E2" s="123" t="s">
         <v>260</v>
       </c>
       <c r="F2" s="93" t="s">
         <v>259</v>
       </c>
-      <c r="G2" s="126"/>
+      <c r="G2" s="124"/>
     </row>
     <row r="3" spans="1:14">
       <c r="B3" s="89" t="s">
@@ -11156,13 +11156,13 @@
       <c r="G6" s="96"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="B7" s="120" t="s">
+      <c r="B7" s="118" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="121"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="124"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="122"/>
       <c r="G7" s="96"/>
     </row>
     <row r="8" spans="1:14">
@@ -12053,58 +12053,58 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:15" ht="15.75" thickBot="1">
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="140" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="127" t="s">
+      <c r="C2" s="125" t="s">
         <v>260</v>
       </c>
-      <c r="D2" s="128" t="s">
+      <c r="D2" s="126" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="128" t="s">
+      <c r="E2" s="126" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="130"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="128"/>
     </row>
     <row r="3" spans="2:15">
-      <c r="B3" s="143" t="s">
+      <c r="B3" s="141" t="s">
         <v>214</v>
       </c>
-      <c r="C3" s="131">
-        <v>0</v>
-      </c>
-      <c r="D3" s="132">
-        <v>0</v>
-      </c>
-      <c r="E3" s="132">
-        <v>0</v>
-      </c>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="132"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132"/>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="N3" s="132"/>
-      <c r="O3" s="133"/>
+      <c r="C3" s="129">
+        <v>0</v>
+      </c>
+      <c r="D3" s="130">
+        <v>0</v>
+      </c>
+      <c r="E3" s="130">
+        <v>0</v>
+      </c>
+      <c r="F3" s="130"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="131"/>
     </row>
     <row r="4" spans="2:15">
-      <c r="B4" s="144" t="s">
+      <c r="B4" s="142" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="134">
+      <c r="C4" s="132">
         <v>0</v>
       </c>
       <c r="D4" s="84">
@@ -12122,13 +12122,13 @@
       <c r="L4" s="84"/>
       <c r="M4" s="84"/>
       <c r="N4" s="84"/>
-      <c r="O4" s="135"/>
+      <c r="O4" s="133"/>
     </row>
     <row r="5" spans="2:15">
-      <c r="B5" s="144" t="s">
+      <c r="B5" s="142" t="s">
         <v>216</v>
       </c>
-      <c r="C5" s="134">
+      <c r="C5" s="132">
         <v>0</v>
       </c>
       <c r="D5" s="84">
@@ -12146,13 +12146,13 @@
       <c r="L5" s="84"/>
       <c r="M5" s="84"/>
       <c r="N5" s="84"/>
-      <c r="O5" s="135"/>
+      <c r="O5" s="133"/>
     </row>
     <row r="6" spans="2:15">
-      <c r="B6" s="144" t="s">
+      <c r="B6" s="142" t="s">
         <v>217</v>
       </c>
-      <c r="C6" s="134">
+      <c r="C6" s="132">
         <v>0</v>
       </c>
       <c r="D6" s="84">
@@ -12170,13 +12170,13 @@
       <c r="L6" s="84"/>
       <c r="M6" s="84"/>
       <c r="N6" s="84"/>
-      <c r="O6" s="135"/>
+      <c r="O6" s="133"/>
     </row>
     <row r="7" spans="2:15">
-      <c r="B7" s="144" t="s">
+      <c r="B7" s="142" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="134">
+      <c r="C7" s="132">
         <v>0</v>
       </c>
       <c r="D7" s="84">
@@ -12194,13 +12194,13 @@
       <c r="L7" s="84"/>
       <c r="M7" s="84"/>
       <c r="N7" s="84"/>
-      <c r="O7" s="135"/>
+      <c r="O7" s="133"/>
     </row>
     <row r="8" spans="2:15">
-      <c r="B8" s="144" t="s">
+      <c r="B8" s="142" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="134">
+      <c r="C8" s="132">
         <v>0</v>
       </c>
       <c r="D8" s="84">
@@ -12218,13 +12218,13 @@
       <c r="L8" s="84"/>
       <c r="M8" s="84"/>
       <c r="N8" s="84"/>
-      <c r="O8" s="135"/>
+      <c r="O8" s="133"/>
     </row>
     <row r="9" spans="2:15">
-      <c r="B9" s="144" t="s">
+      <c r="B9" s="142" t="s">
         <v>220</v>
       </c>
-      <c r="C9" s="134">
+      <c r="C9" s="132">
         <v>0</v>
       </c>
       <c r="D9" s="84">
@@ -12242,13 +12242,13 @@
       <c r="L9" s="84"/>
       <c r="M9" s="84"/>
       <c r="N9" s="84"/>
-      <c r="O9" s="135"/>
+      <c r="O9" s="133"/>
     </row>
     <row r="10" spans="2:15">
-      <c r="B10" s="144" t="s">
+      <c r="B10" s="142" t="s">
         <v>221</v>
       </c>
-      <c r="C10" s="134">
+      <c r="C10" s="132">
         <v>0</v>
       </c>
       <c r="D10" s="84">
@@ -12266,13 +12266,13 @@
       <c r="L10" s="84"/>
       <c r="M10" s="84"/>
       <c r="N10" s="84"/>
-      <c r="O10" s="135"/>
+      <c r="O10" s="133"/>
     </row>
     <row r="11" spans="2:15">
-      <c r="B11" s="144" t="s">
+      <c r="B11" s="142" t="s">
         <v>222</v>
       </c>
-      <c r="C11" s="134">
+      <c r="C11" s="132">
         <v>0</v>
       </c>
       <c r="D11" s="84">
@@ -12290,13 +12290,13 @@
       <c r="L11" s="84"/>
       <c r="M11" s="84"/>
       <c r="N11" s="84"/>
-      <c r="O11" s="135"/>
+      <c r="O11" s="133"/>
     </row>
     <row r="12" spans="2:15">
-      <c r="B12" s="144" t="s">
+      <c r="B12" s="142" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="134">
+      <c r="C12" s="132">
         <v>0</v>
       </c>
       <c r="D12" s="84">
@@ -12314,13 +12314,13 @@
       <c r="L12" s="84"/>
       <c r="M12" s="84"/>
       <c r="N12" s="84"/>
-      <c r="O12" s="135"/>
+      <c r="O12" s="133"/>
     </row>
     <row r="13" spans="2:15">
-      <c r="B13" s="144" t="s">
+      <c r="B13" s="142" t="s">
         <v>224</v>
       </c>
-      <c r="C13" s="134">
+      <c r="C13" s="132">
         <v>0</v>
       </c>
       <c r="D13" s="84">
@@ -12338,13 +12338,13 @@
       <c r="L13" s="84"/>
       <c r="M13" s="84"/>
       <c r="N13" s="84"/>
-      <c r="O13" s="135"/>
+      <c r="O13" s="133"/>
     </row>
     <row r="14" spans="2:15">
-      <c r="B14" s="144" t="s">
+      <c r="B14" s="142" t="s">
         <v>225</v>
       </c>
-      <c r="C14" s="134">
+      <c r="C14" s="132">
         <v>0</v>
       </c>
       <c r="D14" s="84">
@@ -12362,13 +12362,13 @@
       <c r="L14" s="84"/>
       <c r="M14" s="84"/>
       <c r="N14" s="84"/>
-      <c r="O14" s="135"/>
+      <c r="O14" s="133"/>
     </row>
     <row r="15" spans="2:15">
-      <c r="B15" s="144" t="s">
+      <c r="B15" s="142" t="s">
         <v>226</v>
       </c>
-      <c r="C15" s="134">
+      <c r="C15" s="132">
         <v>0</v>
       </c>
       <c r="D15" s="84">
@@ -12386,13 +12386,13 @@
       <c r="L15" s="84"/>
       <c r="M15" s="84"/>
       <c r="N15" s="84"/>
-      <c r="O15" s="135"/>
+      <c r="O15" s="133"/>
     </row>
     <row r="16" spans="2:15">
-      <c r="B16" s="144" t="s">
+      <c r="B16" s="142" t="s">
         <v>227</v>
       </c>
-      <c r="C16" s="134">
+      <c r="C16" s="132">
         <v>0</v>
       </c>
       <c r="D16" s="84">
@@ -12410,13 +12410,13 @@
       <c r="L16" s="84"/>
       <c r="M16" s="84"/>
       <c r="N16" s="84"/>
-      <c r="O16" s="135"/>
+      <c r="O16" s="133"/>
     </row>
     <row r="17" spans="2:15">
-      <c r="B17" s="144" t="s">
+      <c r="B17" s="142" t="s">
         <v>228</v>
       </c>
-      <c r="C17" s="134">
+      <c r="C17" s="132">
         <v>0</v>
       </c>
       <c r="D17" s="84">
@@ -12434,13 +12434,13 @@
       <c r="L17" s="84"/>
       <c r="M17" s="84"/>
       <c r="N17" s="84"/>
-      <c r="O17" s="135"/>
+      <c r="O17" s="133"/>
     </row>
     <row r="18" spans="2:15">
-      <c r="B18" s="144" t="s">
+      <c r="B18" s="142" t="s">
         <v>229</v>
       </c>
-      <c r="C18" s="134">
+      <c r="C18" s="132">
         <v>0</v>
       </c>
       <c r="D18" s="84">
@@ -12458,13 +12458,13 @@
       <c r="L18" s="84"/>
       <c r="M18" s="84"/>
       <c r="N18" s="84"/>
-      <c r="O18" s="135"/>
+      <c r="O18" s="133"/>
     </row>
     <row r="19" spans="2:15">
-      <c r="B19" s="144" t="s">
+      <c r="B19" s="142" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="134">
+      <c r="C19" s="132">
         <v>0</v>
       </c>
       <c r="D19" s="84">
@@ -12482,13 +12482,13 @@
       <c r="L19" s="84"/>
       <c r="M19" s="84"/>
       <c r="N19" s="84"/>
-      <c r="O19" s="135"/>
+      <c r="O19" s="133"/>
     </row>
     <row r="20" spans="2:15">
-      <c r="B20" s="144" t="s">
+      <c r="B20" s="142" t="s">
         <v>231</v>
       </c>
-      <c r="C20" s="134">
+      <c r="C20" s="132">
         <v>0</v>
       </c>
       <c r="D20" s="84">
@@ -12506,13 +12506,13 @@
       <c r="L20" s="84"/>
       <c r="M20" s="84"/>
       <c r="N20" s="84"/>
-      <c r="O20" s="135"/>
+      <c r="O20" s="133"/>
     </row>
     <row r="21" spans="2:15">
-      <c r="B21" s="144" t="s">
+      <c r="B21" s="142" t="s">
         <v>232</v>
       </c>
-      <c r="C21" s="134">
+      <c r="C21" s="132">
         <v>0</v>
       </c>
       <c r="D21" s="84">
@@ -12530,13 +12530,13 @@
       <c r="L21" s="84"/>
       <c r="M21" s="84"/>
       <c r="N21" s="84"/>
-      <c r="O21" s="135"/>
+      <c r="O21" s="133"/>
     </row>
     <row r="22" spans="2:15">
-      <c r="B22" s="144" t="s">
+      <c r="B22" s="142" t="s">
         <v>233</v>
       </c>
-      <c r="C22" s="134">
+      <c r="C22" s="132">
         <v>0</v>
       </c>
       <c r="D22" s="84">
@@ -12554,13 +12554,13 @@
       <c r="L22" s="84"/>
       <c r="M22" s="84"/>
       <c r="N22" s="84"/>
-      <c r="O22" s="135"/>
+      <c r="O22" s="133"/>
     </row>
     <row r="23" spans="2:15">
-      <c r="B23" s="144" t="s">
+      <c r="B23" s="142" t="s">
         <v>234</v>
       </c>
-      <c r="C23" s="134">
+      <c r="C23" s="132">
         <v>0</v>
       </c>
       <c r="D23" s="84">
@@ -12578,13 +12578,13 @@
       <c r="L23" s="84"/>
       <c r="M23" s="84"/>
       <c r="N23" s="84"/>
-      <c r="O23" s="135"/>
+      <c r="O23" s="133"/>
     </row>
     <row r="24" spans="2:15">
-      <c r="B24" s="144" t="s">
+      <c r="B24" s="142" t="s">
         <v>235</v>
       </c>
-      <c r="C24" s="134">
+      <c r="C24" s="132">
         <v>0</v>
       </c>
       <c r="D24" s="84">
@@ -12602,13 +12602,13 @@
       <c r="L24" s="84"/>
       <c r="M24" s="84"/>
       <c r="N24" s="84"/>
-      <c r="O24" s="135"/>
+      <c r="O24" s="133"/>
     </row>
     <row r="25" spans="2:15">
-      <c r="B25" s="144" t="s">
+      <c r="B25" s="142" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="134">
+      <c r="C25" s="132">
         <v>0</v>
       </c>
       <c r="D25" s="84">
@@ -12626,13 +12626,13 @@
       <c r="L25" s="84"/>
       <c r="M25" s="84"/>
       <c r="N25" s="84"/>
-      <c r="O25" s="135"/>
+      <c r="O25" s="133"/>
     </row>
     <row r="26" spans="2:15">
-      <c r="B26" s="144" t="s">
+      <c r="B26" s="142" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="134">
+      <c r="C26" s="132">
         <v>0</v>
       </c>
       <c r="D26" s="84">
@@ -12650,13 +12650,13 @@
       <c r="L26" s="84"/>
       <c r="M26" s="84"/>
       <c r="N26" s="84"/>
-      <c r="O26" s="135"/>
+      <c r="O26" s="133"/>
     </row>
     <row r="27" spans="2:15">
-      <c r="B27" s="144" t="s">
+      <c r="B27" s="142" t="s">
         <v>238</v>
       </c>
-      <c r="C27" s="134">
+      <c r="C27" s="132">
         <v>0</v>
       </c>
       <c r="D27" s="84">
@@ -12674,13 +12674,13 @@
       <c r="L27" s="84"/>
       <c r="M27" s="84"/>
       <c r="N27" s="84"/>
-      <c r="O27" s="135"/>
+      <c r="O27" s="133"/>
     </row>
     <row r="28" spans="2:15">
-      <c r="B28" s="144" t="s">
+      <c r="B28" s="142" t="s">
         <v>239</v>
       </c>
-      <c r="C28" s="134">
+      <c r="C28" s="132">
         <v>0</v>
       </c>
       <c r="D28" s="84">
@@ -12698,13 +12698,13 @@
       <c r="L28" s="84"/>
       <c r="M28" s="84"/>
       <c r="N28" s="84"/>
-      <c r="O28" s="135"/>
+      <c r="O28" s="133"/>
     </row>
     <row r="29" spans="2:15">
-      <c r="B29" s="144" t="s">
+      <c r="B29" s="142" t="s">
         <v>240</v>
       </c>
-      <c r="C29" s="134">
+      <c r="C29" s="132">
         <v>0</v>
       </c>
       <c r="D29" s="84">
@@ -12722,13 +12722,13 @@
       <c r="L29" s="84"/>
       <c r="M29" s="84"/>
       <c r="N29" s="84"/>
-      <c r="O29" s="135"/>
+      <c r="O29" s="133"/>
     </row>
     <row r="30" spans="2:15">
-      <c r="B30" s="144" t="s">
+      <c r="B30" s="142" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="134">
+      <c r="C30" s="132">
         <v>0</v>
       </c>
       <c r="D30" s="84">
@@ -12746,31 +12746,31 @@
       <c r="L30" s="84"/>
       <c r="M30" s="84"/>
       <c r="N30" s="84"/>
-      <c r="O30" s="135"/>
+      <c r="O30" s="133"/>
     </row>
     <row r="31" spans="2:15">
-      <c r="B31" s="145" t="s">
+      <c r="B31" s="143" t="s">
         <v>242</v>
       </c>
-      <c r="C31" s="138">
-        <v>0</v>
-      </c>
-      <c r="D31" s="122">
-        <v>0</v>
-      </c>
-      <c r="E31" s="122">
-        <v>0</v>
-      </c>
-      <c r="F31" s="122"/>
-      <c r="G31" s="122"/>
-      <c r="H31" s="122"/>
-      <c r="I31" s="122"/>
-      <c r="J31" s="122"/>
-      <c r="K31" s="122"/>
-      <c r="L31" s="122"/>
-      <c r="M31" s="122"/>
-      <c r="N31" s="122"/>
-      <c r="O31" s="139"/>
+      <c r="C31" s="136">
+        <v>0</v>
+      </c>
+      <c r="D31" s="120">
+        <v>0</v>
+      </c>
+      <c r="E31" s="120">
+        <v>0</v>
+      </c>
+      <c r="F31" s="120"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="120"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="120"/>
+      <c r="O31" s="137"/>
     </row>
     <row r="32" spans="2:15">
       <c r="B32" s="96"/>
@@ -12811,7 +12811,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:13" ht="30" customHeight="1" thickBot="1">
+    <row r="2" spans="2:13" ht="46.5" customHeight="1" thickBot="1">
       <c r="B2" s="111" t="s">
         <v>252</v>
       </c>
@@ -12842,7 +12842,7 @@
       <c r="K2" s="113" t="s">
         <v>251</v>
       </c>
-      <c r="L2" s="140" t="s">
+      <c r="L2" s="138" t="s">
         <v>262</v>
       </c>
       <c r="M2" s="114" t="s">

--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9328060-3922-4B4F-9519-0E5D671A65AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB26D28-3013-4CD9-BC48-2EE9A94F7B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes properties" sheetId="1" r:id="rId1"/>
@@ -1274,11 +1274,18 @@
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1474,7 +1481,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="61">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -2015,19 +2022,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -2296,163 +2290,163 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2461,34 +2455,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -2498,10 +2477,7 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2509,57 +2485,54 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2568,50 +2541,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="43" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="41" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="58" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10003,10 +9988,10 @@
         <v>149</v>
       </c>
       <c r="G2" s="32"/>
-      <c r="H2" s="147" t="s">
+      <c r="H2" s="140" t="s">
         <v>150</v>
       </c>
-      <c r="I2" s="148"/>
+      <c r="I2" s="141"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="33" t="s">
@@ -11021,24 +11006,24 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:6" ht="45">
-      <c r="B2" s="144" t="s">
+      <c r="B2" s="137" t="s">
         <v>266</v>
       </c>
-      <c r="C2" s="145" t="s">
+      <c r="C2" s="138" t="s">
         <v>267</v>
       </c>
-      <c r="D2" s="145" t="s">
+      <c r="D2" s="138" t="s">
         <v>265</v>
       </c>
-      <c r="E2" s="145" t="s">
+      <c r="E2" s="138" t="s">
         <v>264</v>
       </c>
-      <c r="F2" s="146" t="s">
+      <c r="F2" s="139" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B3" s="134">
+      <c r="B3" s="127">
         <v>1</v>
       </c>
       <c r="C3" s="85">
@@ -11050,7 +11035,7 @@
       <c r="E3" s="85">
         <v>300</v>
       </c>
-      <c r="F3" s="135">
+      <c r="F3" s="128">
         <v>1</v>
       </c>
     </row>
@@ -11069,44 +11054,44 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1">
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="132" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="142" t="s">
+        <v>259</v>
+      </c>
+      <c r="D2" s="144" t="s">
+        <v>259</v>
+      </c>
+      <c r="E2" s="144" t="s">
+        <v>258</v>
+      </c>
+      <c r="F2" s="145" t="s">
         <v>260</v>
       </c>
-      <c r="D2" s="86" t="s">
-        <v>258</v>
-      </c>
-      <c r="E2" s="123" t="s">
-        <v>260</v>
-      </c>
-      <c r="F2" s="93" t="s">
-        <v>259</v>
-      </c>
-      <c r="G2" s="124"/>
+      <c r="G2" s="117"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="87" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="91">
-        <f>C4+C5*60+C6*3600+C7*3600*24</f>
-        <v>3600</v>
-      </c>
-      <c r="D3" s="92">
-        <f>C3+D4+D5*60+D6*3600+D7*3600*24</f>
-        <v>3720</v>
-      </c>
-      <c r="E3" s="92">
-        <f t="shared" ref="E3" si="0">D3+E4+E5*60+E6*3600+E7*3600*24</f>
-        <v>10920</v>
-      </c>
-      <c r="F3" s="94">
-        <f>E3+F4+F5*60+F6*3600+F7*3600*24</f>
-        <v>18120</v>
-      </c>
-      <c r="G3" s="96"/>
+      <c r="C3" s="89">
+        <f>IFERROR(C4+C5*60+C6*3600+C7*3600*24+B3,C4+C5*60+C6*3600+C7*3600*24)</f>
+        <v>32400</v>
+      </c>
+      <c r="D3" s="89">
+        <f t="shared" ref="D3:F3" si="0">IFERROR(D4+D5*60+D6*3600+D7*3600*24+C3,D4+D5*60+D6*3600+D7*3600*24)</f>
+        <v>32400</v>
+      </c>
+      <c r="E3" s="89">
+        <f t="shared" si="0"/>
+        <v>32400</v>
+      </c>
+      <c r="F3" s="89">
+        <f t="shared" si="0"/>
+        <v>32460</v>
+      </c>
+      <c r="G3" s="91"/>
       <c r="H3" s="81"/>
       <c r="I3" s="81"/>
       <c r="J3" s="81"/>
@@ -11116,924 +11101,918 @@
       <c r="N3" s="81"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="B4" s="90" t="s">
+      <c r="B4" s="88" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="88"/>
+      <c r="C4" s="86"/>
       <c r="D4" s="84"/>
       <c r="E4" s="83"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="96"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="91"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="88" t="s">
         <v>255</v>
       </c>
-      <c r="C5" s="88"/>
-      <c r="D5" s="84">
-        <v>2</v>
-      </c>
+      <c r="C5" s="86"/>
+      <c r="D5" s="84"/>
       <c r="E5" s="83"/>
-      <c r="F5" s="95">
-        <v>0</v>
-      </c>
-      <c r="G5" s="96"/>
+      <c r="F5" s="90">
+        <v>1</v>
+      </c>
+      <c r="G5" s="91"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="88" t="s">
         <v>254</v>
       </c>
-      <c r="C6" s="88">
-        <v>1</v>
+      <c r="C6" s="143">
+        <v>9</v>
       </c>
       <c r="D6" s="84"/>
-      <c r="E6" s="83">
-        <v>2</v>
-      </c>
-      <c r="F6" s="95">
-        <v>2</v>
-      </c>
-      <c r="G6" s="96"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="91"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="B7" s="118" t="s">
+      <c r="B7" s="112" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="119"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="96"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="91"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="82">
         <v>1</v>
       </c>
-      <c r="B8" s="97" t="str">
+      <c r="B8" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A8+1)</f>
         <v>Frame 1, +X</v>
       </c>
-      <c r="C8" s="98">
+      <c r="C8" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="99">
+      <c r="D8" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="99">
+      <c r="E8" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="100">
+      <c r="F8" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="100"/>
-      <c r="K8" s="100"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="94"/>
+      <c r="K8" s="94"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="82">
         <v>2</v>
       </c>
-      <c r="B9" s="97" t="str">
+      <c r="B9" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A9+1)</f>
         <v>Frame 2, -X</v>
       </c>
-      <c r="C9" s="98">
+      <c r="C9" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="99">
+      <c r="D9" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="99">
+      <c r="E9" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="100">
+      <c r="F9" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="100"/>
-      <c r="J9" s="100"/>
-      <c r="K9" s="100"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="82">
         <v>3</v>
       </c>
-      <c r="B10" s="97" t="str">
+      <c r="B10" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A10+1)</f>
         <v>Beam -Y +Z</v>
       </c>
-      <c r="C10" s="98">
+      <c r="C10" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="99">
+      <c r="D10" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="99">
+      <c r="E10" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="100">
+      <c r="F10" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="100"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="94"/>
+      <c r="J10" s="94"/>
+      <c r="K10" s="94"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="82">
         <v>4</v>
       </c>
-      <c r="B11" s="97" t="str">
+      <c r="B11" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A11+1)</f>
         <v>Beam +Y +Z</v>
       </c>
-      <c r="C11" s="98">
+      <c r="C11" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="99">
+      <c r="D11" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="99">
+      <c r="E11" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="100">
+      <c r="F11" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="94"/>
+      <c r="K11" s="94"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="82">
         <v>5</v>
       </c>
-      <c r="B12" s="97" t="str">
+      <c r="B12" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A12+1)</f>
         <v>Beam +Y -Z</v>
       </c>
-      <c r="C12" s="98">
+      <c r="C12" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="99">
+      <c r="D12" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="99">
+      <c r="E12" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="100">
+      <c r="F12" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="100"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="82">
         <v>6</v>
       </c>
-      <c r="B13" s="97" t="str">
+      <c r="B13" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A13+1)</f>
         <v>Beam -Y -Z</v>
       </c>
-      <c r="C13" s="98">
+      <c r="C13" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="99">
+      <c r="D13" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="99">
+      <c r="E13" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="100">
+      <c r="F13" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="100"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="94"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="82">
         <v>7</v>
       </c>
-      <c r="B14" s="97" t="str">
+      <c r="B14" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A14+1)</f>
         <v xml:space="preserve">panel +Z, payload plate </v>
       </c>
-      <c r="C14" s="98">
+      <c r="C14" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="99">
+      <c r="D14" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="99">
+      <c r="E14" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="100">
+      <c r="F14" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="100"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="100"/>
-      <c r="K14" s="100"/>
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="94"/>
+      <c r="K14" s="94"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="82">
         <v>8</v>
       </c>
-      <c r="B15" s="97" t="str">
+      <c r="B15" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A15+1)</f>
         <v xml:space="preserve">LED 1 </v>
       </c>
-      <c r="C15" s="98">
+      <c r="C15" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="99">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D15" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E15" s="93">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
         <v>200</v>
       </c>
-      <c r="E15" s="99">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="100">
+      <c r="F15" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="100"/>
-      <c r="K15" s="100"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="94"/>
+      <c r="K15" s="94"/>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="82">
         <v>9</v>
       </c>
-      <c r="B16" s="97" t="str">
+      <c r="B16" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A16+1)</f>
         <v>LED 2</v>
       </c>
-      <c r="C16" s="98">
+      <c r="C16" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="99">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D16" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E16" s="93">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
         <v>200</v>
       </c>
-      <c r="E16" s="99">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="100">
+      <c r="F16" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G16" s="100"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="100"/>
-      <c r="K16" s="100"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="94"/>
+      <c r="K16" s="94"/>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="82">
         <v>10</v>
       </c>
-      <c r="B17" s="97" t="str">
+      <c r="B17" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A17+1)</f>
         <v>LED 3</v>
       </c>
-      <c r="C17" s="98">
+      <c r="C17" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="99">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D17" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E17" s="93">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
         <v>200</v>
       </c>
-      <c r="E17" s="99">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="100">
+      <c r="F17" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="94"/>
+      <c r="K17" s="94"/>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="82">
         <v>11</v>
       </c>
-      <c r="B18" s="97" t="str">
+      <c r="B18" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A18+1)</f>
         <v xml:space="preserve">LED 4 </v>
       </c>
-      <c r="C18" s="98">
+      <c r="C18" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="99">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D18" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E18" s="93">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
         <v>200</v>
       </c>
-      <c r="E18" s="99">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="100">
+      <c r="F18" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="100"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="94"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="82">
         <v>12</v>
       </c>
-      <c r="B19" s="97" t="str">
+      <c r="B19" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A19+1)</f>
         <v>Node 12, BMS</v>
       </c>
-      <c r="C19" s="98">
+      <c r="C19" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="99">
+      <c r="D19" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="99">
+      <c r="E19" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="100">
+      <c r="F19" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="100"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="94"/>
+      <c r="J19" s="94"/>
+      <c r="K19" s="94"/>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="82">
         <v>13</v>
       </c>
-      <c r="B20" s="97" t="str">
+      <c r="B20" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A20+1)</f>
         <v>Node 13, Batteries Isolation</v>
       </c>
-      <c r="C20" s="98">
+      <c r="C20" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="99">
+      <c r="D20" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="99">
+      <c r="E20" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="100">
+      <c r="F20" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="100"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="100"/>
+      <c r="G20" s="94"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="94"/>
+      <c r="J20" s="94"/>
+      <c r="K20" s="94"/>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="82">
         <v>14</v>
       </c>
-      <c r="B21" s="97" t="str">
+      <c r="B21" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A21+1)</f>
         <v>Node 14, LiFePo4 1</v>
       </c>
-      <c r="C21" s="98">
+      <c r="C21" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="99">
+      <c r="D21" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="99">
+      <c r="E21" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="100">
+      <c r="F21" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="100"/>
-      <c r="H21" s="100"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="100"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="94"/>
+      <c r="J21" s="94"/>
+      <c r="K21" s="94"/>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="82">
         <v>15</v>
       </c>
-      <c r="B22" s="97" t="str">
+      <c r="B22" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A22+1)</f>
         <v>Node 15, LiFePo4 3</v>
       </c>
-      <c r="C22" s="98">
+      <c r="C22" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="99">
+      <c r="D22" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="99">
+      <c r="E22" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="100">
+      <c r="F22" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="100"/>
-      <c r="H22" s="100"/>
-      <c r="I22" s="100"/>
-      <c r="J22" s="100"/>
-      <c r="K22" s="100"/>
+      <c r="G22" s="94"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="94"/>
+      <c r="J22" s="94"/>
+      <c r="K22" s="94"/>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="82">
         <v>16</v>
       </c>
-      <c r="B23" s="97" t="str">
+      <c r="B23" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A23+1)</f>
         <v>Node 16, LiFePo4 2</v>
       </c>
-      <c r="C23" s="98">
+      <c r="C23" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="99">
+      <c r="D23" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="99">
+      <c r="E23" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="100">
+      <c r="F23" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="100"/>
+      <c r="G23" s="94"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="94"/>
+      <c r="K23" s="94"/>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="82">
         <v>17</v>
       </c>
-      <c r="B24" s="97" t="str">
+      <c r="B24" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A24+1)</f>
         <v>Node 17, LiFePo4 4</v>
       </c>
-      <c r="C24" s="98">
+      <c r="C24" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="99">
+      <c r="D24" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="99">
+      <c r="E24" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="100">
+      <c r="F24" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="100"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="94"/>
+      <c r="J24" s="94"/>
+      <c r="K24" s="94"/>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="82">
         <v>18</v>
       </c>
-      <c r="B25" s="97" t="str">
+      <c r="B25" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A25+1)</f>
         <v>Node 18, Cell Litio 1</v>
       </c>
-      <c r="C25" s="98">
+      <c r="C25" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="99">
+      <c r="D25" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="99">
+      <c r="E25" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="100">
+      <c r="F25" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="100"/>
-      <c r="H25" s="100"/>
-      <c r="I25" s="100"/>
-      <c r="J25" s="100"/>
-      <c r="K25" s="100"/>
+      <c r="G25" s="94"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="94"/>
+      <c r="J25" s="94"/>
+      <c r="K25" s="94"/>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="82">
         <v>19</v>
       </c>
-      <c r="B26" s="97" t="str">
+      <c r="B26" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A26+1)</f>
         <v>Node 19, Cell Litio 2</v>
       </c>
-      <c r="C26" s="98">
+      <c r="C26" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="99">
+      <c r="D26" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="99">
+      <c r="E26" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="100">
+      <c r="F26" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="100"/>
-      <c r="H26" s="100"/>
-      <c r="I26" s="100"/>
-      <c r="J26" s="100"/>
-      <c r="K26" s="100"/>
+      <c r="G26" s="94"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="94"/>
+      <c r="K26" s="94"/>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="82">
         <v>20</v>
       </c>
-      <c r="B27" s="97" t="str">
+      <c r="B27" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A27+1)</f>
         <v>Node 20, LoMo</v>
       </c>
-      <c r="C27" s="98">
+      <c r="C27" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="99">
+      <c r="D27" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="99">
+      <c r="E27" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="100">
+      <c r="F27" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="100"/>
+      <c r="G27" s="94"/>
+      <c r="H27" s="94"/>
+      <c r="I27" s="94"/>
+      <c r="J27" s="94"/>
+      <c r="K27" s="94"/>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="82">
         <v>21</v>
       </c>
-      <c r="B28" s="97" t="str">
+      <c r="B28" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A28+1)</f>
         <v>Node 21, Transceiver(Tx-Rx)</v>
       </c>
-      <c r="C28" s="98">
+      <c r="C28" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="99">
+      <c r="D28" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="99">
+      <c r="E28" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="100">
+      <c r="F28" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="100"/>
-      <c r="H28" s="100"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
+      <c r="G28" s="94"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="94"/>
+      <c r="J28" s="94"/>
+      <c r="K28" s="94"/>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="82">
         <v>22</v>
       </c>
-      <c r="B29" s="97" t="str">
+      <c r="B29" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A29+1)</f>
         <v>Node 22, Antena module</v>
       </c>
-      <c r="C29" s="98">
+      <c r="C29" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="99">
+      <c r="D29" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="99">
+      <c r="E29" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="100">
+      <c r="F29" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="100"/>
-      <c r="H29" s="100"/>
-      <c r="I29" s="100"/>
-      <c r="J29" s="100"/>
-      <c r="K29" s="100"/>
+      <c r="G29" s="94"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="94"/>
+      <c r="K29" s="94"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="82">
         <v>23</v>
       </c>
-      <c r="B30" s="97" t="str">
+      <c r="B30" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A30+1)</f>
         <v>Node 23, OBC</v>
       </c>
-      <c r="C30" s="98">
+      <c r="C30" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="99">
+      <c r="D30" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="99">
+      <c r="E30" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="100">
+      <c r="F30" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="100"/>
-      <c r="H30" s="100"/>
-      <c r="I30" s="100"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="100"/>
+      <c r="G30" s="94"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="94"/>
+      <c r="J30" s="94"/>
+      <c r="K30" s="94"/>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="82">
         <v>24</v>
       </c>
-      <c r="B31" s="97" t="str">
+      <c r="B31" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A31+1)</f>
         <v>Node 24, Solar Panel (Y)</v>
       </c>
-      <c r="C31" s="98">
+      <c r="C31" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="99">
+      <c r="D31" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="99">
+      <c r="E31" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F31" s="100">
+      <c r="F31" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="100"/>
-      <c r="H31" s="100"/>
-      <c r="I31" s="100"/>
-      <c r="J31" s="100"/>
-      <c r="K31" s="100"/>
+      <c r="G31" s="94"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="94"/>
+      <c r="J31" s="94"/>
+      <c r="K31" s="94"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="82">
         <v>25</v>
       </c>
-      <c r="B32" s="97" t="str">
+      <c r="B32" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A32+1)</f>
         <v>Node 25, Solar Panel (-Y)</v>
       </c>
-      <c r="C32" s="98">
+      <c r="C32" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="99">
+      <c r="D32" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="99">
+      <c r="E32" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="100">
+      <c r="F32" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="100"/>
-      <c r="H32" s="100"/>
-      <c r="I32" s="100"/>
-      <c r="J32" s="100"/>
-      <c r="K32" s="100"/>
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="94"/>
+      <c r="K32" s="94"/>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="82">
         <v>26</v>
       </c>
-      <c r="B33" s="97" t="str">
+      <c r="B33" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A33+1)</f>
         <v>Node 26, Solar Panel (X)</v>
       </c>
-      <c r="C33" s="98">
+      <c r="C33" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="99">
+      <c r="D33" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="99">
+      <c r="E33" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="100">
+      <c r="F33" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G33" s="100"/>
-      <c r="H33" s="100"/>
-      <c r="I33" s="100"/>
-      <c r="J33" s="100"/>
-      <c r="K33" s="100"/>
+      <c r="G33" s="94"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="94"/>
+      <c r="J33" s="94"/>
+      <c r="K33" s="94"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="82">
         <v>27</v>
       </c>
-      <c r="B34" s="97" t="str">
+      <c r="B34" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A34+1)</f>
         <v>Node 27, Solar Panel (-X)RBF</v>
       </c>
-      <c r="C34" s="98">
+      <c r="C34" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D34" s="99">
+      <c r="D34" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="99">
+      <c r="E34" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F34" s="100">
+      <c r="F34" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="100"/>
-      <c r="H34" s="100"/>
-      <c r="I34" s="100"/>
-      <c r="J34" s="100"/>
-      <c r="K34" s="100"/>
+      <c r="G34" s="94"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="94"/>
+      <c r="K34" s="94"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="82">
         <v>28</v>
       </c>
-      <c r="B35" s="97" t="str">
+      <c r="B35" s="92" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A35+1)</f>
         <v>Node 28, Solar Panel (-Z(antenna))</v>
       </c>
-      <c r="C35" s="98">
+      <c r="C35" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="99">
+      <c r="D35" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="99">
+      <c r="E35" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="100">
+      <c r="F35" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="100"/>
-      <c r="H35" s="100"/>
-      <c r="I35" s="100"/>
-      <c r="J35" s="100"/>
-      <c r="K35" s="100"/>
+      <c r="G35" s="94"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="94"/>
+      <c r="J35" s="94"/>
+      <c r="K35" s="94"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" thickBot="1">
       <c r="A36" s="82">
         <v>29</v>
       </c>
-      <c r="B36" s="101" t="str">
+      <c r="B36" s="95" t="str">
         <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A36+1)</f>
         <v>Node 29, EPS de alta</v>
       </c>
-      <c r="C36" s="98">
+      <c r="C36" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D36" s="99">
+      <c r="D36" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="99">
+      <c r="E36" s="93">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="100">
+      <c r="F36" s="93">
         <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="100"/>
-      <c r="J36" s="100"/>
-      <c r="K36" s="100"/>
+      <c r="G36" s="94"/>
+      <c r="H36" s="94"/>
+      <c r="I36" s="94"/>
+      <c r="J36" s="94"/>
+      <c r="K36" s="94"/>
     </row>
     <row r="37" spans="1:11">
       <c r="B37" s="80"/>
@@ -12053,58 +12032,58 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:15" ht="15.75" thickBot="1">
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="133" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="125" t="s">
+      <c r="C2" s="118" t="s">
         <v>260</v>
       </c>
-      <c r="D2" s="126" t="s">
+      <c r="D2" s="119" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="126" t="s">
+      <c r="E2" s="119" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="128"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="121"/>
     </row>
     <row r="3" spans="2:15">
-      <c r="B3" s="141" t="s">
+      <c r="B3" s="134" t="s">
         <v>214</v>
       </c>
-      <c r="C3" s="129">
-        <v>0</v>
-      </c>
-      <c r="D3" s="130">
-        <v>0</v>
-      </c>
-      <c r="E3" s="130">
-        <v>0</v>
-      </c>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="131"/>
+      <c r="C3" s="122">
+        <v>0</v>
+      </c>
+      <c r="D3" s="123">
+        <v>0</v>
+      </c>
+      <c r="E3" s="123">
+        <v>0</v>
+      </c>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="124"/>
     </row>
     <row r="4" spans="2:15">
-      <c r="B4" s="142" t="s">
+      <c r="B4" s="135" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="132">
+      <c r="C4" s="125">
         <v>0</v>
       </c>
       <c r="D4" s="84">
@@ -12122,13 +12101,13 @@
       <c r="L4" s="84"/>
       <c r="M4" s="84"/>
       <c r="N4" s="84"/>
-      <c r="O4" s="133"/>
+      <c r="O4" s="126"/>
     </row>
     <row r="5" spans="2:15">
-      <c r="B5" s="142" t="s">
+      <c r="B5" s="135" t="s">
         <v>216</v>
       </c>
-      <c r="C5" s="132">
+      <c r="C5" s="125">
         <v>0</v>
       </c>
       <c r="D5" s="84">
@@ -12146,13 +12125,13 @@
       <c r="L5" s="84"/>
       <c r="M5" s="84"/>
       <c r="N5" s="84"/>
-      <c r="O5" s="133"/>
+      <c r="O5" s="126"/>
     </row>
     <row r="6" spans="2:15">
-      <c r="B6" s="142" t="s">
+      <c r="B6" s="135" t="s">
         <v>217</v>
       </c>
-      <c r="C6" s="132">
+      <c r="C6" s="125">
         <v>0</v>
       </c>
       <c r="D6" s="84">
@@ -12170,13 +12149,13 @@
       <c r="L6" s="84"/>
       <c r="M6" s="84"/>
       <c r="N6" s="84"/>
-      <c r="O6" s="133"/>
+      <c r="O6" s="126"/>
     </row>
     <row r="7" spans="2:15">
-      <c r="B7" s="142" t="s">
+      <c r="B7" s="135" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="132">
+      <c r="C7" s="125">
         <v>0</v>
       </c>
       <c r="D7" s="84">
@@ -12194,13 +12173,13 @@
       <c r="L7" s="84"/>
       <c r="M7" s="84"/>
       <c r="N7" s="84"/>
-      <c r="O7" s="133"/>
+      <c r="O7" s="126"/>
     </row>
     <row r="8" spans="2:15">
-      <c r="B8" s="142" t="s">
+      <c r="B8" s="135" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="132">
+      <c r="C8" s="125">
         <v>0</v>
       </c>
       <c r="D8" s="84">
@@ -12218,13 +12197,13 @@
       <c r="L8" s="84"/>
       <c r="M8" s="84"/>
       <c r="N8" s="84"/>
-      <c r="O8" s="133"/>
+      <c r="O8" s="126"/>
     </row>
     <row r="9" spans="2:15">
-      <c r="B9" s="142" t="s">
+      <c r="B9" s="135" t="s">
         <v>220</v>
       </c>
-      <c r="C9" s="132">
+      <c r="C9" s="125">
         <v>0</v>
       </c>
       <c r="D9" s="84">
@@ -12242,13 +12221,13 @@
       <c r="L9" s="84"/>
       <c r="M9" s="84"/>
       <c r="N9" s="84"/>
-      <c r="O9" s="133"/>
+      <c r="O9" s="126"/>
     </row>
     <row r="10" spans="2:15">
-      <c r="B10" s="142" t="s">
+      <c r="B10" s="135" t="s">
         <v>221</v>
       </c>
-      <c r="C10" s="132">
+      <c r="C10" s="125">
         <v>0</v>
       </c>
       <c r="D10" s="84">
@@ -12266,13 +12245,13 @@
       <c r="L10" s="84"/>
       <c r="M10" s="84"/>
       <c r="N10" s="84"/>
-      <c r="O10" s="133"/>
+      <c r="O10" s="126"/>
     </row>
     <row r="11" spans="2:15">
-      <c r="B11" s="142" t="s">
+      <c r="B11" s="135" t="s">
         <v>222</v>
       </c>
-      <c r="C11" s="132">
+      <c r="C11" s="125">
         <v>0</v>
       </c>
       <c r="D11" s="84">
@@ -12290,13 +12269,13 @@
       <c r="L11" s="84"/>
       <c r="M11" s="84"/>
       <c r="N11" s="84"/>
-      <c r="O11" s="133"/>
+      <c r="O11" s="126"/>
     </row>
     <row r="12" spans="2:15">
-      <c r="B12" s="142" t="s">
+      <c r="B12" s="135" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="132">
+      <c r="C12" s="125">
         <v>0</v>
       </c>
       <c r="D12" s="84">
@@ -12314,13 +12293,13 @@
       <c r="L12" s="84"/>
       <c r="M12" s="84"/>
       <c r="N12" s="84"/>
-      <c r="O12" s="133"/>
+      <c r="O12" s="126"/>
     </row>
     <row r="13" spans="2:15">
-      <c r="B13" s="142" t="s">
+      <c r="B13" s="135" t="s">
         <v>224</v>
       </c>
-      <c r="C13" s="132">
+      <c r="C13" s="125">
         <v>0</v>
       </c>
       <c r="D13" s="84">
@@ -12338,13 +12317,13 @@
       <c r="L13" s="84"/>
       <c r="M13" s="84"/>
       <c r="N13" s="84"/>
-      <c r="O13" s="133"/>
+      <c r="O13" s="126"/>
     </row>
     <row r="14" spans="2:15">
-      <c r="B14" s="142" t="s">
+      <c r="B14" s="135" t="s">
         <v>225</v>
       </c>
-      <c r="C14" s="132">
+      <c r="C14" s="125">
         <v>0</v>
       </c>
       <c r="D14" s="84">
@@ -12362,13 +12341,13 @@
       <c r="L14" s="84"/>
       <c r="M14" s="84"/>
       <c r="N14" s="84"/>
-      <c r="O14" s="133"/>
+      <c r="O14" s="126"/>
     </row>
     <row r="15" spans="2:15">
-      <c r="B15" s="142" t="s">
+      <c r="B15" s="135" t="s">
         <v>226</v>
       </c>
-      <c r="C15" s="132">
+      <c r="C15" s="125">
         <v>0</v>
       </c>
       <c r="D15" s="84">
@@ -12386,13 +12365,13 @@
       <c r="L15" s="84"/>
       <c r="M15" s="84"/>
       <c r="N15" s="84"/>
-      <c r="O15" s="133"/>
+      <c r="O15" s="126"/>
     </row>
     <row r="16" spans="2:15">
-      <c r="B16" s="142" t="s">
+      <c r="B16" s="135" t="s">
         <v>227</v>
       </c>
-      <c r="C16" s="132">
+      <c r="C16" s="125">
         <v>0</v>
       </c>
       <c r="D16" s="84">
@@ -12410,13 +12389,13 @@
       <c r="L16" s="84"/>
       <c r="M16" s="84"/>
       <c r="N16" s="84"/>
-      <c r="O16" s="133"/>
+      <c r="O16" s="126"/>
     </row>
     <row r="17" spans="2:15">
-      <c r="B17" s="142" t="s">
+      <c r="B17" s="135" t="s">
         <v>228</v>
       </c>
-      <c r="C17" s="132">
+      <c r="C17" s="125">
         <v>0</v>
       </c>
       <c r="D17" s="84">
@@ -12434,13 +12413,13 @@
       <c r="L17" s="84"/>
       <c r="M17" s="84"/>
       <c r="N17" s="84"/>
-      <c r="O17" s="133"/>
+      <c r="O17" s="126"/>
     </row>
     <row r="18" spans="2:15">
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="135" t="s">
         <v>229</v>
       </c>
-      <c r="C18" s="132">
+      <c r="C18" s="125">
         <v>0</v>
       </c>
       <c r="D18" s="84">
@@ -12458,13 +12437,13 @@
       <c r="L18" s="84"/>
       <c r="M18" s="84"/>
       <c r="N18" s="84"/>
-      <c r="O18" s="133"/>
+      <c r="O18" s="126"/>
     </row>
     <row r="19" spans="2:15">
-      <c r="B19" s="142" t="s">
+      <c r="B19" s="135" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="132">
+      <c r="C19" s="125">
         <v>0</v>
       </c>
       <c r="D19" s="84">
@@ -12482,13 +12461,13 @@
       <c r="L19" s="84"/>
       <c r="M19" s="84"/>
       <c r="N19" s="84"/>
-      <c r="O19" s="133"/>
+      <c r="O19" s="126"/>
     </row>
     <row r="20" spans="2:15">
-      <c r="B20" s="142" t="s">
+      <c r="B20" s="135" t="s">
         <v>231</v>
       </c>
-      <c r="C20" s="132">
+      <c r="C20" s="125">
         <v>0</v>
       </c>
       <c r="D20" s="84">
@@ -12506,13 +12485,13 @@
       <c r="L20" s="84"/>
       <c r="M20" s="84"/>
       <c r="N20" s="84"/>
-      <c r="O20" s="133"/>
+      <c r="O20" s="126"/>
     </row>
     <row r="21" spans="2:15">
-      <c r="B21" s="142" t="s">
+      <c r="B21" s="135" t="s">
         <v>232</v>
       </c>
-      <c r="C21" s="132">
+      <c r="C21" s="125">
         <v>0</v>
       </c>
       <c r="D21" s="84">
@@ -12530,13 +12509,13 @@
       <c r="L21" s="84"/>
       <c r="M21" s="84"/>
       <c r="N21" s="84"/>
-      <c r="O21" s="133"/>
+      <c r="O21" s="126"/>
     </row>
     <row r="22" spans="2:15">
-      <c r="B22" s="142" t="s">
+      <c r="B22" s="135" t="s">
         <v>233</v>
       </c>
-      <c r="C22" s="132">
+      <c r="C22" s="125">
         <v>0</v>
       </c>
       <c r="D22" s="84">
@@ -12554,13 +12533,13 @@
       <c r="L22" s="84"/>
       <c r="M22" s="84"/>
       <c r="N22" s="84"/>
-      <c r="O22" s="133"/>
+      <c r="O22" s="126"/>
     </row>
     <row r="23" spans="2:15">
-      <c r="B23" s="142" t="s">
+      <c r="B23" s="135" t="s">
         <v>234</v>
       </c>
-      <c r="C23" s="132">
+      <c r="C23" s="125">
         <v>0</v>
       </c>
       <c r="D23" s="84">
@@ -12578,13 +12557,13 @@
       <c r="L23" s="84"/>
       <c r="M23" s="84"/>
       <c r="N23" s="84"/>
-      <c r="O23" s="133"/>
+      <c r="O23" s="126"/>
     </row>
     <row r="24" spans="2:15">
-      <c r="B24" s="142" t="s">
+      <c r="B24" s="135" t="s">
         <v>235</v>
       </c>
-      <c r="C24" s="132">
+      <c r="C24" s="125">
         <v>0</v>
       </c>
       <c r="D24" s="84">
@@ -12602,13 +12581,13 @@
       <c r="L24" s="84"/>
       <c r="M24" s="84"/>
       <c r="N24" s="84"/>
-      <c r="O24" s="133"/>
+      <c r="O24" s="126"/>
     </row>
     <row r="25" spans="2:15">
-      <c r="B25" s="142" t="s">
+      <c r="B25" s="135" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="132">
+      <c r="C25" s="125">
         <v>0</v>
       </c>
       <c r="D25" s="84">
@@ -12626,13 +12605,13 @@
       <c r="L25" s="84"/>
       <c r="M25" s="84"/>
       <c r="N25" s="84"/>
-      <c r="O25" s="133"/>
+      <c r="O25" s="126"/>
     </row>
     <row r="26" spans="2:15">
-      <c r="B26" s="142" t="s">
+      <c r="B26" s="135" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="132">
+      <c r="C26" s="125">
         <v>0</v>
       </c>
       <c r="D26" s="84">
@@ -12650,13 +12629,13 @@
       <c r="L26" s="84"/>
       <c r="M26" s="84"/>
       <c r="N26" s="84"/>
-      <c r="O26" s="133"/>
+      <c r="O26" s="126"/>
     </row>
     <row r="27" spans="2:15">
-      <c r="B27" s="142" t="s">
+      <c r="B27" s="135" t="s">
         <v>238</v>
       </c>
-      <c r="C27" s="132">
+      <c r="C27" s="125">
         <v>0</v>
       </c>
       <c r="D27" s="84">
@@ -12674,13 +12653,13 @@
       <c r="L27" s="84"/>
       <c r="M27" s="84"/>
       <c r="N27" s="84"/>
-      <c r="O27" s="133"/>
+      <c r="O27" s="126"/>
     </row>
     <row r="28" spans="2:15">
-      <c r="B28" s="142" t="s">
+      <c r="B28" s="135" t="s">
         <v>239</v>
       </c>
-      <c r="C28" s="132">
+      <c r="C28" s="125">
         <v>0</v>
       </c>
       <c r="D28" s="84">
@@ -12698,13 +12677,13 @@
       <c r="L28" s="84"/>
       <c r="M28" s="84"/>
       <c r="N28" s="84"/>
-      <c r="O28" s="133"/>
+      <c r="O28" s="126"/>
     </row>
     <row r="29" spans="2:15">
-      <c r="B29" s="142" t="s">
+      <c r="B29" s="135" t="s">
         <v>240</v>
       </c>
-      <c r="C29" s="132">
+      <c r="C29" s="125">
         <v>0</v>
       </c>
       <c r="D29" s="84">
@@ -12722,13 +12701,13 @@
       <c r="L29" s="84"/>
       <c r="M29" s="84"/>
       <c r="N29" s="84"/>
-      <c r="O29" s="133"/>
+      <c r="O29" s="126"/>
     </row>
     <row r="30" spans="2:15">
-      <c r="B30" s="142" t="s">
+      <c r="B30" s="135" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="132">
+      <c r="C30" s="125">
         <v>0</v>
       </c>
       <c r="D30" s="84">
@@ -12746,47 +12725,47 @@
       <c r="L30" s="84"/>
       <c r="M30" s="84"/>
       <c r="N30" s="84"/>
-      <c r="O30" s="133"/>
+      <c r="O30" s="126"/>
     </row>
     <row r="31" spans="2:15">
-      <c r="B31" s="143" t="s">
+      <c r="B31" s="136" t="s">
         <v>242</v>
       </c>
-      <c r="C31" s="136">
-        <v>0</v>
-      </c>
-      <c r="D31" s="120">
-        <v>0</v>
-      </c>
-      <c r="E31" s="120">
-        <v>0</v>
-      </c>
-      <c r="F31" s="120"/>
-      <c r="G31" s="120"/>
-      <c r="H31" s="120"/>
-      <c r="I31" s="120"/>
-      <c r="J31" s="120"/>
-      <c r="K31" s="120"/>
-      <c r="L31" s="120"/>
-      <c r="M31" s="120"/>
-      <c r="N31" s="120"/>
-      <c r="O31" s="137"/>
+      <c r="C31" s="129">
+        <v>0</v>
+      </c>
+      <c r="D31" s="114">
+        <v>0</v>
+      </c>
+      <c r="E31" s="114">
+        <v>0</v>
+      </c>
+      <c r="F31" s="114"/>
+      <c r="G31" s="114"/>
+      <c r="H31" s="114"/>
+      <c r="I31" s="114"/>
+      <c r="J31" s="114"/>
+      <c r="K31" s="114"/>
+      <c r="L31" s="114"/>
+      <c r="M31" s="114"/>
+      <c r="N31" s="114"/>
+      <c r="O31" s="130"/>
     </row>
     <row r="32" spans="2:15">
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="96"/>
-      <c r="O32" s="96"/>
+      <c r="B32" s="91"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="91"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="91"/>
+      <c r="H32" s="91"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="91"/>
+      <c r="K32" s="91"/>
+      <c r="L32" s="91"/>
+      <c r="M32" s="91"/>
+      <c r="N32" s="91"/>
+      <c r="O32" s="91"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12812,922 +12791,922 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:13" ht="46.5" customHeight="1" thickBot="1">
-      <c r="B2" s="111" t="s">
+      <c r="B2" s="105" t="s">
         <v>252</v>
       </c>
-      <c r="C2" s="112" t="s">
+      <c r="C2" s="106" t="s">
         <v>245</v>
       </c>
-      <c r="D2" s="113" t="s">
+      <c r="D2" s="107" t="s">
         <v>246</v>
       </c>
-      <c r="E2" s="113" t="s">
+      <c r="E2" s="107" t="s">
         <v>248</v>
       </c>
-      <c r="F2" s="113" t="s">
+      <c r="F2" s="107" t="s">
         <v>247</v>
       </c>
-      <c r="G2" s="113" t="s">
+      <c r="G2" s="107" t="s">
         <v>243</v>
       </c>
-      <c r="H2" s="113" t="s">
+      <c r="H2" s="107" t="s">
         <v>244</v>
       </c>
-      <c r="I2" s="113" t="s">
+      <c r="I2" s="107" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="113" t="s">
+      <c r="J2" s="107" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="113" t="s">
+      <c r="K2" s="107" t="s">
         <v>251</v>
       </c>
-      <c r="L2" s="138" t="s">
+      <c r="L2" s="131" t="s">
         <v>262</v>
       </c>
-      <c r="M2" s="114" t="s">
+      <c r="M2" s="108" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="3" spans="2:13">
-      <c r="B3" s="115" t="s">
+      <c r="B3" s="109" t="s">
         <v>214</v>
       </c>
-      <c r="C3" s="108">
+      <c r="C3" s="102">
         <v>4.0280000000000003E-2</v>
       </c>
-      <c r="D3" s="106">
+      <c r="D3" s="100">
         <v>800</v>
       </c>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106">
+      <c r="E3" s="100"/>
+      <c r="F3" s="100">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="G3" s="106">
+      <c r="G3" s="100">
         <v>0.8</v>
       </c>
-      <c r="H3" s="106">
+      <c r="H3" s="100">
         <v>0.8</v>
       </c>
-      <c r="I3" s="106">
+      <c r="I3" s="100">
         <v>1</v>
       </c>
-      <c r="J3" s="106">
-        <v>0</v>
-      </c>
-      <c r="K3" s="106">
-        <v>0</v>
-      </c>
-      <c r="L3" s="106">
+      <c r="J3" s="100">
+        <v>0</v>
+      </c>
+      <c r="K3" s="100">
+        <v>0</v>
+      </c>
+      <c r="L3" s="100">
         <v>1</v>
       </c>
-      <c r="M3" s="107"/>
+      <c r="M3" s="101"/>
     </row>
     <row r="4" spans="2:13">
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="110" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="109">
+      <c r="C4" s="103">
         <v>4.0280000000000003E-2</v>
       </c>
-      <c r="D4" s="102">
+      <c r="D4" s="96">
         <v>800</v>
       </c>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102">
+      <c r="E4" s="96"/>
+      <c r="F4" s="96">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="G4" s="102">
+      <c r="G4" s="96">
         <v>0.8</v>
       </c>
-      <c r="H4" s="102">
+      <c r="H4" s="96">
         <v>0.8</v>
       </c>
-      <c r="I4" s="102">
+      <c r="I4" s="96">
         <v>-1</v>
       </c>
-      <c r="J4" s="102">
-        <v>0</v>
-      </c>
-      <c r="K4" s="102">
-        <v>0</v>
-      </c>
-      <c r="L4" s="102">
+      <c r="J4" s="96">
+        <v>0</v>
+      </c>
+      <c r="K4" s="96">
+        <v>0</v>
+      </c>
+      <c r="L4" s="96">
         <v>1</v>
       </c>
-      <c r="M4" s="104"/>
+      <c r="M4" s="98"/>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="110" t="s">
         <v>216</v>
       </c>
-      <c r="C5" s="109">
+      <c r="C5" s="103">
         <v>7.2909999999999997E-3</v>
       </c>
-      <c r="D5" s="102">
+      <c r="D5" s="96">
         <v>800</v>
       </c>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102">
+      <c r="E5" s="96"/>
+      <c r="F5" s="96">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G5" s="102">
+      <c r="G5" s="96">
         <v>0.8</v>
       </c>
-      <c r="H5" s="102">
+      <c r="H5" s="96">
         <v>0.8</v>
       </c>
-      <c r="I5" s="102">
-        <v>0</v>
-      </c>
-      <c r="J5" s="102">
+      <c r="I5" s="96">
+        <v>0</v>
+      </c>
+      <c r="J5" s="96">
         <v>-1</v>
       </c>
-      <c r="K5" s="102">
+      <c r="K5" s="96">
         <v>1</v>
       </c>
-      <c r="L5" s="102">
+      <c r="L5" s="96">
         <v>1</v>
       </c>
-      <c r="M5" s="104"/>
+      <c r="M5" s="98"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="110" t="s">
         <v>217</v>
       </c>
-      <c r="C6" s="109">
+      <c r="C6" s="103">
         <v>7.2909999999999997E-3</v>
       </c>
-      <c r="D6" s="102">
+      <c r="D6" s="96">
         <v>800</v>
       </c>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102">
+      <c r="E6" s="96"/>
+      <c r="F6" s="96">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G6" s="102">
+      <c r="G6" s="96">
         <v>0.8</v>
       </c>
-      <c r="H6" s="102">
+      <c r="H6" s="96">
         <v>0.8</v>
       </c>
-      <c r="I6" s="102">
-        <v>0</v>
-      </c>
-      <c r="J6" s="102">
+      <c r="I6" s="96">
+        <v>0</v>
+      </c>
+      <c r="J6" s="96">
         <v>1</v>
       </c>
-      <c r="K6" s="102">
+      <c r="K6" s="96">
         <v>1</v>
       </c>
-      <c r="L6" s="102">
+      <c r="L6" s="96">
         <v>1</v>
       </c>
-      <c r="M6" s="104"/>
+      <c r="M6" s="98"/>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="116" t="s">
+      <c r="B7" s="110" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="109">
+      <c r="C7" s="103">
         <v>6.4250000000000002E-3</v>
       </c>
-      <c r="D7" s="102">
+      <c r="D7" s="96">
         <v>800</v>
       </c>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102">
+      <c r="E7" s="96"/>
+      <c r="F7" s="96">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G7" s="102">
+      <c r="G7" s="96">
         <v>0.8</v>
       </c>
-      <c r="H7" s="102">
+      <c r="H7" s="96">
         <v>0.8</v>
       </c>
-      <c r="I7" s="102">
-        <v>0</v>
-      </c>
-      <c r="J7" s="102">
+      <c r="I7" s="96">
+        <v>0</v>
+      </c>
+      <c r="J7" s="96">
         <v>1</v>
       </c>
-      <c r="K7" s="102">
+      <c r="K7" s="96">
         <v>-1</v>
       </c>
-      <c r="L7" s="102">
+      <c r="L7" s="96">
         <v>1</v>
       </c>
-      <c r="M7" s="104"/>
+      <c r="M7" s="98"/>
     </row>
     <row r="8" spans="2:13">
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="110" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="109">
+      <c r="C8" s="103">
         <v>6.4250000000000002E-3</v>
       </c>
-      <c r="D8" s="102">
+      <c r="D8" s="96">
         <v>800</v>
       </c>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102">
+      <c r="E8" s="96"/>
+      <c r="F8" s="96">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G8" s="102">
+      <c r="G8" s="96">
         <v>0.8</v>
       </c>
-      <c r="H8" s="102">
+      <c r="H8" s="96">
         <v>0.8</v>
       </c>
-      <c r="I8" s="102">
-        <v>0</v>
-      </c>
-      <c r="J8" s="102">
+      <c r="I8" s="96">
+        <v>0</v>
+      </c>
+      <c r="J8" s="96">
         <v>-1</v>
       </c>
-      <c r="K8" s="102">
+      <c r="K8" s="96">
         <v>-1</v>
       </c>
-      <c r="L8" s="102">
+      <c r="L8" s="96">
         <v>1</v>
       </c>
-      <c r="M8" s="104"/>
+      <c r="M8" s="98"/>
     </row>
     <row r="9" spans="2:13">
-      <c r="B9" s="116" t="s">
+      <c r="B9" s="110" t="s">
         <v>220</v>
       </c>
-      <c r="C9" s="109">
+      <c r="C9" s="103">
         <v>2.1919999999999999E-2</v>
       </c>
-      <c r="D9" s="102">
+      <c r="D9" s="96">
         <v>800</v>
       </c>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102">
+      <c r="E9" s="96"/>
+      <c r="F9" s="96">
         <v>9.5999999999999992E-3</v>
       </c>
-      <c r="G9" s="102">
+      <c r="G9" s="96">
         <v>0.8</v>
       </c>
-      <c r="H9" s="102">
+      <c r="H9" s="96">
         <v>0.8</v>
       </c>
-      <c r="I9" s="102">
-        <v>0</v>
-      </c>
-      <c r="J9" s="102">
-        <v>0</v>
-      </c>
-      <c r="K9" s="102">
+      <c r="I9" s="96">
+        <v>0</v>
+      </c>
+      <c r="J9" s="96">
+        <v>0</v>
+      </c>
+      <c r="K9" s="96">
         <v>1</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="96">
         <v>1</v>
       </c>
-      <c r="M9" s="104"/>
+      <c r="M9" s="98"/>
     </row>
     <row r="10" spans="2:13">
-      <c r="B10" s="116" t="s">
+      <c r="B10" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="C10" s="109">
+      <c r="C10" s="103">
         <v>1.8E-3</v>
       </c>
-      <c r="D10" s="102">
+      <c r="D10" s="96">
         <v>800</v>
       </c>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102">
+      <c r="E10" s="96"/>
+      <c r="F10" s="96">
         <v>5.7600000000000001E-4</v>
       </c>
-      <c r="G10" s="102">
+      <c r="G10" s="96">
         <v>0.8</v>
       </c>
-      <c r="H10" s="102">
+      <c r="H10" s="96">
         <v>0.8</v>
       </c>
-      <c r="I10" s="102">
-        <v>0</v>
-      </c>
-      <c r="J10" s="102">
-        <v>0</v>
-      </c>
-      <c r="K10" s="102">
+      <c r="I10" s="96">
+        <v>0</v>
+      </c>
+      <c r="J10" s="96">
+        <v>0</v>
+      </c>
+      <c r="K10" s="96">
         <v>1</v>
       </c>
-      <c r="L10" s="102">
+      <c r="L10" s="96">
         <v>1</v>
       </c>
-      <c r="M10" s="104"/>
+      <c r="M10" s="98"/>
     </row>
     <row r="11" spans="2:13">
-      <c r="B11" s="116" t="s">
+      <c r="B11" s="110" t="s">
         <v>222</v>
       </c>
-      <c r="C11" s="109">
+      <c r="C11" s="103">
         <v>1.8E-3</v>
       </c>
-      <c r="D11" s="102">
+      <c r="D11" s="96">
         <v>800</v>
       </c>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102">
+      <c r="E11" s="96"/>
+      <c r="F11" s="96">
         <v>5.7600000000000001E-4</v>
       </c>
-      <c r="G11" s="102">
+      <c r="G11" s="96">
         <v>0.8</v>
       </c>
-      <c r="H11" s="102">
+      <c r="H11" s="96">
         <v>0.8</v>
       </c>
-      <c r="I11" s="102">
-        <v>0</v>
-      </c>
-      <c r="J11" s="102">
-        <v>0</v>
-      </c>
-      <c r="K11" s="102">
+      <c r="I11" s="96">
+        <v>0</v>
+      </c>
+      <c r="J11" s="96">
+        <v>0</v>
+      </c>
+      <c r="K11" s="96">
         <v>1</v>
       </c>
-      <c r="L11" s="102">
+      <c r="L11" s="96">
         <v>1</v>
       </c>
-      <c r="M11" s="104"/>
+      <c r="M11" s="98"/>
     </row>
     <row r="12" spans="2:13">
-      <c r="B12" s="116" t="s">
+      <c r="B12" s="110" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="109">
+      <c r="C12" s="103">
         <v>1.8E-3</v>
       </c>
-      <c r="D12" s="102">
+      <c r="D12" s="96">
         <v>800</v>
       </c>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102">
+      <c r="E12" s="96"/>
+      <c r="F12" s="96">
         <v>5.7600000000000001E-4</v>
       </c>
-      <c r="G12" s="102">
+      <c r="G12" s="96">
         <v>0.8</v>
       </c>
-      <c r="H12" s="102">
+      <c r="H12" s="96">
         <v>0.8</v>
       </c>
-      <c r="I12" s="102">
-        <v>0</v>
-      </c>
-      <c r="J12" s="102">
-        <v>0</v>
-      </c>
-      <c r="K12" s="102">
+      <c r="I12" s="96">
+        <v>0</v>
+      </c>
+      <c r="J12" s="96">
+        <v>0</v>
+      </c>
+      <c r="K12" s="96">
         <v>1</v>
       </c>
-      <c r="L12" s="102">
+      <c r="L12" s="96">
         <v>1</v>
       </c>
-      <c r="M12" s="104"/>
+      <c r="M12" s="98"/>
     </row>
     <row r="13" spans="2:13">
-      <c r="B13" s="116" t="s">
+      <c r="B13" s="110" t="s">
         <v>224</v>
       </c>
-      <c r="C13" s="109">
+      <c r="C13" s="103">
         <v>1.8E-3</v>
       </c>
-      <c r="D13" s="102">
+      <c r="D13" s="96">
         <v>800</v>
       </c>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102">
+      <c r="E13" s="96"/>
+      <c r="F13" s="96">
         <v>5.7600000000000001E-4</v>
       </c>
-      <c r="G13" s="102">
+      <c r="G13" s="96">
         <v>0.8</v>
       </c>
-      <c r="H13" s="102">
+      <c r="H13" s="96">
         <v>0.8</v>
       </c>
-      <c r="I13" s="102">
-        <v>0</v>
-      </c>
-      <c r="J13" s="102">
-        <v>0</v>
-      </c>
-      <c r="K13" s="102">
+      <c r="I13" s="96">
+        <v>0</v>
+      </c>
+      <c r="J13" s="96">
+        <v>0</v>
+      </c>
+      <c r="K13" s="96">
         <v>1</v>
       </c>
-      <c r="L13" s="102">
+      <c r="L13" s="96">
         <v>1</v>
       </c>
-      <c r="M13" s="104"/>
+      <c r="M13" s="98"/>
     </row>
     <row r="14" spans="2:13">
-      <c r="B14" s="116" t="s">
+      <c r="B14" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="C14" s="109">
+      <c r="C14" s="103">
         <v>2.375E-2</v>
       </c>
-      <c r="D14" s="102">
+      <c r="D14" s="96">
         <v>600</v>
       </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102">
+      <c r="E14" s="96"/>
+      <c r="F14" s="96">
         <v>0.01</v>
       </c>
-      <c r="G14" s="102"/>
-      <c r="H14" s="102"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="102">
-        <v>0</v>
-      </c>
-      <c r="M14" s="104"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96">
+        <v>0</v>
+      </c>
+      <c r="M14" s="98"/>
     </row>
     <row r="15" spans="2:13">
-      <c r="B15" s="116" t="s">
+      <c r="B15" s="110" t="s">
         <v>226</v>
       </c>
-      <c r="C15" s="109">
+      <c r="C15" s="103">
         <v>0.125</v>
       </c>
-      <c r="D15" s="102">
+      <c r="D15" s="96">
         <v>800</v>
       </c>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102">
+      <c r="E15" s="96"/>
+      <c r="F15" s="96">
         <v>0.01</v>
       </c>
-      <c r="G15" s="102"/>
-      <c r="H15" s="102"/>
-      <c r="I15" s="102"/>
-      <c r="J15" s="102"/>
-      <c r="K15" s="102"/>
-      <c r="L15" s="102">
-        <v>0</v>
-      </c>
-      <c r="M15" s="104"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="96">
+        <v>0</v>
+      </c>
+      <c r="M15" s="98"/>
     </row>
     <row r="16" spans="2:13">
-      <c r="B16" s="116" t="s">
+      <c r="B16" s="110" t="s">
         <v>227</v>
       </c>
-      <c r="C16" s="109">
+      <c r="C16" s="103">
         <v>3.9E-2</v>
       </c>
-      <c r="D16" s="102">
+      <c r="D16" s="96">
         <v>600</v>
       </c>
-      <c r="E16" s="102"/>
-      <c r="F16" s="102">
+      <c r="E16" s="96"/>
+      <c r="F16" s="96">
         <v>0.01</v>
       </c>
-      <c r="G16" s="102"/>
-      <c r="H16" s="102"/>
-      <c r="I16" s="102"/>
-      <c r="J16" s="102"/>
-      <c r="K16" s="102"/>
-      <c r="L16" s="102">
-        <v>0</v>
-      </c>
-      <c r="M16" s="104"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96">
+        <v>0</v>
+      </c>
+      <c r="M16" s="98"/>
     </row>
     <row r="17" spans="2:13">
-      <c r="B17" s="116" t="s">
+      <c r="B17" s="110" t="s">
         <v>228</v>
       </c>
-      <c r="C17" s="109">
+      <c r="C17" s="103">
         <v>3.9E-2</v>
       </c>
-      <c r="D17" s="102">
+      <c r="D17" s="96">
         <v>600</v>
       </c>
-      <c r="E17" s="102"/>
-      <c r="F17" s="102">
+      <c r="E17" s="96"/>
+      <c r="F17" s="96">
         <v>0.1</v>
       </c>
-      <c r="G17" s="102"/>
-      <c r="H17" s="102"/>
-      <c r="I17" s="102"/>
-      <c r="J17" s="102"/>
-      <c r="K17" s="102"/>
-      <c r="L17" s="102">
-        <v>0</v>
-      </c>
-      <c r="M17" s="104"/>
+      <c r="G17" s="96"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96">
+        <v>0</v>
+      </c>
+      <c r="M17" s="98"/>
     </row>
     <row r="18" spans="2:13">
-      <c r="B18" s="116" t="s">
+      <c r="B18" s="110" t="s">
         <v>229</v>
       </c>
-      <c r="C18" s="109">
+      <c r="C18" s="103">
         <v>3.9E-2</v>
       </c>
-      <c r="D18" s="102">
+      <c r="D18" s="96">
         <v>600</v>
       </c>
-      <c r="E18" s="102"/>
-      <c r="F18" s="102">
+      <c r="E18" s="96"/>
+      <c r="F18" s="96">
         <v>0.1</v>
       </c>
-      <c r="G18" s="102"/>
-      <c r="H18" s="102"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="102"/>
-      <c r="K18" s="102"/>
-      <c r="L18" s="102">
-        <v>0</v>
-      </c>
-      <c r="M18" s="104"/>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96">
+        <v>0</v>
+      </c>
+      <c r="M18" s="98"/>
     </row>
     <row r="19" spans="2:13">
-      <c r="B19" s="116" t="s">
+      <c r="B19" s="110" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="109">
+      <c r="C19" s="103">
         <v>3.9E-2</v>
       </c>
-      <c r="D19" s="102">
+      <c r="D19" s="96">
         <v>600</v>
       </c>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102">
+      <c r="E19" s="96"/>
+      <c r="F19" s="96">
         <v>0.1</v>
       </c>
-      <c r="G19" s="102"/>
-      <c r="H19" s="102"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="102"/>
-      <c r="K19" s="102"/>
-      <c r="L19" s="102">
-        <v>0</v>
-      </c>
-      <c r="M19" s="104"/>
+      <c r="G19" s="96"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96">
+        <v>0</v>
+      </c>
+      <c r="M19" s="98"/>
     </row>
     <row r="20" spans="2:13">
-      <c r="B20" s="116" t="s">
+      <c r="B20" s="110" t="s">
         <v>231</v>
       </c>
-      <c r="C20" s="109">
+      <c r="C20" s="103">
         <v>0.05</v>
       </c>
-      <c r="D20" s="102">
+      <c r="D20" s="96">
         <v>600</v>
       </c>
-      <c r="E20" s="102"/>
-      <c r="F20" s="102">
+      <c r="E20" s="96"/>
+      <c r="F20" s="96">
         <v>0.1</v>
       </c>
-      <c r="G20" s="102"/>
-      <c r="H20" s="102"/>
-      <c r="I20" s="102"/>
-      <c r="J20" s="102"/>
-      <c r="K20" s="102"/>
-      <c r="L20" s="102">
-        <v>0</v>
-      </c>
-      <c r="M20" s="104"/>
+      <c r="G20" s="96"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96">
+        <v>0</v>
+      </c>
+      <c r="M20" s="98"/>
     </row>
     <row r="21" spans="2:13">
-      <c r="B21" s="116" t="s">
+      <c r="B21" s="110" t="s">
         <v>232</v>
       </c>
-      <c r="C21" s="109">
+      <c r="C21" s="103">
         <v>0.05</v>
       </c>
-      <c r="D21" s="102">
+      <c r="D21" s="96">
         <v>600</v>
       </c>
-      <c r="E21" s="102"/>
-      <c r="F21" s="102">
+      <c r="E21" s="96"/>
+      <c r="F21" s="96">
         <v>0.1</v>
       </c>
-      <c r="G21" s="102"/>
-      <c r="H21" s="102"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="102">
-        <v>0</v>
-      </c>
-      <c r="M21" s="104"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96">
+        <v>0</v>
+      </c>
+      <c r="M21" s="98"/>
     </row>
     <row r="22" spans="2:13">
-      <c r="B22" s="116" t="s">
+      <c r="B22" s="110" t="s">
         <v>233</v>
       </c>
-      <c r="C22" s="109">
+      <c r="C22" s="103">
         <v>3.8490000000000003E-2</v>
       </c>
-      <c r="D22" s="102">
+      <c r="D22" s="96">
         <v>600</v>
       </c>
-      <c r="E22" s="102"/>
-      <c r="F22" s="102">
+      <c r="E22" s="96"/>
+      <c r="F22" s="96">
         <v>8.6E-3</v>
       </c>
-      <c r="G22" s="102"/>
-      <c r="H22" s="102"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="102"/>
-      <c r="K22" s="102"/>
-      <c r="L22" s="102">
-        <v>0</v>
-      </c>
-      <c r="M22" s="104"/>
+      <c r="G22" s="96"/>
+      <c r="H22" s="96"/>
+      <c r="I22" s="96"/>
+      <c r="J22" s="96"/>
+      <c r="K22" s="96"/>
+      <c r="L22" s="96">
+        <v>0</v>
+      </c>
+      <c r="M22" s="98"/>
     </row>
     <row r="23" spans="2:13">
-      <c r="B23" s="116" t="s">
+      <c r="B23" s="110" t="s">
         <v>234</v>
       </c>
-      <c r="C23" s="109">
+      <c r="C23" s="103">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="D23" s="102">
+      <c r="D23" s="96">
         <v>600</v>
       </c>
-      <c r="E23" s="102"/>
-      <c r="F23" s="102">
+      <c r="E23" s="96"/>
+      <c r="F23" s="96">
         <v>8.6E-3</v>
       </c>
-      <c r="G23" s="102"/>
-      <c r="H23" s="102"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="102"/>
-      <c r="K23" s="102"/>
-      <c r="L23" s="102">
-        <v>0</v>
-      </c>
-      <c r="M23" s="104"/>
+      <c r="G23" s="96"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="96"/>
+      <c r="L23" s="96">
+        <v>0</v>
+      </c>
+      <c r="M23" s="98"/>
     </row>
     <row r="24" spans="2:13">
-      <c r="B24" s="116" t="s">
+      <c r="B24" s="110" t="s">
         <v>235</v>
       </c>
-      <c r="C24" s="109">
+      <c r="C24" s="103">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="D24" s="102">
+      <c r="D24" s="96">
         <v>600</v>
       </c>
-      <c r="E24" s="102">
+      <c r="E24" s="96">
         <v>15</v>
       </c>
-      <c r="F24" s="102">
+      <c r="F24" s="96">
         <v>0.08</v>
       </c>
-      <c r="G24" s="102"/>
-      <c r="H24" s="102"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="102"/>
-      <c r="L24" s="102">
-        <v>0</v>
-      </c>
-      <c r="M24" s="104">
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="96"/>
+      <c r="L24" s="96">
+        <v>0</v>
+      </c>
+      <c r="M24" s="98">
         <v>0.7</v>
       </c>
     </row>
     <row r="25" spans="2:13">
-      <c r="B25" s="116" t="s">
+      <c r="B25" s="110" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="109">
+      <c r="C25" s="103">
         <v>2.4E-2</v>
       </c>
-      <c r="D25" s="102">
+      <c r="D25" s="96">
         <v>600</v>
       </c>
-      <c r="E25" s="102"/>
-      <c r="F25" s="102">
+      <c r="E25" s="96"/>
+      <c r="F25" s="96">
         <v>0.33</v>
       </c>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="102"/>
-      <c r="K25" s="102"/>
-      <c r="L25" s="102">
-        <v>0</v>
-      </c>
-      <c r="M25" s="104"/>
+      <c r="G25" s="96"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="96"/>
+      <c r="L25" s="96">
+        <v>0</v>
+      </c>
+      <c r="M25" s="98"/>
     </row>
     <row r="26" spans="2:13">
-      <c r="B26" s="116" t="s">
+      <c r="B26" s="110" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="109">
+      <c r="C26" s="103">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="D26" s="102">
+      <c r="D26" s="96">
         <v>600</v>
       </c>
-      <c r="E26" s="102">
+      <c r="E26" s="96">
         <v>15</v>
       </c>
-      <c r="F26" s="102">
+      <c r="F26" s="96">
         <v>8.0940000000000005E-3</v>
       </c>
-      <c r="G26" s="102">
+      <c r="G26" s="96">
         <v>0.8</v>
       </c>
-      <c r="H26" s="102">
+      <c r="H26" s="96">
         <v>0.8</v>
       </c>
-      <c r="I26" s="102">
-        <v>0</v>
-      </c>
-      <c r="J26" s="102">
+      <c r="I26" s="96">
+        <v>0</v>
+      </c>
+      <c r="J26" s="96">
         <v>1</v>
       </c>
-      <c r="K26" s="102">
-        <v>0</v>
-      </c>
-      <c r="L26" s="102">
+      <c r="K26" s="96">
+        <v>0</v>
+      </c>
+      <c r="L26" s="96">
         <v>1</v>
       </c>
-      <c r="M26" s="104">
+      <c r="M26" s="98">
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="27" spans="2:13">
-      <c r="B27" s="116" t="s">
+      <c r="B27" s="110" t="s">
         <v>238</v>
       </c>
-      <c r="C27" s="109">
+      <c r="C27" s="103">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="D27" s="102">
+      <c r="D27" s="96">
         <v>600</v>
       </c>
-      <c r="E27" s="102">
+      <c r="E27" s="96">
         <v>15</v>
       </c>
-      <c r="F27" s="102">
+      <c r="F27" s="96">
         <v>8.0940000000000005E-3</v>
       </c>
-      <c r="G27" s="102">
+      <c r="G27" s="96">
         <v>0.8</v>
       </c>
-      <c r="H27" s="102">
+      <c r="H27" s="96">
         <v>0.8</v>
       </c>
-      <c r="I27" s="102">
-        <v>0</v>
-      </c>
-      <c r="J27" s="102">
+      <c r="I27" s="96">
+        <v>0</v>
+      </c>
+      <c r="J27" s="96">
         <v>-1</v>
       </c>
-      <c r="K27" s="102">
-        <v>0</v>
-      </c>
-      <c r="L27" s="102">
+      <c r="K27" s="96">
+        <v>0</v>
+      </c>
+      <c r="L27" s="96">
         <v>1</v>
       </c>
-      <c r="M27" s="104">
+      <c r="M27" s="98">
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="28" spans="2:13">
-      <c r="B28" s="116" t="s">
+      <c r="B28" s="110" t="s">
         <v>239</v>
       </c>
-      <c r="C28" s="109">
+      <c r="C28" s="103">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="D28" s="102">
+      <c r="D28" s="96">
         <v>600</v>
       </c>
-      <c r="E28" s="102">
+      <c r="E28" s="96">
         <v>15</v>
       </c>
-      <c r="F28" s="102">
+      <c r="F28" s="96">
         <v>8.0940000000000005E-3</v>
       </c>
-      <c r="G28" s="102">
+      <c r="G28" s="96">
         <v>0.8</v>
       </c>
-      <c r="H28" s="102">
+      <c r="H28" s="96">
         <v>0.8</v>
       </c>
-      <c r="I28" s="102">
+      <c r="I28" s="96">
         <v>1</v>
       </c>
-      <c r="J28" s="102">
-        <v>0</v>
-      </c>
-      <c r="K28" s="102">
-        <v>0</v>
-      </c>
-      <c r="L28" s="102">
+      <c r="J28" s="96">
+        <v>0</v>
+      </c>
+      <c r="K28" s="96">
+        <v>0</v>
+      </c>
+      <c r="L28" s="96">
         <v>1</v>
       </c>
-      <c r="M28" s="104">
+      <c r="M28" s="98">
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="29" spans="2:13">
-      <c r="B29" s="116" t="s">
+      <c r="B29" s="110" t="s">
         <v>240</v>
       </c>
-      <c r="C29" s="109">
+      <c r="C29" s="103">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="D29" s="102">
+      <c r="D29" s="96">
         <v>600</v>
       </c>
-      <c r="E29" s="102">
+      <c r="E29" s="96">
         <v>15</v>
       </c>
-      <c r="F29" s="102">
+      <c r="F29" s="96">
         <v>8.0940000000000005E-3</v>
       </c>
-      <c r="G29" s="102">
+      <c r="G29" s="96">
         <v>0.8</v>
       </c>
-      <c r="H29" s="102">
+      <c r="H29" s="96">
         <v>0.8</v>
       </c>
-      <c r="I29" s="102">
+      <c r="I29" s="96">
         <v>-1</v>
       </c>
-      <c r="J29" s="102">
-        <v>0</v>
-      </c>
-      <c r="K29" s="102">
-        <v>0</v>
-      </c>
-      <c r="L29" s="102">
+      <c r="J29" s="96">
+        <v>0</v>
+      </c>
+      <c r="K29" s="96">
+        <v>0</v>
+      </c>
+      <c r="L29" s="96">
         <v>1</v>
       </c>
-      <c r="M29" s="104">
+      <c r="M29" s="98">
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="30" spans="2:13">
-      <c r="B30" s="116" t="s">
+      <c r="B30" s="110" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="109">
+      <c r="C30" s="103">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="D30" s="102">
+      <c r="D30" s="96">
         <v>600</v>
       </c>
-      <c r="E30" s="102">
+      <c r="E30" s="96">
         <v>15</v>
       </c>
-      <c r="F30" s="102">
+      <c r="F30" s="96">
         <v>8.4469999999999996E-3</v>
       </c>
-      <c r="G30" s="102">
+      <c r="G30" s="96">
         <v>0.8</v>
       </c>
-      <c r="H30" s="102">
+      <c r="H30" s="96">
         <v>0.8</v>
       </c>
-      <c r="I30" s="102">
-        <v>0</v>
-      </c>
-      <c r="J30" s="102">
-        <v>0</v>
-      </c>
-      <c r="K30" s="102">
+      <c r="I30" s="96">
+        <v>0</v>
+      </c>
+      <c r="J30" s="96">
+        <v>0</v>
+      </c>
+      <c r="K30" s="96">
         <v>-1</v>
       </c>
-      <c r="L30" s="102">
+      <c r="L30" s="96">
         <v>1</v>
       </c>
-      <c r="M30" s="104">
+      <c r="M30" s="98">
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="31" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B31" s="117" t="s">
+      <c r="B31" s="111" t="s">
         <v>242</v>
       </c>
-      <c r="C31" s="110">
+      <c r="C31" s="104">
         <v>0.04</v>
       </c>
-      <c r="D31" s="103">
+      <c r="D31" s="97">
         <v>600</v>
       </c>
-      <c r="E31" s="103"/>
-      <c r="F31" s="103">
+      <c r="E31" s="97"/>
+      <c r="F31" s="97">
         <v>0.01</v>
       </c>
-      <c r="G31" s="103"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="103"/>
-      <c r="J31" s="103"/>
-      <c r="K31" s="103"/>
-      <c r="L31" s="103">
-        <v>0</v>
-      </c>
-      <c r="M31" s="105"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="97"/>
+      <c r="I31" s="97"/>
+      <c r="J31" s="97"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="97">
+        <v>0</v>
+      </c>
+      <c r="M31" s="99"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="80"/>

--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB26D28-3013-4CD9-BC48-2EE9A94F7B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96163878-F97A-42E9-BAD0-A61ED876CF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes properties" sheetId="1" r:id="rId1"/>
     <sheet name="Conductances determination" sheetId="3" r:id="rId2"/>
-    <sheet name="Startup Parameters" sheetId="7" r:id="rId3"/>
-    <sheet name="Operation" sheetId="5" r:id="rId4"/>
-    <sheet name="Modes" sheetId="6" r:id="rId5"/>
-    <sheet name="Nodes thermal properties" sheetId="4" r:id="rId6"/>
-    <sheet name="Conductances_between_nodes" sheetId="2" r:id="rId7"/>
+    <sheet name="Orbital Parameters" sheetId="8" r:id="rId3"/>
+    <sheet name="Startup Parameters" sheetId="7" r:id="rId4"/>
+    <sheet name="Operation" sheetId="5" r:id="rId5"/>
+    <sheet name="Modes" sheetId="6" r:id="rId6"/>
+    <sheet name="Nodes thermal properties" sheetId="4" r:id="rId7"/>
+    <sheet name="Conductances_between_nodes" sheetId="2" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataSignature="AMtx7mjKFLR0Am3JTZ+8bb0VcOSu/VdiBw=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mjKFLR0Am3JTZ+8bb0VcOSu/VdiBw=="/>
     </ext>
   </extLst>
 </workbook>
@@ -457,7 +458,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="274">
   <si>
     <t>Esta tabla representado el struct con todos los datos de entrada que uso para el satélite,¿que le falta? pues el coeficiente Cp (specific heat capacity ) esta bastamente aproximado y habría que mirar material por material, puede que algo de info útil pueda ser encontrada en la tabla de mecánica</t>
   </si>
@@ -1263,6 +1264,24 @@
   <si>
     <t>Radiation to enviroment (1=Yes, 0=No)</t>
   </si>
+  <si>
+    <t>Yaw</t>
+  </si>
+  <si>
+    <t>Pitch</t>
+  </si>
+  <si>
+    <t>Roll</t>
+  </si>
+  <si>
+    <t>Longitude of ascending node</t>
+  </si>
+  <si>
+    <t>Inclination</t>
+  </si>
+  <si>
+    <t>Orbital height (Km)</t>
+  </si>
 </sst>
 </file>
 
@@ -1274,11 +1293,32 @@
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1353,7 +1393,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1477,6 +1517,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2290,163 +2336,163 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2458,13 +2504,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2492,13 +2538,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2507,7 +2553,7 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2516,17 +2562,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2562,41 +2608,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="43" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9988,10 +10046,10 @@
         <v>149</v>
       </c>
       <c r="G2" s="32"/>
-      <c r="H2" s="140" t="s">
+      <c r="H2" s="145" t="s">
         <v>150</v>
       </c>
-      <c r="I2" s="141"/>
+      <c r="I2" s="146"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="33" t="s">
@@ -10993,6 +11051,63 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E01517-96A7-414C-8030-8BA1AC45135C}">
+  <dimension ref="B1:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="5" max="5" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:7" ht="37.5" customHeight="1">
+      <c r="B2" s="148" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="149" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2" s="149" t="s">
+        <v>270</v>
+      </c>
+      <c r="E2" s="149" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" s="149" t="s">
+        <v>272</v>
+      </c>
+      <c r="G2" s="150" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="15.75" thickBot="1">
+      <c r="B3" s="151">
+        <v>0</v>
+      </c>
+      <c r="C3" s="97">
+        <v>0</v>
+      </c>
+      <c r="D3" s="97">
+        <v>0</v>
+      </c>
+      <c r="E3" s="97">
+        <v>0</v>
+      </c>
+      <c r="F3" s="97">
+        <v>0</v>
+      </c>
+      <c r="G3" s="99">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="147"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFF58F4-2122-4D7A-8536-BCD5250BA286}">
   <dimension ref="B1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -11044,7 +11159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4723E147-5D28-48F2-9A19-B61306348D73}">
   <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -11057,16 +11172,16 @@
       <c r="B2" s="132" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="142" t="s">
+      <c r="C2" s="143" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" s="141" t="s">
         <v>259</v>
       </c>
-      <c r="D2" s="144" t="s">
-        <v>259</v>
-      </c>
-      <c r="E2" s="144" t="s">
+      <c r="E2" s="141" t="s">
         <v>258</v>
       </c>
-      <c r="F2" s="145" t="s">
+      <c r="F2" s="142" t="s">
         <v>260</v>
       </c>
       <c r="G2" s="117"/>
@@ -11077,19 +11192,19 @@
       </c>
       <c r="C3" s="89">
         <f>IFERROR(C4+C5*60+C6*3600+C7*3600*24+B3,C4+C5*60+C6*3600+C7*3600*24)</f>
-        <v>32400</v>
+        <v>25200</v>
       </c>
       <c r="D3" s="89">
         <f t="shared" ref="D3:F3" si="0">IFERROR(D4+D5*60+D6*3600+D7*3600*24+C3,D4+D5*60+D6*3600+D7*3600*24)</f>
-        <v>32400</v>
+        <v>25200</v>
       </c>
       <c r="E3" s="89">
         <f t="shared" si="0"/>
-        <v>32400</v>
+        <v>25200</v>
       </c>
       <c r="F3" s="89">
         <f t="shared" si="0"/>
-        <v>32460</v>
+        <v>25200</v>
       </c>
       <c r="G3" s="91"/>
       <c r="H3" s="81"/>
@@ -11116,29 +11231,35 @@
       </c>
       <c r="C5" s="86"/>
       <c r="D5" s="84"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="90">
-        <v>1</v>
-      </c>
+      <c r="E5" s="83">
+        <v>0</v>
+      </c>
+      <c r="F5" s="90"/>
       <c r="G5" s="91"/>
     </row>
     <row r="6" spans="1:14">
       <c r="B6" s="88" t="s">
         <v>254</v>
       </c>
-      <c r="C6" s="143">
-        <v>9</v>
-      </c>
-      <c r="D6" s="84"/>
+      <c r="C6" s="140">
+        <v>7</v>
+      </c>
+      <c r="D6" s="84">
+        <v>0</v>
+      </c>
       <c r="E6" s="83"/>
-      <c r="F6" s="90"/>
+      <c r="F6" s="90">
+        <v>0</v>
+      </c>
       <c r="G6" s="91"/>
     </row>
     <row r="7" spans="1:14">
       <c r="B7" s="112" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="113"/>
+      <c r="C7" s="113">
+        <v>0</v>
+      </c>
       <c r="D7" s="114"/>
       <c r="E7" s="115"/>
       <c r="F7" s="116"/>
@@ -11364,7 +11485,7 @@
       </c>
       <c r="C15" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
-        <v>5.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="D15" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
@@ -11394,7 +11515,7 @@
       </c>
       <c r="C16" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
-        <v>5.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="D16" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
@@ -11424,7 +11545,7 @@
       </c>
       <c r="C17" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
-        <v>5.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="D17" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
@@ -11454,7 +11575,7 @@
       </c>
       <c r="C18" s="93">
         <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
-        <v>5.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="D18" s="93">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
@@ -12022,7 +12143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B005E130-2D16-4A0C-8BB3-2172273CEA1D}">
   <dimension ref="B1:O32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -12772,7 +12893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4985A03E-5096-4337-92A3-24224C69AEFA}">
   <dimension ref="B1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -12920,10 +13041,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="96">
-        <v>-1</v>
+        <v>-0.70709999999999995</v>
       </c>
       <c r="K5" s="96">
-        <v>1</v>
+        <v>0.70709999999999995</v>
       </c>
       <c r="L5" s="96">
         <v>1</v>
@@ -12954,10 +13075,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="96">
-        <v>1</v>
+        <v>0.70709999999999995</v>
       </c>
       <c r="K6" s="96">
-        <v>1</v>
+        <v>0.70709999999999995</v>
       </c>
       <c r="L6" s="96">
         <v>1</v>
@@ -12988,10 +13109,10 @@
         <v>0</v>
       </c>
       <c r="J7" s="96">
-        <v>1</v>
+        <v>0.70709999999999995</v>
       </c>
       <c r="K7" s="96">
-        <v>-1</v>
+        <v>-0.70709999999999995</v>
       </c>
       <c r="L7" s="96">
         <v>1</v>
@@ -13022,10 +13143,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="96">
-        <v>-1</v>
+        <v>-0.70709999999999995</v>
       </c>
       <c r="K8" s="96">
-        <v>-1</v>
+        <v>-0.70709999999999995</v>
       </c>
       <c r="L8" s="96">
         <v>1</v>
@@ -13033,7 +13154,7 @@
       <c r="M8" s="98"/>
     </row>
     <row r="9" spans="2:13">
-      <c r="B9" s="110" t="s">
+      <c r="B9" s="144" t="s">
         <v>220</v>
       </c>
       <c r="C9" s="103">
@@ -13716,7 +13837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD990"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>

--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96163878-F97A-42E9-BAD0-A61ED876CF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF24A56-D548-47AC-8500-17C06CA24601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Nodes properties" sheetId="1" r:id="rId1"/>
-    <sheet name="Conductances determination" sheetId="3" r:id="rId2"/>
-    <sheet name="Orbital Parameters" sheetId="8" r:id="rId3"/>
+    <sheet name="Instrucciones de uso" sheetId="9" r:id="rId1"/>
+    <sheet name="Nodes properties" sheetId="1" r:id="rId2"/>
+    <sheet name="Conductances determination" sheetId="3" r:id="rId3"/>
     <sheet name="Startup Parameters" sheetId="7" r:id="rId4"/>
-    <sheet name="Operation" sheetId="5" r:id="rId5"/>
-    <sheet name="Modes" sheetId="6" r:id="rId6"/>
-    <sheet name="Nodes thermal properties" sheetId="4" r:id="rId7"/>
-    <sheet name="Conductances_between_nodes" sheetId="2" r:id="rId8"/>
+    <sheet name="Orbital Parameters" sheetId="8" r:id="rId5"/>
+    <sheet name="Nodes thermal properties" sheetId="4" r:id="rId6"/>
+    <sheet name="Operation" sheetId="5" r:id="rId7"/>
+    <sheet name="Modes" sheetId="6" r:id="rId8"/>
+    <sheet name="Conductances_between_nodes" sheetId="2" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mjKFLR0Am3JTZ+8bb0VcOSu/VdiBw=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mjKFLR0Am3JTZ+8bb0VcOSu/VdiBw=="/>
     </ext>
   </extLst>
 </workbook>
@@ -458,7 +459,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="307">
   <si>
     <t>Esta tabla representado el struct con todos los datos de entrada que uso para el satélite,¿que le falta? pues el coeficiente Cp (specific heat capacity ) esta bastamente aproximado y habría que mirar material por material, puede que algo de info útil pueda ser encontrada en la tabla de mecánica</t>
   </si>
@@ -1100,9 +1101,6 @@
     <t>1 &amp; 1</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>Frame 1, +X</t>
   </si>
   <si>
@@ -1205,9 +1203,6 @@
     <t>Radiative area (m2)</t>
   </si>
   <si>
-    <t>Thermal conductivity (W/(mK))</t>
-  </si>
-  <si>
     <t>Norm x</t>
   </si>
   <si>
@@ -1259,28 +1254,322 @@
     <t>Vacuum temperature (K)</t>
   </si>
   <si>
-    <t>Solar radiation and albedo (1=Yes, 0=No)</t>
+    <t>Orbital height (Km)</t>
   </si>
   <si>
-    <t>Radiation to enviroment (1=Yes, 0=No)</t>
+    <t>Instrucciones de uso</t>
   </si>
   <si>
-    <t>Yaw</t>
+    <t>Yaw (º)</t>
   </si>
   <si>
-    <t>Pitch</t>
+    <t>Pitch (º)</t>
   </si>
   <si>
-    <t>Roll</t>
+    <t>Roll (º)</t>
   </si>
   <si>
-    <t>Longitude of ascending node</t>
+    <t>Longitude of ascending node (º)</t>
   </si>
   <si>
-    <t>Inclination</t>
+    <t>Inclination (º)</t>
   </si>
   <si>
-    <t>Orbital height (Km)</t>
+    <t>Thermal conductivity (W/(m*K))</t>
+  </si>
+  <si>
+    <t>Pestañas de la hoja y configuración previa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esta es la hoja de control y cálculo para el código de simulación térmica para el satélite TEIDESAT-I. El código, que se ejecuta en MATHLAB, tiene como objetivo proporcionar una aproximación de la evolución de temperaturas de los distintos componentes del satélite a lo largo del tiempo. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">El código simula mediante un modelo de elementos de bulto. Es decir, trata las distintas piezas como nodos de temperatura uniforme que intercambian calor entre sí y con el entrono. En cada intervalo de tiempo, el código calcula las transferencias de calor y actualiza las temperaturas de cada nodo. Esto se repite iterativamente hasta el final de la simulación. </t>
+  </si>
+  <si>
+    <t>Nodes properties:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Contiene propiedades de interés de los distintos nodos para el análisis, no tiene efectos sobre la ejecución del código por lo que puede ser modificada libremente.</t>
+  </si>
+  <si>
+    <t>Fundamentos de cálculo</t>
+  </si>
+  <si>
+    <t>Conductances determination:</t>
+  </si>
+  <si>
+    <t>Contiene el cálculo de conductancias para uniones atornilladas. Actualmente está enlazada con la matriz de conductancias (conductances_between_nodes), pero si esta se definiese independientemente, la hoja de determinación de conductancias también podría modificarse libremente.</t>
+  </si>
+  <si>
+    <t>Startup parameters:</t>
+  </si>
+  <si>
+    <t>Esta hoja define los parametros de arranque y de simulación del codigo, siendo estos:</t>
+  </si>
+  <si>
+    <t>Radiation to sun and planet (1=Yes, 0=No)</t>
+  </si>
+  <si>
+    <t>Radiation to vacuum (1=Yes, 0=No)</t>
+  </si>
+  <si>
+    <t>Vacuum temperature: Temperatura del vacío. Normalmente es de unos 2,7 K. No obstante definir vacios calientes puede ser útil para analisis estacionarios.</t>
+  </si>
+  <si>
+    <t>Starting temperature: Temperatura inicial de todos los nodos. La temperatura en el segundo 0 de la simulación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dt: Tiempo de un paso en la simulación en segundos. Este parámetro sirve como resolución temporal de la simulación. Un intervalo de tiempo muy pequeño proporciona resultados más precisos, a cambio de mayor uso de memoria y tiempo de ejecución. Un intervalo de tiempo grande disminuye la precisión a cambio de mayor velocidad de cálculo. Un intervalo de tiempo excesivamente grande puede provocar errores importantes en los resultados, fluctuaciones o incluso divergencia. En general, cuando se espera que existan cambios rápidos en la temperatura (ej; modo payload) se debe utilizar intervalos de tiempo más reducidos. </t>
+  </si>
+  <si>
+    <t>Orbital parameters:</t>
+  </si>
+  <si>
+    <t>Esta hoja define las condiciones orbitales y de orientación del satelite.</t>
+  </si>
+  <si>
+    <t>Los tres primeros parámetros (roll pitch and yaw) (Alabeo, cabeceo y guiñada) medidos en grados representan la orientación del satelite en cada eje. Se utiliza la convención de ejes para aeronaves DIN 9300 (consistente con los ya usados en el satélite) y los angulos de Tait-Bryan. En la imagen, phi = roll, theta = pitch, psi = yaw. Los ejes en azul se corresponden tal que: X+ = dirección de movimiento, Z+ = Nadir , Y+ = Lateral. Los ejes en verde ( Solo pintado X) Se corresponden con los ejes de la estructura (Ej: X+ = Dirección en la que se encuentra el panel X+)</t>
+  </si>
+  <si>
+    <t>Los siguientes parametros definen la órbita del satélite, asumiendo siempre órbita circular. La longitud del nodo ascendente y la inclinación (en verde en la imagen) definen la orientación de la órbita mientras que la altura orbital definen la altura sobre el nivel del mar.  Las referencias usadas para estos parámetros son: El plano de la ecliptica (plano en el que todos los planetas se mueven), y el vector solar (linea que une la tierra con el sol). Utilizar estas referencias garantiza que las propiedades térmicas de la órbita (posición respecto al sol) se mantengan constantes durante toda la simulación, permitiendo simular órbitas heliosíncronas. No obstante otros tipos de órbita cambian lentamente su posición respecto al sol con el paso del tiempo. Se considera que para la mayoria de simulaciones, con inclinaciones bajas o tiempos de simulación inferiores a una semana, este cambio es despreciable.</t>
+  </si>
+  <si>
+    <r>
+      <t>Muchas de las hojas de este documento deberán ser leidos por el código, para ello</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hay encabezados cuya posición no debe ser modificada, estos generalmente estan en negrita</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Ver detalles de cada hoja descritos más abajo para conocer más acerca de su uso. En el caso de modificación inadecuada de este documento, se podrá restaurar a una versión anterior disponible en github.</t>
+    </r>
+  </si>
+  <si>
+    <t>Nodes thermal properties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define los nodos y las propiedades de cada uno. El numero de filas y el nombre de los nodos así como sus propiedades pueden ser modificados libremente. El orden en el que se coloquen los nodos es importante, ya que será el mismo orden que el programa tomará para corresponder los datos con los especificados en las otras hojas. El programa emitirá mensajes de error automaticos si el número de nodos entre distintas hojas no coincide, pero no detectará colocación en orden inconsistente o datos incorrectos. </t>
+  </si>
+  <si>
+    <t>Radiation to vacuum: Booleano que define si se va a calcular o no el intercambio de radiación con el vacío circundante. Util para aislar el satélite del entorno y comprobar cumplimiento de la conservación de energía.</t>
+  </si>
+  <si>
+    <t>Algunos parametros a introducir aquí son: Area radiativa, area que está expuesta al exterior y disponible para radiar o absorber calor .Emisividad y absortancia, valores que representan las capacidades de absorción y emisión del material para espectro completo y infrarrojos respectivamente. Componentes del vector normal, dirreción del vector normal a la superficie externa, usado para calcular angulos de incidencia, debe estar normalizado (módulo 1). Radiación, booleano que determina si un nodo tiene superficie con la que radiar al entorno.</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>Modes</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El programa leerá los calores generados en cada modo de funcionamiento y la secuencia de funcionamiento de esta hoja. La simulación terminará cuando llegue al final de la secuencia de funcionamiento. Los tiempos de funcionamiento se definen arriba en segundos (fila azul) , y los calores en la tabla de abajo en vatios. Esta hoja puede ser rellenada manualmente pero, para mayor comodidad, cuenta funciones que permiten calcular el tiempo especificando en días horas minutos y segundos, así como funciones de busqueda que rellenan los calores automáticamente con tan solo especificar el nombre del modo de funcionamiento en la primera fila, usando los datos de la hoja "Modes". Es posible arrastrar estas fórmulas o ampliar los rangos de busqueda en las formulas para aumentar el tamaño de la tabla si se requieren secuencias de operación más complejas o mayor número de nodos. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Esta hoja no puede tener columnas o filas incompletas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, de lo contrario el programa las leerá dando lugar a errores. Así mismo, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>el orden de los nodos debe coincidir con el especificado en Nodes thermal properties</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hoja auxiliar para definir los modos de operación. Si se definen los calores generados (en vatios) por componente en un modo de operación aquí, definiendo el nombre del nodo en la primera fila, estos calores se trasladarán automáticamente a la hoja de "Operation". De nuevo </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>el orden de los nodos debe coincidir con el especificado en Nodes thermal properties.</t>
+    </r>
+  </si>
+  <si>
+    <t>Conductance_between_nodes</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En esta hoja se definen las conductancias entre nodos. De nuevo, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>el orden de los nodos debe coincidir con el especificado en Nodes thermal properties</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Se trata de una </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>matriz simétrica</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, con respecto a la diagonal por lo que una mitad se puede rellenar automáticamente. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Los valores de la diagonal serán siempre 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Para facilitar la visualización, se puede establecer un código de colores. Ahora mismo los nodos con posibilidad de tener contacto entre sí se colocan en rojo.</t>
+    </r>
+  </si>
+  <si>
+    <t>Este modelo solo es aceptable cuando las pieza que representa cada nodo no experimenta un gradiente de temperatura muy elevado. Para piezas demasiado largas o con materiales de conductividad pobre puede ser necesario subdividir la pieza en más nodos.</t>
+  </si>
+  <si>
+    <t>Ejecución del programa</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para ejecutarse, la simulación necesita los siguientes datos: Parametros de inicio y simulación, definición de órbita y orientación, definición de los modos de operación, secuencia de operación (modos),  Listado de piezas y propiedades de cada pieza y conductancias térmicas entre las distintas piezas. Todos estos parámetros se proporcionarán al código desde esta hoja de cálculo. Para su correcta lectura, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">esta hoja debe estar en la misma carpeta que la de ejecución del código, y  los nombres de las pestañas de datos no deben ser modificados. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Además, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cualquier cambio realizado debe ser guardado previamente</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Radiation to sun and planet:  Booleano que define si se va a calcular o no la radiación proveniente de la tierra y el sol así como el albedo. Útil para simulaciones en estado estacionario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para iniciar el código se debe ejecutar el archivo main.m. Un mensaje en consola le preguntará al usuario que desea hacer a continuación: solve (resolver), o load (cargar). La opción de solve ejecuta la simulación con los parametros actuales. Tras finalizar esta se podrán guardar los resultados en excel o un en un archivo de datos de mathlab. La consola preguntará al usuario si desea guardar los archivos y con que nombre. En el caso del excel, los datos tardan un tiempo en guardarse y es necesario esperar a la finalización antes de abrir el archivo generado para evitar errores. La opcion de load permite abrir los archivos de mathlab en un gráfico interactivo tras especificar el nombre. Por defecto todos los archivos se guardan en una carpeta aparte denominada "saves" </t>
   </si>
 </sst>
 </file>
@@ -1293,11 +1582,25 @@
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1391,6 +1694,30 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="23">
@@ -2336,163 +2663,163 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2504,13 +2831,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2538,41 +2859,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2608,58 +2914,102 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="43" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2711,14 +3061,14 @@
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="Nodes properties-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="Conductances between nodes-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2733,6 +3083,111 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>81643</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>77109</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>409955</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>172360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8251DD6-0C31-7341-0C2D-1FD022A2B08B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11098893" y="8586109"/>
+          <a:ext cx="2614312" cy="2952751"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>603251</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>198438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>584537</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>357187</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCEC7FC4-A460-EA27-DC38-110ED126AE61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11620501" y="11564938"/>
+          <a:ext cx="3029286" cy="2730499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2771,14 +3226,14 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7343775" cy="5124450"/>
     <xdr:pic>
@@ -2799,6 +3254,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9029700"/>
+          <a:ext cx="7343775" cy="5124450"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -2810,9 +3269,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6753225" cy="5038725"/>
     <xdr:pic>
@@ -2834,7 +3293,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7353300" y="6448425"/>
+          <a:off x="7429500" y="9067800"/>
           <a:ext cx="6753225" cy="5038725"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2848,9 +3307,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6981825" cy="4943475"/>
     <xdr:pic>
@@ -2872,7 +3331,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14382750" y="6943725"/>
+          <a:off x="14268450" y="9039225"/>
           <a:ext cx="6981825" cy="4943475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2914,7 +3373,7 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A4:AD33">
   <tableColumns count="30">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="conductances [W/K]"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="conductances [W/K]" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="node 1"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="node 2"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="node 3"/>
@@ -3146,6 +3605,220 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E441979D-520C-417D-B82F-50E5924B7888}">
+  <dimension ref="B2:B67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="153.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" ht="23.25">
+      <c r="B2" s="138" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="30">
+      <c r="B4" s="134" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="135"/>
+    </row>
+    <row r="6" spans="2:2" ht="60">
+      <c r="B6" s="134" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="135"/>
+    </row>
+    <row r="8" spans="2:2" ht="15.75">
+      <c r="B8" s="137" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="135"/>
+    </row>
+    <row r="10" spans="2:2" ht="45">
+      <c r="B10" s="134" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="30">
+      <c r="B11" s="134" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="135"/>
+    </row>
+    <row r="13" spans="2:2" ht="15.75">
+      <c r="B13" s="137" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="135"/>
+    </row>
+    <row r="15" spans="2:2" ht="45">
+      <c r="B15" s="134" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="136" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="135" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="135"/>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="136" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="135"/>
+    </row>
+    <row r="23" spans="2:2" ht="30">
+      <c r="B23" s="134" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="135"/>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="136" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="135"/>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="134" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="135"/>
+    </row>
+    <row r="29" spans="2:2" ht="30">
+      <c r="B29" s="134" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="30">
+      <c r="B31" s="134" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="133" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="133" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" ht="60">
+      <c r="B37" s="134" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="150" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="133" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" ht="60">
+      <c r="B43" s="134" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" ht="90">
+      <c r="B45" s="134" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="150" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" ht="52.5" customHeight="1">
+      <c r="B49" s="134" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" ht="60">
+      <c r="B51" s="134" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="150" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" ht="105">
+      <c r="B55" s="134" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="150" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" ht="45">
+      <c r="B59" s="134" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="133" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" ht="45">
+      <c r="B63" s="134" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="15.75">
+      <c r="B65" s="155" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="75">
+      <c r="B67" s="156" t="s">
+        <v>306</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -10014,7 +10687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -10046,10 +10719,10 @@
         <v>149</v>
       </c>
       <c r="G2" s="32"/>
-      <c r="H2" s="145" t="s">
+      <c r="H2" s="158" t="s">
         <v>150</v>
       </c>
-      <c r="I2" s="146"/>
+      <c r="I2" s="159"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="33" t="s">
@@ -11050,70 +11723,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E01517-96A7-414C-8030-8BA1AC45135C}">
-  <dimension ref="B1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="5" max="5" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:7" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:7" ht="37.5" customHeight="1">
-      <c r="B2" s="148" t="s">
-        <v>268</v>
-      </c>
-      <c r="C2" s="149" t="s">
-        <v>269</v>
-      </c>
-      <c r="D2" s="149" t="s">
-        <v>270</v>
-      </c>
-      <c r="E2" s="149" t="s">
-        <v>271</v>
-      </c>
-      <c r="F2" s="149" t="s">
-        <v>272</v>
-      </c>
-      <c r="G2" s="150" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="15.75" thickBot="1">
-      <c r="B3" s="151">
-        <v>0</v>
-      </c>
-      <c r="C3" s="97">
-        <v>0</v>
-      </c>
-      <c r="D3" s="97">
-        <v>0</v>
-      </c>
-      <c r="E3" s="97">
-        <v>0</v>
-      </c>
-      <c r="F3" s="97">
-        <v>0</v>
-      </c>
-      <c r="G3" s="99">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="147"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFF58F4-2122-4D7A-8536-BCD5250BA286}">
   <dimension ref="B1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.140625" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" customWidth="1"/>
@@ -11121,24 +11737,24 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:6" ht="45">
-      <c r="B2" s="137" t="s">
-        <v>266</v>
-      </c>
-      <c r="C2" s="138" t="s">
-        <v>267</v>
-      </c>
-      <c r="D2" s="138" t="s">
-        <v>265</v>
-      </c>
-      <c r="E2" s="138" t="s">
-        <v>264</v>
-      </c>
-      <c r="F2" s="139" t="s">
+      <c r="B2" s="146" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" s="147" t="s">
+        <v>283</v>
+      </c>
+      <c r="D2" s="147" t="s">
         <v>263</v>
       </c>
+      <c r="E2" s="147" t="s">
+        <v>262</v>
+      </c>
+      <c r="F2" s="148" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="3" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B3" s="127">
+      <c r="B3" s="120">
         <v>1</v>
       </c>
       <c r="C3" s="85">
@@ -11150,7 +11766,7 @@
       <c r="E3" s="85">
         <v>300</v>
       </c>
-      <c r="F3" s="128">
+      <c r="F3" s="121">
         <v>1</v>
       </c>
     </row>
@@ -11160,983 +11776,57 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4723E147-5D28-48F2-9A19-B61306348D73}">
-  <dimension ref="A1:N37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E01517-96A7-414C-8030-8BA1AC45135C}">
+  <dimension ref="B1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1"/>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1">
-      <c r="B2" s="132" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" s="143" t="s">
-        <v>260</v>
-      </c>
-      <c r="D2" s="141" t="s">
-        <v>259</v>
-      </c>
-      <c r="E2" s="141" t="s">
-        <v>258</v>
-      </c>
-      <c r="F2" s="142" t="s">
-        <v>260</v>
-      </c>
-      <c r="G2" s="117"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="B3" s="87" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="89">
-        <f>IFERROR(C4+C5*60+C6*3600+C7*3600*24+B3,C4+C5*60+C6*3600+C7*3600*24)</f>
-        <v>25200</v>
-      </c>
-      <c r="D3" s="89">
-        <f t="shared" ref="D3:F3" si="0">IFERROR(D4+D5*60+D6*3600+D7*3600*24+C3,D4+D5*60+D6*3600+D7*3600*24)</f>
-        <v>25200</v>
-      </c>
-      <c r="E3" s="89">
-        <f t="shared" si="0"/>
-        <v>25200</v>
-      </c>
-      <c r="F3" s="89">
-        <f t="shared" si="0"/>
-        <v>25200</v>
-      </c>
-      <c r="G3" s="91"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="B4" s="88" t="s">
-        <v>256</v>
-      </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="91"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="B5" s="88" t="s">
-        <v>255</v>
-      </c>
-      <c r="C5" s="86"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="83">
-        <v>0</v>
-      </c>
-      <c r="F5" s="90"/>
-      <c r="G5" s="91"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="B6" s="88" t="s">
-        <v>254</v>
-      </c>
-      <c r="C6" s="140">
-        <v>7</v>
-      </c>
-      <c r="D6" s="84">
-        <v>0</v>
-      </c>
-      <c r="E6" s="83"/>
-      <c r="F6" s="90">
-        <v>0</v>
-      </c>
-      <c r="G6" s="91"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="B7" s="112" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="113">
-        <v>0</v>
-      </c>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="91"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="82">
-        <v>1</v>
-      </c>
-      <c r="B8" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A8+1)</f>
-        <v>Frame 1, +X</v>
-      </c>
-      <c r="C8" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="94"/>
-      <c r="K8" s="94"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="82">
-        <v>2</v>
-      </c>
-      <c r="B9" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A9+1)</f>
-        <v>Frame 2, -X</v>
-      </c>
-      <c r="C9" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="82">
-        <v>3</v>
-      </c>
-      <c r="B10" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A10+1)</f>
-        <v>Beam -Y +Z</v>
-      </c>
-      <c r="C10" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="94"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="82">
-        <v>4</v>
-      </c>
-      <c r="B11" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A11+1)</f>
-        <v>Beam +Y +Z</v>
-      </c>
-      <c r="C11" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="82">
-        <v>5</v>
-      </c>
-      <c r="B12" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A12+1)</f>
-        <v>Beam +Y -Z</v>
-      </c>
-      <c r="C12" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="82">
-        <v>6</v>
-      </c>
-      <c r="B13" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A13+1)</f>
-        <v>Beam -Y -Z</v>
-      </c>
-      <c r="C13" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="82">
-        <v>7</v>
-      </c>
-      <c r="B14" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A14+1)</f>
-        <v xml:space="preserve">panel +Z, payload plate </v>
-      </c>
-      <c r="C14" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="94"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="82">
-        <v>8</v>
-      </c>
-      <c r="B15" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A15+1)</f>
-        <v xml:space="preserve">LED 1 </v>
-      </c>
-      <c r="C15" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E15" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
-        <v>200</v>
-      </c>
-      <c r="F15" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="94"/>
-      <c r="K15" s="94"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="82">
-        <v>9</v>
-      </c>
-      <c r="B16" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A16+1)</f>
-        <v>LED 2</v>
-      </c>
-      <c r="C16" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E16" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
-        <v>200</v>
-      </c>
-      <c r="F16" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="94"/>
-      <c r="K16" s="94"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="82">
-        <v>10</v>
-      </c>
-      <c r="B17" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A17+1)</f>
-        <v>LED 3</v>
-      </c>
-      <c r="C17" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E17" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
-        <v>200</v>
-      </c>
-      <c r="F17" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="94"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="82">
-        <v>11</v>
-      </c>
-      <c r="B18" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A18+1)</f>
-        <v xml:space="preserve">LED 4 </v>
-      </c>
-      <c r="C18" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E18" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
-        <v>200</v>
-      </c>
-      <c r="F18" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="82">
-        <v>12</v>
-      </c>
-      <c r="B19" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A19+1)</f>
-        <v>Node 12, BMS</v>
-      </c>
-      <c r="C19" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="94"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="94"/>
-      <c r="K19" s="94"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="82">
-        <v>13</v>
-      </c>
-      <c r="B20" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A20+1)</f>
-        <v>Node 13, Batteries Isolation</v>
-      </c>
-      <c r="C20" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="94"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="94"/>
-      <c r="J20" s="94"/>
-      <c r="K20" s="94"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="82">
-        <v>14</v>
-      </c>
-      <c r="B21" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A21+1)</f>
-        <v>Node 14, LiFePo4 1</v>
-      </c>
-      <c r="C21" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="94"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="94"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="82">
-        <v>15</v>
-      </c>
-      <c r="B22" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A22+1)</f>
-        <v>Node 15, LiFePo4 3</v>
-      </c>
-      <c r="C22" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="94"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94"/>
-      <c r="K22" s="94"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="82">
-        <v>16</v>
-      </c>
-      <c r="B23" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A23+1)</f>
-        <v>Node 16, LiFePo4 2</v>
-      </c>
-      <c r="C23" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="94"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="94"/>
-      <c r="K23" s="94"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="82">
-        <v>17</v>
-      </c>
-      <c r="B24" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A24+1)</f>
-        <v>Node 17, LiFePo4 4</v>
-      </c>
-      <c r="C24" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="94"/>
-      <c r="K24" s="94"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="82">
-        <v>18</v>
-      </c>
-      <c r="B25" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A25+1)</f>
-        <v>Node 18, Cell Litio 1</v>
-      </c>
-      <c r="C25" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="94"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="94"/>
-      <c r="J25" s="94"/>
-      <c r="K25" s="94"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="82">
-        <v>19</v>
-      </c>
-      <c r="B26" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A26+1)</f>
-        <v>Node 19, Cell Litio 2</v>
-      </c>
-      <c r="C26" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="94"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="94"/>
-      <c r="K26" s="94"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="82">
-        <v>20</v>
-      </c>
-      <c r="B27" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A27+1)</f>
-        <v>Node 20, LoMo</v>
-      </c>
-      <c r="C27" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="94"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="94"/>
-      <c r="J27" s="94"/>
-      <c r="K27" s="94"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="82">
-        <v>21</v>
-      </c>
-      <c r="B28" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A28+1)</f>
-        <v>Node 21, Transceiver(Tx-Rx)</v>
-      </c>
-      <c r="C28" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="94"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="94"/>
-      <c r="K28" s="94"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="82">
-        <v>22</v>
-      </c>
-      <c r="B29" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A29+1)</f>
-        <v>Node 22, Antena module</v>
-      </c>
-      <c r="C29" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="94"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="94"/>
-      <c r="J29" s="94"/>
-      <c r="K29" s="94"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="82">
-        <v>23</v>
-      </c>
-      <c r="B30" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A30+1)</f>
-        <v>Node 23, OBC</v>
-      </c>
-      <c r="C30" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="94"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="94"/>
-      <c r="J30" s="94"/>
-      <c r="K30" s="94"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="82">
-        <v>24</v>
-      </c>
-      <c r="B31" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A31+1)</f>
-        <v>Node 24, Solar Panel (Y)</v>
-      </c>
-      <c r="C31" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="94"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="94"/>
-      <c r="J31" s="94"/>
-      <c r="K31" s="94"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="82">
-        <v>25</v>
-      </c>
-      <c r="B32" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A32+1)</f>
-        <v>Node 25, Solar Panel (-Y)</v>
-      </c>
-      <c r="C32" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="94"/>
-      <c r="J32" s="94"/>
-      <c r="K32" s="94"/>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="82">
-        <v>26</v>
-      </c>
-      <c r="B33" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A33+1)</f>
-        <v>Node 26, Solar Panel (X)</v>
-      </c>
-      <c r="C33" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="94"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="94"/>
-      <c r="K33" s="94"/>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="82">
-        <v>27</v>
-      </c>
-      <c r="B34" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A34+1)</f>
-        <v>Node 27, Solar Panel (-X)RBF</v>
-      </c>
-      <c r="C34" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="94"/>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="82">
-        <v>28</v>
-      </c>
-      <c r="B35" s="92" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A35+1)</f>
-        <v>Node 28, Solar Panel (-Z(antenna))</v>
-      </c>
-      <c r="C35" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D35" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="94"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="94"/>
-      <c r="J35" s="94"/>
-      <c r="K35" s="94"/>
-    </row>
-    <row r="36" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A36" s="82">
-        <v>29</v>
-      </c>
-      <c r="B36" s="95" t="str">
-        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A36+1)</f>
-        <v>Node 29, EPS de alta</v>
-      </c>
-      <c r="C36" s="93">
-        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="93">
-        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="93">
-        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="93">
-        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="94"/>
-      <c r="H36" s="94"/>
-      <c r="I36" s="94"/>
-      <c r="J36" s="94"/>
-      <c r="K36" s="94"/>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="B37" s="80"/>
+    <row r="1" spans="2:7" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:7" ht="37.5" customHeight="1">
+      <c r="B2" s="143" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="144" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2" s="144" t="s">
+        <v>268</v>
+      </c>
+      <c r="E2" s="144" t="s">
+        <v>269</v>
+      </c>
+      <c r="F2" s="144" t="s">
+        <v>270</v>
+      </c>
+      <c r="G2" s="145" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="15.75" thickBot="1">
+      <c r="B3" s="132">
+        <v>0</v>
+      </c>
+      <c r="C3" s="95">
+        <v>0</v>
+      </c>
+      <c r="D3" s="95">
+        <v>0</v>
+      </c>
+      <c r="E3" s="95">
+        <v>0</v>
+      </c>
+      <c r="F3" s="95">
+        <v>0</v>
+      </c>
+      <c r="G3" s="97">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="131"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12144,758 +11834,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B005E130-2D16-4A0C-8BB3-2172273CEA1D}">
-  <dimension ref="B1:O32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:15" ht="15.75" thickBot="1">
-      <c r="B2" s="133" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" s="118" t="s">
-        <v>260</v>
-      </c>
-      <c r="D2" s="119" t="s">
-        <v>258</v>
-      </c>
-      <c r="E2" s="119" t="s">
-        <v>259</v>
-      </c>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="121"/>
-    </row>
-    <row r="3" spans="2:15">
-      <c r="B3" s="134" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" s="122">
-        <v>0</v>
-      </c>
-      <c r="D3" s="123">
-        <v>0</v>
-      </c>
-      <c r="E3" s="123">
-        <v>0</v>
-      </c>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="123"/>
-      <c r="L3" s="123"/>
-      <c r="M3" s="123"/>
-      <c r="N3" s="123"/>
-      <c r="O3" s="124"/>
-    </row>
-    <row r="4" spans="2:15">
-      <c r="B4" s="135" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="125">
-        <v>0</v>
-      </c>
-      <c r="D4" s="84">
-        <v>0</v>
-      </c>
-      <c r="E4" s="84">
-        <v>0</v>
-      </c>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
-      <c r="N4" s="84"/>
-      <c r="O4" s="126"/>
-    </row>
-    <row r="5" spans="2:15">
-      <c r="B5" s="135" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="125">
-        <v>0</v>
-      </c>
-      <c r="D5" s="84">
-        <v>0</v>
-      </c>
-      <c r="E5" s="84">
-        <v>0</v>
-      </c>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="126"/>
-    </row>
-    <row r="6" spans="2:15">
-      <c r="B6" s="135" t="s">
-        <v>217</v>
-      </c>
-      <c r="C6" s="125">
-        <v>0</v>
-      </c>
-      <c r="D6" s="84">
-        <v>0</v>
-      </c>
-      <c r="E6" s="84">
-        <v>0</v>
-      </c>
-      <c r="F6" s="84"/>
-      <c r="G6" s="84"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="84"/>
-      <c r="J6" s="84"/>
-      <c r="K6" s="84"/>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="84"/>
-      <c r="O6" s="126"/>
-    </row>
-    <row r="7" spans="2:15">
-      <c r="B7" s="135" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="125">
-        <v>0</v>
-      </c>
-      <c r="D7" s="84">
-        <v>0</v>
-      </c>
-      <c r="E7" s="84">
-        <v>0</v>
-      </c>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="84"/>
-      <c r="K7" s="84"/>
-      <c r="L7" s="84"/>
-      <c r="M7" s="84"/>
-      <c r="N7" s="84"/>
-      <c r="O7" s="126"/>
-    </row>
-    <row r="8" spans="2:15">
-      <c r="B8" s="135" t="s">
-        <v>219</v>
-      </c>
-      <c r="C8" s="125">
-        <v>0</v>
-      </c>
-      <c r="D8" s="84">
-        <v>0</v>
-      </c>
-      <c r="E8" s="84">
-        <v>0</v>
-      </c>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="84"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="84"/>
-      <c r="M8" s="84"/>
-      <c r="N8" s="84"/>
-      <c r="O8" s="126"/>
-    </row>
-    <row r="9" spans="2:15">
-      <c r="B9" s="135" t="s">
-        <v>220</v>
-      </c>
-      <c r="C9" s="125">
-        <v>0</v>
-      </c>
-      <c r="D9" s="84">
-        <v>0</v>
-      </c>
-      <c r="E9" s="84">
-        <v>0</v>
-      </c>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="84"/>
-      <c r="K9" s="84"/>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="84"/>
-      <c r="O9" s="126"/>
-    </row>
-    <row r="10" spans="2:15">
-      <c r="B10" s="135" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="125">
-        <v>0</v>
-      </c>
-      <c r="D10" s="84">
-        <v>200</v>
-      </c>
-      <c r="E10" s="84">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="84"/>
-      <c r="K10" s="84"/>
-      <c r="L10" s="84"/>
-      <c r="M10" s="84"/>
-      <c r="N10" s="84"/>
-      <c r="O10" s="126"/>
-    </row>
-    <row r="11" spans="2:15">
-      <c r="B11" s="135" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="125">
-        <v>0</v>
-      </c>
-      <c r="D11" s="84">
-        <v>200</v>
-      </c>
-      <c r="E11" s="84">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="84"/>
-      <c r="L11" s="84"/>
-      <c r="M11" s="84"/>
-      <c r="N11" s="84"/>
-      <c r="O11" s="126"/>
-    </row>
-    <row r="12" spans="2:15">
-      <c r="B12" s="135" t="s">
-        <v>223</v>
-      </c>
-      <c r="C12" s="125">
-        <v>0</v>
-      </c>
-      <c r="D12" s="84">
-        <v>200</v>
-      </c>
-      <c r="E12" s="84">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="84"/>
-      <c r="L12" s="84"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="84"/>
-      <c r="O12" s="126"/>
-    </row>
-    <row r="13" spans="2:15">
-      <c r="B13" s="135" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" s="125">
-        <v>0</v>
-      </c>
-      <c r="D13" s="84">
-        <v>200</v>
-      </c>
-      <c r="E13" s="84">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="84"/>
-      <c r="M13" s="84"/>
-      <c r="N13" s="84"/>
-      <c r="O13" s="126"/>
-    </row>
-    <row r="14" spans="2:15">
-      <c r="B14" s="135" t="s">
-        <v>225</v>
-      </c>
-      <c r="C14" s="125">
-        <v>0</v>
-      </c>
-      <c r="D14" s="84">
-        <v>0</v>
-      </c>
-      <c r="E14" s="84">
-        <v>0</v>
-      </c>
-      <c r="F14" s="84"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="84"/>
-      <c r="K14" s="84"/>
-      <c r="L14" s="84"/>
-      <c r="M14" s="84"/>
-      <c r="N14" s="84"/>
-      <c r="O14" s="126"/>
-    </row>
-    <row r="15" spans="2:15">
-      <c r="B15" s="135" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" s="125">
-        <v>0</v>
-      </c>
-      <c r="D15" s="84">
-        <v>0</v>
-      </c>
-      <c r="E15" s="84">
-        <v>0</v>
-      </c>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="84"/>
-      <c r="O15" s="126"/>
-    </row>
-    <row r="16" spans="2:15">
-      <c r="B16" s="135" t="s">
-        <v>227</v>
-      </c>
-      <c r="C16" s="125">
-        <v>0</v>
-      </c>
-      <c r="D16" s="84">
-        <v>0</v>
-      </c>
-      <c r="E16" s="84">
-        <v>0</v>
-      </c>
-      <c r="F16" s="84"/>
-      <c r="G16" s="84"/>
-      <c r="H16" s="84"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="84"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="84"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="84"/>
-      <c r="O16" s="126"/>
-    </row>
-    <row r="17" spans="2:15">
-      <c r="B17" s="135" t="s">
-        <v>228</v>
-      </c>
-      <c r="C17" s="125">
-        <v>0</v>
-      </c>
-      <c r="D17" s="84">
-        <v>0</v>
-      </c>
-      <c r="E17" s="84">
-        <v>0</v>
-      </c>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="84"/>
-      <c r="L17" s="84"/>
-      <c r="M17" s="84"/>
-      <c r="N17" s="84"/>
-      <c r="O17" s="126"/>
-    </row>
-    <row r="18" spans="2:15">
-      <c r="B18" s="135" t="s">
-        <v>229</v>
-      </c>
-      <c r="C18" s="125">
-        <v>0</v>
-      </c>
-      <c r="D18" s="84">
-        <v>0</v>
-      </c>
-      <c r="E18" s="84">
-        <v>0</v>
-      </c>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="84"/>
-      <c r="J18" s="84"/>
-      <c r="K18" s="84"/>
-      <c r="L18" s="84"/>
-      <c r="M18" s="84"/>
-      <c r="N18" s="84"/>
-      <c r="O18" s="126"/>
-    </row>
-    <row r="19" spans="2:15">
-      <c r="B19" s="135" t="s">
-        <v>230</v>
-      </c>
-      <c r="C19" s="125">
-        <v>0</v>
-      </c>
-      <c r="D19" s="84">
-        <v>0</v>
-      </c>
-      <c r="E19" s="84">
-        <v>0</v>
-      </c>
-      <c r="F19" s="84"/>
-      <c r="G19" s="84"/>
-      <c r="H19" s="84"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="84"/>
-      <c r="K19" s="84"/>
-      <c r="L19" s="84"/>
-      <c r="M19" s="84"/>
-      <c r="N19" s="84"/>
-      <c r="O19" s="126"/>
-    </row>
-    <row r="20" spans="2:15">
-      <c r="B20" s="135" t="s">
-        <v>231</v>
-      </c>
-      <c r="C20" s="125">
-        <v>0</v>
-      </c>
-      <c r="D20" s="84">
-        <v>0</v>
-      </c>
-      <c r="E20" s="84">
-        <v>0</v>
-      </c>
-      <c r="F20" s="84"/>
-      <c r="G20" s="84"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="84"/>
-      <c r="J20" s="84"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="84"/>
-      <c r="M20" s="84"/>
-      <c r="N20" s="84"/>
-      <c r="O20" s="126"/>
-    </row>
-    <row r="21" spans="2:15">
-      <c r="B21" s="135" t="s">
-        <v>232</v>
-      </c>
-      <c r="C21" s="125">
-        <v>0</v>
-      </c>
-      <c r="D21" s="84">
-        <v>0</v>
-      </c>
-      <c r="E21" s="84">
-        <v>0</v>
-      </c>
-      <c r="F21" s="84"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="84"/>
-      <c r="I21" s="84"/>
-      <c r="J21" s="84"/>
-      <c r="K21" s="84"/>
-      <c r="L21" s="84"/>
-      <c r="M21" s="84"/>
-      <c r="N21" s="84"/>
-      <c r="O21" s="126"/>
-    </row>
-    <row r="22" spans="2:15">
-      <c r="B22" s="135" t="s">
-        <v>233</v>
-      </c>
-      <c r="C22" s="125">
-        <v>0</v>
-      </c>
-      <c r="D22" s="84">
-        <v>0</v>
-      </c>
-      <c r="E22" s="84">
-        <v>0</v>
-      </c>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="126"/>
-    </row>
-    <row r="23" spans="2:15">
-      <c r="B23" s="135" t="s">
-        <v>234</v>
-      </c>
-      <c r="C23" s="125">
-        <v>0</v>
-      </c>
-      <c r="D23" s="84">
-        <v>0</v>
-      </c>
-      <c r="E23" s="84">
-        <v>0</v>
-      </c>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="84"/>
-      <c r="N23" s="84"/>
-      <c r="O23" s="126"/>
-    </row>
-    <row r="24" spans="2:15">
-      <c r="B24" s="135" t="s">
-        <v>235</v>
-      </c>
-      <c r="C24" s="125">
-        <v>0</v>
-      </c>
-      <c r="D24" s="84">
-        <v>0</v>
-      </c>
-      <c r="E24" s="84">
-        <v>0</v>
-      </c>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="84"/>
-      <c r="N24" s="84"/>
-      <c r="O24" s="126"/>
-    </row>
-    <row r="25" spans="2:15">
-      <c r="B25" s="135" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="125">
-        <v>0</v>
-      </c>
-      <c r="D25" s="84">
-        <v>0</v>
-      </c>
-      <c r="E25" s="84">
-        <v>0</v>
-      </c>
-      <c r="F25" s="84"/>
-      <c r="G25" s="84"/>
-      <c r="H25" s="84"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="84"/>
-      <c r="K25" s="84"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="84"/>
-      <c r="N25" s="84"/>
-      <c r="O25" s="126"/>
-    </row>
-    <row r="26" spans="2:15">
-      <c r="B26" s="135" t="s">
-        <v>237</v>
-      </c>
-      <c r="C26" s="125">
-        <v>0</v>
-      </c>
-      <c r="D26" s="84">
-        <v>0</v>
-      </c>
-      <c r="E26" s="84">
-        <v>0</v>
-      </c>
-      <c r="F26" s="84"/>
-      <c r="G26" s="84"/>
-      <c r="H26" s="84"/>
-      <c r="I26" s="84"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="84"/>
-      <c r="L26" s="84"/>
-      <c r="M26" s="84"/>
-      <c r="N26" s="84"/>
-      <c r="O26" s="126"/>
-    </row>
-    <row r="27" spans="2:15">
-      <c r="B27" s="135" t="s">
-        <v>238</v>
-      </c>
-      <c r="C27" s="125">
-        <v>0</v>
-      </c>
-      <c r="D27" s="84">
-        <v>0</v>
-      </c>
-      <c r="E27" s="84">
-        <v>0</v>
-      </c>
-      <c r="F27" s="84"/>
-      <c r="G27" s="84"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="84"/>
-      <c r="M27" s="84"/>
-      <c r="N27" s="84"/>
-      <c r="O27" s="126"/>
-    </row>
-    <row r="28" spans="2:15">
-      <c r="B28" s="135" t="s">
-        <v>239</v>
-      </c>
-      <c r="C28" s="125">
-        <v>0</v>
-      </c>
-      <c r="D28" s="84">
-        <v>0</v>
-      </c>
-      <c r="E28" s="84">
-        <v>0</v>
-      </c>
-      <c r="F28" s="84"/>
-      <c r="G28" s="84"/>
-      <c r="H28" s="84"/>
-      <c r="I28" s="84"/>
-      <c r="J28" s="84"/>
-      <c r="K28" s="84"/>
-      <c r="L28" s="84"/>
-      <c r="M28" s="84"/>
-      <c r="N28" s="84"/>
-      <c r="O28" s="126"/>
-    </row>
-    <row r="29" spans="2:15">
-      <c r="B29" s="135" t="s">
-        <v>240</v>
-      </c>
-      <c r="C29" s="125">
-        <v>0</v>
-      </c>
-      <c r="D29" s="84">
-        <v>0</v>
-      </c>
-      <c r="E29" s="84">
-        <v>0</v>
-      </c>
-      <c r="F29" s="84"/>
-      <c r="G29" s="84"/>
-      <c r="H29" s="84"/>
-      <c r="I29" s="84"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="84"/>
-      <c r="L29" s="84"/>
-      <c r="M29" s="84"/>
-      <c r="N29" s="84"/>
-      <c r="O29" s="126"/>
-    </row>
-    <row r="30" spans="2:15">
-      <c r="B30" s="135" t="s">
-        <v>241</v>
-      </c>
-      <c r="C30" s="125">
-        <v>0</v>
-      </c>
-      <c r="D30" s="84">
-        <v>0</v>
-      </c>
-      <c r="E30" s="84">
-        <v>0</v>
-      </c>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="84"/>
-      <c r="K30" s="84"/>
-      <c r="L30" s="84"/>
-      <c r="M30" s="84"/>
-      <c r="N30" s="84"/>
-      <c r="O30" s="126"/>
-    </row>
-    <row r="31" spans="2:15">
-      <c r="B31" s="136" t="s">
-        <v>242</v>
-      </c>
-      <c r="C31" s="129">
-        <v>0</v>
-      </c>
-      <c r="D31" s="114">
-        <v>0</v>
-      </c>
-      <c r="E31" s="114">
-        <v>0</v>
-      </c>
-      <c r="F31" s="114"/>
-      <c r="G31" s="114"/>
-      <c r="H31" s="114"/>
-      <c r="I31" s="114"/>
-      <c r="J31" s="114"/>
-      <c r="K31" s="114"/>
-      <c r="L31" s="114"/>
-      <c r="M31" s="114"/>
-      <c r="N31" s="114"/>
-      <c r="O31" s="130"/>
-    </row>
-    <row r="32" spans="2:15">
-      <c r="B32" s="91"/>
-      <c r="C32" s="91"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="91"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="91"/>
-      <c r="K32" s="91"/>
-      <c r="L32" s="91"/>
-      <c r="M32" s="91"/>
-      <c r="N32" s="91"/>
-      <c r="O32" s="91"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4985A03E-5096-4337-92A3-24224C69AEFA}">
-  <dimension ref="B1:M32"/>
+  <dimension ref="B1:L32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
@@ -12910,927 +11850,1867 @@
     <col min="12" max="12" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:13" ht="46.5" customHeight="1" thickBot="1">
-      <c r="B2" s="105" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="106" t="s">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:12" ht="46.5" customHeight="1" thickBot="1">
+      <c r="B2" s="139" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="140" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="141" t="s">
         <v>245</v>
       </c>
-      <c r="D2" s="107" t="s">
+      <c r="E2" s="141" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" s="141" t="s">
         <v>246</v>
       </c>
-      <c r="E2" s="107" t="s">
+      <c r="G2" s="141" t="s">
+        <v>242</v>
+      </c>
+      <c r="H2" s="141" t="s">
+        <v>243</v>
+      </c>
+      <c r="I2" s="141" t="s">
+        <v>247</v>
+      </c>
+      <c r="J2" s="141" t="s">
         <v>248</v>
       </c>
-      <c r="F2" s="107" t="s">
-        <v>247</v>
-      </c>
-      <c r="G2" s="107" t="s">
-        <v>243</v>
-      </c>
-      <c r="H2" s="107" t="s">
-        <v>244</v>
-      </c>
-      <c r="I2" s="107" t="s">
+      <c r="K2" s="141" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="107" t="s">
-        <v>250</v>
-      </c>
-      <c r="K2" s="107" t="s">
-        <v>251</v>
-      </c>
-      <c r="L2" s="131" t="s">
-        <v>262</v>
-      </c>
-      <c r="M2" s="108" t="s">
+      <c r="L2" s="142" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
+      <c r="B3" s="103" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="3" spans="2:13">
-      <c r="B3" s="109" t="s">
+      <c r="C3" s="100">
+        <v>4.0280000000000003E-2</v>
+      </c>
+      <c r="D3" s="98">
+        <v>800</v>
+      </c>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="G3" s="98">
+        <v>0.8</v>
+      </c>
+      <c r="H3" s="98">
+        <v>0.8</v>
+      </c>
+      <c r="I3" s="98">
+        <v>1</v>
+      </c>
+      <c r="J3" s="98">
+        <v>0</v>
+      </c>
+      <c r="K3" s="98">
+        <v>0</v>
+      </c>
+      <c r="L3" s="99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="104" t="s">
         <v>214</v>
       </c>
-      <c r="C3" s="102">
+      <c r="C4" s="101">
         <v>4.0280000000000003E-2</v>
       </c>
-      <c r="D3" s="100">
+      <c r="D4" s="94">
         <v>800</v>
       </c>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100">
+      <c r="E4" s="94"/>
+      <c r="F4" s="94">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="G3" s="100">
+      <c r="G4" s="94">
         <v>0.8</v>
       </c>
-      <c r="H3" s="100">
+      <c r="H4" s="94">
         <v>0.8</v>
       </c>
-      <c r="I3" s="100">
-        <v>1</v>
-      </c>
-      <c r="J3" s="100">
-        <v>0</v>
-      </c>
-      <c r="K3" s="100">
-        <v>0</v>
-      </c>
-      <c r="L3" s="100">
-        <v>1</v>
-      </c>
-      <c r="M3" s="101"/>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="B4" s="110" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="103">
-        <v>4.0280000000000003E-2</v>
-      </c>
-      <c r="D4" s="96">
-        <v>800</v>
-      </c>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96">
-        <v>5.1999999999999998E-3</v>
-      </c>
-      <c r="G4" s="96">
-        <v>0.8</v>
-      </c>
-      <c r="H4" s="96">
-        <v>0.8</v>
-      </c>
-      <c r="I4" s="96">
+      <c r="I4" s="94">
         <v>-1</v>
       </c>
-      <c r="J4" s="96">
-        <v>0</v>
-      </c>
-      <c r="K4" s="96">
+      <c r="J4" s="94">
+        <v>0</v>
+      </c>
+      <c r="K4" s="94">
         <v>0</v>
       </c>
       <c r="L4" s="96">
         <v>1</v>
       </c>
-      <c r="M4" s="98"/>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="110" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="103">
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" s="104" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="101">
         <v>7.2909999999999997E-3</v>
       </c>
-      <c r="D5" s="96">
+      <c r="D5" s="94">
         <v>800</v>
       </c>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96">
+      <c r="E5" s="94"/>
+      <c r="F5" s="94">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G5" s="96">
+      <c r="G5" s="94">
         <v>0.8</v>
       </c>
-      <c r="H5" s="96">
+      <c r="H5" s="94">
         <v>0.8</v>
       </c>
-      <c r="I5" s="96">
-        <v>0</v>
-      </c>
-      <c r="J5" s="96">
+      <c r="I5" s="94">
+        <v>0</v>
+      </c>
+      <c r="J5" s="94">
         <v>-0.70709999999999995</v>
       </c>
-      <c r="K5" s="96">
+      <c r="K5" s="94">
         <v>0.70709999999999995</v>
       </c>
       <c r="L5" s="96">
         <v>1</v>
       </c>
-      <c r="M5" s="98"/>
-    </row>
-    <row r="6" spans="2:13">
-      <c r="B6" s="110" t="s">
-        <v>217</v>
-      </c>
-      <c r="C6" s="103">
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" s="104" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="101">
         <v>7.2909999999999997E-3</v>
       </c>
-      <c r="D6" s="96">
+      <c r="D6" s="94">
         <v>800</v>
       </c>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96">
+      <c r="E6" s="94"/>
+      <c r="F6" s="94">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G6" s="96">
+      <c r="G6" s="94">
         <v>0.8</v>
       </c>
-      <c r="H6" s="96">
+      <c r="H6" s="94">
         <v>0.8</v>
       </c>
-      <c r="I6" s="96">
-        <v>0</v>
-      </c>
-      <c r="J6" s="96">
+      <c r="I6" s="94">
+        <v>0</v>
+      </c>
+      <c r="J6" s="94">
         <v>0.70709999999999995</v>
       </c>
-      <c r="K6" s="96">
+      <c r="K6" s="94">
         <v>0.70709999999999995</v>
       </c>
       <c r="L6" s="96">
         <v>1</v>
       </c>
-      <c r="M6" s="98"/>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="110" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="103">
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" s="104" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="101">
         <v>6.4250000000000002E-3</v>
       </c>
-      <c r="D7" s="96">
+      <c r="D7" s="94">
         <v>800</v>
       </c>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96">
+      <c r="E7" s="94"/>
+      <c r="F7" s="94">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G7" s="96">
+      <c r="G7" s="94">
         <v>0.8</v>
       </c>
-      <c r="H7" s="96">
+      <c r="H7" s="94">
         <v>0.8</v>
       </c>
-      <c r="I7" s="96">
-        <v>0</v>
-      </c>
-      <c r="J7" s="96">
+      <c r="I7" s="94">
+        <v>0</v>
+      </c>
+      <c r="J7" s="94">
         <v>0.70709999999999995</v>
       </c>
-      <c r="K7" s="96">
+      <c r="K7" s="94">
         <v>-0.70709999999999995</v>
       </c>
       <c r="L7" s="96">
         <v>1</v>
       </c>
-      <c r="M7" s="98"/>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="110" t="s">
-        <v>219</v>
-      </c>
-      <c r="C8" s="103">
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" s="104" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="101">
         <v>6.4250000000000002E-3</v>
       </c>
-      <c r="D8" s="96">
+      <c r="D8" s="94">
         <v>800</v>
       </c>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96">
+      <c r="E8" s="94"/>
+      <c r="F8" s="94">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G8" s="96">
+      <c r="G8" s="94">
         <v>0.8</v>
       </c>
-      <c r="H8" s="96">
+      <c r="H8" s="94">
         <v>0.8</v>
       </c>
-      <c r="I8" s="96">
-        <v>0</v>
-      </c>
-      <c r="J8" s="96">
+      <c r="I8" s="94">
+        <v>0</v>
+      </c>
+      <c r="J8" s="94">
         <v>-0.70709999999999995</v>
       </c>
-      <c r="K8" s="96">
+      <c r="K8" s="94">
         <v>-0.70709999999999995</v>
       </c>
       <c r="L8" s="96">
         <v>1</v>
       </c>
-      <c r="M8" s="98"/>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="144" t="s">
-        <v>220</v>
-      </c>
-      <c r="C9" s="103">
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" s="130" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="101">
         <v>2.1919999999999999E-2</v>
       </c>
-      <c r="D9" s="96">
+      <c r="D9" s="94">
         <v>800</v>
       </c>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96">
+      <c r="E9" s="94"/>
+      <c r="F9" s="94">
         <v>9.5999999999999992E-3</v>
       </c>
-      <c r="G9" s="96">
+      <c r="G9" s="94">
         <v>0.8</v>
       </c>
-      <c r="H9" s="96">
+      <c r="H9" s="94">
         <v>0.8</v>
       </c>
-      <c r="I9" s="96">
-        <v>0</v>
-      </c>
-      <c r="J9" s="96">
-        <v>0</v>
-      </c>
-      <c r="K9" s="96">
+      <c r="I9" s="94">
+        <v>0</v>
+      </c>
+      <c r="J9" s="94">
+        <v>0</v>
+      </c>
+      <c r="K9" s="94">
         <v>1</v>
       </c>
       <c r="L9" s="96">
         <v>1</v>
       </c>
-      <c r="M9" s="98"/>
-    </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="110" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="103">
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="104" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="101">
         <v>1.8E-3</v>
       </c>
-      <c r="D10" s="96">
+      <c r="D10" s="94">
         <v>800</v>
       </c>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96">
+      <c r="E10" s="94"/>
+      <c r="F10" s="94">
         <v>5.7600000000000001E-4</v>
       </c>
-      <c r="G10" s="96">
+      <c r="G10" s="94">
         <v>0.8</v>
       </c>
-      <c r="H10" s="96">
+      <c r="H10" s="94">
         <v>0.8</v>
       </c>
-      <c r="I10" s="96">
-        <v>0</v>
-      </c>
-      <c r="J10" s="96">
-        <v>0</v>
-      </c>
-      <c r="K10" s="96">
+      <c r="I10" s="94">
+        <v>0</v>
+      </c>
+      <c r="J10" s="94">
+        <v>0</v>
+      </c>
+      <c r="K10" s="94">
         <v>1</v>
       </c>
       <c r="L10" s="96">
         <v>1</v>
       </c>
-      <c r="M10" s="98"/>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="110" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="103">
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" s="104" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="101">
         <v>1.8E-3</v>
       </c>
-      <c r="D11" s="96">
+      <c r="D11" s="94">
         <v>800</v>
       </c>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96">
+      <c r="E11" s="94"/>
+      <c r="F11" s="94">
         <v>5.7600000000000001E-4</v>
       </c>
-      <c r="G11" s="96">
+      <c r="G11" s="94">
         <v>0.8</v>
       </c>
-      <c r="H11" s="96">
+      <c r="H11" s="94">
         <v>0.8</v>
       </c>
-      <c r="I11" s="96">
-        <v>0</v>
-      </c>
-      <c r="J11" s="96">
-        <v>0</v>
-      </c>
-      <c r="K11" s="96">
+      <c r="I11" s="94">
+        <v>0</v>
+      </c>
+      <c r="J11" s="94">
+        <v>0</v>
+      </c>
+      <c r="K11" s="94">
         <v>1</v>
       </c>
       <c r="L11" s="96">
         <v>1</v>
       </c>
-      <c r="M11" s="98"/>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="B12" s="110" t="s">
-        <v>223</v>
-      </c>
-      <c r="C12" s="103">
+    </row>
+    <row r="12" spans="2:12">
+      <c r="B12" s="104" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="101">
         <v>1.8E-3</v>
       </c>
-      <c r="D12" s="96">
+      <c r="D12" s="94">
         <v>800</v>
       </c>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96">
+      <c r="E12" s="94"/>
+      <c r="F12" s="94">
         <v>5.7600000000000001E-4</v>
       </c>
-      <c r="G12" s="96">
+      <c r="G12" s="94">
         <v>0.8</v>
       </c>
-      <c r="H12" s="96">
+      <c r="H12" s="94">
         <v>0.8</v>
       </c>
-      <c r="I12" s="96">
-        <v>0</v>
-      </c>
-      <c r="J12" s="96">
-        <v>0</v>
-      </c>
-      <c r="K12" s="96">
+      <c r="I12" s="94">
+        <v>0</v>
+      </c>
+      <c r="J12" s="94">
+        <v>0</v>
+      </c>
+      <c r="K12" s="94">
         <v>1</v>
       </c>
       <c r="L12" s="96">
         <v>1</v>
       </c>
-      <c r="M12" s="98"/>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="110" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" s="103">
+    </row>
+    <row r="13" spans="2:12">
+      <c r="B13" s="104" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="101">
         <v>1.8E-3</v>
       </c>
-      <c r="D13" s="96">
+      <c r="D13" s="94">
         <v>800</v>
       </c>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96">
+      <c r="E13" s="94"/>
+      <c r="F13" s="94">
         <v>5.7600000000000001E-4</v>
       </c>
-      <c r="G13" s="96">
+      <c r="G13" s="94">
         <v>0.8</v>
       </c>
-      <c r="H13" s="96">
+      <c r="H13" s="94">
         <v>0.8</v>
       </c>
-      <c r="I13" s="96">
-        <v>0</v>
-      </c>
-      <c r="J13" s="96">
-        <v>0</v>
-      </c>
-      <c r="K13" s="96">
+      <c r="I13" s="94">
+        <v>0</v>
+      </c>
+      <c r="J13" s="94">
+        <v>0</v>
+      </c>
+      <c r="K13" s="94">
         <v>1</v>
       </c>
       <c r="L13" s="96">
         <v>1</v>
       </c>
-      <c r="M13" s="98"/>
-    </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="110" t="s">
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="104" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="101">
+        <v>2.375E-2</v>
+      </c>
+      <c r="D14" s="94">
+        <v>600</v>
+      </c>
+      <c r="E14" s="94"/>
+      <c r="F14" s="94">
+        <v>0.01</v>
+      </c>
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="94"/>
+      <c r="K14" s="94"/>
+      <c r="L14" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="104" t="s">
         <v>225</v>
       </c>
-      <c r="C14" s="103">
-        <v>2.375E-2</v>
-      </c>
-      <c r="D14" s="96">
+      <c r="C15" s="101">
+        <v>0.125</v>
+      </c>
+      <c r="D15" s="94">
+        <v>800</v>
+      </c>
+      <c r="E15" s="94"/>
+      <c r="F15" s="94">
+        <v>0.01</v>
+      </c>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="94"/>
+      <c r="K15" s="94"/>
+      <c r="L15" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="104" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" s="101">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D16" s="94">
         <v>600</v>
       </c>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96">
+      <c r="E16" s="94"/>
+      <c r="F16" s="94">
         <v>0.01</v>
       </c>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96">
-        <v>0</v>
-      </c>
-      <c r="M14" s="98"/>
-    </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="110" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" s="103">
-        <v>0.125</v>
-      </c>
-      <c r="D15" s="96">
-        <v>800</v>
-      </c>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96">
-        <v>0.01</v>
-      </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="96">
-        <v>0</v>
-      </c>
-      <c r="M15" s="98"/>
-    </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="110" t="s">
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="94"/>
+      <c r="K16" s="94"/>
+      <c r="L16" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" s="104" t="s">
         <v>227</v>
       </c>
-      <c r="C16" s="103">
+      <c r="C17" s="101">
         <v>3.9E-2</v>
       </c>
-      <c r="D16" s="96">
+      <c r="D17" s="94">
         <v>600</v>
       </c>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96">
-        <v>0.01</v>
-      </c>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96">
-        <v>0</v>
-      </c>
-      <c r="M16" s="98"/>
-    </row>
-    <row r="17" spans="2:13">
-      <c r="B17" s="110" t="s">
+      <c r="E17" s="94"/>
+      <c r="F17" s="94">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="94"/>
+      <c r="K17" s="94"/>
+      <c r="L17" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="B18" s="104" t="s">
         <v>228</v>
       </c>
-      <c r="C17" s="103">
+      <c r="C18" s="101">
         <v>3.9E-2</v>
       </c>
-      <c r="D17" s="96">
+      <c r="D18" s="94">
         <v>600</v>
       </c>
-      <c r="E17" s="96"/>
-      <c r="F17" s="96">
+      <c r="E18" s="94"/>
+      <c r="F18" s="94">
         <v>0.1</v>
       </c>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96">
-        <v>0</v>
-      </c>
-      <c r="M17" s="98"/>
-    </row>
-    <row r="18" spans="2:13">
-      <c r="B18" s="110" t="s">
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="94"/>
+      <c r="L18" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="104" t="s">
         <v>229</v>
       </c>
-      <c r="C18" s="103">
+      <c r="C19" s="101">
         <v>3.9E-2</v>
       </c>
-      <c r="D18" s="96">
+      <c r="D19" s="94">
         <v>600</v>
       </c>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96">
+      <c r="E19" s="94"/>
+      <c r="F19" s="94">
         <v>0.1</v>
       </c>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="96">
-        <v>0</v>
-      </c>
-      <c r="M18" s="98"/>
-    </row>
-    <row r="19" spans="2:13">
-      <c r="B19" s="110" t="s">
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="94"/>
+      <c r="J19" s="94"/>
+      <c r="K19" s="94"/>
+      <c r="L19" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="104" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="103">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D19" s="96">
+      <c r="C20" s="101">
+        <v>0.05</v>
+      </c>
+      <c r="D20" s="94">
         <v>600</v>
       </c>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96">
+      <c r="E20" s="94"/>
+      <c r="F20" s="94">
         <v>0.1</v>
       </c>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="96">
-        <v>0</v>
-      </c>
-      <c r="M19" s="98"/>
-    </row>
-    <row r="20" spans="2:13">
-      <c r="B20" s="110" t="s">
+      <c r="G20" s="94"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="94"/>
+      <c r="J20" s="94"/>
+      <c r="K20" s="94"/>
+      <c r="L20" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="B21" s="104" t="s">
         <v>231</v>
       </c>
-      <c r="C20" s="103">
+      <c r="C21" s="101">
         <v>0.05</v>
       </c>
-      <c r="D20" s="96">
+      <c r="D21" s="94">
         <v>600</v>
       </c>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96">
+      <c r="E21" s="94"/>
+      <c r="F21" s="94">
         <v>0.1</v>
       </c>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="96"/>
-      <c r="L20" s="96">
-        <v>0</v>
-      </c>
-      <c r="M20" s="98"/>
-    </row>
-    <row r="21" spans="2:13">
-      <c r="B21" s="110" t="s">
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="94"/>
+      <c r="J21" s="94"/>
+      <c r="K21" s="94"/>
+      <c r="L21" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="B22" s="104" t="s">
         <v>232</v>
       </c>
-      <c r="C21" s="103">
-        <v>0.05</v>
-      </c>
-      <c r="D21" s="96">
+      <c r="C22" s="101">
+        <v>3.8490000000000003E-2</v>
+      </c>
+      <c r="D22" s="94">
         <v>600</v>
       </c>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96">
-        <v>0.1</v>
-      </c>
-      <c r="G21" s="96"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="96"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="96">
-        <v>0</v>
-      </c>
-      <c r="M21" s="98"/>
-    </row>
-    <row r="22" spans="2:13">
-      <c r="B22" s="110" t="s">
+      <c r="E22" s="94"/>
+      <c r="F22" s="94">
+        <v>8.6E-3</v>
+      </c>
+      <c r="G22" s="94"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="94"/>
+      <c r="J22" s="94"/>
+      <c r="K22" s="94"/>
+      <c r="L22" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12">
+      <c r="B23" s="104" t="s">
         <v>233</v>
       </c>
-      <c r="C22" s="103">
-        <v>3.8490000000000003E-2</v>
-      </c>
-      <c r="D22" s="96">
+      <c r="C23" s="101">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="D23" s="94">
         <v>600</v>
       </c>
-      <c r="E22" s="96"/>
-      <c r="F22" s="96">
+      <c r="E23" s="94"/>
+      <c r="F23" s="94">
         <v>8.6E-3</v>
       </c>
-      <c r="G22" s="96"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="96"/>
-      <c r="K22" s="96"/>
-      <c r="L22" s="96">
-        <v>0</v>
-      </c>
-      <c r="M22" s="98"/>
-    </row>
-    <row r="23" spans="2:13">
-      <c r="B23" s="110" t="s">
+      <c r="G23" s="94"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="94"/>
+      <c r="K23" s="94"/>
+      <c r="L23" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12">
+      <c r="B24" s="104" t="s">
         <v>234</v>
       </c>
-      <c r="C23" s="103">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="D23" s="96">
+      <c r="C24" s="101">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="D24" s="94">
         <v>600</v>
       </c>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96">
-        <v>8.6E-3</v>
-      </c>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96"/>
-      <c r="K23" s="96"/>
-      <c r="L23" s="96">
-        <v>0</v>
-      </c>
-      <c r="M23" s="98"/>
-    </row>
-    <row r="24" spans="2:13">
-      <c r="B24" s="110" t="s">
+      <c r="E24" s="94">
+        <v>15</v>
+      </c>
+      <c r="F24" s="94">
+        <v>0.08</v>
+      </c>
+      <c r="G24" s="94"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="94"/>
+      <c r="J24" s="94"/>
+      <c r="K24" s="94"/>
+      <c r="L24" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12">
+      <c r="B25" s="104" t="s">
         <v>235</v>
       </c>
-      <c r="C24" s="103">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="D24" s="96">
+      <c r="C25" s="101">
+        <v>2.4E-2</v>
+      </c>
+      <c r="D25" s="94">
         <v>600</v>
       </c>
-      <c r="E24" s="96">
+      <c r="E25" s="94"/>
+      <c r="F25" s="94">
+        <v>0.33</v>
+      </c>
+      <c r="G25" s="94"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="94"/>
+      <c r="J25" s="94"/>
+      <c r="K25" s="94"/>
+      <c r="L25" s="96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12">
+      <c r="B26" s="104" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="101">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="D26" s="94">
+        <v>600</v>
+      </c>
+      <c r="E26" s="94">
         <v>15</v>
       </c>
-      <c r="F24" s="96">
-        <v>0.08</v>
-      </c>
-      <c r="G24" s="96"/>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="96"/>
-      <c r="K24" s="96"/>
-      <c r="L24" s="96">
-        <v>0</v>
-      </c>
-      <c r="M24" s="98">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13">
-      <c r="B25" s="110" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="103">
-        <v>2.4E-2</v>
-      </c>
-      <c r="D25" s="96">
-        <v>600</v>
-      </c>
-      <c r="E25" s="96"/>
-      <c r="F25" s="96">
-        <v>0.33</v>
-      </c>
-      <c r="G25" s="96"/>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96"/>
-      <c r="K25" s="96"/>
-      <c r="L25" s="96">
-        <v>0</v>
-      </c>
-      <c r="M25" s="98"/>
-    </row>
-    <row r="26" spans="2:13">
-      <c r="B26" s="110" t="s">
-        <v>237</v>
-      </c>
-      <c r="C26" s="103">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="D26" s="96">
-        <v>600</v>
-      </c>
-      <c r="E26" s="96">
-        <v>15</v>
-      </c>
-      <c r="F26" s="96">
+      <c r="F26" s="94">
         <v>8.0940000000000005E-3</v>
       </c>
-      <c r="G26" s="96">
+      <c r="G26" s="94">
         <v>0.8</v>
       </c>
-      <c r="H26" s="96">
+      <c r="H26" s="94">
         <v>0.8</v>
       </c>
-      <c r="I26" s="96">
-        <v>0</v>
-      </c>
-      <c r="J26" s="96">
+      <c r="I26" s="94">
+        <v>0</v>
+      </c>
+      <c r="J26" s="94">
         <v>1</v>
       </c>
-      <c r="K26" s="96">
+      <c r="K26" s="94">
         <v>0</v>
       </c>
       <c r="L26" s="96">
         <v>1</v>
       </c>
-      <c r="M26" s="98">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13">
-      <c r="B27" s="110" t="s">
-        <v>238</v>
-      </c>
-      <c r="C27" s="103">
+    </row>
+    <row r="27" spans="2:12">
+      <c r="B27" s="104" t="s">
+        <v>237</v>
+      </c>
+      <c r="C27" s="101">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="D27" s="96">
+      <c r="D27" s="94">
         <v>600</v>
       </c>
-      <c r="E27" s="96">
+      <c r="E27" s="94">
         <v>15</v>
       </c>
-      <c r="F27" s="96">
+      <c r="F27" s="94">
         <v>8.0940000000000005E-3</v>
       </c>
-      <c r="G27" s="96">
+      <c r="G27" s="94">
         <v>0.8</v>
       </c>
-      <c r="H27" s="96">
+      <c r="H27" s="94">
         <v>0.8</v>
       </c>
-      <c r="I27" s="96">
-        <v>0</v>
-      </c>
-      <c r="J27" s="96">
+      <c r="I27" s="94">
+        <v>0</v>
+      </c>
+      <c r="J27" s="94">
         <v>-1</v>
       </c>
-      <c r="K27" s="96">
+      <c r="K27" s="94">
         <v>0</v>
       </c>
       <c r="L27" s="96">
         <v>1</v>
       </c>
-      <c r="M27" s="98">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13">
-      <c r="B28" s="110" t="s">
-        <v>239</v>
-      </c>
-      <c r="C28" s="103">
+    </row>
+    <row r="28" spans="2:12">
+      <c r="B28" s="104" t="s">
+        <v>238</v>
+      </c>
+      <c r="C28" s="101">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="D28" s="96">
+      <c r="D28" s="94">
         <v>600</v>
       </c>
-      <c r="E28" s="96">
+      <c r="E28" s="94">
         <v>15</v>
       </c>
-      <c r="F28" s="96">
+      <c r="F28" s="94">
         <v>8.0940000000000005E-3</v>
       </c>
-      <c r="G28" s="96">
+      <c r="G28" s="94">
         <v>0.8</v>
       </c>
-      <c r="H28" s="96">
+      <c r="H28" s="94">
         <v>0.8</v>
       </c>
-      <c r="I28" s="96">
+      <c r="I28" s="94">
         <v>1</v>
       </c>
-      <c r="J28" s="96">
-        <v>0</v>
-      </c>
-      <c r="K28" s="96">
+      <c r="J28" s="94">
+        <v>0</v>
+      </c>
+      <c r="K28" s="94">
         <v>0</v>
       </c>
       <c r="L28" s="96">
         <v>1</v>
       </c>
-      <c r="M28" s="98">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13">
-      <c r="B29" s="110" t="s">
-        <v>240</v>
-      </c>
-      <c r="C29" s="103">
+    </row>
+    <row r="29" spans="2:12">
+      <c r="B29" s="104" t="s">
+        <v>239</v>
+      </c>
+      <c r="C29" s="101">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="D29" s="96">
+      <c r="D29" s="94">
         <v>600</v>
       </c>
-      <c r="E29" s="96">
+      <c r="E29" s="94">
         <v>15</v>
       </c>
-      <c r="F29" s="96">
+      <c r="F29" s="94">
         <v>8.0940000000000005E-3</v>
       </c>
-      <c r="G29" s="96">
+      <c r="G29" s="94">
         <v>0.8</v>
       </c>
-      <c r="H29" s="96">
+      <c r="H29" s="94">
         <v>0.8</v>
       </c>
-      <c r="I29" s="96">
+      <c r="I29" s="94">
         <v>-1</v>
       </c>
-      <c r="J29" s="96">
-        <v>0</v>
-      </c>
-      <c r="K29" s="96">
+      <c r="J29" s="94">
+        <v>0</v>
+      </c>
+      <c r="K29" s="94">
         <v>0</v>
       </c>
       <c r="L29" s="96">
         <v>1</v>
       </c>
-      <c r="M29" s="98">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13">
-      <c r="B30" s="110" t="s">
-        <v>241</v>
-      </c>
-      <c r="C30" s="103">
+    </row>
+    <row r="30" spans="2:12">
+      <c r="B30" s="104" t="s">
+        <v>240</v>
+      </c>
+      <c r="C30" s="101">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="D30" s="96">
+      <c r="D30" s="94">
         <v>600</v>
       </c>
-      <c r="E30" s="96">
+      <c r="E30" s="94">
         <v>15</v>
       </c>
-      <c r="F30" s="96">
+      <c r="F30" s="94">
         <v>8.4469999999999996E-3</v>
       </c>
-      <c r="G30" s="96">
+      <c r="G30" s="94">
         <v>0.8</v>
       </c>
-      <c r="H30" s="96">
+      <c r="H30" s="94">
         <v>0.8</v>
       </c>
-      <c r="I30" s="96">
-        <v>0</v>
-      </c>
-      <c r="J30" s="96">
-        <v>0</v>
-      </c>
-      <c r="K30" s="96">
+      <c r="I30" s="94">
+        <v>0</v>
+      </c>
+      <c r="J30" s="94">
+        <v>0</v>
+      </c>
+      <c r="K30" s="94">
         <v>-1</v>
       </c>
       <c r="L30" s="96">
         <v>1</v>
       </c>
-      <c r="M30" s="98">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" ht="15.75" thickBot="1">
-      <c r="B31" s="111" t="s">
-        <v>242</v>
-      </c>
-      <c r="C31" s="104">
+    </row>
+    <row r="31" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B31" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="C31" s="102">
         <v>0.04</v>
       </c>
-      <c r="D31" s="97">
+      <c r="D31" s="95">
         <v>600</v>
       </c>
-      <c r="E31" s="97"/>
-      <c r="F31" s="97">
+      <c r="E31" s="95"/>
+      <c r="F31" s="95">
         <v>0.01</v>
       </c>
-      <c r="G31" s="97"/>
-      <c r="H31" s="97"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="97"/>
-      <c r="K31" s="97"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="95"/>
+      <c r="K31" s="95"/>
       <c r="L31" s="97">
         <v>0</v>
       </c>
-      <c r="M31" s="99"/>
-    </row>
-    <row r="32" spans="2:13">
+    </row>
+    <row r="32" spans="2:12">
       <c r="B32" s="80"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4723E147-5D28-48F2-9A19-B61306348D73}">
+  <dimension ref="A1:N37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.75" thickBot="1"/>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1">
+      <c r="B2" s="151" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="157" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="128" t="s">
+        <v>257</v>
+      </c>
+      <c r="E2" s="128" t="s">
+        <v>256</v>
+      </c>
+      <c r="F2" s="129" t="s">
+        <v>258</v>
+      </c>
+      <c r="G2" s="110"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="B3" s="152" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="87">
+        <f>IFERROR(C4+C5*60+C6*3600+C7*3600*24+B3,C4+C5*60+C6*3600+C7*3600*24)</f>
+        <v>259200</v>
+      </c>
+      <c r="D3" s="87">
+        <f t="shared" ref="D3:F3" si="0">IFERROR(D4+D5*60+D6*3600+D7*3600*24+C3,D4+D5*60+D6*3600+D7*3600*24)</f>
+        <v>259200</v>
+      </c>
+      <c r="E3" s="87">
+        <f t="shared" si="0"/>
+        <v>259200</v>
+      </c>
+      <c r="F3" s="87">
+        <f t="shared" si="0"/>
+        <v>259200</v>
+      </c>
+      <c r="G3" s="89"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="B4" s="153" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="86"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="89"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="B5" s="153" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="86"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="83">
+        <v>0</v>
+      </c>
+      <c r="F5" s="88"/>
+      <c r="G5" s="89"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="153" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="127">
+        <v>0</v>
+      </c>
+      <c r="D6" s="84">
+        <v>0</v>
+      </c>
+      <c r="E6" s="83"/>
+      <c r="F6" s="88">
+        <v>0</v>
+      </c>
+      <c r="G6" s="89"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7" s="154" t="s">
+        <v>259</v>
+      </c>
+      <c r="C7" s="106">
+        <v>3</v>
+      </c>
+      <c r="D7" s="107"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="89"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="82">
+        <v>1</v>
+      </c>
+      <c r="B8" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A8+1)</f>
+        <v>Frame 1, +X</v>
+      </c>
+      <c r="C8" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A8+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="92"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="82">
+        <v>2</v>
+      </c>
+      <c r="B9" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A9+1)</f>
+        <v>Frame 2, -X</v>
+      </c>
+      <c r="C9" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A9+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="92"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="82">
+        <v>3</v>
+      </c>
+      <c r="B10" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A10+1)</f>
+        <v>Beam -Y +Z</v>
+      </c>
+      <c r="C10" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A10+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="82">
+        <v>4</v>
+      </c>
+      <c r="B11" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A11+1)</f>
+        <v>Beam +Y +Z</v>
+      </c>
+      <c r="C11" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A11+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="92"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="82">
+        <v>5</v>
+      </c>
+      <c r="B12" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A12+1)</f>
+        <v>Beam +Y -Z</v>
+      </c>
+      <c r="C12" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A12+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="82">
+        <v>6</v>
+      </c>
+      <c r="B13" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A13+1)</f>
+        <v>Beam -Y -Z</v>
+      </c>
+      <c r="C13" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A13+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="92"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="82">
+        <v>7</v>
+      </c>
+      <c r="B14" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A14+1)</f>
+        <v xml:space="preserve">panel +Z, payload plate </v>
+      </c>
+      <c r="C14" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A14+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="92"/>
+      <c r="H14" s="92"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="92"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="82">
+        <v>8</v>
+      </c>
+      <c r="B15" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A15+1)</f>
+        <v xml:space="preserve">LED 1 </v>
+      </c>
+      <c r="C15" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E15" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="F15" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A15+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="92"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="82">
+        <v>9</v>
+      </c>
+      <c r="B16" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A16+1)</f>
+        <v>LED 2</v>
+      </c>
+      <c r="C16" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E16" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="F16" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A16+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="92"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="82">
+        <v>10</v>
+      </c>
+      <c r="B17" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A17+1)</f>
+        <v>LED 3</v>
+      </c>
+      <c r="C17" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E17" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="F17" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A17+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="92"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="92"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="82">
+        <v>11</v>
+      </c>
+      <c r="B18" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A18+1)</f>
+        <v xml:space="preserve">LED 4 </v>
+      </c>
+      <c r="C18" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E18" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
+        <v>200</v>
+      </c>
+      <c r="F18" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A18+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="92"/>
+      <c r="H18" s="92"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="92"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="82">
+        <v>12</v>
+      </c>
+      <c r="B19" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A19+1)</f>
+        <v>Node 12, BMS</v>
+      </c>
+      <c r="C19" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A19+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="92"/>
+      <c r="K19" s="92"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="82">
+        <v>13</v>
+      </c>
+      <c r="B20" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A20+1)</f>
+        <v>Node 13, Batteries Isolation</v>
+      </c>
+      <c r="C20" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A20+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="92"/>
+      <c r="H20" s="92"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="92"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="82">
+        <v>14</v>
+      </c>
+      <c r="B21" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A21+1)</f>
+        <v>Node 14, LiFePo4 1</v>
+      </c>
+      <c r="C21" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A21+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="92"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="82">
+        <v>15</v>
+      </c>
+      <c r="B22" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A22+1)</f>
+        <v>Node 15, LiFePo4 3</v>
+      </c>
+      <c r="C22" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A22+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="92"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="92"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="82">
+        <v>16</v>
+      </c>
+      <c r="B23" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A23+1)</f>
+        <v>Node 16, LiFePo4 2</v>
+      </c>
+      <c r="C23" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A23+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="82">
+        <v>17</v>
+      </c>
+      <c r="B24" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A24+1)</f>
+        <v>Node 17, LiFePo4 4</v>
+      </c>
+      <c r="C24" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A24+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="92"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="82">
+        <v>18</v>
+      </c>
+      <c r="B25" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A25+1)</f>
+        <v>Node 18, Cell Litio 1</v>
+      </c>
+      <c r="C25" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A25+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="92"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="92"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="82">
+        <v>19</v>
+      </c>
+      <c r="B26" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A26+1)</f>
+        <v>Node 19, Cell Litio 2</v>
+      </c>
+      <c r="C26" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A26+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="82">
+        <v>20</v>
+      </c>
+      <c r="B27" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A27+1)</f>
+        <v>Node 20, LoMo</v>
+      </c>
+      <c r="C27" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A27+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="92"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="92"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="82">
+        <v>21</v>
+      </c>
+      <c r="B28" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A28+1)</f>
+        <v>Node 21, Transceiver(Tx-Rx)</v>
+      </c>
+      <c r="C28" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A28+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="92"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="92"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="82">
+        <v>22</v>
+      </c>
+      <c r="B29" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A29+1)</f>
+        <v>Node 22, Antena module</v>
+      </c>
+      <c r="C29" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A29+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="92"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="92"/>
+      <c r="J29" s="92"/>
+      <c r="K29" s="92"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="82">
+        <v>23</v>
+      </c>
+      <c r="B30" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A30+1)</f>
+        <v>Node 23, OBC</v>
+      </c>
+      <c r="C30" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A30+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="92"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="92"/>
+      <c r="J30" s="92"/>
+      <c r="K30" s="92"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="82">
+        <v>24</v>
+      </c>
+      <c r="B31" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A31+1)</f>
+        <v>Node 24, Solar Panel (Y)</v>
+      </c>
+      <c r="C31" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A31+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="92"/>
+      <c r="K31" s="92"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="82">
+        <v>25</v>
+      </c>
+      <c r="B32" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A32+1)</f>
+        <v>Node 25, Solar Panel (-Y)</v>
+      </c>
+      <c r="C32" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A32+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="92"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="92"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="92"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="82">
+        <v>26</v>
+      </c>
+      <c r="B33" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A33+1)</f>
+        <v>Node 26, Solar Panel (X)</v>
+      </c>
+      <c r="C33" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A33+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="92"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="92"/>
+      <c r="J33" s="92"/>
+      <c r="K33" s="92"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="82">
+        <v>27</v>
+      </c>
+      <c r="B34" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A34+1)</f>
+        <v>Node 27, Solar Panel (-X)RBF</v>
+      </c>
+      <c r="C34" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A34+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="92"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="92"/>
+      <c r="K34" s="92"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="82">
+        <v>28</v>
+      </c>
+      <c r="B35" s="90" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A35+1)</f>
+        <v>Node 28, Solar Panel (-Z(antenna))</v>
+      </c>
+      <c r="C35" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A35+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="92"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="92"/>
+    </row>
+    <row r="36" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A36" s="82">
+        <v>29</v>
+      </c>
+      <c r="B36" s="93" t="str">
+        <f>HLOOKUP(B$2,Modes!$B$2:$E$31,$A36+1)</f>
+        <v>Node 29, EPS de alta</v>
+      </c>
+      <c r="C36" s="91">
+        <f>HLOOKUP(C$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="91">
+        <f>HLOOKUP(D$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="91">
+        <f>HLOOKUP(E$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="91">
+        <f>HLOOKUP(F$2,Modes!$B$2:$O$31,$A36+1,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="92"/>
+      <c r="H36" s="92"/>
+      <c r="I36" s="92"/>
+      <c r="J36" s="92"/>
+      <c r="K36" s="92"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="B37" s="80"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13838,6 +13718,756 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B005E130-2D16-4A0C-8BB3-2172273CEA1D}">
+  <dimension ref="B1:O32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:15" ht="15.75" thickBot="1">
+      <c r="B2" s="149" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="111" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="112" t="s">
+        <v>256</v>
+      </c>
+      <c r="E2" s="112" t="s">
+        <v>257</v>
+      </c>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="114"/>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3" s="124" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="115">
+        <v>0</v>
+      </c>
+      <c r="D3" s="116">
+        <v>0</v>
+      </c>
+      <c r="E3" s="116">
+        <v>0</v>
+      </c>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="117"/>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="B4" s="125" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="118">
+        <v>0</v>
+      </c>
+      <c r="D4" s="84">
+        <v>0</v>
+      </c>
+      <c r="E4" s="84">
+        <v>0</v>
+      </c>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="84"/>
+      <c r="O4" s="119"/>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="B5" s="125" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="118">
+        <v>0</v>
+      </c>
+      <c r="D5" s="84">
+        <v>0</v>
+      </c>
+      <c r="E5" s="84">
+        <v>0</v>
+      </c>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="119"/>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="B6" s="125" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="118">
+        <v>0</v>
+      </c>
+      <c r="D6" s="84">
+        <v>0</v>
+      </c>
+      <c r="E6" s="84">
+        <v>0</v>
+      </c>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="84"/>
+      <c r="O6" s="119"/>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="B7" s="125" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="118">
+        <v>0</v>
+      </c>
+      <c r="D7" s="84">
+        <v>0</v>
+      </c>
+      <c r="E7" s="84">
+        <v>0</v>
+      </c>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="84"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="84"/>
+      <c r="O7" s="119"/>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="B8" s="125" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="118">
+        <v>0</v>
+      </c>
+      <c r="D8" s="84">
+        <v>0</v>
+      </c>
+      <c r="E8" s="84">
+        <v>0</v>
+      </c>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="84"/>
+      <c r="J8" s="84"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="84"/>
+      <c r="O8" s="119"/>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="B9" s="125" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="118">
+        <v>0</v>
+      </c>
+      <c r="D9" s="84">
+        <v>0</v>
+      </c>
+      <c r="E9" s="84">
+        <v>0</v>
+      </c>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="84"/>
+      <c r="K9" s="84"/>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="84"/>
+      <c r="O9" s="119"/>
+    </row>
+    <row r="10" spans="2:15">
+      <c r="B10" s="125" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="118">
+        <v>0</v>
+      </c>
+      <c r="D10" s="84">
+        <v>200</v>
+      </c>
+      <c r="E10" s="84">
+        <v>6</v>
+      </c>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="84"/>
+      <c r="M10" s="84"/>
+      <c r="N10" s="84"/>
+      <c r="O10" s="119"/>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="B11" s="125" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="118">
+        <v>0</v>
+      </c>
+      <c r="D11" s="84">
+        <v>200</v>
+      </c>
+      <c r="E11" s="84">
+        <v>6</v>
+      </c>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="84"/>
+      <c r="O11" s="119"/>
+    </row>
+    <row r="12" spans="2:15">
+      <c r="B12" s="125" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="118">
+        <v>0</v>
+      </c>
+      <c r="D12" s="84">
+        <v>200</v>
+      </c>
+      <c r="E12" s="84">
+        <v>6</v>
+      </c>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84"/>
+      <c r="O12" s="119"/>
+    </row>
+    <row r="13" spans="2:15">
+      <c r="B13" s="125" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="118">
+        <v>0</v>
+      </c>
+      <c r="D13" s="84">
+        <v>200</v>
+      </c>
+      <c r="E13" s="84">
+        <v>6</v>
+      </c>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="119"/>
+    </row>
+    <row r="14" spans="2:15">
+      <c r="B14" s="125" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="118">
+        <v>0</v>
+      </c>
+      <c r="D14" s="84">
+        <v>0</v>
+      </c>
+      <c r="E14" s="84">
+        <v>0</v>
+      </c>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="84"/>
+      <c r="O14" s="119"/>
+    </row>
+    <row r="15" spans="2:15">
+      <c r="B15" s="125" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="118">
+        <v>0</v>
+      </c>
+      <c r="D15" s="84">
+        <v>0</v>
+      </c>
+      <c r="E15" s="84">
+        <v>0</v>
+      </c>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="119"/>
+    </row>
+    <row r="16" spans="2:15">
+      <c r="B16" s="125" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" s="118">
+        <v>0</v>
+      </c>
+      <c r="D16" s="84">
+        <v>0</v>
+      </c>
+      <c r="E16" s="84">
+        <v>0</v>
+      </c>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="119"/>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17" s="125" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17" s="118">
+        <v>0</v>
+      </c>
+      <c r="D17" s="84">
+        <v>0</v>
+      </c>
+      <c r="E17" s="84">
+        <v>0</v>
+      </c>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="84"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="119"/>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="B18" s="125" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" s="118">
+        <v>0</v>
+      </c>
+      <c r="D18" s="84">
+        <v>0</v>
+      </c>
+      <c r="E18" s="84">
+        <v>0</v>
+      </c>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="119"/>
+    </row>
+    <row r="19" spans="2:15">
+      <c r="B19" s="125" t="s">
+        <v>229</v>
+      </c>
+      <c r="C19" s="118">
+        <v>0</v>
+      </c>
+      <c r="D19" s="84">
+        <v>0</v>
+      </c>
+      <c r="E19" s="84">
+        <v>0</v>
+      </c>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="119"/>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20" s="125" t="s">
+        <v>230</v>
+      </c>
+      <c r="C20" s="118">
+        <v>0</v>
+      </c>
+      <c r="D20" s="84">
+        <v>0</v>
+      </c>
+      <c r="E20" s="84">
+        <v>0</v>
+      </c>
+      <c r="F20" s="84"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="119"/>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21" s="125" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="118">
+        <v>0</v>
+      </c>
+      <c r="D21" s="84">
+        <v>0</v>
+      </c>
+      <c r="E21" s="84">
+        <v>0</v>
+      </c>
+      <c r="F21" s="84"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="119"/>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22" s="125" t="s">
+        <v>232</v>
+      </c>
+      <c r="C22" s="118">
+        <v>0</v>
+      </c>
+      <c r="D22" s="84">
+        <v>0</v>
+      </c>
+      <c r="E22" s="84">
+        <v>0</v>
+      </c>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="119"/>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23" s="125" t="s">
+        <v>233</v>
+      </c>
+      <c r="C23" s="118">
+        <v>0</v>
+      </c>
+      <c r="D23" s="84">
+        <v>0</v>
+      </c>
+      <c r="E23" s="84">
+        <v>0</v>
+      </c>
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="119"/>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="B24" s="125" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="118">
+        <v>0</v>
+      </c>
+      <c r="D24" s="84">
+        <v>0</v>
+      </c>
+      <c r="E24" s="84">
+        <v>0</v>
+      </c>
+      <c r="F24" s="84"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="84"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="119"/>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="B25" s="125" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" s="118">
+        <v>0</v>
+      </c>
+      <c r="D25" s="84">
+        <v>0</v>
+      </c>
+      <c r="E25" s="84">
+        <v>0</v>
+      </c>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="119"/>
+    </row>
+    <row r="26" spans="2:15">
+      <c r="B26" s="125" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="118">
+        <v>0</v>
+      </c>
+      <c r="D26" s="84">
+        <v>0</v>
+      </c>
+      <c r="E26" s="84">
+        <v>0</v>
+      </c>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="119"/>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="B27" s="125" t="s">
+        <v>237</v>
+      </c>
+      <c r="C27" s="118">
+        <v>0</v>
+      </c>
+      <c r="D27" s="84">
+        <v>0</v>
+      </c>
+      <c r="E27" s="84">
+        <v>0</v>
+      </c>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="119"/>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="B28" s="125" t="s">
+        <v>238</v>
+      </c>
+      <c r="C28" s="118">
+        <v>0</v>
+      </c>
+      <c r="D28" s="84">
+        <v>0</v>
+      </c>
+      <c r="E28" s="84">
+        <v>0</v>
+      </c>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="119"/>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="B29" s="125" t="s">
+        <v>239</v>
+      </c>
+      <c r="C29" s="118">
+        <v>0</v>
+      </c>
+      <c r="D29" s="84">
+        <v>0</v>
+      </c>
+      <c r="E29" s="84">
+        <v>0</v>
+      </c>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="119"/>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="B30" s="125" t="s">
+        <v>240</v>
+      </c>
+      <c r="C30" s="118">
+        <v>0</v>
+      </c>
+      <c r="D30" s="84">
+        <v>0</v>
+      </c>
+      <c r="E30" s="84">
+        <v>0</v>
+      </c>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="119"/>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="B31" s="126" t="s">
+        <v>241</v>
+      </c>
+      <c r="C31" s="122">
+        <v>0</v>
+      </c>
+      <c r="D31" s="107">
+        <v>0</v>
+      </c>
+      <c r="E31" s="107">
+        <v>0</v>
+      </c>
+      <c r="F31" s="107"/>
+      <c r="G31" s="107"/>
+      <c r="H31" s="107"/>
+      <c r="I31" s="107"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="107"/>
+      <c r="L31" s="107"/>
+      <c r="M31" s="107"/>
+      <c r="N31" s="107"/>
+      <c r="O31" s="123"/>
+    </row>
+    <row r="32" spans="2:15">
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="89"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="89"/>
+      <c r="K32" s="89"/>
+      <c r="L32" s="89"/>
+      <c r="M32" s="89"/>
+      <c r="N32" s="89"/>
+      <c r="O32" s="89"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD990"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -14040,7 +14670,7 @@
       </c>
     </row>
     <row r="5" spans="1:30">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="24">
@@ -14139,7 +14769,7 @@
       </c>
     </row>
     <row r="6" spans="1:30">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="23" t="s">
         <v>32</v>
       </c>
       <c r="B6" s="27">
@@ -14239,7 +14869,7 @@
       </c>
     </row>
     <row r="7" spans="1:30">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="23" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="27">
@@ -14336,7 +14966,7 @@
       </c>
     </row>
     <row r="8" spans="1:30">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="23" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="27">
@@ -14434,7 +15064,7 @@
       </c>
     </row>
     <row r="9" spans="1:30">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="23" t="s">
         <v>46</v>
       </c>
       <c r="B9" s="27">
@@ -14533,7 +15163,7 @@
       </c>
     </row>
     <row r="10" spans="1:30">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="23" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="27">
@@ -14633,7 +15263,7 @@
       </c>
     </row>
     <row r="11" spans="1:30">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="23" t="s">
         <v>56</v>
       </c>
       <c r="B11" s="27">
@@ -14736,7 +15366,7 @@
       </c>
     </row>
     <row r="12" spans="1:30">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="23" t="s">
         <v>61</v>
       </c>
       <c r="B12" s="27">
@@ -14835,7 +15465,7 @@
       </c>
     </row>
     <row r="13" spans="1:30">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="23" t="s">
         <v>67</v>
       </c>
       <c r="B13" s="27">
@@ -14935,7 +15565,7 @@
       </c>
     </row>
     <row r="14" spans="1:30">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="23" t="s">
         <v>69</v>
       </c>
       <c r="B14" s="27">
@@ -15036,7 +15666,7 @@
       </c>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="23" t="s">
         <v>71</v>
       </c>
       <c r="B15" s="27">
@@ -15138,7 +15768,7 @@
       </c>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="23" t="s">
         <v>73</v>
       </c>
       <c r="B16" s="27">
@@ -15242,7 +15872,7 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="23" t="s">
         <v>78</v>
       </c>
       <c r="B17" s="27">
@@ -15353,7 +15983,7 @@
       </c>
     </row>
     <row r="18" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="23" t="s">
         <v>83</v>
       </c>
       <c r="B18" s="27">
@@ -15458,7 +16088,7 @@
       </c>
     </row>
     <row r="19" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="23" t="s">
         <v>87</v>
       </c>
       <c r="B19" s="27">
@@ -15564,7 +16194,7 @@
       </c>
     </row>
     <row r="20" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="23" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="27">
@@ -15671,7 +16301,7 @@
       </c>
     </row>
     <row r="21" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="23" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="27">
@@ -15779,7 +16409,7 @@
       </c>
     </row>
     <row r="22" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="23" t="s">
         <v>93</v>
       </c>
       <c r="B22" s="27">
@@ -15888,7 +16518,7 @@
       </c>
     </row>
     <row r="23" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="23" t="s">
         <v>97</v>
       </c>
       <c r="B23" s="27">
@@ -15998,7 +16628,7 @@
       </c>
     </row>
     <row r="24" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="23" t="s">
         <v>99</v>
       </c>
       <c r="B24" s="27">
@@ -16111,7 +16741,7 @@
       </c>
     </row>
     <row r="25" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="23" t="s">
         <v>103</v>
       </c>
       <c r="B25" s="27">
@@ -16223,7 +16853,7 @@
       </c>
     </row>
     <row r="26" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="23" t="s">
         <v>107</v>
       </c>
       <c r="B26" s="27">
@@ -16337,7 +16967,7 @@
       </c>
     </row>
     <row r="27" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="23" t="s">
         <v>112</v>
       </c>
       <c r="B27" s="27">
@@ -16451,7 +17081,7 @@
       </c>
     </row>
     <row r="28" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="23" t="s">
         <v>116</v>
       </c>
       <c r="B28" s="27">
@@ -16566,7 +17196,7 @@
       </c>
     </row>
     <row r="29" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="23" t="s">
         <v>122</v>
       </c>
       <c r="B29" s="27">
@@ -16682,7 +17312,7 @@
       </c>
     </row>
     <row r="30" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="23" t="s">
         <v>127</v>
       </c>
       <c r="B30" s="27">
@@ -16799,7 +17429,7 @@
       </c>
     </row>
     <row r="31" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="23" t="s">
         <v>131</v>
       </c>
       <c r="B31" s="27">
@@ -16917,7 +17547,7 @@
       </c>
     </row>
     <row r="32" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="23" t="s">
         <v>134</v>
       </c>
       <c r="B32" s="27">
@@ -17036,7 +17666,7 @@
       </c>
     </row>
     <row r="33" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="23" t="s">
         <v>139</v>
       </c>
       <c r="B33" s="27">

--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C046AC-85D6-417F-9D79-6143E57E1310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3856FACD-16CC-4A56-9640-7E210D7CB034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones de uso" sheetId="9" r:id="rId1"/>
@@ -459,7 +459,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="287">
   <si>
     <t>Esta tabla representado el struct con todos los datos de entrada que uso para el satélite,¿que le falta? pues el coeficiente Cp (specific heat capacity ) esta bastamente aproximado y habría que mirar material por material, puede que algo de info útil pueda ser encontrada en la tabla de mecánica</t>
   </si>
@@ -1283,9 +1283,6 @@
     <t>Radiation to vacuum: Booleano que define si se va a calcular o no el intercambio de radiación con el vacío circundante. Util para aislar el satélite del entorno y comprobar cumplimiento de la conservación de energía.</t>
   </si>
   <si>
-    <t>Algunos parametros a introducir aquí son: Area radiativa, area que está expuesta al exterior y disponible para radiar o absorber calor .Emisividad y absortancia, valores que representan las capacidades de absorción y emisión del material para espectro completo y infrarrojos respectivamente. Componentes del vector normal, dirreción del vector normal a la superficie externa, usado para calcular angulos de incidencia, debe estar normalizado (módulo 1). Radiación, booleano que determina si un nodo tiene superficie con la que radiar al entorno.</t>
-  </si>
-  <si>
     <t>Operation</t>
   </si>
   <si>
@@ -1508,6 +1505,12 @@
   <si>
     <t xml:space="preserve"> 'Solar Panel (-Y)'</t>
   </si>
+  <si>
+    <t>Display? 1=Yes, 0=No</t>
+  </si>
+  <si>
+    <t>Algunos parametros a introducir aquí son: Area radiativa, area que está expuesta al exterior y disponible para radiar o absorber calor .Emisividad y absortancia, valores que representan las capacidades de absorción y emisión del material para espectro completo y infrarrojos respectivamente. Componentes del vector normal, dirreción del vector normal a la superficie externa, usado para calcular angulos de incidencia, debe estar normalizado (módulo 1). Radiación, booleano que determina si un nodo tiene superficie con la que radiar al entorno. Display, booleano que determina si los nodos serán representados en las gráficas que genere el programa.</t>
+  </si>
 </sst>
 </file>
 
@@ -1519,11 +1522,18 @@
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1821,7 +1831,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="69">
+  <borders count="66">
     <border>
       <left/>
       <right/>
@@ -2287,19 +2297,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -2433,58 +2430,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2715,149 +2660,173 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2869,59 +2838,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2930,207 +2892,223 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="59" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="60" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="62" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="63" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="61" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="64" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="65" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="67" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="68" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="66" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="60" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="64" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="65" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3702,203 +3680,203 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:2" ht="23.25">
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="122" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="30">
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="118" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="5" spans="2:2">
-      <c r="B5" s="126"/>
+      <c r="B5" s="119"/>
     </row>
     <row r="6" spans="2:2" ht="60">
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="118" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="119"/>
+    </row>
+    <row r="8" spans="2:2" ht="15.75">
+      <c r="B8" s="121" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="119"/>
+    </row>
+    <row r="10" spans="2:2" ht="45">
+      <c r="B10" s="118" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="30">
+      <c r="B11" s="118" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="119"/>
+    </row>
+    <row r="13" spans="2:2" ht="15.75">
+      <c r="B13" s="121" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="119"/>
+    </row>
+    <row r="15" spans="2:2" ht="45">
+      <c r="B15" s="118" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="120" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="119" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="119"/>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="120" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="119"/>
+    </row>
+    <row r="23" spans="2:2" ht="30">
+      <c r="B23" s="118" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="119"/>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="120" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="119"/>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="118" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="119"/>
+    </row>
+    <row r="29" spans="2:2" ht="30">
+      <c r="B29" s="118" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="126"/>
-    </row>
-    <row r="8" spans="2:2" ht="15.75">
-      <c r="B8" s="128" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="126"/>
-    </row>
-    <row r="10" spans="2:2" ht="45">
-      <c r="B10" s="125" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" ht="30">
-      <c r="B11" s="125" t="s">
+    <row r="31" spans="2:2" ht="30">
+      <c r="B31" s="118" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="117" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="117" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" ht="60">
+      <c r="B37" s="118" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="131" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="117" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" ht="60">
+      <c r="B43" s="118" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" ht="90">
+      <c r="B45" s="118" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="131" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" ht="52.5" customHeight="1">
+      <c r="B49" s="118" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" ht="60">
+      <c r="B51" s="194" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="131" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" ht="105">
+      <c r="B55" s="118" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="131" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" ht="45">
+      <c r="B59" s="118" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="117" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" ht="45">
+      <c r="B63" s="118" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="15.75">
+      <c r="B65" s="136" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="126"/>
-    </row>
-    <row r="13" spans="2:2" ht="15.75">
-      <c r="B13" s="128" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="126"/>
-    </row>
-    <row r="15" spans="2:2" ht="45">
-      <c r="B15" s="125" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="127" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="126" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="126"/>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="127" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="126"/>
-    </row>
-    <row r="23" spans="2:2" ht="30">
-      <c r="B23" s="125" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="126"/>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" s="127" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="126"/>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" s="125" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="126"/>
-    </row>
-    <row r="29" spans="2:2" ht="30">
-      <c r="B29" s="125" t="s">
+    <row r="67" spans="2:2" ht="75">
+      <c r="B67" s="137" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" ht="30">
-      <c r="B31" s="125" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="124" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="124" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" ht="60">
-      <c r="B37" s="125" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="141" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="124" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" ht="60">
-      <c r="B43" s="125" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" ht="90">
-      <c r="B45" s="125" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="141" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" ht="52.5" customHeight="1">
-      <c r="B49" s="125" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" ht="60">
-      <c r="B51" s="125" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="141" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" ht="105">
-      <c r="B55" s="125" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2">
-      <c r="B57" s="141" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" ht="45">
-      <c r="B59" s="125" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" s="124" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2" ht="45">
-      <c r="B63" s="125" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" ht="15.75">
-      <c r="B65" s="146" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" ht="75">
-      <c r="B67" s="147" t="s">
-        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -10808,10 +10786,10 @@
         <v>149</v>
       </c>
       <c r="G2" s="26"/>
-      <c r="H2" s="189" t="s">
+      <c r="H2" s="178" t="s">
         <v>150</v>
       </c>
-      <c r="I2" s="190"/>
+      <c r="I2" s="179"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="27" t="s">
@@ -11826,25 +11804,25 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:6" ht="45">
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="127" t="s">
         <v>253</v>
       </c>
-      <c r="C2" s="138" t="s">
+      <c r="C2" s="128" t="s">
         <v>254</v>
       </c>
-      <c r="D2" s="138" t="s">
+      <c r="D2" s="128" t="s">
         <v>234</v>
       </c>
-      <c r="E2" s="138" t="s">
+      <c r="E2" s="128" t="s">
         <v>233</v>
       </c>
-      <c r="F2" s="139" t="s">
+      <c r="F2" s="129" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B3" s="113">
-        <v>1</v>
+      <c r="B3" s="106">
+        <v>0</v>
       </c>
       <c r="C3" s="79">
         <v>1</v>
@@ -11855,7 +11833,7 @@
       <c r="E3" s="79">
         <v>300</v>
       </c>
-      <c r="F3" s="114">
+      <c r="F3" s="107">
         <v>1</v>
       </c>
     </row>
@@ -11875,27 +11853,27 @@
   <sheetData>
     <row r="1" spans="2:7" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:7" ht="37.5" customHeight="1">
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="124" t="s">
         <v>237</v>
       </c>
-      <c r="C2" s="135" t="s">
+      <c r="C2" s="125" t="s">
         <v>238</v>
       </c>
-      <c r="D2" s="135" t="s">
+      <c r="D2" s="125" t="s">
         <v>239</v>
       </c>
-      <c r="E2" s="135" t="s">
+      <c r="E2" s="125" t="s">
         <v>240</v>
       </c>
-      <c r="F2" s="135" t="s">
+      <c r="F2" s="125" t="s">
         <v>241</v>
       </c>
-      <c r="G2" s="136" t="s">
+      <c r="G2" s="126" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1">
-      <c r="B3" s="123">
+      <c r="B3" s="116">
         <v>0</v>
       </c>
       <c r="C3" s="89">
@@ -11915,7 +11893,7 @@
       </c>
     </row>
     <row r="5" spans="2:7">
-      <c r="B5" s="122"/>
+      <c r="B5" s="115"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11924,7 +11902,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4985A03E-5096-4337-92A3-24224C69AEFA}">
-  <dimension ref="B1:L32"/>
+  <dimension ref="B1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
@@ -11937,95 +11915,102 @@
     <col min="9" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1"/>
-    <row r="2" spans="2:12" ht="46.5" customHeight="1" thickBot="1">
-      <c r="B2" s="130" t="s">
+    <row r="1" spans="2:13" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:13" ht="46.5" customHeight="1" thickBot="1">
+      <c r="B2" s="123" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="131" t="s">
+      <c r="C2" s="192" t="s">
         <v>215</v>
       </c>
-      <c r="D2" s="132" t="s">
+      <c r="D2" s="184" t="s">
         <v>216</v>
       </c>
-      <c r="E2" s="132" t="s">
+      <c r="E2" s="184" t="s">
         <v>242</v>
       </c>
-      <c r="F2" s="132" t="s">
+      <c r="F2" s="184" t="s">
         <v>217</v>
       </c>
-      <c r="G2" s="132" t="s">
+      <c r="G2" s="184" t="s">
         <v>213</v>
       </c>
-      <c r="H2" s="132" t="s">
+      <c r="H2" s="184" t="s">
         <v>214</v>
       </c>
-      <c r="I2" s="132" t="s">
+      <c r="I2" s="184" t="s">
         <v>218</v>
       </c>
-      <c r="J2" s="132" t="s">
+      <c r="J2" s="184" t="s">
         <v>219</v>
       </c>
-      <c r="K2" s="132" t="s">
+      <c r="K2" s="184" t="s">
         <v>220</v>
       </c>
-      <c r="L2" s="133" t="s">
+      <c r="L2" s="184" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="3" spans="2:12">
-      <c r="B3" s="97" t="s">
-        <v>278</v>
-      </c>
-      <c r="C3" s="94">
+      <c r="M2" s="185" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13">
+      <c r="B3" s="193" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3" s="186">
         <v>4.0280000000000003E-2</v>
       </c>
-      <c r="D3" s="92">
+      <c r="D3" s="187">
         <v>800</v>
       </c>
-      <c r="E3" s="92"/>
-      <c r="F3" s="155">
+      <c r="E3" s="187"/>
+      <c r="F3" s="188">
         <v>4.1389E-3</v>
       </c>
-      <c r="G3" s="156">
+      <c r="G3" s="189">
         <v>0.25</v>
       </c>
-      <c r="H3" s="156">
+      <c r="H3" s="189">
         <v>0.25</v>
       </c>
-      <c r="I3" s="92">
+      <c r="I3" s="187">
         <v>1</v>
       </c>
-      <c r="J3" s="92">
+      <c r="J3" s="187">
         <v>0</v>
       </c>
-      <c r="K3" s="92">
+      <c r="K3" s="187">
         <v>0</v>
       </c>
-      <c r="L3" s="93">
+      <c r="L3" s="187">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="97" t="s">
+      <c r="M3" s="190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" s="182" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="95">
+      <c r="C4" s="191">
         <v>4.0280000000000003E-2</v>
       </c>
       <c r="D4" s="88">
         <v>800</v>
       </c>
       <c r="E4" s="88"/>
-      <c r="F4" s="155">
+      <c r="F4" s="180">
         <v>4.1389E-3</v>
       </c>
-      <c r="G4" s="156">
+      <c r="G4" s="181">
         <v>0.25</v>
       </c>
-      <c r="H4" s="156">
+      <c r="H4" s="181">
         <v>0.25</v>
       </c>
       <c r="I4" s="88">
@@ -12037,28 +12022,31 @@
       <c r="K4" s="88">
         <v>0</v>
       </c>
-      <c r="L4" s="90">
+      <c r="L4" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="97" t="s">
+      <c r="M4" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="182" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="95">
+      <c r="C5" s="191">
         <v>7.2909999999999997E-3</v>
       </c>
       <c r="D5" s="88">
         <v>800</v>
       </c>
       <c r="E5" s="88"/>
-      <c r="F5" s="156">
+      <c r="F5" s="181">
         <v>0</v>
       </c>
-      <c r="G5" s="156">
+      <c r="G5" s="181">
         <v>0.25</v>
       </c>
-      <c r="H5" s="156">
+      <c r="H5" s="181">
         <v>0.25</v>
       </c>
       <c r="I5" s="88">
@@ -12070,28 +12058,31 @@
       <c r="K5" s="88">
         <v>0.70709999999999995</v>
       </c>
-      <c r="L5" s="90">
+      <c r="L5" s="88">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" s="97" t="s">
+      <c r="M5" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="182" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="95">
+      <c r="C6" s="191">
         <v>7.2909999999999997E-3</v>
       </c>
       <c r="D6" s="88">
         <v>800</v>
       </c>
       <c r="E6" s="88"/>
-      <c r="F6" s="156">
+      <c r="F6" s="181">
         <v>0</v>
       </c>
-      <c r="G6" s="156">
+      <c r="G6" s="181">
         <v>0.25</v>
       </c>
-      <c r="H6" s="156">
+      <c r="H6" s="181">
         <v>0.25</v>
       </c>
       <c r="I6" s="88">
@@ -12103,28 +12094,31 @@
       <c r="K6" s="88">
         <v>0.70709999999999995</v>
       </c>
-      <c r="L6" s="90">
+      <c r="L6" s="88">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" s="97" t="s">
+      <c r="M6" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="182" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="95">
+      <c r="C7" s="191">
         <v>6.4250000000000002E-3</v>
       </c>
       <c r="D7" s="88">
         <v>800</v>
       </c>
       <c r="E7" s="88"/>
-      <c r="F7" s="156">
+      <c r="F7" s="181">
         <v>0</v>
       </c>
-      <c r="G7" s="156">
+      <c r="G7" s="181">
         <v>0.25</v>
       </c>
-      <c r="H7" s="156">
+      <c r="H7" s="181">
         <v>0.25</v>
       </c>
       <c r="I7" s="88">
@@ -12136,28 +12130,31 @@
       <c r="K7" s="88">
         <v>-0.70709999999999995</v>
       </c>
-      <c r="L7" s="90">
+      <c r="L7" s="88">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" s="97" t="s">
+      <c r="M7" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="182" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="95">
+      <c r="C8" s="191">
         <v>6.4250000000000002E-3</v>
       </c>
       <c r="D8" s="88">
         <v>800</v>
       </c>
       <c r="E8" s="88"/>
-      <c r="F8" s="156">
+      <c r="F8" s="181">
         <v>0</v>
       </c>
-      <c r="G8" s="156">
+      <c r="G8" s="181">
         <v>0.25</v>
       </c>
-      <c r="H8" s="156">
+      <c r="H8" s="181">
         <v>0.25</v>
       </c>
       <c r="I8" s="88">
@@ -12169,28 +12166,31 @@
       <c r="K8" s="88">
         <v>-0.70709999999999995</v>
       </c>
-      <c r="L8" s="90">
+      <c r="L8" s="88">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" s="97" t="s">
+      <c r="M8" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="95">
+      <c r="C9" s="191">
         <v>2.1919999999999999E-2</v>
       </c>
       <c r="D9" s="88">
         <v>800</v>
       </c>
       <c r="E9" s="88"/>
-      <c r="F9" s="155">
+      <c r="F9" s="180">
         <v>6.8542999999999998E-3</v>
       </c>
-      <c r="G9" s="156">
+      <c r="G9" s="181">
         <v>0.25</v>
       </c>
-      <c r="H9" s="156">
+      <c r="H9" s="181">
         <v>0.25</v>
       </c>
       <c r="I9" s="88">
@@ -12202,28 +12202,31 @@
       <c r="K9" s="88">
         <v>1</v>
       </c>
-      <c r="L9" s="90">
+      <c r="L9" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" s="97" t="s">
+      <c r="M9" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="182" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="95">
+      <c r="C10" s="191">
         <v>1.8E-3</v>
       </c>
       <c r="D10" s="88">
         <v>800</v>
       </c>
       <c r="E10" s="88"/>
-      <c r="F10" s="155">
+      <c r="F10" s="180">
         <v>7.0522E-4</v>
       </c>
-      <c r="G10" s="156">
+      <c r="G10" s="181">
         <v>0.8</v>
       </c>
-      <c r="H10" s="156">
+      <c r="H10" s="181">
         <v>0.8</v>
       </c>
       <c r="I10" s="88">
@@ -12235,28 +12238,31 @@
       <c r="K10" s="88">
         <v>1</v>
       </c>
-      <c r="L10" s="90">
+      <c r="L10" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" s="97" t="s">
+      <c r="M10" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="182" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="95">
+      <c r="C11" s="191">
         <v>1.8E-3</v>
       </c>
       <c r="D11" s="88">
         <v>800</v>
       </c>
       <c r="E11" s="88"/>
-      <c r="F11" s="155">
+      <c r="F11" s="180">
         <v>7.0522E-4</v>
       </c>
-      <c r="G11" s="156">
+      <c r="G11" s="181">
         <v>0.8</v>
       </c>
-      <c r="H11" s="156">
+      <c r="H11" s="181">
         <v>0.8</v>
       </c>
       <c r="I11" s="88">
@@ -12268,28 +12274,31 @@
       <c r="K11" s="88">
         <v>1</v>
       </c>
-      <c r="L11" s="90">
+      <c r="L11" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="B12" s="97" t="s">
+      <c r="M11" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" s="182" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="95">
+      <c r="C12" s="191">
         <v>1.8E-3</v>
       </c>
       <c r="D12" s="88">
         <v>800</v>
       </c>
       <c r="E12" s="88"/>
-      <c r="F12" s="155">
+      <c r="F12" s="180">
         <v>7.0522E-4</v>
       </c>
-      <c r="G12" s="156">
+      <c r="G12" s="181">
         <v>0.8</v>
       </c>
-      <c r="H12" s="156">
+      <c r="H12" s="181">
         <v>0.8</v>
       </c>
       <c r="I12" s="88">
@@ -12301,28 +12310,31 @@
       <c r="K12" s="88">
         <v>1</v>
       </c>
-      <c r="L12" s="90">
+      <c r="L12" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="97" t="s">
+      <c r="M12" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="182" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="95">
+      <c r="C13" s="191">
         <v>1.8E-3</v>
       </c>
       <c r="D13" s="88">
         <v>800</v>
       </c>
       <c r="E13" s="88"/>
-      <c r="F13" s="155">
+      <c r="F13" s="180">
         <v>7.0522E-4</v>
       </c>
-      <c r="G13" s="156">
+      <c r="G13" s="181">
         <v>0.8</v>
       </c>
-      <c r="H13" s="156">
+      <c r="H13" s="181">
         <v>0.8</v>
       </c>
       <c r="I13" s="88">
@@ -12334,28 +12346,31 @@
       <c r="K13" s="88">
         <v>1</v>
       </c>
-      <c r="L13" s="90">
+      <c r="L13" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="97" t="s">
-        <v>279</v>
-      </c>
-      <c r="C14" s="95">
+      <c r="M13" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14" s="182" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" s="191">
         <v>2.375E-2</v>
       </c>
       <c r="D14" s="88">
         <v>600</v>
       </c>
       <c r="E14" s="88"/>
-      <c r="F14" s="155">
+      <c r="F14" s="180">
         <v>1.3284E-3</v>
       </c>
-      <c r="G14" s="156">
+      <c r="G14" s="181">
         <v>0.85</v>
       </c>
-      <c r="H14" s="156">
+      <c r="H14" s="181">
         <v>0.85</v>
       </c>
       <c r="I14" s="88">
@@ -12367,28 +12382,31 @@
       <c r="K14" s="88">
         <v>-1</v>
       </c>
-      <c r="L14" s="90">
+      <c r="L14" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="B15" s="97" t="s">
-        <v>280</v>
-      </c>
-      <c r="C15" s="95">
+      <c r="M14" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15" s="182" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" s="191">
         <v>0.125</v>
       </c>
       <c r="D15" s="88">
         <v>800</v>
       </c>
       <c r="E15" s="88"/>
-      <c r="F15" s="155">
+      <c r="F15" s="180">
         <v>8.2383000000000005E-3</v>
       </c>
-      <c r="G15" s="156">
+      <c r="G15" s="181">
         <v>0.8</v>
       </c>
-      <c r="H15" s="156">
+      <c r="H15" s="181">
         <v>0.8</v>
       </c>
       <c r="I15" s="88">
@@ -12400,28 +12418,31 @@
       <c r="K15" s="88">
         <v>0</v>
       </c>
-      <c r="L15" s="90">
+      <c r="L15" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="B16" s="97" t="s">
-        <v>285</v>
-      </c>
-      <c r="C16" s="95">
+      <c r="M15" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16" s="182" t="s">
+        <v>284</v>
+      </c>
+      <c r="C16" s="191">
         <v>3.9E-2</v>
       </c>
       <c r="D16" s="88">
         <v>600</v>
       </c>
       <c r="E16" s="88"/>
-      <c r="F16" s="155">
+      <c r="F16" s="180">
         <v>8.2383000000000005E-3</v>
       </c>
-      <c r="G16" s="156">
+      <c r="G16" s="181">
         <v>0.8</v>
       </c>
-      <c r="H16" s="156">
+      <c r="H16" s="181">
         <v>0.8</v>
       </c>
       <c r="I16" s="88">
@@ -12433,28 +12454,31 @@
       <c r="K16" s="88">
         <v>0</v>
       </c>
-      <c r="L16" s="90">
+      <c r="L16" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="2:12">
-      <c r="B17" s="97" t="s">
-        <v>282</v>
-      </c>
-      <c r="C17" s="95">
+      <c r="M16" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="B17" s="182" t="s">
+        <v>281</v>
+      </c>
+      <c r="C17" s="191">
         <v>3.9E-2</v>
       </c>
       <c r="D17" s="88">
         <v>600</v>
       </c>
       <c r="E17" s="88"/>
-      <c r="F17" s="155">
+      <c r="F17" s="180">
         <v>8.2383000000000005E-3</v>
       </c>
-      <c r="G17" s="156">
+      <c r="G17" s="181">
         <v>0.8</v>
       </c>
-      <c r="H17" s="156">
+      <c r="H17" s="181">
         <v>0.8</v>
       </c>
       <c r="I17" s="88">
@@ -12466,28 +12490,31 @@
       <c r="K17" s="88">
         <v>1</v>
       </c>
-      <c r="L17" s="90">
+      <c r="L17" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:12">
-      <c r="B18" s="97" t="s">
-        <v>283</v>
-      </c>
-      <c r="C18" s="95">
+      <c r="M17" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" s="182" t="s">
+        <v>282</v>
+      </c>
+      <c r="C18" s="191">
         <v>3.9E-2</v>
       </c>
       <c r="D18" s="88">
         <v>600</v>
       </c>
       <c r="E18" s="88"/>
-      <c r="F18" s="155">
+      <c r="F18" s="180">
         <v>8.2383000000000005E-3</v>
       </c>
-      <c r="G18" s="156">
+      <c r="G18" s="181">
         <v>0.8</v>
       </c>
-      <c r="H18" s="156">
+      <c r="H18" s="181">
         <v>0.8</v>
       </c>
       <c r="I18" s="88">
@@ -12499,28 +12526,31 @@
       <c r="K18" s="88">
         <v>1</v>
       </c>
-      <c r="L18" s="90">
+      <c r="L18" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="2:12">
-      <c r="B19" s="97" t="s">
-        <v>284</v>
-      </c>
-      <c r="C19" s="95">
+      <c r="M18" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" s="182" t="s">
+        <v>283</v>
+      </c>
+      <c r="C19" s="191">
         <v>3.9E-2</v>
       </c>
       <c r="D19" s="88">
         <v>600</v>
       </c>
       <c r="E19" s="88"/>
-      <c r="F19" s="155">
+      <c r="F19" s="180">
         <v>9.8408000000000002E-3</v>
       </c>
-      <c r="G19" s="156">
+      <c r="G19" s="181">
         <v>0.8</v>
       </c>
-      <c r="H19" s="156">
+      <c r="H19" s="181">
         <v>0.8</v>
       </c>
       <c r="I19" s="88">
@@ -12532,13 +12562,16 @@
       <c r="K19" s="88">
         <v>-1</v>
       </c>
-      <c r="L19" s="90">
+      <c r="L19" s="88">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="2:12">
-      <c r="B20" s="97"/>
-      <c r="C20" s="95"/>
+      <c r="M19" s="90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="182"/>
+      <c r="C20" s="191"/>
       <c r="D20" s="88"/>
       <c r="E20" s="88"/>
       <c r="F20" s="88"/>
@@ -12547,11 +12580,12 @@
       <c r="I20" s="88"/>
       <c r="J20" s="88"/>
       <c r="K20" s="88"/>
-      <c r="L20" s="90"/>
-    </row>
-    <row r="21" spans="2:12">
-      <c r="B21" s="97"/>
-      <c r="C21" s="95"/>
+      <c r="L20" s="88"/>
+      <c r="M20" s="90"/>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="182"/>
+      <c r="C21" s="191"/>
       <c r="D21" s="88"/>
       <c r="E21" s="88"/>
       <c r="F21" s="88"/>
@@ -12560,11 +12594,12 @@
       <c r="I21" s="88"/>
       <c r="J21" s="88"/>
       <c r="K21" s="88"/>
-      <c r="L21" s="90"/>
-    </row>
-    <row r="22" spans="2:12">
-      <c r="B22" s="97"/>
-      <c r="C22" s="95"/>
+      <c r="L21" s="88"/>
+      <c r="M21" s="90"/>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="B22" s="182"/>
+      <c r="C22" s="191"/>
       <c r="D22" s="88"/>
       <c r="E22" s="88"/>
       <c r="F22" s="88"/>
@@ -12573,11 +12608,12 @@
       <c r="I22" s="88"/>
       <c r="J22" s="88"/>
       <c r="K22" s="88"/>
-      <c r="L22" s="90"/>
-    </row>
-    <row r="23" spans="2:12">
-      <c r="B23" s="97"/>
-      <c r="C23" s="95"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="90"/>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="B23" s="182"/>
+      <c r="C23" s="191"/>
       <c r="D23" s="88"/>
       <c r="E23" s="88"/>
       <c r="F23" s="88"/>
@@ -12586,11 +12622,12 @@
       <c r="I23" s="88"/>
       <c r="J23" s="88"/>
       <c r="K23" s="88"/>
-      <c r="L23" s="90"/>
-    </row>
-    <row r="24" spans="2:12">
-      <c r="B24" s="97"/>
-      <c r="C24" s="95"/>
+      <c r="L23" s="88"/>
+      <c r="M23" s="90"/>
+    </row>
+    <row r="24" spans="2:13">
+      <c r="B24" s="182"/>
+      <c r="C24" s="191"/>
       <c r="D24" s="88"/>
       <c r="E24" s="88"/>
       <c r="F24" s="88"/>
@@ -12599,11 +12636,12 @@
       <c r="I24" s="88"/>
       <c r="J24" s="88"/>
       <c r="K24" s="88"/>
-      <c r="L24" s="90"/>
-    </row>
-    <row r="25" spans="2:12">
-      <c r="B25" s="97"/>
-      <c r="C25" s="95"/>
+      <c r="L24" s="88"/>
+      <c r="M24" s="90"/>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="B25" s="182"/>
+      <c r="C25" s="191"/>
       <c r="D25" s="88"/>
       <c r="E25" s="88"/>
       <c r="F25" s="88"/>
@@ -12612,11 +12650,12 @@
       <c r="I25" s="88"/>
       <c r="J25" s="88"/>
       <c r="K25" s="88"/>
-      <c r="L25" s="90"/>
-    </row>
-    <row r="26" spans="2:12">
-      <c r="B26" s="97"/>
-      <c r="C26" s="95"/>
+      <c r="L25" s="88"/>
+      <c r="M25" s="90"/>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="B26" s="182"/>
+      <c r="C26" s="191"/>
       <c r="D26" s="88"/>
       <c r="E26" s="88"/>
       <c r="F26" s="88"/>
@@ -12625,11 +12664,12 @@
       <c r="I26" s="88"/>
       <c r="J26" s="88"/>
       <c r="K26" s="88"/>
-      <c r="L26" s="90"/>
-    </row>
-    <row r="27" spans="2:12">
-      <c r="B27" s="97"/>
-      <c r="C27" s="95"/>
+      <c r="L26" s="88"/>
+      <c r="M26" s="90"/>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="B27" s="182"/>
+      <c r="C27" s="191"/>
       <c r="D27" s="88"/>
       <c r="E27" s="88"/>
       <c r="F27" s="88"/>
@@ -12638,11 +12678,12 @@
       <c r="I27" s="88"/>
       <c r="J27" s="88"/>
       <c r="K27" s="88"/>
-      <c r="L27" s="90"/>
-    </row>
-    <row r="28" spans="2:12">
-      <c r="B28" s="97"/>
-      <c r="C28" s="95"/>
+      <c r="L27" s="88"/>
+      <c r="M27" s="90"/>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="B28" s="182"/>
+      <c r="C28" s="191"/>
       <c r="D28" s="88"/>
       <c r="E28" s="88"/>
       <c r="F28" s="88"/>
@@ -12651,11 +12692,12 @@
       <c r="I28" s="88"/>
       <c r="J28" s="88"/>
       <c r="K28" s="88"/>
-      <c r="L28" s="90"/>
-    </row>
-    <row r="29" spans="2:12">
-      <c r="B29" s="97"/>
-      <c r="C29" s="95"/>
+      <c r="L28" s="88"/>
+      <c r="M28" s="90"/>
+    </row>
+    <row r="29" spans="2:13">
+      <c r="B29" s="182"/>
+      <c r="C29" s="191"/>
       <c r="D29" s="88"/>
       <c r="E29" s="88"/>
       <c r="F29" s="88"/>
@@ -12664,11 +12706,12 @@
       <c r="I29" s="88"/>
       <c r="J29" s="88"/>
       <c r="K29" s="88"/>
-      <c r="L29" s="90"/>
-    </row>
-    <row r="30" spans="2:12">
-      <c r="B30" s="97"/>
-      <c r="C30" s="95"/>
+      <c r="L29" s="88"/>
+      <c r="M29" s="90"/>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="B30" s="182"/>
+      <c r="C30" s="191"/>
       <c r="D30" s="88"/>
       <c r="E30" s="88"/>
       <c r="F30" s="88"/>
@@ -12677,11 +12720,12 @@
       <c r="I30" s="88"/>
       <c r="J30" s="88"/>
       <c r="K30" s="88"/>
-      <c r="L30" s="90"/>
-    </row>
-    <row r="31" spans="2:12" ht="15.75" thickBot="1">
-      <c r="B31" s="98"/>
-      <c r="C31" s="96"/>
+      <c r="L30" s="88"/>
+      <c r="M30" s="90"/>
+    </row>
+    <row r="31" spans="2:13" ht="15.75" thickBot="1">
+      <c r="B31" s="183"/>
+      <c r="C31" s="116"/>
       <c r="D31" s="89"/>
       <c r="E31" s="89"/>
       <c r="F31" s="89"/>
@@ -12690,9 +12734,10 @@
       <c r="I31" s="89"/>
       <c r="J31" s="89"/>
       <c r="K31" s="89"/>
-      <c r="L31" s="91"/>
-    </row>
-    <row r="32" spans="2:12">
+      <c r="L31" s="89"/>
+      <c r="M31" s="91"/>
+    </row>
+    <row r="32" spans="2:13">
       <c r="B32" s="74"/>
     </row>
   </sheetData>
@@ -12710,42 +12755,42 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1">
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="132" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="191" t="s">
+      <c r="C2" s="177" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="120" t="s">
+      <c r="D2" s="113" t="s">
         <v>228</v>
       </c>
-      <c r="E2" s="120" t="s">
+      <c r="E2" s="113" t="s">
         <v>227</v>
       </c>
-      <c r="F2" s="121" t="s">
+      <c r="F2" s="114" t="s">
         <v>229</v>
       </c>
-      <c r="G2" s="103"/>
+      <c r="G2" s="96"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="B3" s="143" t="s">
+      <c r="B3" s="133" t="s">
         <v>222</v>
       </c>
       <c r="C3" s="81">
         <f>IFERROR(C4+C5*60+C6*3600+C7*3600*24+B3,C4+C5*60+C6*3600+C7*3600*24)</f>
-        <v>259200</v>
+        <v>3600</v>
       </c>
       <c r="D3" s="81">
         <f t="shared" ref="D3:F3" si="0">IFERROR(D4+D5*60+D6*3600+D7*3600*24+C3,D4+D5*60+D6*3600+D7*3600*24)</f>
-        <v>259200</v>
+        <v>90000</v>
       </c>
       <c r="E3" s="81">
         <f t="shared" si="0"/>
-        <v>259200</v>
+        <v>90000</v>
       </c>
       <c r="F3" s="81">
         <f t="shared" si="0"/>
-        <v>259200</v>
+        <v>90000</v>
       </c>
       <c r="G3" s="83"/>
       <c r="H3" s="75"/>
@@ -12757,7 +12802,7 @@
       <c r="N3" s="75"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="B4" s="144" t="s">
+      <c r="B4" s="134" t="s">
         <v>225</v>
       </c>
       <c r="C4" s="80"/>
@@ -12767,7 +12812,7 @@
       <c r="G4" s="83"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="B5" s="144" t="s">
+      <c r="B5" s="134" t="s">
         <v>224</v>
       </c>
       <c r="C5" s="80"/>
@@ -12779,11 +12824,11 @@
       <c r="G5" s="83"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="B6" s="144" t="s">
+      <c r="B6" s="134" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="119">
-        <v>0</v>
+      <c r="C6" s="112">
+        <v>1</v>
       </c>
       <c r="D6" s="78">
         <v>0</v>
@@ -12795,15 +12840,17 @@
       <c r="G6" s="83"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="B7" s="145" t="s">
+      <c r="B7" s="135" t="s">
         <v>230</v>
       </c>
-      <c r="C7" s="99">
-        <v>3</v>
-      </c>
-      <c r="D7" s="100"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="102"/>
+      <c r="C7" s="92">
+        <v>0</v>
+      </c>
+      <c r="D7" s="93">
+        <v>1</v>
+      </c>
+      <c r="E7" s="94"/>
+      <c r="F7" s="95"/>
       <c r="G7" s="83"/>
     </row>
     <row r="8" spans="1:14">
@@ -13490,58 +13537,58 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:15" ht="15.75" thickBot="1">
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="130" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="104" t="s">
+      <c r="C2" s="97" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="105" t="s">
+      <c r="D2" s="98" t="s">
         <v>227</v>
       </c>
-      <c r="E2" s="105" t="s">
+      <c r="E2" s="98" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="107"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="100"/>
     </row>
     <row r="3" spans="2:15">
-      <c r="B3" s="150" t="s">
+      <c r="B3" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="108">
+      <c r="C3" s="101">
         <v>0</v>
       </c>
-      <c r="D3" s="109">
+      <c r="D3" s="102">
         <v>0</v>
       </c>
-      <c r="E3" s="109">
+      <c r="E3" s="102">
         <v>0</v>
       </c>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="109"/>
-      <c r="L3" s="109"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="110"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="103"/>
     </row>
     <row r="4" spans="2:15">
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="111">
+      <c r="C4" s="104">
         <v>0</v>
       </c>
       <c r="D4" s="78">
@@ -13559,13 +13606,13 @@
       <c r="L4" s="78"/>
       <c r="M4" s="78"/>
       <c r="N4" s="78"/>
-      <c r="O4" s="112"/>
+      <c r="O4" s="105"/>
     </row>
     <row r="5" spans="2:15">
-      <c r="B5" s="151" t="s">
+      <c r="B5" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="111">
+      <c r="C5" s="104">
         <v>0</v>
       </c>
       <c r="D5" s="78">
@@ -13583,13 +13630,13 @@
       <c r="L5" s="78"/>
       <c r="M5" s="78"/>
       <c r="N5" s="78"/>
-      <c r="O5" s="112"/>
+      <c r="O5" s="105"/>
     </row>
     <row r="6" spans="2:15">
-      <c r="B6" s="151" t="s">
+      <c r="B6" s="141" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="111">
+      <c r="C6" s="104">
         <v>0</v>
       </c>
       <c r="D6" s="78">
@@ -13607,13 +13654,13 @@
       <c r="L6" s="78"/>
       <c r="M6" s="78"/>
       <c r="N6" s="78"/>
-      <c r="O6" s="112"/>
+      <c r="O6" s="105"/>
     </row>
     <row r="7" spans="2:15">
-      <c r="B7" s="151" t="s">
+      <c r="B7" s="141" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="111">
+      <c r="C7" s="104">
         <v>0</v>
       </c>
       <c r="D7" s="78">
@@ -13631,13 +13678,13 @@
       <c r="L7" s="78"/>
       <c r="M7" s="78"/>
       <c r="N7" s="78"/>
-      <c r="O7" s="112"/>
+      <c r="O7" s="105"/>
     </row>
     <row r="8" spans="2:15">
-      <c r="B8" s="151" t="s">
+      <c r="B8" s="141" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="111">
+      <c r="C8" s="104">
         <v>0</v>
       </c>
       <c r="D8" s="78">
@@ -13655,13 +13702,13 @@
       <c r="L8" s="78"/>
       <c r="M8" s="78"/>
       <c r="N8" s="78"/>
-      <c r="O8" s="112"/>
+      <c r="O8" s="105"/>
     </row>
     <row r="9" spans="2:15">
-      <c r="B9" s="151" t="s">
+      <c r="B9" s="141" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="111">
+      <c r="C9" s="104">
         <v>0</v>
       </c>
       <c r="D9" s="78">
@@ -13679,13 +13726,13 @@
       <c r="L9" s="78"/>
       <c r="M9" s="78"/>
       <c r="N9" s="78"/>
-      <c r="O9" s="112"/>
+      <c r="O9" s="105"/>
     </row>
     <row r="10" spans="2:15">
-      <c r="B10" s="151" t="s">
+      <c r="B10" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="111">
+      <c r="C10" s="104">
         <v>0</v>
       </c>
       <c r="D10" s="78">
@@ -13703,13 +13750,13 @@
       <c r="L10" s="78"/>
       <c r="M10" s="78"/>
       <c r="N10" s="78"/>
-      <c r="O10" s="112"/>
+      <c r="O10" s="105"/>
     </row>
     <row r="11" spans="2:15">
-      <c r="B11" s="151" t="s">
+      <c r="B11" s="141" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="111">
+      <c r="C11" s="104">
         <v>0</v>
       </c>
       <c r="D11" s="78">
@@ -13727,13 +13774,13 @@
       <c r="L11" s="78"/>
       <c r="M11" s="78"/>
       <c r="N11" s="78"/>
-      <c r="O11" s="112"/>
+      <c r="O11" s="105"/>
     </row>
     <row r="12" spans="2:15">
-      <c r="B12" s="151" t="s">
+      <c r="B12" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="111">
+      <c r="C12" s="104">
         <v>0</v>
       </c>
       <c r="D12" s="78">
@@ -13751,13 +13798,13 @@
       <c r="L12" s="78"/>
       <c r="M12" s="78"/>
       <c r="N12" s="78"/>
-      <c r="O12" s="112"/>
+      <c r="O12" s="105"/>
     </row>
     <row r="13" spans="2:15">
-      <c r="B13" s="151" t="s">
+      <c r="B13" s="141" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="111">
+      <c r="C13" s="104">
         <v>0</v>
       </c>
       <c r="D13" s="78">
@@ -13775,13 +13822,13 @@
       <c r="L13" s="78"/>
       <c r="M13" s="78"/>
       <c r="N13" s="78"/>
-      <c r="O13" s="112"/>
+      <c r="O13" s="105"/>
     </row>
     <row r="14" spans="2:15">
-      <c r="B14" s="152" t="s">
-        <v>279</v>
-      </c>
-      <c r="C14" s="111">
+      <c r="B14" s="142" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" s="104">
         <v>0</v>
       </c>
       <c r="D14" s="78">
@@ -13799,13 +13846,13 @@
       <c r="L14" s="78"/>
       <c r="M14" s="78"/>
       <c r="N14" s="78"/>
-      <c r="O14" s="112"/>
+      <c r="O14" s="105"/>
     </row>
     <row r="15" spans="2:15">
-      <c r="B15" s="153" t="s">
-        <v>280</v>
-      </c>
-      <c r="C15" s="111">
+      <c r="B15" s="143" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" s="104">
         <v>0</v>
       </c>
       <c r="D15" s="78">
@@ -13823,13 +13870,13 @@
       <c r="L15" s="78"/>
       <c r="M15" s="78"/>
       <c r="N15" s="78"/>
-      <c r="O15" s="112"/>
+      <c r="O15" s="105"/>
     </row>
     <row r="16" spans="2:15">
-      <c r="B16" s="153" t="s">
-        <v>281</v>
-      </c>
-      <c r="C16" s="111">
+      <c r="B16" s="143" t="s">
+        <v>280</v>
+      </c>
+      <c r="C16" s="104">
         <v>0</v>
       </c>
       <c r="D16" s="78">
@@ -13847,13 +13894,13 @@
       <c r="L16" s="78"/>
       <c r="M16" s="78"/>
       <c r="N16" s="78"/>
-      <c r="O16" s="112"/>
+      <c r="O16" s="105"/>
     </row>
     <row r="17" spans="2:15">
-      <c r="B17" s="153" t="s">
-        <v>282</v>
-      </c>
-      <c r="C17" s="111">
+      <c r="B17" s="143" t="s">
+        <v>281</v>
+      </c>
+      <c r="C17" s="104">
         <v>0</v>
       </c>
       <c r="D17" s="78">
@@ -13871,13 +13918,13 @@
       <c r="L17" s="78"/>
       <c r="M17" s="78"/>
       <c r="N17" s="78"/>
-      <c r="O17" s="112"/>
+      <c r="O17" s="105"/>
     </row>
     <row r="18" spans="2:15">
-      <c r="B18" s="153" t="s">
-        <v>283</v>
-      </c>
-      <c r="C18" s="111">
+      <c r="B18" s="143" t="s">
+        <v>282</v>
+      </c>
+      <c r="C18" s="104">
         <v>0</v>
       </c>
       <c r="D18" s="78">
@@ -13895,13 +13942,13 @@
       <c r="L18" s="78"/>
       <c r="M18" s="78"/>
       <c r="N18" s="78"/>
-      <c r="O18" s="112"/>
+      <c r="O18" s="105"/>
     </row>
     <row r="19" spans="2:15">
-      <c r="B19" s="154" t="s">
-        <v>284</v>
-      </c>
-      <c r="C19" s="111">
+      <c r="B19" s="144" t="s">
+        <v>283</v>
+      </c>
+      <c r="C19" s="104">
         <v>0</v>
       </c>
       <c r="D19" s="78">
@@ -13919,11 +13966,11 @@
       <c r="L19" s="78"/>
       <c r="M19" s="78"/>
       <c r="N19" s="78"/>
-      <c r="O19" s="112"/>
+      <c r="O19" s="105"/>
     </row>
     <row r="20" spans="2:15">
-      <c r="B20" s="117"/>
-      <c r="C20" s="111"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="104"/>
       <c r="D20" s="78"/>
       <c r="E20" s="78"/>
       <c r="F20" s="78"/>
@@ -13935,11 +13982,11 @@
       <c r="L20" s="78"/>
       <c r="M20" s="78"/>
       <c r="N20" s="78"/>
-      <c r="O20" s="112"/>
+      <c r="O20" s="105"/>
     </row>
     <row r="21" spans="2:15">
-      <c r="B21" s="117"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="110"/>
+      <c r="C21" s="104"/>
       <c r="D21" s="78"/>
       <c r="E21" s="78"/>
       <c r="F21" s="78"/>
@@ -13951,11 +13998,11 @@
       <c r="L21" s="78"/>
       <c r="M21" s="78"/>
       <c r="N21" s="78"/>
-      <c r="O21" s="112"/>
+      <c r="O21" s="105"/>
     </row>
     <row r="22" spans="2:15">
-      <c r="B22" s="117"/>
-      <c r="C22" s="111"/>
+      <c r="B22" s="110"/>
+      <c r="C22" s="104"/>
       <c r="D22" s="78"/>
       <c r="E22" s="78"/>
       <c r="F22" s="78"/>
@@ -13967,11 +14014,11 @@
       <c r="L22" s="78"/>
       <c r="M22" s="78"/>
       <c r="N22" s="78"/>
-      <c r="O22" s="112"/>
+      <c r="O22" s="105"/>
     </row>
     <row r="23" spans="2:15">
-      <c r="B23" s="117"/>
-      <c r="C23" s="111"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="104"/>
       <c r="D23" s="78"/>
       <c r="E23" s="78"/>
       <c r="F23" s="78"/>
@@ -13983,11 +14030,11 @@
       <c r="L23" s="78"/>
       <c r="M23" s="78"/>
       <c r="N23" s="78"/>
-      <c r="O23" s="112"/>
+      <c r="O23" s="105"/>
     </row>
     <row r="24" spans="2:15">
-      <c r="B24" s="117"/>
-      <c r="C24" s="111"/>
+      <c r="B24" s="110"/>
+      <c r="C24" s="104"/>
       <c r="D24" s="78"/>
       <c r="E24" s="78"/>
       <c r="F24" s="78"/>
@@ -13999,11 +14046,11 @@
       <c r="L24" s="78"/>
       <c r="M24" s="78"/>
       <c r="N24" s="78"/>
-      <c r="O24" s="112"/>
+      <c r="O24" s="105"/>
     </row>
     <row r="25" spans="2:15">
-      <c r="B25" s="117"/>
-      <c r="C25" s="111"/>
+      <c r="B25" s="110"/>
+      <c r="C25" s="104"/>
       <c r="D25" s="78"/>
       <c r="E25" s="78"/>
       <c r="F25" s="78"/>
@@ -14015,11 +14062,11 @@
       <c r="L25" s="78"/>
       <c r="M25" s="78"/>
       <c r="N25" s="78"/>
-      <c r="O25" s="112"/>
+      <c r="O25" s="105"/>
     </row>
     <row r="26" spans="2:15">
-      <c r="B26" s="117"/>
-      <c r="C26" s="111"/>
+      <c r="B26" s="110"/>
+      <c r="C26" s="104"/>
       <c r="D26" s="78"/>
       <c r="E26" s="78"/>
       <c r="F26" s="78"/>
@@ -14031,11 +14078,11 @@
       <c r="L26" s="78"/>
       <c r="M26" s="78"/>
       <c r="N26" s="78"/>
-      <c r="O26" s="112"/>
+      <c r="O26" s="105"/>
     </row>
     <row r="27" spans="2:15">
-      <c r="B27" s="117"/>
-      <c r="C27" s="111"/>
+      <c r="B27" s="110"/>
+      <c r="C27" s="104"/>
       <c r="D27" s="78"/>
       <c r="E27" s="78"/>
       <c r="F27" s="78"/>
@@ -14047,11 +14094,11 @@
       <c r="L27" s="78"/>
       <c r="M27" s="78"/>
       <c r="N27" s="78"/>
-      <c r="O27" s="112"/>
+      <c r="O27" s="105"/>
     </row>
     <row r="28" spans="2:15">
-      <c r="B28" s="117"/>
-      <c r="C28" s="111"/>
+      <c r="B28" s="110"/>
+      <c r="C28" s="104"/>
       <c r="D28" s="78"/>
       <c r="E28" s="78"/>
       <c r="F28" s="78"/>
@@ -14063,11 +14110,11 @@
       <c r="L28" s="78"/>
       <c r="M28" s="78"/>
       <c r="N28" s="78"/>
-      <c r="O28" s="112"/>
+      <c r="O28" s="105"/>
     </row>
     <row r="29" spans="2:15">
-      <c r="B29" s="117"/>
-      <c r="C29" s="111"/>
+      <c r="B29" s="110"/>
+      <c r="C29" s="104"/>
       <c r="D29" s="78"/>
       <c r="E29" s="78"/>
       <c r="F29" s="78"/>
@@ -14079,11 +14126,11 @@
       <c r="L29" s="78"/>
       <c r="M29" s="78"/>
       <c r="N29" s="78"/>
-      <c r="O29" s="112"/>
+      <c r="O29" s="105"/>
     </row>
     <row r="30" spans="2:15">
-      <c r="B30" s="117"/>
-      <c r="C30" s="111"/>
+      <c r="B30" s="110"/>
+      <c r="C30" s="104"/>
       <c r="D30" s="78"/>
       <c r="E30" s="78"/>
       <c r="F30" s="78"/>
@@ -14095,23 +14142,23 @@
       <c r="L30" s="78"/>
       <c r="M30" s="78"/>
       <c r="N30" s="78"/>
-      <c r="O30" s="112"/>
+      <c r="O30" s="105"/>
     </row>
     <row r="31" spans="2:15">
-      <c r="B31" s="118"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="100"/>
-      <c r="H31" s="100"/>
-      <c r="I31" s="100"/>
-      <c r="J31" s="100"/>
-      <c r="K31" s="100"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="100"/>
-      <c r="N31" s="100"/>
-      <c r="O31" s="116"/>
+      <c r="B31" s="111"/>
+      <c r="C31" s="108"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93"/>
+      <c r="J31" s="93"/>
+      <c r="K31" s="93"/>
+      <c r="L31" s="93"/>
+      <c r="M31" s="93"/>
+      <c r="N31" s="93"/>
+      <c r="O31" s="109"/>
     </row>
     <row r="32" spans="2:15">
       <c r="B32" s="83"/>
@@ -14260,1612 +14307,1612 @@
       <c r="AD3" s="21"/>
     </row>
     <row r="4" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="145" t="s">
         <v>145</v>
       </c>
-      <c r="B4" s="158" t="s">
+      <c r="B4" s="146" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" s="139" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="139" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="139" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="139" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="139" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="139" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="139" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" s="139" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" s="139" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" s="139" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4" s="147" t="s">
         <v>278</v>
       </c>
-      <c r="C4" s="149" t="s">
+      <c r="N4" s="139" t="s">
+        <v>117</v>
+      </c>
+      <c r="O4" s="139" t="s">
+        <v>123</v>
+      </c>
+      <c r="P4" s="139" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q4" s="139" t="s">
+        <v>132</v>
+      </c>
+      <c r="R4" s="139" t="s">
+        <v>135</v>
+      </c>
+      <c r="S4" s="148"/>
+      <c r="T4" s="148"/>
+      <c r="U4" s="148"/>
+      <c r="V4" s="148"/>
+      <c r="W4" s="148"/>
+      <c r="X4" s="148"/>
+      <c r="Y4" s="148"/>
+      <c r="Z4" s="148"/>
+      <c r="AA4" s="148"/>
+      <c r="AB4" s="148"/>
+      <c r="AC4" s="148"/>
+      <c r="AD4" s="149"/>
+    </row>
+    <row r="5" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A5" s="150" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="151">
+        <v>0</v>
+      </c>
+      <c r="C5" s="152">
+        <v>0</v>
+      </c>
+      <c r="D5" s="153">
+        <v>0.37</v>
+      </c>
+      <c r="E5" s="153">
+        <v>0.37</v>
+      </c>
+      <c r="F5" s="153">
+        <v>0.37</v>
+      </c>
+      <c r="G5" s="153">
+        <v>0.37</v>
+      </c>
+      <c r="H5" s="154">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="I5" s="152">
+        <v>0</v>
+      </c>
+      <c r="J5" s="152">
+        <v>0</v>
+      </c>
+      <c r="K5" s="152">
+        <v>0</v>
+      </c>
+      <c r="L5" s="152">
+        <v>0</v>
+      </c>
+      <c r="M5" s="155">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="N5" s="152">
+        <v>0</v>
+      </c>
+      <c r="O5" s="152">
+        <v>0</v>
+      </c>
+      <c r="P5" s="156">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="Q5" s="152">
+        <v>0</v>
+      </c>
+      <c r="R5" s="156">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="S5" s="157"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="158"/>
+      <c r="V5" s="158"/>
+      <c r="W5" s="158"/>
+      <c r="X5" s="158"/>
+      <c r="Y5" s="158"/>
+      <c r="Z5" s="158"/>
+      <c r="AA5" s="158"/>
+      <c r="AB5" s="158"/>
+      <c r="AC5" s="158"/>
+      <c r="AD5" s="158"/>
+    </row>
+    <row r="6" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A6" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="149" t="s">
+      <c r="B6" s="159">
+        <v>0</v>
+      </c>
+      <c r="C6" s="160">
+        <v>0</v>
+      </c>
+      <c r="D6" s="161">
+        <v>0.37</v>
+      </c>
+      <c r="E6" s="161">
+        <v>0.37</v>
+      </c>
+      <c r="F6" s="161">
+        <v>0.37</v>
+      </c>
+      <c r="G6" s="161">
+        <v>0.37</v>
+      </c>
+      <c r="H6" s="155">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="I6" s="160">
+        <v>0</v>
+      </c>
+      <c r="J6" s="160">
+        <v>0</v>
+      </c>
+      <c r="K6" s="160">
+        <v>0</v>
+      </c>
+      <c r="L6" s="160">
+        <v>0</v>
+      </c>
+      <c r="M6" s="155">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="N6" s="160">
+        <v>0</v>
+      </c>
+      <c r="O6" s="160">
+        <v>0</v>
+      </c>
+      <c r="P6" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="162">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="R6" s="160">
+        <v>0</v>
+      </c>
+      <c r="S6" s="163"/>
+      <c r="T6" s="138"/>
+      <c r="U6" s="138"/>
+      <c r="V6" s="138"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="138"/>
+      <c r="Y6" s="138"/>
+      <c r="Z6" s="138"/>
+      <c r="AA6" s="138"/>
+      <c r="AB6" s="138"/>
+      <c r="AC6" s="138"/>
+      <c r="AD6" s="138"/>
+    </row>
+    <row r="7" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A7" s="150" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="149" t="s">
+      <c r="B7" s="164">
+        <v>0.37</v>
+      </c>
+      <c r="C7" s="161">
+        <v>0.37</v>
+      </c>
+      <c r="D7" s="160">
+        <v>0</v>
+      </c>
+      <c r="E7" s="160">
+        <v>0</v>
+      </c>
+      <c r="F7" s="160">
+        <v>0</v>
+      </c>
+      <c r="G7" s="160">
+        <v>0</v>
+      </c>
+      <c r="H7" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="I7" s="160">
+        <v>0</v>
+      </c>
+      <c r="J7" s="160">
+        <v>0</v>
+      </c>
+      <c r="K7" s="160">
+        <v>0</v>
+      </c>
+      <c r="L7" s="160">
+        <v>0</v>
+      </c>
+      <c r="M7" s="166">
+        <v>0</v>
+      </c>
+      <c r="N7" s="160">
+        <v>0</v>
+      </c>
+      <c r="O7" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="P7" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="160">
+        <v>0</v>
+      </c>
+      <c r="R7" s="160">
+        <v>0</v>
+      </c>
+      <c r="S7" s="163"/>
+      <c r="T7" s="138"/>
+      <c r="U7" s="138"/>
+      <c r="V7" s="138"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="138"/>
+      <c r="Y7" s="138"/>
+      <c r="Z7" s="138"/>
+      <c r="AA7" s="138"/>
+      <c r="AB7" s="138"/>
+      <c r="AC7" s="138"/>
+      <c r="AD7" s="138"/>
+    </row>
+    <row r="8" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A8" s="150" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="149" t="s">
+      <c r="B8" s="164">
+        <v>0.37</v>
+      </c>
+      <c r="C8" s="161">
+        <v>0.37</v>
+      </c>
+      <c r="D8" s="160">
+        <v>0</v>
+      </c>
+      <c r="E8" s="160">
+        <v>0</v>
+      </c>
+      <c r="F8" s="160">
+        <v>0</v>
+      </c>
+      <c r="G8" s="160">
+        <v>0</v>
+      </c>
+      <c r="H8" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="I8" s="160">
+        <v>0</v>
+      </c>
+      <c r="J8" s="160">
+        <v>0</v>
+      </c>
+      <c r="K8" s="160">
+        <v>0</v>
+      </c>
+      <c r="L8" s="160">
+        <v>0</v>
+      </c>
+      <c r="M8" s="166">
+        <v>0</v>
+      </c>
+      <c r="N8" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="O8" s="160">
+        <v>0</v>
+      </c>
+      <c r="P8" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="160">
+        <v>0</v>
+      </c>
+      <c r="R8" s="160">
+        <v>0</v>
+      </c>
+      <c r="S8" s="163"/>
+      <c r="T8" s="138"/>
+      <c r="U8" s="138"/>
+      <c r="V8" s="138"/>
+      <c r="W8" s="138"/>
+      <c r="X8" s="138"/>
+      <c r="Y8" s="138"/>
+      <c r="Z8" s="138"/>
+      <c r="AA8" s="138"/>
+      <c r="AB8" s="138"/>
+      <c r="AC8" s="138"/>
+      <c r="AD8" s="138"/>
+    </row>
+    <row r="9" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A9" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="149" t="s">
+      <c r="B9" s="164">
+        <v>0.37</v>
+      </c>
+      <c r="C9" s="161">
+        <v>0.37</v>
+      </c>
+      <c r="D9" s="160">
+        <v>0</v>
+      </c>
+      <c r="E9" s="160">
+        <v>0</v>
+      </c>
+      <c r="F9" s="160">
+        <v>0</v>
+      </c>
+      <c r="G9" s="160">
+        <v>0</v>
+      </c>
+      <c r="H9" s="160">
+        <v>0</v>
+      </c>
+      <c r="I9" s="160">
+        <v>0</v>
+      </c>
+      <c r="J9" s="160">
+        <v>0</v>
+      </c>
+      <c r="K9" s="160">
+        <v>0</v>
+      </c>
+      <c r="L9" s="160">
+        <v>0</v>
+      </c>
+      <c r="M9" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="N9" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="O9" s="160">
+        <v>0</v>
+      </c>
+      <c r="P9" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="160">
+        <v>0</v>
+      </c>
+      <c r="R9" s="160">
+        <v>0</v>
+      </c>
+      <c r="S9" s="163"/>
+      <c r="T9" s="138"/>
+      <c r="U9" s="138"/>
+      <c r="V9" s="138"/>
+      <c r="W9" s="138"/>
+      <c r="X9" s="138"/>
+      <c r="Y9" s="138"/>
+      <c r="Z9" s="138"/>
+      <c r="AA9" s="138"/>
+      <c r="AB9" s="138"/>
+      <c r="AC9" s="138"/>
+      <c r="AD9" s="138"/>
+    </row>
+    <row r="10" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A10" s="150" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="149" t="s">
+      <c r="B10" s="164">
+        <v>0.37</v>
+      </c>
+      <c r="C10" s="161">
+        <v>0.37</v>
+      </c>
+      <c r="D10" s="160">
+        <v>0</v>
+      </c>
+      <c r="E10" s="160">
+        <v>0</v>
+      </c>
+      <c r="F10" s="160">
+        <v>0</v>
+      </c>
+      <c r="G10" s="160">
+        <v>0</v>
+      </c>
+      <c r="H10" s="160">
+        <v>0</v>
+      </c>
+      <c r="I10" s="160">
+        <v>0</v>
+      </c>
+      <c r="J10" s="160">
+        <v>0</v>
+      </c>
+      <c r="K10" s="160">
+        <v>0</v>
+      </c>
+      <c r="L10" s="160">
+        <v>0</v>
+      </c>
+      <c r="M10" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="N10" s="160">
+        <v>0</v>
+      </c>
+      <c r="O10" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="P10" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="160">
+        <v>0</v>
+      </c>
+      <c r="R10" s="160">
+        <v>0</v>
+      </c>
+      <c r="S10" s="163"/>
+      <c r="T10" s="138"/>
+      <c r="U10" s="138"/>
+      <c r="V10" s="138"/>
+      <c r="W10" s="138"/>
+      <c r="X10" s="138"/>
+      <c r="Y10" s="138"/>
+      <c r="Z10" s="138"/>
+      <c r="AA10" s="138"/>
+      <c r="AB10" s="138"/>
+      <c r="AC10" s="138"/>
+      <c r="AD10" s="138"/>
+    </row>
+    <row r="11" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A11" s="150" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="149" t="s">
+      <c r="B11" s="167">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="C11" s="155">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D11" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="E11" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="F11" s="160">
+        <v>0</v>
+      </c>
+      <c r="G11" s="160">
+        <v>0</v>
+      </c>
+      <c r="H11" s="160">
+        <v>0</v>
+      </c>
+      <c r="I11" s="168">
+        <v>5.6840000000000002</v>
+      </c>
+      <c r="J11" s="168">
+        <v>5.6840000000000002</v>
+      </c>
+      <c r="K11" s="168">
+        <v>5.6840000000000002</v>
+      </c>
+      <c r="L11" s="168">
+        <v>5.6840000000000002</v>
+      </c>
+      <c r="M11" s="160">
+        <v>0</v>
+      </c>
+      <c r="N11" s="160">
+        <v>0</v>
+      </c>
+      <c r="O11" s="160">
+        <v>0</v>
+      </c>
+      <c r="P11" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="160">
+        <v>0</v>
+      </c>
+      <c r="R11" s="169">
+        <v>0</v>
+      </c>
+      <c r="S11" s="163"/>
+      <c r="T11" s="138"/>
+      <c r="U11" s="138"/>
+      <c r="V11" s="138"/>
+      <c r="W11" s="138"/>
+      <c r="X11" s="138"/>
+      <c r="Y11" s="138"/>
+      <c r="Z11" s="138"/>
+      <c r="AA11" s="138"/>
+      <c r="AB11" s="138"/>
+      <c r="AC11" s="138"/>
+      <c r="AD11" s="138"/>
+    </row>
+    <row r="12" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A12" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="J4" s="149" t="s">
+      <c r="B12" s="159">
+        <v>0</v>
+      </c>
+      <c r="C12" s="160">
+        <v>0</v>
+      </c>
+      <c r="D12" s="160">
+        <v>0</v>
+      </c>
+      <c r="E12" s="160">
+        <v>0</v>
+      </c>
+      <c r="F12" s="160">
+        <v>0</v>
+      </c>
+      <c r="G12" s="160">
+        <v>0</v>
+      </c>
+      <c r="H12" s="168">
+        <v>5.6840000000000002</v>
+      </c>
+      <c r="I12" s="160">
+        <v>0</v>
+      </c>
+      <c r="J12" s="160">
+        <v>0</v>
+      </c>
+      <c r="K12" s="160">
+        <v>0</v>
+      </c>
+      <c r="L12" s="160">
+        <v>0</v>
+      </c>
+      <c r="M12" s="160">
+        <v>0</v>
+      </c>
+      <c r="N12" s="160">
+        <v>0</v>
+      </c>
+      <c r="O12" s="160">
+        <v>0</v>
+      </c>
+      <c r="P12" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="160">
+        <v>0</v>
+      </c>
+      <c r="R12" s="169">
+        <v>0</v>
+      </c>
+      <c r="S12" s="163"/>
+      <c r="T12" s="138"/>
+      <c r="U12" s="138"/>
+      <c r="V12" s="138"/>
+      <c r="W12" s="138"/>
+      <c r="X12" s="138"/>
+      <c r="Y12" s="138"/>
+      <c r="Z12" s="138"/>
+      <c r="AA12" s="138"/>
+      <c r="AB12" s="138"/>
+      <c r="AC12" s="138"/>
+      <c r="AD12" s="138"/>
+    </row>
+    <row r="13" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A13" s="150" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="149" t="s">
+      <c r="B13" s="159">
+        <v>0</v>
+      </c>
+      <c r="C13" s="160">
+        <v>0</v>
+      </c>
+      <c r="D13" s="160">
+        <v>0</v>
+      </c>
+      <c r="E13" s="160">
+        <v>0</v>
+      </c>
+      <c r="F13" s="160">
+        <v>0</v>
+      </c>
+      <c r="G13" s="160">
+        <v>0</v>
+      </c>
+      <c r="H13" s="168">
+        <v>5.6840000000000002</v>
+      </c>
+      <c r="I13" s="160">
+        <v>0</v>
+      </c>
+      <c r="J13" s="160">
+        <v>0</v>
+      </c>
+      <c r="K13" s="160">
+        <v>0</v>
+      </c>
+      <c r="L13" s="160">
+        <v>0</v>
+      </c>
+      <c r="M13" s="160">
+        <v>0</v>
+      </c>
+      <c r="N13" s="160">
+        <v>0</v>
+      </c>
+      <c r="O13" s="160">
+        <v>0</v>
+      </c>
+      <c r="P13" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="160">
+        <v>0</v>
+      </c>
+      <c r="R13" s="169">
+        <v>0</v>
+      </c>
+      <c r="S13" s="163"/>
+      <c r="T13" s="138"/>
+      <c r="U13" s="138"/>
+      <c r="V13" s="138"/>
+      <c r="W13" s="138"/>
+      <c r="X13" s="138"/>
+      <c r="Y13" s="138"/>
+      <c r="Z13" s="138"/>
+      <c r="AA13" s="138"/>
+      <c r="AB13" s="138"/>
+      <c r="AC13" s="138"/>
+      <c r="AD13" s="138"/>
+    </row>
+    <row r="14" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A14" s="150" t="s">
         <v>70</v>
       </c>
-      <c r="L4" s="149" t="s">
+      <c r="B14" s="159">
+        <v>0</v>
+      </c>
+      <c r="C14" s="160">
+        <v>0</v>
+      </c>
+      <c r="D14" s="160">
+        <v>0</v>
+      </c>
+      <c r="E14" s="160">
+        <v>0</v>
+      </c>
+      <c r="F14" s="160">
+        <v>0</v>
+      </c>
+      <c r="G14" s="160">
+        <v>0</v>
+      </c>
+      <c r="H14" s="168">
+        <v>5.6840000000000002</v>
+      </c>
+      <c r="I14" s="160">
+        <v>0</v>
+      </c>
+      <c r="J14" s="160">
+        <v>0</v>
+      </c>
+      <c r="K14" s="160">
+        <v>0</v>
+      </c>
+      <c r="L14" s="160">
+        <v>0</v>
+      </c>
+      <c r="M14" s="160">
+        <v>0</v>
+      </c>
+      <c r="N14" s="160">
+        <v>0</v>
+      </c>
+      <c r="O14" s="160">
+        <v>0</v>
+      </c>
+      <c r="P14" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="160">
+        <v>0</v>
+      </c>
+      <c r="R14" s="169">
+        <v>0</v>
+      </c>
+      <c r="S14" s="163"/>
+      <c r="T14" s="138"/>
+      <c r="U14" s="138"/>
+      <c r="V14" s="138"/>
+      <c r="W14" s="138"/>
+      <c r="X14" s="138"/>
+      <c r="Y14" s="138"/>
+      <c r="Z14" s="138"/>
+      <c r="AA14" s="138"/>
+      <c r="AB14" s="138"/>
+      <c r="AC14" s="138"/>
+      <c r="AD14" s="138"/>
+    </row>
+    <row r="15" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A15" s="150" t="s">
         <v>72</v>
       </c>
-      <c r="M4" s="159" t="s">
+      <c r="B15" s="159">
+        <v>0</v>
+      </c>
+      <c r="C15" s="160">
+        <v>0</v>
+      </c>
+      <c r="D15" s="160">
+        <v>0</v>
+      </c>
+      <c r="E15" s="160">
+        <v>0</v>
+      </c>
+      <c r="F15" s="160">
+        <v>0</v>
+      </c>
+      <c r="G15" s="160">
+        <v>0</v>
+      </c>
+      <c r="H15" s="168">
+        <v>5.6840000000000002</v>
+      </c>
+      <c r="I15" s="160">
+        <v>0</v>
+      </c>
+      <c r="J15" s="160">
+        <v>0</v>
+      </c>
+      <c r="K15" s="160">
+        <v>0</v>
+      </c>
+      <c r="L15" s="160">
+        <v>0</v>
+      </c>
+      <c r="M15" s="160">
+        <v>0</v>
+      </c>
+      <c r="N15" s="160">
+        <v>0</v>
+      </c>
+      <c r="O15" s="160">
+        <v>0</v>
+      </c>
+      <c r="P15" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="160">
+        <v>0</v>
+      </c>
+      <c r="R15" s="169">
+        <v>0</v>
+      </c>
+      <c r="S15" s="163"/>
+      <c r="T15" s="138"/>
+      <c r="U15" s="138"/>
+      <c r="V15" s="138"/>
+      <c r="W15" s="138"/>
+      <c r="X15" s="138"/>
+      <c r="Y15" s="138"/>
+      <c r="Z15" s="138"/>
+      <c r="AA15" s="138"/>
+      <c r="AB15" s="138"/>
+      <c r="AC15" s="138"/>
+      <c r="AD15" s="138"/>
+    </row>
+    <row r="16" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A16" s="170" t="s">
+        <v>278</v>
+      </c>
+      <c r="B16" s="167">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="C16" s="155">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D16" s="166">
+        <v>0</v>
+      </c>
+      <c r="E16" s="166">
+        <v>0</v>
+      </c>
+      <c r="F16" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="G16" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="H16" s="160">
+        <v>0</v>
+      </c>
+      <c r="I16" s="160">
+        <v>0</v>
+      </c>
+      <c r="J16" s="160">
+        <v>0</v>
+      </c>
+      <c r="K16" s="160">
+        <v>0</v>
+      </c>
+      <c r="L16" s="160">
+        <v>0</v>
+      </c>
+      <c r="M16" s="160">
+        <v>0</v>
+      </c>
+      <c r="N16" s="160">
+        <v>0</v>
+      </c>
+      <c r="O16" s="160">
+        <v>0</v>
+      </c>
+      <c r="P16" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="160">
+        <v>0</v>
+      </c>
+      <c r="R16" s="162">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="S16" s="163"/>
+      <c r="T16" s="138"/>
+      <c r="U16" s="138"/>
+      <c r="V16" s="138"/>
+      <c r="W16" s="138"/>
+      <c r="X16" s="138"/>
+      <c r="Y16" s="138"/>
+      <c r="Z16" s="138"/>
+      <c r="AA16" s="138"/>
+      <c r="AB16" s="138"/>
+      <c r="AC16" s="138"/>
+      <c r="AD16" s="138"/>
+    </row>
+    <row r="17" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A17" s="150" t="s">
         <v>279</v>
       </c>
-      <c r="N4" s="149" t="s">
-        <v>117</v>
-      </c>
-      <c r="O4" s="149" t="s">
-        <v>123</v>
-      </c>
-      <c r="P4" s="149" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q4" s="149" t="s">
-        <v>132</v>
-      </c>
-      <c r="R4" s="149" t="s">
-        <v>135</v>
-      </c>
-      <c r="S4" s="160"/>
-      <c r="T4" s="160"/>
-      <c r="U4" s="160"/>
-      <c r="V4" s="160"/>
-      <c r="W4" s="160"/>
-      <c r="X4" s="160"/>
-      <c r="Y4" s="160"/>
-      <c r="Z4" s="160"/>
-      <c r="AA4" s="160"/>
-      <c r="AB4" s="160"/>
-      <c r="AC4" s="160"/>
-      <c r="AD4" s="161"/>
-    </row>
-    <row r="5" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A5" s="162" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="163">
+      <c r="B17" s="159">
         <v>0</v>
       </c>
-      <c r="C5" s="164">
+      <c r="C17" s="160">
         <v>0</v>
       </c>
-      <c r="D5" s="165">
-        <v>0.37</v>
-      </c>
-      <c r="E5" s="165">
-        <v>0.37</v>
-      </c>
-      <c r="F5" s="165">
-        <v>0.37</v>
-      </c>
-      <c r="G5" s="165">
-        <v>0.37</v>
-      </c>
-      <c r="H5" s="166">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="I5" s="164">
+      <c r="D17" s="160">
         <v>0</v>
       </c>
-      <c r="J5" s="164">
+      <c r="E17" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="F17" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="G17" s="160">
         <v>0</v>
       </c>
-      <c r="K5" s="164">
+      <c r="H17" s="160">
         <v>0</v>
       </c>
-      <c r="L5" s="164">
+      <c r="I17" s="160">
         <v>0</v>
       </c>
-      <c r="M5" s="167">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="N5" s="164">
+      <c r="J17" s="160">
         <v>0</v>
       </c>
-      <c r="O5" s="164">
+      <c r="K17" s="160">
         <v>0</v>
       </c>
-      <c r="P5" s="168">
+      <c r="L17" s="160">
+        <v>0</v>
+      </c>
+      <c r="M17" s="160">
+        <v>0</v>
+      </c>
+      <c r="N17" s="160">
+        <v>0</v>
+      </c>
+      <c r="O17" s="160">
+        <v>0</v>
+      </c>
+      <c r="P17" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="160">
+        <v>0</v>
+      </c>
+      <c r="R17" s="169">
+        <v>0</v>
+      </c>
+      <c r="S17" s="163"/>
+      <c r="T17" s="138"/>
+      <c r="U17" s="138"/>
+      <c r="V17" s="138"/>
+      <c r="W17" s="138"/>
+      <c r="X17" s="138"/>
+      <c r="Y17" s="138"/>
+      <c r="Z17" s="138"/>
+      <c r="AA17" s="138"/>
+      <c r="AB17" s="138"/>
+      <c r="AC17" s="138"/>
+      <c r="AD17" s="138"/>
+    </row>
+    <row r="18" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A18" s="150" t="s">
+        <v>280</v>
+      </c>
+      <c r="B18" s="159">
+        <v>0</v>
+      </c>
+      <c r="C18" s="160">
+        <v>0</v>
+      </c>
+      <c r="D18" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="E18" s="160">
+        <v>0</v>
+      </c>
+      <c r="F18" s="160">
+        <v>0</v>
+      </c>
+      <c r="G18" s="165">
+        <v>0.184</v>
+      </c>
+      <c r="H18" s="160">
+        <v>0</v>
+      </c>
+      <c r="I18" s="160">
+        <v>0</v>
+      </c>
+      <c r="J18" s="160">
+        <v>0</v>
+      </c>
+      <c r="K18" s="160">
+        <v>0</v>
+      </c>
+      <c r="L18" s="160">
+        <v>0</v>
+      </c>
+      <c r="M18" s="160">
+        <v>0</v>
+      </c>
+      <c r="N18" s="160">
+        <v>0</v>
+      </c>
+      <c r="O18" s="160">
+        <v>0</v>
+      </c>
+      <c r="P18" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="160">
+        <v>0</v>
+      </c>
+      <c r="R18" s="169">
+        <v>0</v>
+      </c>
+      <c r="S18" s="163"/>
+      <c r="T18" s="138"/>
+      <c r="U18" s="138"/>
+      <c r="V18" s="138"/>
+      <c r="W18" s="138"/>
+      <c r="X18" s="138"/>
+      <c r="Y18" s="138"/>
+      <c r="Z18" s="138"/>
+      <c r="AA18" s="138"/>
+      <c r="AB18" s="138"/>
+      <c r="AC18" s="138"/>
+      <c r="AD18" s="138"/>
+    </row>
+    <row r="19" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A19" s="150" t="s">
+        <v>281</v>
+      </c>
+      <c r="B19" s="171">
         <v>0.36699999999999999</v>
       </c>
-      <c r="Q5" s="164">
+      <c r="C19" s="160">
         <v>0</v>
       </c>
-      <c r="R5" s="168">
+      <c r="D19" s="160">
+        <v>0</v>
+      </c>
+      <c r="E19" s="160">
+        <v>0</v>
+      </c>
+      <c r="F19" s="160">
+        <v>0</v>
+      </c>
+      <c r="G19" s="160">
+        <v>0</v>
+      </c>
+      <c r="H19" s="160">
+        <v>0</v>
+      </c>
+      <c r="I19" s="160">
+        <v>0</v>
+      </c>
+      <c r="J19" s="160">
+        <v>0</v>
+      </c>
+      <c r="K19" s="160">
+        <v>0</v>
+      </c>
+      <c r="L19" s="160">
+        <v>0</v>
+      </c>
+      <c r="M19" s="160">
+        <v>0</v>
+      </c>
+      <c r="N19" s="160">
+        <v>0</v>
+      </c>
+      <c r="O19" s="160">
+        <v>0</v>
+      </c>
+      <c r="P19" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="160">
+        <v>0</v>
+      </c>
+      <c r="R19" s="169">
+        <v>0</v>
+      </c>
+      <c r="S19" s="163"/>
+      <c r="T19" s="138"/>
+      <c r="U19" s="138"/>
+      <c r="V19" s="138"/>
+      <c r="W19" s="138"/>
+      <c r="X19" s="138"/>
+      <c r="Y19" s="138"/>
+      <c r="Z19" s="138"/>
+      <c r="AA19" s="138"/>
+      <c r="AB19" s="138"/>
+      <c r="AC19" s="138"/>
+      <c r="AD19" s="138"/>
+    </row>
+    <row r="20" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A20" s="150" t="s">
+        <v>282</v>
+      </c>
+      <c r="B20" s="159">
+        <v>0</v>
+      </c>
+      <c r="C20" s="162">
         <v>0.36699999999999999</v>
       </c>
-      <c r="S5" s="169"/>
-      <c r="T5" s="170"/>
-      <c r="U5" s="170"/>
-      <c r="V5" s="170"/>
-      <c r="W5" s="170"/>
-      <c r="X5" s="170"/>
-      <c r="Y5" s="170"/>
-      <c r="Z5" s="170"/>
-      <c r="AA5" s="170"/>
-      <c r="AB5" s="170"/>
-      <c r="AC5" s="170"/>
-      <c r="AD5" s="170"/>
-    </row>
-    <row r="6" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A6" s="162" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="171">
+      <c r="D20" s="160">
         <v>0</v>
       </c>
-      <c r="C6" s="172">
+      <c r="E20" s="160">
         <v>0</v>
       </c>
-      <c r="D6" s="173">
-        <v>0.37</v>
-      </c>
-      <c r="E6" s="173">
-        <v>0.37</v>
-      </c>
-      <c r="F6" s="173">
-        <v>0.37</v>
-      </c>
-      <c r="G6" s="173">
-        <v>0.37</v>
-      </c>
-      <c r="H6" s="167">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="I6" s="172">
+      <c r="F20" s="160">
         <v>0</v>
       </c>
-      <c r="J6" s="172">
+      <c r="G20" s="160">
         <v>0</v>
       </c>
-      <c r="K6" s="172">
+      <c r="H20" s="160">
         <v>0</v>
       </c>
-      <c r="L6" s="172">
+      <c r="I20" s="160">
         <v>0</v>
       </c>
-      <c r="M6" s="167">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="N6" s="172">
+      <c r="J20" s="160">
         <v>0</v>
       </c>
-      <c r="O6" s="172">
+      <c r="K20" s="160">
         <v>0</v>
       </c>
-      <c r="P6" s="172">
+      <c r="L20" s="160">
         <v>0</v>
       </c>
-      <c r="Q6" s="174">
+      <c r="M20" s="160">
+        <v>0</v>
+      </c>
+      <c r="N20" s="160">
+        <v>0</v>
+      </c>
+      <c r="O20" s="160">
+        <v>0</v>
+      </c>
+      <c r="P20" s="160">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="160">
+        <v>0</v>
+      </c>
+      <c r="R20" s="169">
+        <v>0</v>
+      </c>
+      <c r="S20" s="163"/>
+      <c r="T20" s="138"/>
+      <c r="U20" s="138"/>
+      <c r="V20" s="138"/>
+      <c r="W20" s="138"/>
+      <c r="X20" s="138"/>
+      <c r="Y20" s="138"/>
+      <c r="Z20" s="138"/>
+      <c r="AA20" s="138"/>
+      <c r="AB20" s="138"/>
+      <c r="AC20" s="138"/>
+      <c r="AD20" s="138"/>
+    </row>
+    <row r="21" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A21" s="172" t="s">
+        <v>283</v>
+      </c>
+      <c r="B21" s="171">
         <v>0.36699999999999999</v>
       </c>
-      <c r="R6" s="172">
+      <c r="C21" s="160">
         <v>0</v>
       </c>
-      <c r="S6" s="175"/>
-      <c r="T6" s="148"/>
-      <c r="U6" s="148"/>
-      <c r="V6" s="148"/>
-      <c r="W6" s="148"/>
-      <c r="X6" s="148"/>
-      <c r="Y6" s="148"/>
-      <c r="Z6" s="148"/>
-      <c r="AA6" s="148"/>
-      <c r="AB6" s="148"/>
-      <c r="AC6" s="148"/>
-      <c r="AD6" s="148"/>
-    </row>
-    <row r="7" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A7" s="162" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="176">
-        <v>0.37</v>
-      </c>
-      <c r="C7" s="173">
-        <v>0.37</v>
-      </c>
-      <c r="D7" s="172">
+      <c r="D21" s="160">
         <v>0</v>
       </c>
-      <c r="E7" s="172">
+      <c r="E21" s="160">
         <v>0</v>
       </c>
-      <c r="F7" s="172">
+      <c r="F21" s="160">
         <v>0</v>
       </c>
-      <c r="G7" s="172">
+      <c r="G21" s="160">
         <v>0</v>
       </c>
-      <c r="H7" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="I7" s="172">
+      <c r="H21" s="160">
         <v>0</v>
       </c>
-      <c r="J7" s="172">
+      <c r="I21" s="160">
         <v>0</v>
       </c>
-      <c r="K7" s="172">
+      <c r="J21" s="160">
         <v>0</v>
       </c>
-      <c r="L7" s="172">
+      <c r="K21" s="160">
         <v>0</v>
       </c>
-      <c r="M7" s="178">
+      <c r="L21" s="160">
         <v>0</v>
       </c>
-      <c r="N7" s="172">
+      <c r="M21" s="162">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="N21" s="160">
         <v>0</v>
       </c>
-      <c r="O7" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="P7" s="172">
+      <c r="O21" s="160">
         <v>0</v>
       </c>
-      <c r="Q7" s="172">
+      <c r="P21" s="160">
         <v>0</v>
       </c>
-      <c r="R7" s="172">
+      <c r="Q21" s="160">
         <v>0</v>
       </c>
-      <c r="S7" s="175"/>
-      <c r="T7" s="148"/>
-      <c r="U7" s="148"/>
-      <c r="V7" s="148"/>
-      <c r="W7" s="148"/>
-      <c r="X7" s="148"/>
-      <c r="Y7" s="148"/>
-      <c r="Z7" s="148"/>
-      <c r="AA7" s="148"/>
-      <c r="AB7" s="148"/>
-      <c r="AC7" s="148"/>
-      <c r="AD7" s="148"/>
-    </row>
-    <row r="8" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A8" s="162" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="176">
-        <v>0.37</v>
-      </c>
-      <c r="C8" s="173">
-        <v>0.37</v>
-      </c>
-      <c r="D8" s="172">
+      <c r="R21" s="169">
         <v>0</v>
       </c>
-      <c r="E8" s="172">
-        <v>0</v>
-      </c>
-      <c r="F8" s="172">
-        <v>0</v>
-      </c>
-      <c r="G8" s="172">
-        <v>0</v>
-      </c>
-      <c r="H8" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="I8" s="172">
-        <v>0</v>
-      </c>
-      <c r="J8" s="172">
-        <v>0</v>
-      </c>
-      <c r="K8" s="172">
-        <v>0</v>
-      </c>
-      <c r="L8" s="172">
-        <v>0</v>
-      </c>
-      <c r="M8" s="178">
-        <v>0</v>
-      </c>
-      <c r="N8" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="O8" s="172">
-        <v>0</v>
-      </c>
-      <c r="P8" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="172">
-        <v>0</v>
-      </c>
-      <c r="R8" s="172">
-        <v>0</v>
-      </c>
-      <c r="S8" s="175"/>
-      <c r="T8" s="148"/>
-      <c r="U8" s="148"/>
-      <c r="V8" s="148"/>
-      <c r="W8" s="148"/>
-      <c r="X8" s="148"/>
-      <c r="Y8" s="148"/>
-      <c r="Z8" s="148"/>
-      <c r="AA8" s="148"/>
-      <c r="AB8" s="148"/>
-      <c r="AC8" s="148"/>
-      <c r="AD8" s="148"/>
-    </row>
-    <row r="9" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A9" s="162" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="176">
-        <v>0.37</v>
-      </c>
-      <c r="C9" s="173">
-        <v>0.37</v>
-      </c>
-      <c r="D9" s="172">
-        <v>0</v>
-      </c>
-      <c r="E9" s="172">
-        <v>0</v>
-      </c>
-      <c r="F9" s="172">
-        <v>0</v>
-      </c>
-      <c r="G9" s="172">
-        <v>0</v>
-      </c>
-      <c r="H9" s="172">
-        <v>0</v>
-      </c>
-      <c r="I9" s="172">
-        <v>0</v>
-      </c>
-      <c r="J9" s="172">
-        <v>0</v>
-      </c>
-      <c r="K9" s="172">
-        <v>0</v>
-      </c>
-      <c r="L9" s="172">
-        <v>0</v>
-      </c>
-      <c r="M9" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="N9" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="O9" s="172">
-        <v>0</v>
-      </c>
-      <c r="P9" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="172">
-        <v>0</v>
-      </c>
-      <c r="R9" s="172">
-        <v>0</v>
-      </c>
-      <c r="S9" s="175"/>
-      <c r="T9" s="148"/>
-      <c r="U9" s="148"/>
-      <c r="V9" s="148"/>
-      <c r="W9" s="148"/>
-      <c r="X9" s="148"/>
-      <c r="Y9" s="148"/>
-      <c r="Z9" s="148"/>
-      <c r="AA9" s="148"/>
-      <c r="AB9" s="148"/>
-      <c r="AC9" s="148"/>
-      <c r="AD9" s="148"/>
-    </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A10" s="162" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="176">
-        <v>0.37</v>
-      </c>
-      <c r="C10" s="173">
-        <v>0.37</v>
-      </c>
-      <c r="D10" s="172">
-        <v>0</v>
-      </c>
-      <c r="E10" s="172">
-        <v>0</v>
-      </c>
-      <c r="F10" s="172">
-        <v>0</v>
-      </c>
-      <c r="G10" s="172">
-        <v>0</v>
-      </c>
-      <c r="H10" s="172">
-        <v>0</v>
-      </c>
-      <c r="I10" s="172">
-        <v>0</v>
-      </c>
-      <c r="J10" s="172">
-        <v>0</v>
-      </c>
-      <c r="K10" s="172">
-        <v>0</v>
-      </c>
-      <c r="L10" s="172">
-        <v>0</v>
-      </c>
-      <c r="M10" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="N10" s="172">
-        <v>0</v>
-      </c>
-      <c r="O10" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="P10" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="172">
-        <v>0</v>
-      </c>
-      <c r="R10" s="172">
-        <v>0</v>
-      </c>
-      <c r="S10" s="175"/>
-      <c r="T10" s="148"/>
-      <c r="U10" s="148"/>
-      <c r="V10" s="148"/>
-      <c r="W10" s="148"/>
-      <c r="X10" s="148"/>
-      <c r="Y10" s="148"/>
-      <c r="Z10" s="148"/>
-      <c r="AA10" s="148"/>
-      <c r="AB10" s="148"/>
-      <c r="AC10" s="148"/>
-      <c r="AD10" s="148"/>
-    </row>
-    <row r="11" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A11" s="162" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="179">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="C11" s="167">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="D11" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="E11" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="F11" s="172">
-        <v>0</v>
-      </c>
-      <c r="G11" s="172">
-        <v>0</v>
-      </c>
-      <c r="H11" s="172">
-        <v>0</v>
-      </c>
-      <c r="I11" s="180">
-        <v>5.6840000000000002</v>
-      </c>
-      <c r="J11" s="180">
-        <v>5.6840000000000002</v>
-      </c>
-      <c r="K11" s="180">
-        <v>5.6840000000000002</v>
-      </c>
-      <c r="L11" s="180">
-        <v>5.6840000000000002</v>
-      </c>
-      <c r="M11" s="172">
-        <v>0</v>
-      </c>
-      <c r="N11" s="172">
-        <v>0</v>
-      </c>
-      <c r="O11" s="172">
-        <v>0</v>
-      </c>
-      <c r="P11" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="172">
-        <v>0</v>
-      </c>
-      <c r="R11" s="181">
-        <v>0</v>
-      </c>
-      <c r="S11" s="175"/>
-      <c r="T11" s="148"/>
-      <c r="U11" s="148"/>
-      <c r="V11" s="148"/>
-      <c r="W11" s="148"/>
-      <c r="X11" s="148"/>
-      <c r="Y11" s="148"/>
-      <c r="Z11" s="148"/>
-      <c r="AA11" s="148"/>
-      <c r="AB11" s="148"/>
-      <c r="AC11" s="148"/>
-      <c r="AD11" s="148"/>
-    </row>
-    <row r="12" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A12" s="162" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="171">
-        <v>0</v>
-      </c>
-      <c r="C12" s="172">
-        <v>0</v>
-      </c>
-      <c r="D12" s="172">
-        <v>0</v>
-      </c>
-      <c r="E12" s="172">
-        <v>0</v>
-      </c>
-      <c r="F12" s="172">
-        <v>0</v>
-      </c>
-      <c r="G12" s="172">
-        <v>0</v>
-      </c>
-      <c r="H12" s="180">
-        <v>5.6840000000000002</v>
-      </c>
-      <c r="I12" s="172">
-        <v>0</v>
-      </c>
-      <c r="J12" s="172">
-        <v>0</v>
-      </c>
-      <c r="K12" s="172">
-        <v>0</v>
-      </c>
-      <c r="L12" s="172">
-        <v>0</v>
-      </c>
-      <c r="M12" s="172">
-        <v>0</v>
-      </c>
-      <c r="N12" s="172">
-        <v>0</v>
-      </c>
-      <c r="O12" s="172">
-        <v>0</v>
-      </c>
-      <c r="P12" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="172">
-        <v>0</v>
-      </c>
-      <c r="R12" s="181">
-        <v>0</v>
-      </c>
-      <c r="S12" s="175"/>
-      <c r="T12" s="148"/>
-      <c r="U12" s="148"/>
-      <c r="V12" s="148"/>
-      <c r="W12" s="148"/>
-      <c r="X12" s="148"/>
-      <c r="Y12" s="148"/>
-      <c r="Z12" s="148"/>
-      <c r="AA12" s="148"/>
-      <c r="AB12" s="148"/>
-      <c r="AC12" s="148"/>
-      <c r="AD12" s="148"/>
-    </row>
-    <row r="13" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A13" s="162" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="171">
-        <v>0</v>
-      </c>
-      <c r="C13" s="172">
-        <v>0</v>
-      </c>
-      <c r="D13" s="172">
-        <v>0</v>
-      </c>
-      <c r="E13" s="172">
-        <v>0</v>
-      </c>
-      <c r="F13" s="172">
-        <v>0</v>
-      </c>
-      <c r="G13" s="172">
-        <v>0</v>
-      </c>
-      <c r="H13" s="180">
-        <v>5.6840000000000002</v>
-      </c>
-      <c r="I13" s="172">
-        <v>0</v>
-      </c>
-      <c r="J13" s="172">
-        <v>0</v>
-      </c>
-      <c r="K13" s="172">
-        <v>0</v>
-      </c>
-      <c r="L13" s="172">
-        <v>0</v>
-      </c>
-      <c r="M13" s="172">
-        <v>0</v>
-      </c>
-      <c r="N13" s="172">
-        <v>0</v>
-      </c>
-      <c r="O13" s="172">
-        <v>0</v>
-      </c>
-      <c r="P13" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="172">
-        <v>0</v>
-      </c>
-      <c r="R13" s="181">
-        <v>0</v>
-      </c>
-      <c r="S13" s="175"/>
-      <c r="T13" s="148"/>
-      <c r="U13" s="148"/>
-      <c r="V13" s="148"/>
-      <c r="W13" s="148"/>
-      <c r="X13" s="148"/>
-      <c r="Y13" s="148"/>
-      <c r="Z13" s="148"/>
-      <c r="AA13" s="148"/>
-      <c r="AB13" s="148"/>
-      <c r="AC13" s="148"/>
-      <c r="AD13" s="148"/>
-    </row>
-    <row r="14" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A14" s="162" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="171">
-        <v>0</v>
-      </c>
-      <c r="C14" s="172">
-        <v>0</v>
-      </c>
-      <c r="D14" s="172">
-        <v>0</v>
-      </c>
-      <c r="E14" s="172">
-        <v>0</v>
-      </c>
-      <c r="F14" s="172">
-        <v>0</v>
-      </c>
-      <c r="G14" s="172">
-        <v>0</v>
-      </c>
-      <c r="H14" s="180">
-        <v>5.6840000000000002</v>
-      </c>
-      <c r="I14" s="172">
-        <v>0</v>
-      </c>
-      <c r="J14" s="172">
-        <v>0</v>
-      </c>
-      <c r="K14" s="172">
-        <v>0</v>
-      </c>
-      <c r="L14" s="172">
-        <v>0</v>
-      </c>
-      <c r="M14" s="172">
-        <v>0</v>
-      </c>
-      <c r="N14" s="172">
-        <v>0</v>
-      </c>
-      <c r="O14" s="172">
-        <v>0</v>
-      </c>
-      <c r="P14" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="172">
-        <v>0</v>
-      </c>
-      <c r="R14" s="181">
-        <v>0</v>
-      </c>
-      <c r="S14" s="175"/>
-      <c r="T14" s="148"/>
-      <c r="U14" s="148"/>
-      <c r="V14" s="148"/>
-      <c r="W14" s="148"/>
-      <c r="X14" s="148"/>
-      <c r="Y14" s="148"/>
-      <c r="Z14" s="148"/>
-      <c r="AA14" s="148"/>
-      <c r="AB14" s="148"/>
-      <c r="AC14" s="148"/>
-      <c r="AD14" s="148"/>
-    </row>
-    <row r="15" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A15" s="162" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="171">
-        <v>0</v>
-      </c>
-      <c r="C15" s="172">
-        <v>0</v>
-      </c>
-      <c r="D15" s="172">
-        <v>0</v>
-      </c>
-      <c r="E15" s="172">
-        <v>0</v>
-      </c>
-      <c r="F15" s="172">
-        <v>0</v>
-      </c>
-      <c r="G15" s="172">
-        <v>0</v>
-      </c>
-      <c r="H15" s="180">
-        <v>5.6840000000000002</v>
-      </c>
-      <c r="I15" s="172">
-        <v>0</v>
-      </c>
-      <c r="J15" s="172">
-        <v>0</v>
-      </c>
-      <c r="K15" s="172">
-        <v>0</v>
-      </c>
-      <c r="L15" s="172">
-        <v>0</v>
-      </c>
-      <c r="M15" s="172">
-        <v>0</v>
-      </c>
-      <c r="N15" s="172">
-        <v>0</v>
-      </c>
-      <c r="O15" s="172">
-        <v>0</v>
-      </c>
-      <c r="P15" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="172">
-        <v>0</v>
-      </c>
-      <c r="R15" s="181">
-        <v>0</v>
-      </c>
-      <c r="S15" s="175"/>
-      <c r="T15" s="148"/>
-      <c r="U15" s="148"/>
-      <c r="V15" s="148"/>
-      <c r="W15" s="148"/>
-      <c r="X15" s="148"/>
-      <c r="Y15" s="148"/>
-      <c r="Z15" s="148"/>
-      <c r="AA15" s="148"/>
-      <c r="AB15" s="148"/>
-      <c r="AC15" s="148"/>
-      <c r="AD15" s="148"/>
-    </row>
-    <row r="16" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A16" s="182" t="s">
-        <v>279</v>
-      </c>
-      <c r="B16" s="179">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="C16" s="167">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="D16" s="178">
-        <v>0</v>
-      </c>
-      <c r="E16" s="178">
-        <v>0</v>
-      </c>
-      <c r="F16" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="G16" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="H16" s="172">
-        <v>0</v>
-      </c>
-      <c r="I16" s="172">
-        <v>0</v>
-      </c>
-      <c r="J16" s="172">
-        <v>0</v>
-      </c>
-      <c r="K16" s="172">
-        <v>0</v>
-      </c>
-      <c r="L16" s="172">
-        <v>0</v>
-      </c>
-      <c r="M16" s="172">
-        <v>0</v>
-      </c>
-      <c r="N16" s="172">
-        <v>0</v>
-      </c>
-      <c r="O16" s="172">
-        <v>0</v>
-      </c>
-      <c r="P16" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="172">
-        <v>0</v>
-      </c>
-      <c r="R16" s="174">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="S16" s="175"/>
-      <c r="T16" s="148"/>
-      <c r="U16" s="148"/>
-      <c r="V16" s="148"/>
-      <c r="W16" s="148"/>
-      <c r="X16" s="148"/>
-      <c r="Y16" s="148"/>
-      <c r="Z16" s="148"/>
-      <c r="AA16" s="148"/>
-      <c r="AB16" s="148"/>
-      <c r="AC16" s="148"/>
-      <c r="AD16" s="148"/>
-    </row>
-    <row r="17" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A17" s="162" t="s">
-        <v>280</v>
-      </c>
-      <c r="B17" s="171">
-        <v>0</v>
-      </c>
-      <c r="C17" s="172">
-        <v>0</v>
-      </c>
-      <c r="D17" s="172">
-        <v>0</v>
-      </c>
-      <c r="E17" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="F17" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="G17" s="172">
-        <v>0</v>
-      </c>
-      <c r="H17" s="172">
-        <v>0</v>
-      </c>
-      <c r="I17" s="172">
-        <v>0</v>
-      </c>
-      <c r="J17" s="172">
-        <v>0</v>
-      </c>
-      <c r="K17" s="172">
-        <v>0</v>
-      </c>
-      <c r="L17" s="172">
-        <v>0</v>
-      </c>
-      <c r="M17" s="172">
-        <v>0</v>
-      </c>
-      <c r="N17" s="172">
-        <v>0</v>
-      </c>
-      <c r="O17" s="172">
-        <v>0</v>
-      </c>
-      <c r="P17" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="172">
-        <v>0</v>
-      </c>
-      <c r="R17" s="181">
-        <v>0</v>
-      </c>
-      <c r="S17" s="175"/>
-      <c r="T17" s="148"/>
-      <c r="U17" s="148"/>
-      <c r="V17" s="148"/>
-      <c r="W17" s="148"/>
-      <c r="X17" s="148"/>
-      <c r="Y17" s="148"/>
-      <c r="Z17" s="148"/>
-      <c r="AA17" s="148"/>
-      <c r="AB17" s="148"/>
-      <c r="AC17" s="148"/>
-      <c r="AD17" s="148"/>
-    </row>
-    <row r="18" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A18" s="162" t="s">
-        <v>281</v>
-      </c>
-      <c r="B18" s="171">
-        <v>0</v>
-      </c>
-      <c r="C18" s="172">
-        <v>0</v>
-      </c>
-      <c r="D18" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="E18" s="172">
-        <v>0</v>
-      </c>
-      <c r="F18" s="172">
-        <v>0</v>
-      </c>
-      <c r="G18" s="177">
-        <v>0.184</v>
-      </c>
-      <c r="H18" s="172">
-        <v>0</v>
-      </c>
-      <c r="I18" s="172">
-        <v>0</v>
-      </c>
-      <c r="J18" s="172">
-        <v>0</v>
-      </c>
-      <c r="K18" s="172">
-        <v>0</v>
-      </c>
-      <c r="L18" s="172">
-        <v>0</v>
-      </c>
-      <c r="M18" s="172">
-        <v>0</v>
-      </c>
-      <c r="N18" s="172">
-        <v>0</v>
-      </c>
-      <c r="O18" s="172">
-        <v>0</v>
-      </c>
-      <c r="P18" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="172">
-        <v>0</v>
-      </c>
-      <c r="R18" s="181">
-        <v>0</v>
-      </c>
-      <c r="S18" s="175"/>
-      <c r="T18" s="148"/>
-      <c r="U18" s="148"/>
-      <c r="V18" s="148"/>
-      <c r="W18" s="148"/>
-      <c r="X18" s="148"/>
-      <c r="Y18" s="148"/>
-      <c r="Z18" s="148"/>
-      <c r="AA18" s="148"/>
-      <c r="AB18" s="148"/>
-      <c r="AC18" s="148"/>
-      <c r="AD18" s="148"/>
-    </row>
-    <row r="19" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A19" s="162" t="s">
-        <v>282</v>
-      </c>
-      <c r="B19" s="183">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="C19" s="172">
-        <v>0</v>
-      </c>
-      <c r="D19" s="172">
-        <v>0</v>
-      </c>
-      <c r="E19" s="172">
-        <v>0</v>
-      </c>
-      <c r="F19" s="172">
-        <v>0</v>
-      </c>
-      <c r="G19" s="172">
-        <v>0</v>
-      </c>
-      <c r="H19" s="172">
-        <v>0</v>
-      </c>
-      <c r="I19" s="172">
-        <v>0</v>
-      </c>
-      <c r="J19" s="172">
-        <v>0</v>
-      </c>
-      <c r="K19" s="172">
-        <v>0</v>
-      </c>
-      <c r="L19" s="172">
-        <v>0</v>
-      </c>
-      <c r="M19" s="172">
-        <v>0</v>
-      </c>
-      <c r="N19" s="172">
-        <v>0</v>
-      </c>
-      <c r="O19" s="172">
-        <v>0</v>
-      </c>
-      <c r="P19" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="172">
-        <v>0</v>
-      </c>
-      <c r="R19" s="181">
-        <v>0</v>
-      </c>
-      <c r="S19" s="175"/>
-      <c r="T19" s="148"/>
-      <c r="U19" s="148"/>
-      <c r="V19" s="148"/>
-      <c r="W19" s="148"/>
-      <c r="X19" s="148"/>
-      <c r="Y19" s="148"/>
-      <c r="Z19" s="148"/>
-      <c r="AA19" s="148"/>
-      <c r="AB19" s="148"/>
-      <c r="AC19" s="148"/>
-      <c r="AD19" s="148"/>
-    </row>
-    <row r="20" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A20" s="162" t="s">
-        <v>283</v>
-      </c>
-      <c r="B20" s="171">
-        <v>0</v>
-      </c>
-      <c r="C20" s="174">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="D20" s="172">
-        <v>0</v>
-      </c>
-      <c r="E20" s="172">
-        <v>0</v>
-      </c>
-      <c r="F20" s="172">
-        <v>0</v>
-      </c>
-      <c r="G20" s="172">
-        <v>0</v>
-      </c>
-      <c r="H20" s="172">
-        <v>0</v>
-      </c>
-      <c r="I20" s="172">
-        <v>0</v>
-      </c>
-      <c r="J20" s="172">
-        <v>0</v>
-      </c>
-      <c r="K20" s="172">
-        <v>0</v>
-      </c>
-      <c r="L20" s="172">
-        <v>0</v>
-      </c>
-      <c r="M20" s="172">
-        <v>0</v>
-      </c>
-      <c r="N20" s="172">
-        <v>0</v>
-      </c>
-      <c r="O20" s="172">
-        <v>0</v>
-      </c>
-      <c r="P20" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="172">
-        <v>0</v>
-      </c>
-      <c r="R20" s="181">
-        <v>0</v>
-      </c>
-      <c r="S20" s="175"/>
-      <c r="T20" s="148"/>
-      <c r="U20" s="148"/>
-      <c r="V20" s="148"/>
-      <c r="W20" s="148"/>
-      <c r="X20" s="148"/>
-      <c r="Y20" s="148"/>
-      <c r="Z20" s="148"/>
-      <c r="AA20" s="148"/>
-      <c r="AB20" s="148"/>
-      <c r="AC20" s="148"/>
-      <c r="AD20" s="148"/>
-    </row>
-    <row r="21" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A21" s="184" t="s">
-        <v>284</v>
-      </c>
-      <c r="B21" s="183">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="C21" s="172">
-        <v>0</v>
-      </c>
-      <c r="D21" s="172">
-        <v>0</v>
-      </c>
-      <c r="E21" s="172">
-        <v>0</v>
-      </c>
-      <c r="F21" s="172">
-        <v>0</v>
-      </c>
-      <c r="G21" s="172">
-        <v>0</v>
-      </c>
-      <c r="H21" s="172">
-        <v>0</v>
-      </c>
-      <c r="I21" s="172">
-        <v>0</v>
-      </c>
-      <c r="J21" s="172">
-        <v>0</v>
-      </c>
-      <c r="K21" s="172">
-        <v>0</v>
-      </c>
-      <c r="L21" s="172">
-        <v>0</v>
-      </c>
-      <c r="M21" s="174">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="N21" s="172">
-        <v>0</v>
-      </c>
-      <c r="O21" s="172">
-        <v>0</v>
-      </c>
-      <c r="P21" s="172">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="172">
-        <v>0</v>
-      </c>
-      <c r="R21" s="181">
-        <v>0</v>
-      </c>
-      <c r="S21" s="175"/>
-      <c r="T21" s="148"/>
-      <c r="U21" s="148"/>
-      <c r="V21" s="148"/>
-      <c r="W21" s="148"/>
-      <c r="X21" s="148"/>
-      <c r="Y21" s="148"/>
-      <c r="Z21" s="148"/>
-      <c r="AA21" s="148"/>
-      <c r="AB21" s="148"/>
-      <c r="AC21" s="148"/>
-      <c r="AD21" s="148"/>
+      <c r="S21" s="163"/>
+      <c r="T21" s="138"/>
+      <c r="U21" s="138"/>
+      <c r="V21" s="138"/>
+      <c r="W21" s="138"/>
+      <c r="X21" s="138"/>
+      <c r="Y21" s="138"/>
+      <c r="Z21" s="138"/>
+      <c r="AA21" s="138"/>
+      <c r="AB21" s="138"/>
+      <c r="AC21" s="138"/>
+      <c r="AD21" s="138"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A22" s="160"/>
-      <c r="B22" s="185"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="186"/>
-      <c r="E22" s="186"/>
-      <c r="F22" s="186"/>
-      <c r="G22" s="186"/>
-      <c r="H22" s="186"/>
-      <c r="I22" s="186"/>
-      <c r="J22" s="186"/>
-      <c r="K22" s="186"/>
-      <c r="L22" s="186"/>
-      <c r="M22" s="186"/>
-      <c r="N22" s="186"/>
-      <c r="O22" s="186"/>
-      <c r="P22" s="186"/>
-      <c r="Q22" s="186"/>
-      <c r="R22" s="186"/>
-      <c r="S22" s="148"/>
-      <c r="T22" s="148"/>
-      <c r="U22" s="148"/>
-      <c r="V22" s="148"/>
-      <c r="W22" s="148"/>
-      <c r="X22" s="148"/>
-      <c r="Y22" s="148"/>
-      <c r="Z22" s="148"/>
-      <c r="AA22" s="148"/>
-      <c r="AB22" s="148"/>
-      <c r="AC22" s="148"/>
-      <c r="AD22" s="148"/>
+      <c r="A22" s="148"/>
+      <c r="B22" s="173"/>
+      <c r="C22" s="174"/>
+      <c r="D22" s="174"/>
+      <c r="E22" s="174"/>
+      <c r="F22" s="174"/>
+      <c r="G22" s="174"/>
+      <c r="H22" s="174"/>
+      <c r="I22" s="174"/>
+      <c r="J22" s="174"/>
+      <c r="K22" s="174"/>
+      <c r="L22" s="174"/>
+      <c r="M22" s="174"/>
+      <c r="N22" s="174"/>
+      <c r="O22" s="174"/>
+      <c r="P22" s="174"/>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="174"/>
+      <c r="S22" s="138"/>
+      <c r="T22" s="138"/>
+      <c r="U22" s="138"/>
+      <c r="V22" s="138"/>
+      <c r="W22" s="138"/>
+      <c r="X22" s="138"/>
+      <c r="Y22" s="138"/>
+      <c r="Z22" s="138"/>
+      <c r="AA22" s="138"/>
+      <c r="AB22" s="138"/>
+      <c r="AC22" s="138"/>
+      <c r="AD22" s="138"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A23" s="160"/>
-      <c r="B23" s="187"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="148"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="148"/>
-      <c r="G23" s="148"/>
-      <c r="H23" s="148"/>
-      <c r="I23" s="148"/>
-      <c r="J23" s="148"/>
-      <c r="K23" s="148"/>
-      <c r="L23" s="148"/>
-      <c r="M23" s="148"/>
-      <c r="N23" s="148"/>
-      <c r="O23" s="148"/>
-      <c r="P23" s="148"/>
-      <c r="Q23" s="148"/>
-      <c r="R23" s="148"/>
-      <c r="S23" s="148"/>
-      <c r="T23" s="148"/>
-      <c r="U23" s="148"/>
-      <c r="V23" s="148"/>
-      <c r="W23" s="148"/>
-      <c r="X23" s="148"/>
-      <c r="Y23" s="148"/>
-      <c r="Z23" s="148"/>
-      <c r="AA23" s="148"/>
-      <c r="AB23" s="148"/>
-      <c r="AC23" s="148"/>
-      <c r="AD23" s="148"/>
+      <c r="A23" s="148"/>
+      <c r="B23" s="175"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="138"/>
+      <c r="F23" s="138"/>
+      <c r="G23" s="138"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="138"/>
+      <c r="K23" s="138"/>
+      <c r="L23" s="138"/>
+      <c r="M23" s="138"/>
+      <c r="N23" s="138"/>
+      <c r="O23" s="138"/>
+      <c r="P23" s="138"/>
+      <c r="Q23" s="138"/>
+      <c r="R23" s="138"/>
+      <c r="S23" s="138"/>
+      <c r="T23" s="138"/>
+      <c r="U23" s="138"/>
+      <c r="V23" s="138"/>
+      <c r="W23" s="138"/>
+      <c r="X23" s="138"/>
+      <c r="Y23" s="138"/>
+      <c r="Z23" s="138"/>
+      <c r="AA23" s="138"/>
+      <c r="AB23" s="138"/>
+      <c r="AC23" s="138"/>
+      <c r="AD23" s="138"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A24" s="160"/>
-      <c r="B24" s="187"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="148"/>
-      <c r="H24" s="148"/>
-      <c r="I24" s="148"/>
-      <c r="J24" s="148"/>
-      <c r="K24" s="148"/>
-      <c r="L24" s="148"/>
-      <c r="M24" s="148"/>
-      <c r="N24" s="148"/>
-      <c r="O24" s="148"/>
-      <c r="P24" s="148"/>
-      <c r="Q24" s="148"/>
-      <c r="R24" s="148"/>
-      <c r="S24" s="148"/>
-      <c r="T24" s="148"/>
-      <c r="U24" s="148"/>
-      <c r="V24" s="148"/>
-      <c r="W24" s="148"/>
-      <c r="X24" s="148"/>
-      <c r="Y24" s="148"/>
-      <c r="Z24" s="148"/>
-      <c r="AA24" s="148"/>
-      <c r="AB24" s="148"/>
-      <c r="AC24" s="148"/>
-      <c r="AD24" s="148"/>
+      <c r="A24" s="148"/>
+      <c r="B24" s="175"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="138"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="138"/>
+      <c r="J24" s="138"/>
+      <c r="K24" s="138"/>
+      <c r="L24" s="138"/>
+      <c r="M24" s="138"/>
+      <c r="N24" s="138"/>
+      <c r="O24" s="138"/>
+      <c r="P24" s="138"/>
+      <c r="Q24" s="138"/>
+      <c r="R24" s="138"/>
+      <c r="S24" s="138"/>
+      <c r="T24" s="138"/>
+      <c r="U24" s="138"/>
+      <c r="V24" s="138"/>
+      <c r="W24" s="138"/>
+      <c r="X24" s="138"/>
+      <c r="Y24" s="138"/>
+      <c r="Z24" s="138"/>
+      <c r="AA24" s="138"/>
+      <c r="AB24" s="138"/>
+      <c r="AC24" s="138"/>
+      <c r="AD24" s="138"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A25" s="160"/>
-      <c r="B25" s="187"/>
-      <c r="C25" s="148"/>
-      <c r="D25" s="148"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="148"/>
-      <c r="G25" s="148"/>
-      <c r="H25" s="148"/>
-      <c r="I25" s="148"/>
-      <c r="J25" s="148"/>
-      <c r="K25" s="148"/>
-      <c r="L25" s="148"/>
-      <c r="M25" s="148"/>
-      <c r="N25" s="148"/>
-      <c r="O25" s="148"/>
-      <c r="P25" s="148"/>
-      <c r="Q25" s="148"/>
-      <c r="R25" s="148"/>
-      <c r="S25" s="148"/>
-      <c r="T25" s="148"/>
-      <c r="U25" s="148"/>
-      <c r="V25" s="148"/>
-      <c r="W25" s="148"/>
-      <c r="X25" s="148"/>
-      <c r="Y25" s="148"/>
-      <c r="Z25" s="148"/>
-      <c r="AA25" s="148"/>
-      <c r="AB25" s="148"/>
-      <c r="AC25" s="148"/>
-      <c r="AD25" s="148"/>
+      <c r="A25" s="148"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="138"/>
+      <c r="E25" s="138"/>
+      <c r="F25" s="138"/>
+      <c r="G25" s="138"/>
+      <c r="H25" s="138"/>
+      <c r="I25" s="138"/>
+      <c r="J25" s="138"/>
+      <c r="K25" s="138"/>
+      <c r="L25" s="138"/>
+      <c r="M25" s="138"/>
+      <c r="N25" s="138"/>
+      <c r="O25" s="138"/>
+      <c r="P25" s="138"/>
+      <c r="Q25" s="138"/>
+      <c r="R25" s="138"/>
+      <c r="S25" s="138"/>
+      <c r="T25" s="138"/>
+      <c r="U25" s="138"/>
+      <c r="V25" s="138"/>
+      <c r="W25" s="138"/>
+      <c r="X25" s="138"/>
+      <c r="Y25" s="138"/>
+      <c r="Z25" s="138"/>
+      <c r="AA25" s="138"/>
+      <c r="AB25" s="138"/>
+      <c r="AC25" s="138"/>
+      <c r="AD25" s="138"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A26" s="160"/>
-      <c r="B26" s="187"/>
-      <c r="C26" s="148"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
-      <c r="H26" s="148"/>
-      <c r="I26" s="148"/>
-      <c r="J26" s="148"/>
-      <c r="K26" s="148"/>
-      <c r="L26" s="148"/>
-      <c r="M26" s="148"/>
-      <c r="N26" s="148"/>
-      <c r="O26" s="148"/>
-      <c r="P26" s="148"/>
-      <c r="Q26" s="148"/>
-      <c r="R26" s="148"/>
-      <c r="S26" s="148"/>
-      <c r="T26" s="148"/>
-      <c r="U26" s="148"/>
-      <c r="V26" s="148"/>
-      <c r="W26" s="148"/>
-      <c r="X26" s="148"/>
-      <c r="Y26" s="148"/>
-      <c r="Z26" s="148"/>
-      <c r="AA26" s="148"/>
-      <c r="AB26" s="148"/>
-      <c r="AC26" s="148"/>
-      <c r="AD26" s="148"/>
+      <c r="A26" s="148"/>
+      <c r="B26" s="175"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="138"/>
+      <c r="K26" s="138"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="138"/>
+      <c r="N26" s="138"/>
+      <c r="O26" s="138"/>
+      <c r="P26" s="138"/>
+      <c r="Q26" s="138"/>
+      <c r="R26" s="138"/>
+      <c r="S26" s="138"/>
+      <c r="T26" s="138"/>
+      <c r="U26" s="138"/>
+      <c r="V26" s="138"/>
+      <c r="W26" s="138"/>
+      <c r="X26" s="138"/>
+      <c r="Y26" s="138"/>
+      <c r="Z26" s="138"/>
+      <c r="AA26" s="138"/>
+      <c r="AB26" s="138"/>
+      <c r="AC26" s="138"/>
+      <c r="AD26" s="138"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A27" s="160"/>
-      <c r="B27" s="187"/>
-      <c r="C27" s="148"/>
-      <c r="D27" s="148"/>
-      <c r="E27" s="148"/>
-      <c r="F27" s="148"/>
-      <c r="G27" s="148"/>
-      <c r="H27" s="148"/>
-      <c r="I27" s="148"/>
-      <c r="J27" s="148"/>
-      <c r="K27" s="148"/>
-      <c r="L27" s="148"/>
-      <c r="M27" s="148"/>
-      <c r="N27" s="148"/>
-      <c r="O27" s="148"/>
-      <c r="P27" s="148"/>
-      <c r="Q27" s="148"/>
-      <c r="R27" s="148"/>
-      <c r="S27" s="148"/>
-      <c r="T27" s="148"/>
-      <c r="U27" s="148"/>
-      <c r="V27" s="148"/>
-      <c r="W27" s="148"/>
-      <c r="X27" s="148"/>
-      <c r="Y27" s="148"/>
-      <c r="Z27" s="148"/>
-      <c r="AA27" s="148"/>
-      <c r="AB27" s="148"/>
-      <c r="AC27" s="148"/>
-      <c r="AD27" s="148"/>
+      <c r="A27" s="148"/>
+      <c r="B27" s="175"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="138"/>
+      <c r="E27" s="138"/>
+      <c r="F27" s="138"/>
+      <c r="G27" s="138"/>
+      <c r="H27" s="138"/>
+      <c r="I27" s="138"/>
+      <c r="J27" s="138"/>
+      <c r="K27" s="138"/>
+      <c r="L27" s="138"/>
+      <c r="M27" s="138"/>
+      <c r="N27" s="138"/>
+      <c r="O27" s="138"/>
+      <c r="P27" s="138"/>
+      <c r="Q27" s="138"/>
+      <c r="R27" s="138"/>
+      <c r="S27" s="138"/>
+      <c r="T27" s="138"/>
+      <c r="U27" s="138"/>
+      <c r="V27" s="138"/>
+      <c r="W27" s="138"/>
+      <c r="X27" s="138"/>
+      <c r="Y27" s="138"/>
+      <c r="Z27" s="138"/>
+      <c r="AA27" s="138"/>
+      <c r="AB27" s="138"/>
+      <c r="AC27" s="138"/>
+      <c r="AD27" s="138"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A28" s="160"/>
-      <c r="B28" s="187"/>
-      <c r="C28" s="148"/>
-      <c r="D28" s="148"/>
-      <c r="E28" s="148"/>
-      <c r="F28" s="148"/>
-      <c r="G28" s="148"/>
-      <c r="H28" s="148"/>
-      <c r="I28" s="148"/>
-      <c r="J28" s="148"/>
-      <c r="K28" s="148"/>
-      <c r="L28" s="148"/>
-      <c r="M28" s="148"/>
-      <c r="N28" s="148"/>
-      <c r="O28" s="148"/>
-      <c r="P28" s="148"/>
-      <c r="Q28" s="148"/>
-      <c r="R28" s="148"/>
-      <c r="S28" s="148"/>
-      <c r="T28" s="148"/>
-      <c r="U28" s="148"/>
-      <c r="V28" s="148"/>
-      <c r="W28" s="148"/>
-      <c r="X28" s="148"/>
-      <c r="Y28" s="148"/>
-      <c r="Z28" s="148"/>
-      <c r="AA28" s="148"/>
-      <c r="AB28" s="148"/>
-      <c r="AC28" s="148"/>
-      <c r="AD28" s="148"/>
+      <c r="A28" s="148"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="138"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="138"/>
+      <c r="K28" s="138"/>
+      <c r="L28" s="138"/>
+      <c r="M28" s="138"/>
+      <c r="N28" s="138"/>
+      <c r="O28" s="138"/>
+      <c r="P28" s="138"/>
+      <c r="Q28" s="138"/>
+      <c r="R28" s="138"/>
+      <c r="S28" s="138"/>
+      <c r="T28" s="138"/>
+      <c r="U28" s="138"/>
+      <c r="V28" s="138"/>
+      <c r="W28" s="138"/>
+      <c r="X28" s="138"/>
+      <c r="Y28" s="138"/>
+      <c r="Z28" s="138"/>
+      <c r="AA28" s="138"/>
+      <c r="AB28" s="138"/>
+      <c r="AC28" s="138"/>
+      <c r="AD28" s="138"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A29" s="160"/>
-      <c r="B29" s="187"/>
-      <c r="C29" s="148"/>
-      <c r="D29" s="148"/>
-      <c r="E29" s="148"/>
-      <c r="F29" s="148"/>
-      <c r="G29" s="148"/>
-      <c r="H29" s="148"/>
-      <c r="I29" s="148"/>
-      <c r="J29" s="148"/>
-      <c r="K29" s="148"/>
-      <c r="L29" s="148"/>
-      <c r="M29" s="148"/>
-      <c r="N29" s="148"/>
-      <c r="O29" s="148"/>
-      <c r="P29" s="148"/>
-      <c r="Q29" s="148"/>
-      <c r="R29" s="148"/>
-      <c r="S29" s="148"/>
-      <c r="T29" s="148"/>
-      <c r="U29" s="148"/>
-      <c r="V29" s="148"/>
-      <c r="W29" s="148"/>
-      <c r="X29" s="148"/>
-      <c r="Y29" s="148"/>
-      <c r="Z29" s="148"/>
-      <c r="AA29" s="148"/>
-      <c r="AB29" s="148"/>
-      <c r="AC29" s="148"/>
-      <c r="AD29" s="148"/>
+      <c r="A29" s="148"/>
+      <c r="B29" s="175"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="138"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="138"/>
+      <c r="K29" s="138"/>
+      <c r="L29" s="138"/>
+      <c r="M29" s="138"/>
+      <c r="N29" s="138"/>
+      <c r="O29" s="138"/>
+      <c r="P29" s="138"/>
+      <c r="Q29" s="138"/>
+      <c r="R29" s="138"/>
+      <c r="S29" s="138"/>
+      <c r="T29" s="138"/>
+      <c r="U29" s="138"/>
+      <c r="V29" s="138"/>
+      <c r="W29" s="138"/>
+      <c r="X29" s="138"/>
+      <c r="Y29" s="138"/>
+      <c r="Z29" s="138"/>
+      <c r="AA29" s="138"/>
+      <c r="AB29" s="138"/>
+      <c r="AC29" s="138"/>
+      <c r="AD29" s="138"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A30" s="160"/>
-      <c r="B30" s="187"/>
-      <c r="C30" s="148"/>
-      <c r="D30" s="148"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="148"/>
-      <c r="G30" s="148"/>
-      <c r="H30" s="148"/>
-      <c r="I30" s="148"/>
-      <c r="J30" s="148"/>
-      <c r="K30" s="148"/>
-      <c r="L30" s="148"/>
-      <c r="M30" s="148"/>
-      <c r="N30" s="148"/>
-      <c r="O30" s="148"/>
-      <c r="P30" s="148"/>
-      <c r="Q30" s="148"/>
-      <c r="R30" s="148"/>
-      <c r="S30" s="148"/>
-      <c r="T30" s="148"/>
-      <c r="U30" s="148"/>
-      <c r="V30" s="148"/>
-      <c r="W30" s="148"/>
-      <c r="X30" s="148"/>
-      <c r="Y30" s="148"/>
-      <c r="Z30" s="148"/>
-      <c r="AA30" s="148"/>
-      <c r="AB30" s="148"/>
-      <c r="AC30" s="148"/>
-      <c r="AD30" s="148"/>
+      <c r="A30" s="148"/>
+      <c r="B30" s="175"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="138"/>
+      <c r="K30" s="138"/>
+      <c r="L30" s="138"/>
+      <c r="M30" s="138"/>
+      <c r="N30" s="138"/>
+      <c r="O30" s="138"/>
+      <c r="P30" s="138"/>
+      <c r="Q30" s="138"/>
+      <c r="R30" s="138"/>
+      <c r="S30" s="138"/>
+      <c r="T30" s="138"/>
+      <c r="U30" s="138"/>
+      <c r="V30" s="138"/>
+      <c r="W30" s="138"/>
+      <c r="X30" s="138"/>
+      <c r="Y30" s="138"/>
+      <c r="Z30" s="138"/>
+      <c r="AA30" s="138"/>
+      <c r="AB30" s="138"/>
+      <c r="AC30" s="138"/>
+      <c r="AD30" s="138"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A31" s="160"/>
-      <c r="B31" s="187"/>
-      <c r="C31" s="148"/>
-      <c r="D31" s="148"/>
-      <c r="E31" s="148"/>
-      <c r="F31" s="148"/>
-      <c r="G31" s="148"/>
-      <c r="H31" s="148"/>
-      <c r="I31" s="148"/>
-      <c r="J31" s="148"/>
-      <c r="K31" s="148"/>
-      <c r="L31" s="148"/>
-      <c r="M31" s="148"/>
-      <c r="N31" s="148"/>
-      <c r="O31" s="148"/>
-      <c r="P31" s="148"/>
-      <c r="Q31" s="148"/>
-      <c r="R31" s="148"/>
-      <c r="S31" s="148"/>
-      <c r="T31" s="148"/>
-      <c r="U31" s="148"/>
-      <c r="V31" s="148"/>
-      <c r="W31" s="148"/>
-      <c r="X31" s="148"/>
-      <c r="Y31" s="148"/>
-      <c r="Z31" s="148"/>
-      <c r="AA31" s="148"/>
-      <c r="AB31" s="148"/>
-      <c r="AC31" s="148"/>
-      <c r="AD31" s="148"/>
+      <c r="A31" s="148"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="138"/>
+      <c r="M31" s="138"/>
+      <c r="N31" s="138"/>
+      <c r="O31" s="138"/>
+      <c r="P31" s="138"/>
+      <c r="Q31" s="138"/>
+      <c r="R31" s="138"/>
+      <c r="S31" s="138"/>
+      <c r="T31" s="138"/>
+      <c r="U31" s="138"/>
+      <c r="V31" s="138"/>
+      <c r="W31" s="138"/>
+      <c r="X31" s="138"/>
+      <c r="Y31" s="138"/>
+      <c r="Z31" s="138"/>
+      <c r="AA31" s="138"/>
+      <c r="AB31" s="138"/>
+      <c r="AC31" s="138"/>
+      <c r="AD31" s="138"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A32" s="160"/>
-      <c r="B32" s="187"/>
-      <c r="C32" s="148"/>
-      <c r="D32" s="148"/>
-      <c r="E32" s="148"/>
-      <c r="F32" s="148"/>
-      <c r="G32" s="148"/>
-      <c r="H32" s="148"/>
-      <c r="I32" s="148"/>
-      <c r="J32" s="148"/>
-      <c r="K32" s="148"/>
-      <c r="L32" s="148"/>
-      <c r="M32" s="148"/>
-      <c r="N32" s="148"/>
-      <c r="O32" s="148"/>
-      <c r="P32" s="148"/>
-      <c r="Q32" s="148"/>
-      <c r="R32" s="148"/>
-      <c r="S32" s="148"/>
-      <c r="T32" s="148"/>
-      <c r="U32" s="148"/>
-      <c r="V32" s="148"/>
-      <c r="W32" s="148"/>
-      <c r="X32" s="148"/>
-      <c r="Y32" s="148"/>
-      <c r="Z32" s="148"/>
-      <c r="AA32" s="148"/>
-      <c r="AB32" s="148"/>
-      <c r="AC32" s="148"/>
-      <c r="AD32" s="148"/>
+      <c r="A32" s="148"/>
+      <c r="B32" s="175"/>
+      <c r="C32" s="138"/>
+      <c r="D32" s="138"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="138"/>
+      <c r="G32" s="138"/>
+      <c r="H32" s="138"/>
+      <c r="I32" s="138"/>
+      <c r="J32" s="138"/>
+      <c r="K32" s="138"/>
+      <c r="L32" s="138"/>
+      <c r="M32" s="138"/>
+      <c r="N32" s="138"/>
+      <c r="O32" s="138"/>
+      <c r="P32" s="138"/>
+      <c r="Q32" s="138"/>
+      <c r="R32" s="138"/>
+      <c r="S32" s="138"/>
+      <c r="T32" s="138"/>
+      <c r="U32" s="138"/>
+      <c r="V32" s="138"/>
+      <c r="W32" s="138"/>
+      <c r="X32" s="138"/>
+      <c r="Y32" s="138"/>
+      <c r="Z32" s="138"/>
+      <c r="AA32" s="138"/>
+      <c r="AB32" s="138"/>
+      <c r="AC32" s="138"/>
+      <c r="AD32" s="138"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" customHeight="1">
-      <c r="A33" s="188"/>
-      <c r="B33" s="187"/>
-      <c r="C33" s="148"/>
-      <c r="D33" s="148"/>
-      <c r="E33" s="148"/>
-      <c r="F33" s="148"/>
-      <c r="G33" s="148"/>
-      <c r="H33" s="148"/>
-      <c r="I33" s="148"/>
-      <c r="J33" s="148"/>
-      <c r="K33" s="148"/>
-      <c r="L33" s="148"/>
-      <c r="M33" s="148"/>
-      <c r="N33" s="148"/>
-      <c r="O33" s="148"/>
-      <c r="P33" s="148"/>
-      <c r="Q33" s="148"/>
-      <c r="R33" s="148"/>
-      <c r="S33" s="148"/>
-      <c r="T33" s="148"/>
-      <c r="U33" s="148"/>
-      <c r="V33" s="148"/>
-      <c r="W33" s="148"/>
-      <c r="X33" s="148"/>
-      <c r="Y33" s="148"/>
-      <c r="Z33" s="148"/>
-      <c r="AA33" s="148"/>
-      <c r="AB33" s="148"/>
-      <c r="AC33" s="148"/>
-      <c r="AD33" s="148"/>
+      <c r="A33" s="176"/>
+      <c r="B33" s="175"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="138"/>
+      <c r="G33" s="138"/>
+      <c r="H33" s="138"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="138"/>
+      <c r="K33" s="138"/>
+      <c r="L33" s="138"/>
+      <c r="M33" s="138"/>
+      <c r="N33" s="138"/>
+      <c r="O33" s="138"/>
+      <c r="P33" s="138"/>
+      <c r="Q33" s="138"/>
+      <c r="R33" s="138"/>
+      <c r="S33" s="138"/>
+      <c r="T33" s="138"/>
+      <c r="U33" s="138"/>
+      <c r="V33" s="138"/>
+      <c r="W33" s="138"/>
+      <c r="X33" s="138"/>
+      <c r="Y33" s="138"/>
+      <c r="Z33" s="138"/>
+      <c r="AA33" s="138"/>
+      <c r="AB33" s="138"/>
+      <c r="AC33" s="138"/>
+      <c r="AD33" s="138"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" customHeight="1">
       <c r="A34" s="21"/>

--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ADAB008-51EE-420F-BB0B-22BB2C3147AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3EA6DA-7DE2-42BF-A0CF-9C6319EBC8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions of use" sheetId="10" r:id="rId1"/>
@@ -825,7 +825,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -73726,12 +73726,12 @@
         <v>86400</v>
       </c>
       <c r="D3" s="38">
-        <f t="shared" ref="D3" si="0">IFERROR(D4+D5*60+D6*3600+D7*3600*24+C3,D4+D5*60+D6*3600+D7*3600*24)</f>
+        <f>IFERROR(D4+D5*60+D6*3600+D7*3600*24+C3,D4+D5*60+D6*3600+D7*3600*24)</f>
         <v>122400</v>
       </c>
       <c r="E3" s="38">
-        <f>IFERROR(E4+E5*60+E6*3600+E7*3600*24+#REF!,E4+E5*60+E6*3600+E7*3600*24)</f>
-        <v>0</v>
+        <f>IFERROR(E4+E5*60+E6*3600+E7*3600*24+D3,E4+E5*60+E6*3600+E7*3600*24)</f>
+        <v>122400</v>
       </c>
       <c r="F3" s="40"/>
       <c r="G3" s="33"/>

--- a/teidecode_v1/Thermal_Data.xlsx
+++ b/teidecode_v1/Thermal_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Navarro\Desktop\Cosas\Teidesat\Nueva carpeta\TeideThermal\teidecode_v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3EA6DA-7DE2-42BF-A0CF-9C6319EBC8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17966D35-6141-4328-A181-1EF3F9427832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions of use" sheetId="10" r:id="rId1"/>
@@ -271,6 +271,20 @@
 @teidesat29@ull.edu.es
 cual es la generación de calor del eps de alta?
 _Asignado a Juan Francisco Hernández Cabrera_</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N49" authorId="1" shapeId="0" xr:uid="{CD16FD44-19D4-4CD8-8BBC-D3E33E181B06}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Stability criteria</t>
         </r>
       </text>
     </comment>
@@ -847,7 +861,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="292">
   <si>
     <t>name</t>
   </si>
@@ -2121,6 +2135,21 @@
       <t>, so one half can be auto-filled. The diagonal values are always zero. Color coding can be used to improve readability.</t>
     </r>
   </si>
+  <si>
+    <t>Maximum allowed temperature (K)</t>
+  </si>
+  <si>
+    <t>Current dt (s)</t>
+  </si>
+  <si>
+    <t>Max dt (s)</t>
+  </si>
+  <si>
+    <t>Max dt (s )</t>
+  </si>
+  <si>
+    <t>Stability Check</t>
+  </si>
 </sst>
 </file>
 
@@ -3226,7 +3255,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="280">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3773,15 +3802,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3891,12 +3911,84 @@
     <xf numFmtId="0" fontId="15" fillId="13" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3948,14 +4040,14 @@
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="Nodes properties-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="secondRowStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="Conductances between nodes-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="secondRowStripe" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -4188,16 +4280,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>53696</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>183279</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1282421</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>97554</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>815172</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>51097</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>176997</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>12997</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4226,8 +4318,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22075496" y="9136779"/>
+          <a:off x="19570421" y="11775204"/>
           <a:ext cx="7762351" cy="4106443"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1628775</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>143331</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>19188</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{420BBA99-7F8A-B017-CBFA-08404467E7B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19916775" y="10515600"/>
+          <a:ext cx="3267531" cy="990738"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4897,7 +5033,7 @@
       </c>
     </row>
     <row r="63" spans="2:2" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="266" t="s">
+      <c r="B63" s="263" t="s">
         <v>286</v>
       </c>
     </row>
@@ -5042,7 +5178,7 @@
       <c r="AD1" s="12"/>
     </row>
     <row r="2" spans="1:79" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="240" t="s">
+      <c r="A2" s="237" t="s">
         <v>260</v>
       </c>
       <c r="B2" s="12"/>
@@ -5111,239 +5247,239 @@
       <c r="A4" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="239" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="239" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="242" t="s">
+      <c r="D4" s="239" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="242" t="s">
+      <c r="E4" s="239" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="242" t="s">
+      <c r="F4" s="239" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="243" t="s">
+      <c r="G4" s="240" t="s">
         <v>153</v>
       </c>
-      <c r="H4" s="243" t="s">
+      <c r="H4" s="240" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="242" t="s">
+      <c r="I4" s="239" t="s">
         <v>154</v>
       </c>
-      <c r="J4" s="242" t="s">
+      <c r="J4" s="239" t="s">
         <v>156</v>
       </c>
-      <c r="K4" s="242" t="s">
+      <c r="K4" s="239" t="s">
         <v>157</v>
       </c>
-      <c r="L4" s="242" t="s">
+      <c r="L4" s="239" t="s">
         <v>158</v>
       </c>
-      <c r="M4" s="243" t="s">
+      <c r="M4" s="240" t="s">
         <v>261</v>
       </c>
-      <c r="N4" s="242" t="s">
+      <c r="N4" s="239" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="242" t="s">
+      <c r="O4" s="239" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="242" t="s">
+      <c r="P4" s="239" t="s">
         <v>98</v>
       </c>
-      <c r="Q4" s="242" t="s">
+      <c r="Q4" s="239" t="s">
         <v>143</v>
       </c>
-      <c r="R4" s="242" t="s">
+      <c r="R4" s="239" t="s">
         <v>144</v>
       </c>
-      <c r="S4" s="242" t="s">
+      <c r="S4" s="239" t="s">
         <v>145</v>
       </c>
-      <c r="T4" s="242" t="s">
+      <c r="T4" s="239" t="s">
         <v>146</v>
       </c>
-      <c r="U4" s="242" t="s">
+      <c r="U4" s="239" t="s">
         <v>147</v>
       </c>
-      <c r="V4" s="242" t="s">
+      <c r="V4" s="239" t="s">
         <v>148</v>
       </c>
-      <c r="W4" s="242" t="s">
+      <c r="W4" s="239" t="s">
         <v>149</v>
       </c>
-      <c r="X4" s="242" t="s">
+      <c r="X4" s="239" t="s">
         <v>150</v>
       </c>
-      <c r="Y4" s="242" t="s">
+      <c r="Y4" s="239" t="s">
         <v>116</v>
       </c>
-      <c r="Z4" s="246" t="s">
+      <c r="Z4" s="243" t="s">
         <v>188</v>
       </c>
-      <c r="AA4" s="248" t="s">
+      <c r="AA4" s="245" t="s">
         <v>115</v>
       </c>
-      <c r="AB4" s="248" t="s">
+      <c r="AB4" s="245" t="s">
         <v>155</v>
       </c>
-      <c r="AC4" s="248" t="s">
+      <c r="AC4" s="245" t="s">
         <v>132</v>
       </c>
-      <c r="AD4" s="248" t="s">
+      <c r="AD4" s="245" t="s">
         <v>117</v>
       </c>
-      <c r="AE4" s="249" t="s">
+      <c r="AE4" s="246" t="s">
         <v>189</v>
       </c>
-      <c r="AF4" s="249" t="s">
+      <c r="AF4" s="246" t="s">
         <v>190</v>
       </c>
-      <c r="AG4" s="249" t="s">
+      <c r="AG4" s="246" t="s">
         <v>229</v>
       </c>
-      <c r="AH4" s="249" t="s">
+      <c r="AH4" s="246" t="s">
         <v>191</v>
       </c>
-      <c r="AI4" s="249" t="s">
+      <c r="AI4" s="246" t="s">
         <v>192</v>
       </c>
-      <c r="AJ4" s="249" t="s">
+      <c r="AJ4" s="246" t="s">
         <v>160</v>
       </c>
-      <c r="AK4" s="249" t="s">
+      <c r="AK4" s="246" t="s">
         <v>161</v>
       </c>
-      <c r="AL4" s="249" t="s">
+      <c r="AL4" s="246" t="s">
         <v>230</v>
       </c>
-      <c r="AM4" s="249" t="s">
+      <c r="AM4" s="246" t="s">
         <v>162</v>
       </c>
-      <c r="AN4" s="249" t="s">
+      <c r="AN4" s="246" t="s">
         <v>163</v>
       </c>
-      <c r="AO4" s="249" t="s">
+      <c r="AO4" s="246" t="s">
         <v>164</v>
       </c>
-      <c r="AP4" s="249" t="s">
+      <c r="AP4" s="246" t="s">
         <v>165</v>
       </c>
-      <c r="AQ4" s="249" t="s">
+      <c r="AQ4" s="246" t="s">
         <v>231</v>
       </c>
-      <c r="AR4" s="249" t="s">
+      <c r="AR4" s="246" t="s">
         <v>166</v>
       </c>
-      <c r="AS4" s="249" t="s">
+      <c r="AS4" s="246" t="s">
         <v>167</v>
       </c>
-      <c r="AT4" s="249" t="s">
+      <c r="AT4" s="246" t="s">
         <v>168</v>
       </c>
-      <c r="AU4" s="249" t="s">
+      <c r="AU4" s="246" t="s">
         <v>169</v>
       </c>
-      <c r="AV4" s="249" t="s">
+      <c r="AV4" s="246" t="s">
         <v>232</v>
       </c>
-      <c r="AW4" s="249" t="s">
+      <c r="AW4" s="246" t="s">
         <v>170</v>
       </c>
-      <c r="AX4" s="249" t="s">
+      <c r="AX4" s="246" t="s">
         <v>171</v>
       </c>
-      <c r="AY4" s="250" t="s">
+      <c r="AY4" s="247" t="s">
         <v>172</v>
       </c>
-      <c r="AZ4" s="250" t="s">
+      <c r="AZ4" s="247" t="s">
         <v>173</v>
       </c>
-      <c r="BA4" s="250" t="s">
+      <c r="BA4" s="247" t="s">
         <v>233</v>
       </c>
-      <c r="BB4" s="250" t="s">
+      <c r="BB4" s="247" t="s">
         <v>174</v>
       </c>
-      <c r="BC4" s="250" t="s">
+      <c r="BC4" s="247" t="s">
         <v>175</v>
       </c>
-      <c r="BD4" s="250" t="s">
+      <c r="BD4" s="247" t="s">
         <v>176</v>
       </c>
-      <c r="BE4" s="250" t="s">
+      <c r="BE4" s="247" t="s">
         <v>177</v>
       </c>
-      <c r="BF4" s="250" t="s">
+      <c r="BF4" s="247" t="s">
         <v>234</v>
       </c>
-      <c r="BG4" s="250" t="s">
+      <c r="BG4" s="247" t="s">
         <v>178</v>
       </c>
-      <c r="BH4" s="250" t="s">
+      <c r="BH4" s="247" t="s">
         <v>179</v>
       </c>
-      <c r="BI4" s="250" t="s">
+      <c r="BI4" s="247" t="s">
         <v>180</v>
       </c>
-      <c r="BJ4" s="250" t="s">
+      <c r="BJ4" s="247" t="s">
         <v>181</v>
       </c>
-      <c r="BK4" s="250" t="s">
+      <c r="BK4" s="247" t="s">
         <v>235</v>
       </c>
-      <c r="BL4" s="250" t="s">
+      <c r="BL4" s="247" t="s">
         <v>182</v>
       </c>
-      <c r="BM4" s="250" t="s">
+      <c r="BM4" s="247" t="s">
         <v>183</v>
       </c>
-      <c r="BN4" s="250" t="s">
+      <c r="BN4" s="247" t="s">
         <v>184</v>
       </c>
-      <c r="BO4" s="250" t="s">
+      <c r="BO4" s="247" t="s">
         <v>185</v>
       </c>
-      <c r="BP4" s="250" t="s">
+      <c r="BP4" s="247" t="s">
         <v>236</v>
       </c>
-      <c r="BQ4" s="250" t="s">
+      <c r="BQ4" s="247" t="s">
         <v>186</v>
       </c>
-      <c r="BR4" s="250" t="s">
+      <c r="BR4" s="247" t="s">
         <v>187</v>
       </c>
-      <c r="BS4" s="248" t="s">
+      <c r="BS4" s="245" t="s">
         <v>159</v>
       </c>
-      <c r="BT4" s="248" t="s">
+      <c r="BT4" s="245" t="s">
         <v>133</v>
       </c>
-      <c r="BU4" s="254" t="str" cm="1">
+      <c r="BU4" s="251" t="str" cm="1">
         <f t="array" ref="BU4:CA4">TRANSPOSE(A76:A82)</f>
         <v>PCB LEDs</v>
       </c>
-      <c r="BV4" s="254" t="str">
+      <c r="BV4" s="251" t="str">
         <v>PCB LEDs Driver(s)</v>
       </c>
-      <c r="BW4" s="254" t="str">
+      <c r="BW4" s="251" t="str">
         <v>PCB BMS &amp; Deploy &amp; RBF</v>
       </c>
-      <c r="BX4" s="254" t="str">
+      <c r="BX4" s="251" t="str">
         <v>PCB MPPTs</v>
       </c>
-      <c r="BY4" s="254" t="str">
+      <c r="BY4" s="251" t="str">
         <v>PCB ADCS</v>
       </c>
-      <c r="BZ4" s="254" t="str">
+      <c r="BZ4" s="251" t="str">
         <v>PCB EPS</v>
       </c>
-      <c r="CA4" s="254" t="str">
+      <c r="CA4" s="251" t="str">
         <v>PCB Memories</v>
       </c>
     </row>
@@ -22365,25 +22501,25 @@
       <c r="P76" s="12">
         <v>3.0345750227525516</v>
       </c>
-      <c r="Q76" s="241">
-        <v>0</v>
-      </c>
-      <c r="R76" s="241">
-        <v>0</v>
-      </c>
-      <c r="S76" s="241">
-        <v>0</v>
-      </c>
-      <c r="T76" s="241">
-        <v>0</v>
-      </c>
-      <c r="U76" s="241">
-        <v>0</v>
-      </c>
-      <c r="V76" s="241">
-        <v>0</v>
-      </c>
-      <c r="W76" s="241">
+      <c r="Q76" s="238">
+        <v>0</v>
+      </c>
+      <c r="R76" s="238">
+        <v>0</v>
+      </c>
+      <c r="S76" s="238">
+        <v>0</v>
+      </c>
+      <c r="T76" s="238">
+        <v>0</v>
+      </c>
+      <c r="U76" s="238">
+        <v>0</v>
+      </c>
+      <c r="V76" s="238">
+        <v>0</v>
+      </c>
+      <c r="W76" s="238">
         <v>0</v>
       </c>
       <c r="X76" s="12">
@@ -61147,7 +61283,7 @@
       </c>
     </row>
     <row r="63" spans="2:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B63" s="265" t="s">
+      <c r="B63" s="262" t="s">
         <v>285</v>
       </c>
     </row>
@@ -61187,7 +61323,7 @@
     <col min="13" max="13" width="21" customWidth="1"/>
     <col min="14" max="14" width="15.7109375" customWidth="1"/>
     <col min="15" max="15" width="25" customWidth="1"/>
-    <col min="16" max="16" width="31" customWidth="1"/>
+    <col min="16" max="16" width="31.85546875" customWidth="1"/>
     <col min="18" max="18" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -62932,74 +63068,93 @@
     <row r="46" spans="1:26" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="2:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="214" t="s">
+    <row r="49" spans="2:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="272" t="s">
         <v>36</v>
       </c>
-      <c r="C49" s="215" t="s">
+      <c r="C49" s="273" t="s">
         <v>30</v>
       </c>
-      <c r="D49" s="215" t="s">
+      <c r="D49" s="273" t="s">
         <v>31</v>
       </c>
-      <c r="E49" s="215" t="s">
+      <c r="E49" s="273" t="s">
         <v>55</v>
       </c>
-      <c r="F49" s="215" t="s">
+      <c r="F49" s="273" t="s">
         <v>32</v>
       </c>
-      <c r="G49" s="215" t="s">
+      <c r="G49" s="273" t="s">
         <v>28</v>
       </c>
-      <c r="H49" s="215" t="s">
+      <c r="H49" s="273" t="s">
         <v>29</v>
       </c>
-      <c r="I49" s="215" t="s">
+      <c r="I49" s="273" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="215" t="s">
+      <c r="J49" s="273" t="s">
         <v>34</v>
       </c>
-      <c r="K49" s="215" t="s">
+      <c r="K49" s="273" t="s">
         <v>35</v>
       </c>
-      <c r="L49" s="215" t="s">
+      <c r="L49" s="273" t="s">
         <v>44</v>
       </c>
-      <c r="M49" s="216" t="s">
+      <c r="M49" s="273" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B50" s="131" t="s">
+      <c r="N49" s="274" t="s">
+        <v>290</v>
+      </c>
+      <c r="P49" s="269" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q49" s="278" t="str">
+        <f>IF(Q52&lt;=Q51,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B50" s="203" t="s">
         <v>88</v>
       </c>
-      <c r="C50" s="133">
+      <c r="C50" s="204">
         <v>1.3869999999999999E-2</v>
       </c>
-      <c r="D50" s="133">
+      <c r="D50" s="204">
         <v>896</v>
       </c>
-      <c r="E50" s="133">
+      <c r="E50" s="204">
         <v>180</v>
       </c>
-      <c r="F50" s="133">
-        <v>0</v>
-      </c>
-      <c r="G50" s="133"/>
-      <c r="H50" s="133"/>
-      <c r="I50" s="134"/>
-      <c r="J50" s="134"/>
-      <c r="K50" s="134"/>
-      <c r="L50" s="134">
-        <v>0</v>
-      </c>
-      <c r="M50" s="135">
-        <v>0</v>
-      </c>
-      <c r="N50" s="40"/>
-    </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F50" s="204">
+        <v>0</v>
+      </c>
+      <c r="G50" s="204"/>
+      <c r="H50" s="204"/>
+      <c r="I50" s="205"/>
+      <c r="J50" s="205"/>
+      <c r="K50" s="205"/>
+      <c r="L50" s="205">
+        <v>0</v>
+      </c>
+      <c r="M50" s="205">
+        <v>0</v>
+      </c>
+      <c r="N50" s="275">
+        <f>(C50*D50)/(F50*G50*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B5:CA5))</f>
+        <v>22.384378248739868</v>
+      </c>
+      <c r="P50" s="270" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q50" s="232">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B51" s="131" t="s">
         <v>89</v>
       </c>
@@ -63023,11 +63178,22 @@
       <c r="L51" s="134">
         <v>0</v>
       </c>
-      <c r="M51" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="M51" s="134">
+        <v>0</v>
+      </c>
+      <c r="N51" s="276">
+        <f>(C51*D51)/(F51*G51*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B6:CA6))</f>
+        <v>11.165026732298825</v>
+      </c>
+      <c r="P51" s="270" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q51" s="232">
+        <f>MIN(N50:N127)</f>
+        <v>1.0278138563623331</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="131" t="s">
         <v>90</v>
       </c>
@@ -63051,11 +63217,22 @@
       <c r="L52" s="134">
         <v>0</v>
       </c>
-      <c r="M52" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="M52" s="134">
+        <v>0</v>
+      </c>
+      <c r="N52" s="276">
+        <f>(C52*D52)/(F52*G52*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B7:CA7))</f>
+        <v>22.029326827346736</v>
+      </c>
+      <c r="P52" s="271" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q52" s="43">
+        <f>'Startup Parameters'!F3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B53" s="131" t="s">
         <v>91</v>
       </c>
@@ -63079,11 +63256,15 @@
       <c r="L53" s="134">
         <v>0</v>
       </c>
-      <c r="M53" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="M53" s="134">
+        <v>0</v>
+      </c>
+      <c r="N53" s="276">
+        <f>(C53*D53)/(F53*G53*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B8:CA8))</f>
+        <v>10.947526211539756</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="131" t="s">
         <v>151</v>
       </c>
@@ -63107,11 +63288,15 @@
       <c r="L54" s="134">
         <v>0</v>
       </c>
-      <c r="M54" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="M54" s="134">
+        <v>0</v>
+      </c>
+      <c r="N54" s="276">
+        <f>(C54*D54)/(F54*G54*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B9:CA9))</f>
+        <v>20.409312</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="131" t="s">
         <v>153</v>
       </c>
@@ -63135,14 +63320,17 @@
       <c r="L55" s="134">
         <v>0</v>
       </c>
-      <c r="M55" s="135">
-        <v>0</v>
-      </c>
-      <c r="N55" s="10"/>
+      <c r="M55" s="134">
+        <v>0</v>
+      </c>
+      <c r="N55" s="276">
+        <f>(C55*D55)/(F55*G55*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B10:CA10))</f>
+        <v>10.148276685082875</v>
+      </c>
       <c r="O55" s="10"/>
       <c r="P55" s="10"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B56" s="131" t="s">
         <v>152</v>
       </c>
@@ -63167,14 +63355,17 @@
       <c r="L56" s="134">
         <v>0</v>
       </c>
-      <c r="M56" s="135">
-        <v>0</v>
-      </c>
-      <c r="N56" s="10"/>
+      <c r="M56" s="134">
+        <v>0</v>
+      </c>
+      <c r="N56" s="276">
+        <f>(C56*D56)/(F56*G56*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B11:CA11))</f>
+        <v>11.822764800000002</v>
+      </c>
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="131" t="s">
         <v>154</v>
       </c>
@@ -63199,14 +63390,17 @@
       <c r="L57" s="134">
         <v>0</v>
       </c>
-      <c r="M57" s="135">
-        <v>0</v>
-      </c>
-      <c r="N57" s="10"/>
+      <c r="M57" s="134">
+        <v>0</v>
+      </c>
+      <c r="N57" s="276">
+        <f>(C57*D57)/(F57*G57*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B12:CA12))</f>
+        <v>5.8787228287292832</v>
+      </c>
       <c r="O57" s="10"/>
       <c r="P57" s="10"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B58" s="131" t="s">
         <v>156</v>
       </c>
@@ -63241,14 +63435,17 @@
       <c r="L58" s="134">
         <v>1</v>
       </c>
-      <c r="M58" s="135">
-        <v>0</v>
-      </c>
-      <c r="N58" s="10"/>
+      <c r="M58" s="134">
+        <v>0</v>
+      </c>
+      <c r="N58" s="276">
+        <f>(C58*D58)/(F58*G58*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B13:CA13))</f>
+        <v>47.544631132059472</v>
+      </c>
       <c r="O58" s="10"/>
       <c r="P58" s="10"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B59" s="131" t="s">
         <v>157</v>
       </c>
@@ -63283,14 +63480,17 @@
       <c r="L59" s="134">
         <v>1</v>
       </c>
-      <c r="M59" s="135">
-        <v>0</v>
-      </c>
-      <c r="N59" s="10"/>
+      <c r="M59" s="134">
+        <v>0</v>
+      </c>
+      <c r="N59" s="276">
+        <f>(C59*D59)/(F59*G59*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B14:CA14))</f>
+        <v>47.544631132059472</v>
+      </c>
       <c r="O59" s="10"/>
       <c r="P59" s="10"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B60" s="131" t="s">
         <v>158</v>
       </c>
@@ -63325,14 +63525,17 @@
       <c r="L60" s="134">
         <v>1</v>
       </c>
-      <c r="M60" s="135">
-        <v>0</v>
-      </c>
-      <c r="N60" s="10"/>
+      <c r="M60" s="134">
+        <v>0</v>
+      </c>
+      <c r="N60" s="276">
+        <f>(C60*D60)/(F60*G60*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B15:CA15))</f>
+        <v>47.544631132059472</v>
+      </c>
       <c r="O60" s="10"/>
       <c r="P60" s="10"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B61" s="131" t="s">
         <v>261</v>
       </c>
@@ -63367,14 +63570,17 @@
       <c r="L61" s="134">
         <v>1</v>
       </c>
-      <c r="M61" s="135">
-        <v>0</v>
-      </c>
-      <c r="N61" s="10"/>
+      <c r="M61" s="134">
+        <v>0</v>
+      </c>
+      <c r="N61" s="276">
+        <f>(C61*D61)/(F61*G61*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B16:CA16))</f>
+        <v>47.544631132059472</v>
+      </c>
       <c r="O61" s="10"/>
       <c r="P61" s="10"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B62" s="131" t="s">
         <v>96</v>
       </c>
@@ -63398,11 +63604,15 @@
       <c r="L62" s="134">
         <v>0</v>
       </c>
-      <c r="M62" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="M62" s="134">
+        <v>0</v>
+      </c>
+      <c r="N62" s="276">
+        <f>(C62*D62)/(F62*G62*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B17:CA17))</f>
+        <v>11.819375770382667</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63" s="131" t="s">
         <v>97</v>
       </c>
@@ -63426,11 +63636,15 @@
       <c r="L63" s="134">
         <v>0</v>
       </c>
-      <c r="M63" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="M63" s="134">
+        <v>0</v>
+      </c>
+      <c r="N63" s="276">
+        <f>(C63*D63)/(F63*G63*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B18:CA18))</f>
+        <v>11.819375770382667</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B64" s="131" t="s">
         <v>98</v>
       </c>
@@ -63454,11 +63668,15 @@
       <c r="L64" s="134">
         <v>0</v>
       </c>
-      <c r="M64" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M64" s="134">
+        <v>0</v>
+      </c>
+      <c r="N64" s="276">
+        <f>(C64*D64)/(F64*G64*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B19:CA19))</f>
+        <v>5.1384353569002599</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B65" s="131" t="s">
         <v>143</v>
       </c>
@@ -63483,11 +63701,15 @@
       <c r="L65" s="134">
         <v>0</v>
       </c>
-      <c r="M65" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M65" s="134">
+        <v>0</v>
+      </c>
+      <c r="N65" s="276">
+        <f>(C65*D65)/(F65*G65*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B20:CA20))</f>
+        <v>269.78200650367336</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B66" s="131" t="s">
         <v>144</v>
       </c>
@@ -63512,11 +63734,15 @@
       <c r="L66" s="134">
         <v>0</v>
       </c>
-      <c r="M66" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M66" s="134">
+        <v>0</v>
+      </c>
+      <c r="N66" s="276">
+        <f>(C66*D66)/(F66*G66*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B21:CA21))</f>
+        <v>236.05037146319614</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B67" s="131" t="s">
         <v>145</v>
       </c>
@@ -63541,11 +63767,15 @@
       <c r="L67" s="134">
         <v>0</v>
       </c>
-      <c r="M67" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M67" s="134">
+        <v>0</v>
+      </c>
+      <c r="N67" s="276">
+        <f>(C67*D67)/(F67*G67*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B22:CA22))</f>
+        <v>269.78200650367336</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B68" s="131" t="s">
         <v>146</v>
       </c>
@@ -63570,11 +63800,15 @@
       <c r="L68" s="134">
         <v>0</v>
       </c>
-      <c r="M68" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M68" s="134">
+        <v>0</v>
+      </c>
+      <c r="N68" s="276">
+        <f>(C68*D68)/(F68*G68*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B23:CA23))</f>
+        <v>236.05037146319614</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B69" s="131" t="s">
         <v>147</v>
       </c>
@@ -63599,11 +63833,15 @@
       <c r="L69" s="134">
         <v>0</v>
       </c>
-      <c r="M69" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M69" s="134">
+        <v>0</v>
+      </c>
+      <c r="N69" s="276">
+        <f>(C69*D69)/(F69*G69*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B24:CA24))</f>
+        <v>269.78200650367336</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B70" s="131" t="s">
         <v>148</v>
       </c>
@@ -63628,11 +63866,15 @@
       <c r="L70" s="134">
         <v>0</v>
       </c>
-      <c r="M70" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M70" s="134">
+        <v>0</v>
+      </c>
+      <c r="N70" s="276">
+        <f>(C70*D70)/(F70*G70*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B25:CA25))</f>
+        <v>236.05037146319614</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B71" s="131" t="s">
         <v>149</v>
       </c>
@@ -63657,11 +63899,15 @@
       <c r="L71" s="134">
         <v>0</v>
       </c>
-      <c r="M71" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M71" s="134">
+        <v>0</v>
+      </c>
+      <c r="N71" s="276">
+        <f>(C71*D71)/(F71*G71*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B26:CA26))</f>
+        <v>269.78200650367336</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B72" s="131" t="s">
         <v>150</v>
       </c>
@@ -63686,11 +63932,15 @@
       <c r="L72" s="134">
         <v>0</v>
       </c>
-      <c r="M72" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M72" s="134">
+        <v>0</v>
+      </c>
+      <c r="N72" s="276">
+        <f>(C72*D72)/(F72*G72*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B27:CA27))</f>
+        <v>236.05037146319614</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B73" s="131" t="s">
         <v>116</v>
       </c>
@@ -63714,43 +63964,47 @@
       <c r="L73" s="134">
         <v>0</v>
       </c>
-      <c r="M73" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M73" s="134">
+        <v>0</v>
+      </c>
+      <c r="N73" s="276">
+        <f>(C73*D73)/(F73*G73*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B28:CA28))</f>
+        <v>205.20160886306059</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B74" s="118" t="s">
         <v>188</v>
       </c>
       <c r="C74" s="139">
         <v>0.2</v>
       </c>
-      <c r="D74" s="141">
+      <c r="D74" s="140">
         <v>800</v>
       </c>
-      <c r="E74" s="141">
+      <c r="E74" s="140">
         <v>50</v>
       </c>
-      <c r="F74" s="140">
-        <v>800</v>
-      </c>
-      <c r="G74" s="140">
-        <v>50</v>
-      </c>
-      <c r="H74" s="139">
-        <v>0</v>
-      </c>
+      <c r="F74" s="141">
+        <v>0</v>
+      </c>
+      <c r="G74" s="140"/>
+      <c r="H74" s="139"/>
       <c r="I74" s="141"/>
       <c r="J74" s="141"/>
       <c r="K74" s="141"/>
       <c r="L74" s="142">
         <v>0</v>
       </c>
-      <c r="M74" s="143">
+      <c r="M74" s="142">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N74" s="276">
+        <f>(C74*D74)/(F74*G74*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B29:CA29))</f>
+        <v>33712.600084281497</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B75" s="119" t="s">
         <v>115</v>
       </c>
@@ -63784,11 +64038,15 @@
       <c r="L75" s="147">
         <v>1</v>
       </c>
-      <c r="M75" s="148">
+      <c r="M75" s="147">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N75" s="276">
+        <f>(C75*D75)/(F75*G75*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B30:CA30))</f>
+        <v>189.39046738055939</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B76" s="119" t="s">
         <v>155</v>
       </c>
@@ -63823,11 +64081,15 @@
       <c r="L76" s="147">
         <v>1</v>
       </c>
-      <c r="M76" s="148">
+      <c r="M76" s="147">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N76" s="276">
+        <f>(C76*D76)/(F76*G76*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B31:CA31))</f>
+        <v>1.0278138563623331</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B77" s="119" t="s">
         <v>132</v>
       </c>
@@ -63851,11 +64113,15 @@
       <c r="L77" s="147">
         <v>0</v>
       </c>
-      <c r="M77" s="148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M77" s="147">
+        <v>0</v>
+      </c>
+      <c r="N77" s="276">
+        <f>(C77*D77)/(F77*G77*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B32:CA32))</f>
+        <v>19384.74504846186</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B78" s="119" t="s">
         <v>117</v>
       </c>
@@ -63879,11 +64145,15 @@
       <c r="L78" s="147">
         <v>0</v>
       </c>
-      <c r="M78" s="148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M78" s="147">
+        <v>0</v>
+      </c>
+      <c r="N78" s="276">
+        <f>(C78*D78)/(F78*G78*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B33:CA33))</f>
+        <v>20.276652994877129</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B79" s="120" t="s">
         <v>189</v>
       </c>
@@ -63919,11 +64189,15 @@
       <c r="L79" s="156">
         <v>1</v>
       </c>
-      <c r="M79" s="157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M79" s="156">
+        <v>0</v>
+      </c>
+      <c r="N79" s="276">
+        <f>(C79*D79)/(F79*G79*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B34:CA34))</f>
+        <v>32.606399429572654</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B80" s="120" t="s">
         <v>190</v>
       </c>
@@ -63959,11 +64233,15 @@
       <c r="L80" s="156">
         <v>1</v>
       </c>
-      <c r="M80" s="157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M80" s="156">
+        <v>0</v>
+      </c>
+      <c r="N80" s="276">
+        <f>(C80*D80)/(F80*G80*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B35:CA35))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B81" s="120" t="s">
         <v>229</v>
       </c>
@@ -63999,11 +64277,15 @@
       <c r="L81" s="156">
         <v>1</v>
       </c>
-      <c r="M81" s="157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M81" s="156">
+        <v>0</v>
+      </c>
+      <c r="N81" s="276">
+        <f>(C81*D81)/(F81*G81*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B36:CA36))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B82" s="120" t="s">
         <v>191</v>
       </c>
@@ -64039,11 +64321,15 @@
       <c r="L82" s="156">
         <v>1</v>
       </c>
-      <c r="M82" s="157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M82" s="156">
+        <v>0</v>
+      </c>
+      <c r="N82" s="276">
+        <f>(C82*D82)/(F82*G82*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B37:CA37))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B83" s="120" t="s">
         <v>192</v>
       </c>
@@ -64079,11 +64365,15 @@
       <c r="L83" s="156">
         <v>1</v>
       </c>
-      <c r="M83" s="157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M83" s="156">
+        <v>0</v>
+      </c>
+      <c r="N83" s="276">
+        <f>(C83*D83)/(F83*G83*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B38:CA38))</f>
+        <v>16.568449908477973</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B84" s="121" t="s">
         <v>160</v>
       </c>
@@ -64119,11 +64409,15 @@
       <c r="L84" s="161">
         <v>1</v>
       </c>
-      <c r="M84" s="162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M84" s="161">
+        <v>0</v>
+      </c>
+      <c r="N84" s="276">
+        <f>(C84*D84)/(F84*G84*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B39:CA39))</f>
+        <v>32.606399429572654</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B85" s="121" t="s">
         <v>161</v>
       </c>
@@ -64159,11 +64453,15 @@
       <c r="L85" s="161">
         <v>1</v>
       </c>
-      <c r="M85" s="162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M85" s="161">
+        <v>0</v>
+      </c>
+      <c r="N85" s="276">
+        <f>(C85*D85)/(F85*G85*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B40:CA40))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="86" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B86" s="121" t="s">
         <v>230</v>
       </c>
@@ -64199,11 +64497,15 @@
       <c r="L86" s="161">
         <v>1</v>
       </c>
-      <c r="M86" s="162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M86" s="161">
+        <v>0</v>
+      </c>
+      <c r="N86" s="276">
+        <f>(C86*D86)/(F86*G86*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B41:CA41))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B87" s="121" t="s">
         <v>162</v>
       </c>
@@ -64239,11 +64541,15 @@
       <c r="L87" s="161">
         <v>1</v>
       </c>
-      <c r="M87" s="162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M87" s="161">
+        <v>0</v>
+      </c>
+      <c r="N87" s="276">
+        <f>(C87*D87)/(F87*G87*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B42:CA42))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="88" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B88" s="121" t="s">
         <v>163</v>
       </c>
@@ -64279,11 +64585,15 @@
       <c r="L88" s="161">
         <v>1</v>
       </c>
-      <c r="M88" s="162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M88" s="161">
+        <v>0</v>
+      </c>
+      <c r="N88" s="276">
+        <f>(C88*D88)/(F88*G88*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B43:CA43))</f>
+        <v>16.568449908477973</v>
+      </c>
+    </row>
+    <row r="89" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B89" s="122" t="s">
         <v>164</v>
       </c>
@@ -64319,11 +64629,15 @@
       <c r="L89" s="166">
         <v>1</v>
       </c>
-      <c r="M89" s="167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M89" s="166">
+        <v>0</v>
+      </c>
+      <c r="N89" s="276">
+        <f>(C89*D89)/(F89*G89*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B44:CA44))</f>
+        <v>32.606399429572654</v>
+      </c>
+    </row>
+    <row r="90" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B90" s="122" t="s">
         <v>165</v>
       </c>
@@ -64359,11 +64673,15 @@
       <c r="L90" s="166">
         <v>1</v>
       </c>
-      <c r="M90" s="167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M90" s="166">
+        <v>0</v>
+      </c>
+      <c r="N90" s="276">
+        <f>(C90*D90)/(F90*G90*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B45:CA45))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="91" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B91" s="122" t="s">
         <v>231</v>
       </c>
@@ -64399,11 +64717,15 @@
       <c r="L91" s="166">
         <v>1</v>
       </c>
-      <c r="M91" s="167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M91" s="166">
+        <v>0</v>
+      </c>
+      <c r="N91" s="276">
+        <f>(C91*D91)/(F91*G91*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B46:CA46))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="92" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B92" s="122" t="s">
         <v>166</v>
       </c>
@@ -64439,11 +64761,15 @@
       <c r="L92" s="166">
         <v>1</v>
       </c>
-      <c r="M92" s="167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M92" s="166">
+        <v>0</v>
+      </c>
+      <c r="N92" s="276">
+        <f>(C92*D92)/(F92*G92*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B47:CA47))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="93" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B93" s="122" t="s">
         <v>167</v>
       </c>
@@ -64479,11 +64805,15 @@
       <c r="L93" s="166">
         <v>1</v>
       </c>
-      <c r="M93" s="167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M93" s="166">
+        <v>0</v>
+      </c>
+      <c r="N93" s="276">
+        <f>(C93*D93)/(F93*G93*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B48:CA48))</f>
+        <v>16.568449908477973</v>
+      </c>
+    </row>
+    <row r="94" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B94" s="123" t="s">
         <v>168</v>
       </c>
@@ -64519,11 +64849,15 @@
       <c r="L94" s="171">
         <v>1</v>
       </c>
-      <c r="M94" s="172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M94" s="171">
+        <v>0</v>
+      </c>
+      <c r="N94" s="276">
+        <f>(C94*D94)/(F94*G94*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B49:CA49))</f>
+        <v>32.606399429572654</v>
+      </c>
+    </row>
+    <row r="95" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B95" s="123" t="s">
         <v>169</v>
       </c>
@@ -64559,11 +64893,15 @@
       <c r="L95" s="171">
         <v>1</v>
       </c>
-      <c r="M95" s="172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M95" s="171">
+        <v>0</v>
+      </c>
+      <c r="N95" s="276">
+        <f>(C95*D95)/(F95*G95*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B50:CA50))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="96" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B96" s="123" t="s">
         <v>232</v>
       </c>
@@ -64599,11 +64937,15 @@
       <c r="L96" s="171">
         <v>1</v>
       </c>
-      <c r="M96" s="172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M96" s="171">
+        <v>0</v>
+      </c>
+      <c r="N96" s="276">
+        <f>(C96*D96)/(F96*G96*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B51:CA51))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="97" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B97" s="123" t="s">
         <v>170</v>
       </c>
@@ -64639,11 +64981,15 @@
       <c r="L97" s="171">
         <v>1</v>
       </c>
-      <c r="M97" s="172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M97" s="171">
+        <v>0</v>
+      </c>
+      <c r="N97" s="276">
+        <f>(C97*D97)/(F97*G97*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B52:CA52))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="98" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B98" s="123" t="s">
         <v>171</v>
       </c>
@@ -64679,11 +65025,15 @@
       <c r="L98" s="171">
         <v>1</v>
       </c>
-      <c r="M98" s="172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M98" s="171">
+        <v>0</v>
+      </c>
+      <c r="N98" s="276">
+        <f>(C98*D98)/(F98*G98*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B53:CA53))</f>
+        <v>16.568449908477973</v>
+      </c>
+    </row>
+    <row r="99" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B99" s="124" t="s">
         <v>172</v>
       </c>
@@ -64719,11 +65069,15 @@
       <c r="L99" s="176">
         <v>1</v>
       </c>
-      <c r="M99" s="177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M99" s="176">
+        <v>0</v>
+      </c>
+      <c r="N99" s="276">
+        <f>(C99*D99)/(F99*G99*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B54:CA54))</f>
+        <v>33.347453962062943</v>
+      </c>
+    </row>
+    <row r="100" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B100" s="124" t="s">
         <v>173</v>
       </c>
@@ -64759,11 +65113,15 @@
       <c r="L100" s="176">
         <v>1</v>
       </c>
-      <c r="M100" s="177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M100" s="176">
+        <v>0</v>
+      </c>
+      <c r="N100" s="276">
+        <f>(C100*D100)/(F100*G100*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B55:CA55))</f>
+        <v>874.38305576136258</v>
+      </c>
+    </row>
+    <row r="101" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B101" s="124" t="s">
         <v>233</v>
       </c>
@@ -64799,11 +65157,15 @@
       <c r="L101" s="176">
         <v>1</v>
       </c>
-      <c r="M101" s="177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M101" s="176">
+        <v>0</v>
+      </c>
+      <c r="N101" s="276">
+        <f>(C101*D101)/(F101*G101*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B56:CA56))</f>
+        <v>874.38305576136258</v>
+      </c>
+    </row>
+    <row r="102" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B102" s="124" t="s">
         <v>174</v>
       </c>
@@ -64839,11 +65201,15 @@
       <c r="L102" s="176">
         <v>1</v>
       </c>
-      <c r="M102" s="177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M102" s="176">
+        <v>0</v>
+      </c>
+      <c r="N102" s="276">
+        <f>(C102*D102)/(F102*G102*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B57:CA57))</f>
+        <v>874.38305576136258</v>
+      </c>
+    </row>
+    <row r="103" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B103" s="124" t="s">
         <v>175</v>
       </c>
@@ -64879,11 +65245,15 @@
       <c r="L103" s="176">
         <v>1</v>
       </c>
-      <c r="M103" s="177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M103" s="176">
+        <v>0</v>
+      </c>
+      <c r="N103" s="276">
+        <f>(C103*D103)/(F103*G103*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B58:CA58))</f>
+        <v>16.945005588216112</v>
+      </c>
+    </row>
+    <row r="104" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B104" s="125" t="s">
         <v>176</v>
       </c>
@@ -64919,11 +65289,15 @@
       <c r="L104" s="181">
         <v>1</v>
       </c>
-      <c r="M104" s="182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M104" s="181">
+        <v>0</v>
+      </c>
+      <c r="N104" s="276">
+        <f>(C104*D104)/(F104*G104*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B59:CA59))</f>
+        <v>39.27589022198525</v>
+      </c>
+    </row>
+    <row r="105" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B105" s="125" t="s">
         <v>177</v>
       </c>
@@ -64959,11 +65333,15 @@
       <c r="L105" s="181">
         <v>1</v>
       </c>
-      <c r="M105" s="182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M105" s="181">
+        <v>0</v>
+      </c>
+      <c r="N105" s="276">
+        <f>(C105*D105)/(F105*G105*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B60:CA60))</f>
+        <v>1029.8289323411605</v>
+      </c>
+    </row>
+    <row r="106" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B106" s="125" t="s">
         <v>234</v>
       </c>
@@ -64999,11 +65377,15 @@
       <c r="L106" s="181">
         <v>1</v>
       </c>
-      <c r="M106" s="182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M106" s="181">
+        <v>0</v>
+      </c>
+      <c r="N106" s="276">
+        <f>(C106*D106)/(F106*G106*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B61:CA61))</f>
+        <v>1029.8289323411605</v>
+      </c>
+    </row>
+    <row r="107" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B107" s="125" t="s">
         <v>178</v>
       </c>
@@ -65039,11 +65421,15 @@
       <c r="L107" s="181">
         <v>1</v>
       </c>
-      <c r="M107" s="182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M107" s="181">
+        <v>0</v>
+      </c>
+      <c r="N107" s="276">
+        <f>(C107*D107)/(F107*G107*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B62:CA62))</f>
+        <v>1029.8289323411605</v>
+      </c>
+    </row>
+    <row r="108" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B108" s="125" t="s">
         <v>179</v>
       </c>
@@ -65079,11 +65465,15 @@
       <c r="L108" s="181">
         <v>1</v>
       </c>
-      <c r="M108" s="182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M108" s="181">
+        <v>0</v>
+      </c>
+      <c r="N108" s="276">
+        <f>(C108*D108)/(F108*G108*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B63:CA63))</f>
+        <v>19.957451026121198</v>
+      </c>
+    </row>
+    <row r="109" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B109" s="126" t="s">
         <v>180</v>
       </c>
@@ -65108,10 +65498,10 @@
         <v>0.95</v>
       </c>
       <c r="I109" s="185">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109" s="185">
         <v>0</v>
@@ -65119,11 +65509,15 @@
       <c r="L109" s="186">
         <v>1</v>
       </c>
-      <c r="M109" s="187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M109" s="186">
+        <v>0</v>
+      </c>
+      <c r="N109" s="276">
+        <f>(C109*D109)/(F109*G109*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B64:CA64))</f>
+        <v>39.27589022198525</v>
+      </c>
+    </row>
+    <row r="110" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B110" s="126" t="s">
         <v>181</v>
       </c>
@@ -65148,10 +65542,10 @@
         <v>0.95</v>
       </c>
       <c r="I110" s="185">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J110" s="185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K110" s="185">
         <v>0</v>
@@ -65159,11 +65553,15 @@
       <c r="L110" s="186">
         <v>1</v>
       </c>
-      <c r="M110" s="187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M110" s="186">
+        <v>0</v>
+      </c>
+      <c r="N110" s="276">
+        <f>(C110*D110)/(F110*G110*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B65:CA65))</f>
+        <v>1029.8289323411605</v>
+      </c>
+    </row>
+    <row r="111" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B111" s="126" t="s">
         <v>235</v>
       </c>
@@ -65188,10 +65586,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" s="185">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K111" s="185">
         <v>0</v>
@@ -65199,11 +65597,15 @@
       <c r="L111" s="186">
         <v>1</v>
       </c>
-      <c r="M111" s="187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M111" s="186">
+        <v>0</v>
+      </c>
+      <c r="N111" s="276">
+        <f>(C111*D111)/(F111*G111*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B66:CA66))</f>
+        <v>1029.8289323411605</v>
+      </c>
+    </row>
+    <row r="112" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B112" s="126" t="s">
         <v>182</v>
       </c>
@@ -65228,10 +65630,10 @@
         <v>0.95</v>
       </c>
       <c r="I112" s="185">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J112" s="185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" s="185">
         <v>0</v>
@@ -65239,11 +65641,15 @@
       <c r="L112" s="186">
         <v>1</v>
       </c>
-      <c r="M112" s="187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M112" s="186">
+        <v>0</v>
+      </c>
+      <c r="N112" s="276">
+        <f>(C112*D112)/(F112*G112*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B67:CA67))</f>
+        <v>1029.8289323411605</v>
+      </c>
+    </row>
+    <row r="113" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B113" s="126" t="s">
         <v>183</v>
       </c>
@@ -65268,10 +65674,10 @@
         <v>0.95</v>
       </c>
       <c r="I113" s="185">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K113" s="185">
         <v>0</v>
@@ -65279,11 +65685,15 @@
       <c r="L113" s="186">
         <v>1</v>
       </c>
-      <c r="M113" s="187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M113" s="186">
+        <v>0</v>
+      </c>
+      <c r="N113" s="276">
+        <f>(C113*D113)/(F113*G113*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B68:CA68))</f>
+        <v>19.957451026121198</v>
+      </c>
+    </row>
+    <row r="114" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B114" s="127" t="s">
         <v>184</v>
       </c>
@@ -65319,11 +65729,15 @@
       <c r="L114" s="191">
         <v>1</v>
       </c>
-      <c r="M114" s="192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M114" s="191">
+        <v>0</v>
+      </c>
+      <c r="N114" s="276">
+        <f>(C114*D114)/(F114*G114*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B69:CA69))</f>
+        <v>32.606399429572654</v>
+      </c>
+    </row>
+    <row r="115" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B115" s="127" t="s">
         <v>185</v>
       </c>
@@ -65359,11 +65773,15 @@
       <c r="L115" s="191">
         <v>1</v>
       </c>
-      <c r="M115" s="192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M115" s="191">
+        <v>0</v>
+      </c>
+      <c r="N115" s="276">
+        <f>(C115*D115)/(F115*G115*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B70:CA70))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="116" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B116" s="127" t="s">
         <v>236</v>
       </c>
@@ -65399,11 +65817,15 @@
       <c r="L116" s="191">
         <v>1</v>
       </c>
-      <c r="M116" s="192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M116" s="191">
+        <v>0</v>
+      </c>
+      <c r="N116" s="276">
+        <f>(C116*D116)/(F116*G116*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B71:CA71))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="117" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B117" s="127" t="s">
         <v>186</v>
       </c>
@@ -65439,11 +65861,15 @@
       <c r="L117" s="191">
         <v>1</v>
       </c>
-      <c r="M117" s="192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M117" s="191">
+        <v>0</v>
+      </c>
+      <c r="N117" s="276">
+        <f>(C117*D117)/(F117*G117*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B72:CA72))</f>
+        <v>854.95232118888782</v>
+      </c>
+    </row>
+    <row r="118" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B118" s="127" t="s">
         <v>187</v>
       </c>
@@ -65479,11 +65905,15 @@
       <c r="L118" s="191">
         <v>1</v>
       </c>
-      <c r="M118" s="192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M118" s="191">
+        <v>0</v>
+      </c>
+      <c r="N118" s="276">
+        <f>(C118*D118)/(F118*G118*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B73:CA73))</f>
+        <v>16.568449908477973</v>
+      </c>
+    </row>
+    <row r="119" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B119" s="119" t="s">
         <v>159</v>
       </c>
@@ -65518,11 +65948,15 @@
       <c r="L119" s="147">
         <v>1</v>
       </c>
-      <c r="M119" s="148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M119" s="147">
+        <v>0</v>
+      </c>
+      <c r="N119" s="276">
+        <f>(C119*D119)/(F119*G119*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B74:CA74))</f>
+        <v>54.492793205074868</v>
+      </c>
+    </row>
+    <row r="120" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B120" s="128" t="s">
         <v>133</v>
       </c>
@@ -65546,11 +65980,15 @@
       <c r="L120" s="147">
         <v>0</v>
       </c>
-      <c r="M120" s="148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M120" s="147">
+        <v>0</v>
+      </c>
+      <c r="N120" s="276">
+        <f>(C120*D120)/(F120*G120*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B75:CA75))</f>
+        <v>50568.900126422246</v>
+      </c>
+    </row>
+    <row r="121" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B121" s="129" t="s">
         <v>123</v>
       </c>
@@ -65585,11 +66023,15 @@
       <c r="L121" s="196">
         <v>1</v>
       </c>
-      <c r="M121" s="197">
+      <c r="M121" s="196">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N121" s="276">
+        <f>(C121*D121)/(F121*G121*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B76:CA76))</f>
+        <v>13.274948795356936</v>
+      </c>
+    </row>
+    <row r="122" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B122" s="129" t="s">
         <v>126</v>
       </c>
@@ -65613,11 +66055,15 @@
       <c r="L122" s="196">
         <v>0</v>
       </c>
-      <c r="M122" s="197">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M122" s="196">
+        <v>0</v>
+      </c>
+      <c r="N122" s="276">
+        <f>(C122*D122)/(F122*G122*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B77:CA77))</f>
+        <v>11588.706278971766</v>
+      </c>
+    </row>
+    <row r="123" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B123" s="129" t="s">
         <v>125</v>
       </c>
@@ -65641,11 +66087,15 @@
       <c r="L123" s="196">
         <v>0</v>
       </c>
-      <c r="M123" s="197">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M123" s="196">
+        <v>0</v>
+      </c>
+      <c r="N123" s="276">
+        <f>(C123*D123)/(F123*G123*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B78:CA78))</f>
+        <v>11588.706278971766</v>
+      </c>
+    </row>
+    <row r="124" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B124" s="129" t="s">
         <v>124</v>
       </c>
@@ -65669,11 +66119,15 @@
       <c r="L124" s="196">
         <v>0</v>
       </c>
-      <c r="M124" s="197">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M124" s="196">
+        <v>0</v>
+      </c>
+      <c r="N124" s="276">
+        <f>(C124*D124)/(F124*G124*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B79:CA79))</f>
+        <v>11588.706278971766</v>
+      </c>
+    </row>
+    <row r="125" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B125" s="129" t="s">
         <v>127</v>
       </c>
@@ -65697,11 +66151,15 @@
       <c r="L125" s="196">
         <v>0</v>
       </c>
-      <c r="M125" s="197">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M125" s="196">
+        <v>0</v>
+      </c>
+      <c r="N125" s="276">
+        <f>(C125*D125)/(F125*G125*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B80:CA80))</f>
+        <v>11588.706278971766</v>
+      </c>
+    </row>
+    <row r="126" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B126" s="129" t="s">
         <v>129</v>
       </c>
@@ -65725,11 +66183,15 @@
       <c r="L126" s="196">
         <v>0</v>
       </c>
-      <c r="M126" s="197">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M126" s="196">
+        <v>0</v>
+      </c>
+      <c r="N126" s="276">
+        <f>(C126*D126)/(F126*G126*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B81:CA81))</f>
+        <v>11588.706278971766</v>
+      </c>
+    </row>
+    <row r="127" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B127" s="130" t="s">
         <v>128</v>
       </c>
@@ -65753,11 +66215,15 @@
       <c r="L127" s="201">
         <v>0</v>
       </c>
-      <c r="M127" s="202">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M127" s="201">
+        <v>0</v>
+      </c>
+      <c r="N127" s="277">
+        <f>(C127*D127)/(F127*G127*56.703*10^(-9)*$Q$50^3+SUM(Conductances_between_nodes!B82:CA82))</f>
+        <v>11588.706278971766</v>
+      </c>
+    </row>
+    <row r="128" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I128" s="132"/>
       <c r="J128" s="132"/>
       <c r="K128" s="132"/>
@@ -69644,6 +70110,19 @@
       <c r="E1050" s="1"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="Q49">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>$Q$49="FAIL"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>$Q$49="PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N50:N127">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>N50&lt;$Q$52</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -69686,14 +70165,14 @@
       <c r="B3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="217" t="s">
+      <c r="C3" s="214" t="s">
         <v>248</v>
       </c>
       <c r="H3" s="17"/>
-      <c r="I3" s="267" t="s">
+      <c r="I3" s="264" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="268"/>
+      <c r="J3" s="265"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4" s="18" t="s">
@@ -69716,7 +70195,7 @@
       <c r="B5" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="217" t="s">
+      <c r="C5" s="214" t="s">
         <v>246</v>
       </c>
       <c r="H5" s="23">
@@ -69733,7 +70212,7 @@
       <c r="B6" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="217" t="s">
+      <c r="C6" s="214" t="s">
         <v>247</v>
       </c>
       <c r="H6" s="27">
@@ -69783,527 +70262,527 @@
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="231" t="s">
+      <c r="B11" s="228" t="s">
         <v>224</v>
       </c>
-      <c r="C11" s="232" t="s">
+      <c r="C11" s="229" t="s">
         <v>223</v>
       </c>
-      <c r="D11" s="233" t="s">
+      <c r="D11" s="230" t="s">
         <v>257</v>
       </c>
-      <c r="E11" s="232" t="s">
+      <c r="E11" s="229" t="s">
         <v>222</v>
       </c>
-      <c r="F11" s="233" t="s">
+      <c r="F11" s="230" t="s">
         <v>237</v>
       </c>
-      <c r="G11" s="232" t="s">
+      <c r="G11" s="229" t="s">
         <v>228</v>
       </c>
-      <c r="H11" s="232" t="s">
+      <c r="H11" s="229" t="s">
         <v>225</v>
       </c>
-      <c r="I11" s="232" t="s">
+      <c r="I11" s="229" t="s">
         <v>227</v>
       </c>
-      <c r="J11" s="232" t="s">
+      <c r="J11" s="229" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="232" t="s">
+      <c r="K11" s="229" t="s">
         <v>226</v>
       </c>
-      <c r="L11" s="234" t="s">
+      <c r="L11" s="231" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="245" t="s">
+      <c r="A12" s="242" t="s">
         <v>263</v>
       </c>
       <c r="B12" s="119" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="219" t="s">
+      <c r="C12" s="216" t="s">
         <v>238</v>
       </c>
       <c r="D12" s="85">
         <v>180</v>
       </c>
-      <c r="E12" s="220" t="s">
+      <c r="E12" s="217" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="218">
+      <c r="F12" s="215">
         <v>303.95999999999998</v>
       </c>
-      <c r="G12" s="218">
+      <c r="G12" s="215">
         <v>50</v>
       </c>
-      <c r="H12" s="218"/>
-      <c r="I12" s="218">
-        <v>0</v>
-      </c>
-      <c r="J12" s="218"/>
-      <c r="K12" s="218">
+      <c r="H12" s="215"/>
+      <c r="I12" s="215">
+        <v>0</v>
+      </c>
+      <c r="J12" s="215"/>
+      <c r="K12" s="215">
         <v>10.89</v>
       </c>
-      <c r="L12" s="224">
+      <c r="L12" s="221">
         <f>F12*G12/10^6+I12*1/K12</f>
         <v>1.5197999999999998E-2</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="245" t="s">
+      <c r="A13" s="242" t="s">
         <v>263</v>
       </c>
       <c r="B13" s="119" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="244" t="s">
+      <c r="C13" s="241" t="s">
         <v>266</v>
       </c>
       <c r="D13" s="100">
         <v>50</v>
       </c>
-      <c r="E13" s="220" t="s">
+      <c r="E13" s="217" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="219">
+      <c r="F13" s="216">
         <v>23.73</v>
       </c>
-      <c r="G13" s="218">
+      <c r="G13" s="215">
         <v>50</v>
       </c>
-      <c r="H13" s="218"/>
-      <c r="I13" s="218">
-        <v>0</v>
-      </c>
-      <c r="J13" s="218"/>
-      <c r="K13" s="218">
+      <c r="H13" s="215"/>
+      <c r="I13" s="215">
+        <v>0</v>
+      </c>
+      <c r="J13" s="215"/>
+      <c r="K13" s="215">
         <v>10.89</v>
       </c>
-      <c r="L13" s="224">
+      <c r="L13" s="221">
         <f t="shared" ref="L13:L32" si="0">F13*G13/10^6+I13*1/K13</f>
         <v>1.1865000000000001E-3</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="245" t="s">
+      <c r="A14" s="242" t="s">
         <v>263</v>
       </c>
       <c r="B14" s="119" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="244" t="s">
+      <c r="C14" s="241" t="s">
         <v>267</v>
       </c>
       <c r="D14" s="106">
         <v>177</v>
       </c>
-      <c r="E14" s="221" t="s">
+      <c r="E14" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="218">
+      <c r="F14" s="215">
         <v>470.9</v>
       </c>
-      <c r="G14" s="218">
-        <v>0</v>
-      </c>
-      <c r="H14" s="218">
+      <c r="G14" s="215">
+        <v>0</v>
+      </c>
+      <c r="H14" s="215">
         <v>4</v>
       </c>
-      <c r="I14" s="218">
+      <c r="I14" s="215">
         <v>2</v>
       </c>
-      <c r="J14" s="219" t="s">
+      <c r="J14" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="218">
+      <c r="K14" s="215">
         <v>2.7</v>
       </c>
-      <c r="L14" s="224">
+      <c r="L14" s="221">
         <f t="shared" si="0"/>
         <v>0.7407407407407407</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="247" t="s">
+      <c r="A15" s="244" t="s">
         <v>263</v>
       </c>
       <c r="B15" s="119" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="219" t="s">
+      <c r="C15" s="216" t="s">
         <v>245</v>
       </c>
       <c r="D15" s="106">
         <v>177</v>
       </c>
-      <c r="E15" s="220" t="s">
+      <c r="E15" s="217" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="218">
+      <c r="F15" s="215">
         <v>166.55</v>
       </c>
-      <c r="G15" s="218">
+      <c r="G15" s="215">
         <v>50</v>
       </c>
-      <c r="H15" s="218"/>
-      <c r="I15" s="218">
-        <v>0</v>
-      </c>
-      <c r="J15" s="219"/>
-      <c r="K15" s="218">
+      <c r="H15" s="215"/>
+      <c r="I15" s="215">
+        <v>0</v>
+      </c>
+      <c r="J15" s="216"/>
+      <c r="K15" s="215">
         <v>10.89</v>
       </c>
-      <c r="L15" s="224">
+      <c r="L15" s="221">
         <f t="shared" si="0"/>
         <v>8.3274999999999998E-3</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="247" t="s">
+      <c r="A16" s="244" t="s">
         <v>263</v>
       </c>
       <c r="B16" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="C16" s="219" t="s">
+      <c r="C16" s="216" t="s">
         <v>243</v>
       </c>
       <c r="D16" s="107">
         <v>0.4</v>
       </c>
-      <c r="E16" s="221" t="s">
+      <c r="E16" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="218">
+      <c r="F16" s="215">
         <v>651.29999999999995</v>
       </c>
-      <c r="G16" s="218">
-        <v>0</v>
-      </c>
-      <c r="H16" s="218">
+      <c r="G16" s="215">
+        <v>0</v>
+      </c>
+      <c r="H16" s="215">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I16" s="218">
+      <c r="I16" s="215">
         <v>2</v>
       </c>
-      <c r="J16" s="219" t="s">
+      <c r="J16" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="218">
+      <c r="K16" s="215">
         <v>10.89</v>
       </c>
-      <c r="L16" s="224">
+      <c r="L16" s="221">
         <f t="shared" si="0"/>
         <v>0.18365472910927455</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="247" t="s">
+      <c r="A17" s="244" t="s">
         <v>263</v>
       </c>
       <c r="B17" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="C17" s="244" t="s">
+      <c r="C17" s="241" t="s">
         <v>262</v>
       </c>
       <c r="D17" s="107">
         <v>0.4</v>
       </c>
-      <c r="E17" s="221" t="s">
+      <c r="E17" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="218">
+      <c r="F17" s="215">
         <v>1311.67</v>
       </c>
-      <c r="G17" s="218">
-        <v>0</v>
-      </c>
-      <c r="H17" s="218">
+      <c r="G17" s="215">
+        <v>0</v>
+      </c>
+      <c r="H17" s="215">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I17" s="218">
+      <c r="I17" s="215">
         <v>2</v>
       </c>
-      <c r="J17" s="219" t="s">
+      <c r="J17" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="218">
+      <c r="K17" s="215">
         <v>10.89</v>
       </c>
-      <c r="L17" s="224">
+      <c r="L17" s="221">
         <f t="shared" si="0"/>
         <v>0.18365472910927455</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="247" t="s">
+      <c r="A18" s="244" t="s">
         <v>263</v>
       </c>
       <c r="B18" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="241" t="s">
         <v>92</v>
       </c>
       <c r="D18" s="107">
         <v>0.4</v>
       </c>
-      <c r="E18" s="221" t="s">
+      <c r="E18" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="218">
+      <c r="F18" s="215">
         <v>650.79999999999995</v>
       </c>
-      <c r="G18" s="218">
-        <v>0</v>
-      </c>
-      <c r="H18" s="218">
+      <c r="G18" s="215">
+        <v>0</v>
+      </c>
+      <c r="H18" s="215">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I18" s="218">
+      <c r="I18" s="215">
         <v>2</v>
       </c>
-      <c r="J18" s="219" t="s">
+      <c r="J18" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="215">
         <v>10.89</v>
       </c>
-      <c r="L18" s="224">
+      <c r="L18" s="221">
         <f t="shared" si="0"/>
         <v>0.18365472910927455</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="247" t="s">
+      <c r="A19" s="244" t="s">
         <v>263</v>
       </c>
       <c r="B19" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="C19" s="244" t="s">
+      <c r="C19" s="241" t="s">
         <v>93</v>
       </c>
       <c r="D19" s="107">
         <v>0.4</v>
       </c>
-      <c r="E19" s="221" t="s">
+      <c r="E19" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="218">
+      <c r="F19" s="215">
         <v>830.59</v>
       </c>
-      <c r="G19" s="218">
-        <v>0</v>
-      </c>
-      <c r="H19" s="218">
+      <c r="G19" s="215">
+        <v>0</v>
+      </c>
+      <c r="H19" s="215">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I19" s="218">
+      <c r="I19" s="215">
         <v>2</v>
       </c>
-      <c r="J19" s="219" t="s">
+      <c r="J19" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K19" s="218">
+      <c r="K19" s="215">
         <v>10.89</v>
       </c>
-      <c r="L19" s="224">
+      <c r="L19" s="221">
         <f t="shared" si="0"/>
         <v>0.18365472910927455</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="247" t="s">
+      <c r="A20" s="244" t="s">
         <v>263</v>
       </c>
       <c r="B20" s="119" t="s">
         <v>240</v>
       </c>
-      <c r="C20" s="219" t="s">
+      <c r="C20" s="216" t="s">
         <v>117</v>
       </c>
       <c r="D20" s="107">
         <v>0.4</v>
       </c>
-      <c r="E20" s="221" t="s">
+      <c r="E20" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="218">
+      <c r="F20" s="215">
         <v>9306.35</v>
       </c>
-      <c r="G20" s="218">
-        <v>0</v>
-      </c>
-      <c r="H20" s="218">
+      <c r="G20" s="215">
+        <v>0</v>
+      </c>
+      <c r="H20" s="215">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I20" s="218">
+      <c r="I20" s="215">
         <v>8</v>
       </c>
-      <c r="J20" s="219" t="s">
+      <c r="J20" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K20" s="218">
+      <c r="K20" s="215">
         <v>10.89</v>
       </c>
-      <c r="L20" s="224">
+      <c r="L20" s="221">
         <f t="shared" si="0"/>
         <v>0.7346189164370982</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="247" t="s">
+      <c r="A21" s="244" t="s">
         <v>263</v>
       </c>
       <c r="B21" s="128" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="244" t="s">
+      <c r="C21" s="241" t="s">
         <v>266</v>
       </c>
       <c r="D21" s="100">
         <v>0.12</v>
       </c>
-      <c r="E21" s="220" t="s">
+      <c r="E21" s="217" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="219">
+      <c r="F21" s="216">
         <v>23.73</v>
       </c>
-      <c r="G21" s="218">
+      <c r="G21" s="215">
         <v>50</v>
       </c>
-      <c r="H21" s="218"/>
-      <c r="I21" s="218">
-        <v>0</v>
-      </c>
-      <c r="J21" s="219"/>
-      <c r="K21" s="218">
+      <c r="H21" s="215"/>
+      <c r="I21" s="215">
+        <v>0</v>
+      </c>
+      <c r="J21" s="216"/>
+      <c r="K21" s="215">
         <v>10.89</v>
       </c>
-      <c r="L21" s="224">
+      <c r="L21" s="221">
         <f t="shared" si="0"/>
         <v>1.1865000000000001E-3</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="247" t="s">
+      <c r="A22" s="244" t="s">
         <v>263</v>
       </c>
       <c r="B22" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="C22" s="244" t="s">
+      <c r="C22" s="241" t="s">
         <v>268</v>
       </c>
       <c r="D22" s="117">
         <v>50</v>
       </c>
-      <c r="E22" s="220" t="s">
+      <c r="E22" s="217" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="219">
+      <c r="F22" s="216">
         <v>23.73</v>
       </c>
-      <c r="G22" s="218">
+      <c r="G22" s="215">
         <v>50</v>
       </c>
-      <c r="H22" s="218"/>
-      <c r="I22" s="218">
-        <v>0</v>
-      </c>
-      <c r="J22" s="219"/>
-      <c r="K22" s="218">
+      <c r="H22" s="215"/>
+      <c r="I22" s="215">
+        <v>0</v>
+      </c>
+      <c r="J22" s="216"/>
+      <c r="K22" s="215">
         <v>10.89</v>
       </c>
-      <c r="L22" s="224">
+      <c r="L22" s="221">
         <f t="shared" si="0"/>
         <v>1.1865000000000001E-3</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="247" t="s">
+      <c r="A23" s="244" t="s">
         <v>263</v>
       </c>
       <c r="B23" s="129" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="219" t="s">
+      <c r="C23" s="216" t="s">
         <v>98</v>
       </c>
       <c r="D23" s="90">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E23" s="222" t="s">
+      <c r="E23" s="219" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="219">
+      <c r="F23" s="216">
         <v>9086.0300000000007</v>
       </c>
-      <c r="G23" s="218">
+      <c r="G23" s="215">
         <v>1000</v>
       </c>
-      <c r="H23" s="218">
+      <c r="H23" s="215">
         <v>1.2</v>
       </c>
-      <c r="I23" s="218">
+      <c r="I23" s="215">
         <v>8</v>
       </c>
-      <c r="J23" s="219" t="s">
+      <c r="J23" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K23" s="218">
+      <c r="K23" s="215">
         <v>10.89</v>
       </c>
-      <c r="L23" s="251">
+      <c r="L23" s="248">
         <f>F23*G23/10^6+I23*1/K23</f>
         <v>9.8206489164370971</v>
       </c>
-      <c r="M23" s="252">
+      <c r="M23" s="249">
         <f>($F$37^(-1)+L23^(-1))^-1</f>
         <v>3.0345750227525516</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="247" t="s">
+      <c r="A24" s="244" t="s">
         <v>263</v>
       </c>
       <c r="B24" s="129" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="219" t="s">
+      <c r="C24" s="216" t="s">
         <v>244</v>
       </c>
       <c r="D24" s="90">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E24" s="223" t="s">
+      <c r="E24" s="220" t="s">
         <v>25</v>
       </c>
-      <c r="F24" s="219">
+      <c r="F24" s="216">
         <v>1441</v>
       </c>
-      <c r="G24" s="218">
+      <c r="G24" s="215">
         <v>1000</v>
       </c>
-      <c r="H24" s="218"/>
-      <c r="I24" s="218">
-        <v>0</v>
-      </c>
-      <c r="J24" s="219"/>
-      <c r="K24" s="218">
+      <c r="H24" s="215"/>
+      <c r="I24" s="215">
+        <v>0</v>
+      </c>
+      <c r="J24" s="216"/>
+      <c r="K24" s="215">
         <v>10.89</v>
       </c>
-      <c r="L24" s="251">
+      <c r="L24" s="248">
         <f>F24*G24/10^6+I24*1/K24</f>
         <v>1.4410000000000001</v>
       </c>
-      <c r="M24" s="253">
+      <c r="M24" s="250">
         <f>($F$37^(-1)+L24^(-1))^-1</f>
         <v>1.0849850380335702</v>
       </c>
@@ -70312,273 +70791,273 @@
       <c r="B25" s="129" t="s">
         <v>249</v>
       </c>
-      <c r="C25" s="219" t="s">
+      <c r="C25" s="216" t="s">
         <v>241</v>
       </c>
       <c r="D25" s="90">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E25" s="220" t="s">
+      <c r="E25" s="217" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="219">
+      <c r="F25" s="216">
         <v>23.73</v>
       </c>
-      <c r="G25" s="218">
+      <c r="G25" s="215">
         <v>50</v>
       </c>
-      <c r="H25" s="218"/>
-      <c r="I25" s="218">
-        <v>0</v>
-      </c>
-      <c r="J25" s="219"/>
-      <c r="K25" s="218">
+      <c r="H25" s="215"/>
+      <c r="I25" s="215">
+        <v>0</v>
+      </c>
+      <c r="J25" s="216"/>
+      <c r="K25" s="215">
         <v>10.89</v>
       </c>
-      <c r="L25" s="224">
+      <c r="L25" s="221">
         <f t="shared" si="0"/>
         <v>1.1865000000000001E-3</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="245" t="s">
+      <c r="A26" s="242" t="s">
         <v>263</v>
       </c>
-      <c r="B26" s="225" t="s">
+      <c r="B26" s="222" t="s">
         <v>245</v>
       </c>
-      <c r="C26" s="219" t="s">
+      <c r="C26" s="216" t="s">
         <v>242</v>
       </c>
       <c r="D26" s="81">
         <v>180</v>
       </c>
-      <c r="E26" s="221" t="s">
+      <c r="E26" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="218">
+      <c r="F26" s="215">
         <v>154.44999999999999</v>
       </c>
-      <c r="G26" s="218">
-        <v>0</v>
-      </c>
-      <c r="H26" s="218">
+      <c r="G26" s="215">
+        <v>0</v>
+      </c>
+      <c r="H26" s="215">
         <v>2</v>
       </c>
-      <c r="I26" s="218">
+      <c r="I26" s="215">
         <v>1</v>
       </c>
-      <c r="J26" s="219" t="s">
+      <c r="J26" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K26" s="218">
+      <c r="K26" s="215">
         <v>10.89</v>
       </c>
-      <c r="L26" s="224">
+      <c r="L26" s="221">
         <f t="shared" si="0"/>
         <v>9.1827364554637275E-2</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="245" t="s">
+      <c r="A27" s="242" t="s">
         <v>263</v>
       </c>
-      <c r="B27" s="225" t="s">
+      <c r="B27" s="222" t="s">
         <v>245</v>
       </c>
-      <c r="C27" s="219" t="s">
+      <c r="C27" s="216" t="s">
         <v>243</v>
       </c>
       <c r="D27" s="81">
         <v>180</v>
       </c>
-      <c r="E27" s="221" t="s">
+      <c r="E27" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="218">
+      <c r="F27" s="215">
         <v>73.22</v>
       </c>
-      <c r="G27" s="218">
-        <v>0</v>
-      </c>
-      <c r="H27" s="218">
+      <c r="G27" s="215">
+        <v>0</v>
+      </c>
+      <c r="H27" s="215">
         <v>6</v>
       </c>
-      <c r="I27" s="218">
+      <c r="I27" s="215">
         <v>1</v>
       </c>
-      <c r="J27" s="219" t="s">
+      <c r="J27" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K27" s="218">
+      <c r="K27" s="215">
         <v>2.7</v>
       </c>
-      <c r="L27" s="224">
+      <c r="L27" s="221">
         <f t="shared" si="0"/>
         <v>0.37037037037037035</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="245" t="s">
+      <c r="A28" s="242" t="s">
         <v>263</v>
       </c>
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="222" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="244" t="s">
+      <c r="C28" s="241" t="s">
         <v>262</v>
       </c>
       <c r="D28" s="81">
         <v>34</v>
       </c>
-      <c r="E28" s="220" t="s">
+      <c r="E28" s="217" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="219">
+      <c r="F28" s="216">
         <v>42.23</v>
       </c>
-      <c r="G28" s="218">
+      <c r="G28" s="215">
         <v>50</v>
       </c>
-      <c r="H28" s="218"/>
-      <c r="I28" s="218">
-        <v>0</v>
-      </c>
-      <c r="J28" s="219"/>
-      <c r="K28" s="218">
+      <c r="H28" s="215"/>
+      <c r="I28" s="215">
+        <v>0</v>
+      </c>
+      <c r="J28" s="216"/>
+      <c r="K28" s="215">
         <v>10.89</v>
       </c>
-      <c r="L28" s="224">
+      <c r="L28" s="221">
         <f t="shared" si="0"/>
         <v>2.1115000000000001E-3</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="245" t="s">
+      <c r="A29" s="242" t="s">
         <v>263</v>
       </c>
-      <c r="B29" s="225" t="s">
+      <c r="B29" s="222" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="219" t="s">
+      <c r="C29" s="216" t="s">
         <v>243</v>
       </c>
       <c r="D29" s="81">
         <v>34</v>
       </c>
-      <c r="E29" s="220" t="s">
+      <c r="E29" s="217" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="219">
+      <c r="F29" s="216">
         <v>28.91</v>
       </c>
-      <c r="G29" s="218">
+      <c r="G29" s="215">
         <v>50</v>
       </c>
-      <c r="H29" s="218"/>
-      <c r="I29" s="218">
-        <v>0</v>
-      </c>
-      <c r="J29" s="219"/>
-      <c r="K29" s="218">
+      <c r="H29" s="215"/>
+      <c r="I29" s="215">
+        <v>0</v>
+      </c>
+      <c r="J29" s="216"/>
+      <c r="K29" s="215">
         <v>10.89</v>
       </c>
-      <c r="L29" s="224">
+      <c r="L29" s="221">
         <f t="shared" si="0"/>
         <v>1.4455E-3</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="245" t="s">
+      <c r="A30" s="242" t="s">
         <v>263</v>
       </c>
-      <c r="B30" s="225" t="s">
+      <c r="B30" s="222" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="244" t="s">
+      <c r="C30" s="241" t="s">
         <v>264</v>
       </c>
       <c r="D30" s="81">
         <v>180</v>
       </c>
-      <c r="E30" s="221" t="s">
+      <c r="E30" s="218" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="219">
+      <c r="F30" s="216">
         <v>470.09</v>
       </c>
-      <c r="G30" s="218">
-        <v>0</v>
-      </c>
-      <c r="H30" s="218">
+      <c r="G30" s="215">
+        <v>0</v>
+      </c>
+      <c r="H30" s="215">
         <v>1.2</v>
       </c>
-      <c r="I30" s="218">
+      <c r="I30" s="215">
         <v>2</v>
       </c>
-      <c r="J30" s="219" t="s">
+      <c r="J30" s="216" t="s">
         <v>27</v>
       </c>
-      <c r="K30" s="218">
+      <c r="K30" s="215">
         <v>10.89</v>
       </c>
-      <c r="L30" s="224">
+      <c r="L30" s="221">
         <f t="shared" si="0"/>
         <v>0.18365472910927455</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="245" t="s">
+      <c r="A31" s="242" t="s">
         <v>263</v>
       </c>
-      <c r="B31" s="225" t="s">
+      <c r="B31" s="222" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="219" t="s">
+      <c r="C31" s="216" t="s">
         <v>245</v>
       </c>
       <c r="D31" s="81">
         <v>180</v>
       </c>
-      <c r="E31" s="220" t="s">
+      <c r="E31" s="217" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="219">
+      <c r="F31" s="216">
         <v>166.55</v>
       </c>
-      <c r="G31" s="218">
+      <c r="G31" s="215">
         <v>50</v>
       </c>
-      <c r="H31" s="218"/>
-      <c r="I31" s="218">
-        <v>0</v>
-      </c>
-      <c r="J31" s="219"/>
-      <c r="K31" s="218">
+      <c r="H31" s="215"/>
+      <c r="I31" s="215">
+        <v>0</v>
+      </c>
+      <c r="J31" s="216"/>
+      <c r="K31" s="215">
         <v>10.89</v>
       </c>
-      <c r="L31" s="224">
+      <c r="L31" s="221">
         <f t="shared" si="0"/>
         <v>8.3274999999999998E-3</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="245" t="s">
+      <c r="A32" s="242" t="s">
         <v>263</v>
       </c>
-      <c r="B32" s="226" t="s">
+      <c r="B32" s="223" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="227" t="s">
+      <c r="C32" s="224" t="s">
         <v>238</v>
       </c>
-      <c r="D32" s="228">
+      <c r="D32" s="225">
         <v>180</v>
       </c>
-      <c r="E32" s="229" t="s">
+      <c r="E32" s="226" t="s">
         <v>23</v>
       </c>
-      <c r="F32" s="227">
+      <c r="F32" s="224">
         <v>394.67</v>
       </c>
       <c r="G32" s="42">
@@ -70588,64 +71067,64 @@
       <c r="I32" s="42">
         <v>0</v>
       </c>
-      <c r="J32" s="227"/>
+      <c r="J32" s="224"/>
       <c r="K32" s="42">
         <v>10.89</v>
       </c>
-      <c r="L32" s="230">
+      <c r="L32" s="227">
         <f t="shared" si="0"/>
         <v>1.9733500000000001E-2</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="269" t="s">
+      <c r="B34" s="266" t="s">
         <v>252</v>
       </c>
-      <c r="C34" s="270"/>
-      <c r="D34" s="270"/>
-      <c r="E34" s="270"/>
-      <c r="F34" s="271"/>
+      <c r="C34" s="267"/>
+      <c r="D34" s="267"/>
+      <c r="E34" s="267"/>
+      <c r="F34" s="268"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="129" t="s">
         <v>254</v>
       </c>
-      <c r="C35" s="236" t="s">
+      <c r="C35" s="233" t="s">
         <v>256</v>
       </c>
-      <c r="D35" s="236" t="s">
+      <c r="D35" s="233" t="s">
         <v>258</v>
       </c>
-      <c r="E35" s="236" t="s">
+      <c r="E35" s="233" t="s">
         <v>259</v>
       </c>
-      <c r="F35" s="237" t="s">
+      <c r="F35" s="234" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="238" t="s">
+      <c r="B36" s="235" t="s">
         <v>253</v>
       </c>
-      <c r="C36" s="218">
+      <c r="C36" s="215">
         <f>2.2*86.2/10^6</f>
         <v>1.8964000000000001E-4</v>
       </c>
-      <c r="D36" s="218">
+      <c r="D36" s="215">
         <v>0.12</v>
       </c>
-      <c r="E36" s="218">
+      <c r="E36" s="215">
         <f>98/5/10^3</f>
         <v>1.9600000000000003E-2</v>
       </c>
-      <c r="F36" s="235">
+      <c r="F36" s="232">
         <f>D36*C36/E36</f>
         <v>1.1610612244897956E-3</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="239" t="s">
+      <c r="B37" s="236" t="s">
         <v>265</v>
       </c>
       <c r="C37" s="42">
@@ -70668,7 +71147,7 @@
     <row r="39" spans="2:6" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25"/>
     <row r="41" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="245" t="s">
+      <c r="B41" s="242" t="s">
         <v>277</v>
       </c>
     </row>
@@ -70854,7 +71333,7 @@
         <v>26.5</v>
       </c>
       <c r="G3" s="43">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -73038,10 +73517,10 @@
         <v>0.95</v>
       </c>
       <c r="I62" s="185">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" s="185">
         <v>0</v>
@@ -73078,10 +73557,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" s="185">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" s="185">
         <v>0</v>
@@ -73118,10 +73597,10 @@
         <v>0.95</v>
       </c>
       <c r="I64" s="185">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J64" s="185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" s="185">
         <v>0</v>
@@ -73158,10 +73637,10 @@
         <v>0.95</v>
       </c>
       <c r="I65" s="185">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J65" s="185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" s="185">
         <v>0</v>
@@ -73198,10 +73677,10 @@
         <v>0.95</v>
       </c>
       <c r="I66" s="185">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" s="185">
         <v>0</v>
@@ -73709,8 +74188,8 @@
       <c r="C2" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="263" t="s">
-        <v>278</v>
+      <c r="D2" s="279" t="s">
+        <v>281</v>
       </c>
       <c r="E2" s="54" t="s">
         <v>42</v>
@@ -73723,15 +74202,15 @@
       </c>
       <c r="C3" s="38">
         <f>IFERROR(C4+C5*60+C6*3600+C7*3600*24+B3,C4+C5*60+C6*3600+C7*3600*24)</f>
-        <v>86400</v>
+        <v>28800</v>
       </c>
       <c r="D3" s="38">
         <f>IFERROR(D4+D5*60+D6*3600+D7*3600*24+C3,D4+D5*60+D6*3600+D7*3600*24)</f>
-        <v>122400</v>
+        <v>28920</v>
       </c>
       <c r="E3" s="38">
         <f>IFERROR(E4+E5*60+E6*3600+E7*3600*24+D3,E4+E5*60+E6*3600+E7*3600*24)</f>
-        <v>122400</v>
+        <v>57720</v>
       </c>
       <c r="F3" s="40"/>
       <c r="G3" s="33"/>
@@ -73747,7 +74226,9 @@
         <v>40</v>
       </c>
       <c r="C4" s="37"/>
-      <c r="D4" s="35"/>
+      <c r="D4" s="35">
+        <v>120</v>
+      </c>
       <c r="E4" s="39"/>
       <c r="F4" s="40"/>
     </row>
@@ -73765,13 +74246,13 @@
         <v>38</v>
       </c>
       <c r="C6" s="53">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D6" s="35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E6" s="39">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F6" s="40"/>
     </row>
@@ -73780,10 +74261,12 @@
         <v>43</v>
       </c>
       <c r="C7" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="45"/>
-      <c r="E7" s="46"/>
+      <c r="E7" s="46">
+        <v>0</v>
+      </c>
       <c r="F7" s="40"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -74279,7 +74762,7 @@
       </c>
       <c r="D32" s="41">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$80,$A32+1,FALSE)</f>
-        <v>5.61</v>
+        <v>10.098000000000001</v>
       </c>
       <c r="E32" s="41">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$80,$A32+1,FALSE)</f>
@@ -75199,7 +75682,7 @@
       </c>
       <c r="D78" s="41">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$80,$A78+1,FALSE)</f>
-        <v>0</v>
+        <v>27.400000000000002</v>
       </c>
       <c r="E78" s="41">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$80,$A78+1,FALSE)</f>
@@ -75219,7 +75702,7 @@
       </c>
       <c r="D79" s="41">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$80,$A79+1,FALSE)</f>
-        <v>0</v>
+        <v>244.40800000000002</v>
       </c>
       <c r="E79" s="41">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$80,$A79+1,FALSE)</f>
@@ -75239,7 +75722,7 @@
       </c>
       <c r="D80" s="41">
         <f>HLOOKUP(D$2,Modes!$B$2:$O$80,$A80+1,FALSE)</f>
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="E80" s="41">
         <f>HLOOKUP(E$2,Modes!$B$2:$O$80,$A80+1,FALSE)</f>
@@ -75381,69 +75864,69 @@
       <c r="B2" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="256" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="256" t="s">
+      <c r="D2" s="253" t="s">
         <v>279</v>
       </c>
-      <c r="E2" s="260" t="s">
+      <c r="E2" s="257" t="s">
         <v>278</v>
       </c>
-      <c r="F2" s="263" t="s">
+      <c r="F2" s="260" t="s">
         <v>280</v>
       </c>
-      <c r="G2" s="263" t="s">
+      <c r="G2" s="260" t="s">
         <v>281</v>
       </c>
-      <c r="H2" s="263" t="s">
+      <c r="H2" s="260" t="s">
         <v>282</v>
       </c>
-      <c r="I2" s="263" t="s">
+      <c r="I2" s="260" t="s">
         <v>283</v>
       </c>
-      <c r="J2" s="263" t="s">
+      <c r="J2" s="260" t="s">
         <v>284</v>
       </c>
-      <c r="K2" s="261"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="261"/>
-      <c r="O2" s="262"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
+      <c r="M2" s="258"/>
+      <c r="N2" s="258"/>
+      <c r="O2" s="259"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="203" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="257">
-        <v>0</v>
-      </c>
-      <c r="D3" s="255">
-        <v>0</v>
-      </c>
-      <c r="E3" s="255">
-        <v>0</v>
-      </c>
-      <c r="F3" s="255">
-        <v>0</v>
-      </c>
-      <c r="G3" s="255">
-        <v>0</v>
-      </c>
-      <c r="H3" s="255">
-        <v>0</v>
-      </c>
-      <c r="I3" s="255">
-        <v>0</v>
-      </c>
-      <c r="J3" s="255">
-        <v>0</v>
-      </c>
-      <c r="K3" s="255"/>
-      <c r="L3" s="255"/>
-      <c r="M3" s="255"/>
-      <c r="N3" s="255"/>
-      <c r="O3" s="258"/>
+      <c r="C3" s="254">
+        <v>0</v>
+      </c>
+      <c r="D3" s="252">
+        <v>0</v>
+      </c>
+      <c r="E3" s="252">
+        <v>0</v>
+      </c>
+      <c r="F3" s="252">
+        <v>0</v>
+      </c>
+      <c r="G3" s="252">
+        <v>0</v>
+      </c>
+      <c r="H3" s="252">
+        <v>0</v>
+      </c>
+      <c r="I3" s="252">
+        <v>0</v>
+      </c>
+      <c r="J3" s="252">
+        <v>0</v>
+      </c>
+      <c r="K3" s="252"/>
+      <c r="L3" s="252"/>
+      <c r="M3" s="252"/>
+      <c r="N3" s="252"/>
+      <c r="O3" s="255"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="131" t="s">
@@ -75452,25 +75935,25 @@
       <c r="C4" s="48">
         <v>0</v>
       </c>
-      <c r="D4" s="255">
-        <v>0</v>
-      </c>
-      <c r="E4" s="255">
-        <v>0</v>
-      </c>
-      <c r="F4" s="255">
-        <v>0</v>
-      </c>
-      <c r="G4" s="255">
-        <v>0</v>
-      </c>
-      <c r="H4" s="255">
-        <v>0</v>
-      </c>
-      <c r="I4" s="255">
-        <v>0</v>
-      </c>
-      <c r="J4" s="255">
+      <c r="D4" s="252">
+        <v>0</v>
+      </c>
+      <c r="E4" s="252">
+        <v>0</v>
+      </c>
+      <c r="F4" s="252">
+        <v>0</v>
+      </c>
+      <c r="G4" s="252">
+        <v>0</v>
+      </c>
+      <c r="H4" s="252">
+        <v>0</v>
+      </c>
+      <c r="I4" s="252">
+        <v>0</v>
+      </c>
+      <c r="J4" s="252">
         <v>0</v>
       </c>
       <c r="K4" s="35"/>
@@ -75486,25 +75969,25 @@
       <c r="C5" s="48">
         <v>0</v>
       </c>
-      <c r="D5" s="255">
-        <v>0</v>
-      </c>
-      <c r="E5" s="255">
-        <v>0</v>
-      </c>
-      <c r="F5" s="255">
-        <v>0</v>
-      </c>
-      <c r="G5" s="255">
-        <v>0</v>
-      </c>
-      <c r="H5" s="255">
-        <v>0</v>
-      </c>
-      <c r="I5" s="255">
-        <v>0</v>
-      </c>
-      <c r="J5" s="255">
+      <c r="D5" s="252">
+        <v>0</v>
+      </c>
+      <c r="E5" s="252">
+        <v>0</v>
+      </c>
+      <c r="F5" s="252">
+        <v>0</v>
+      </c>
+      <c r="G5" s="252">
+        <v>0</v>
+      </c>
+      <c r="H5" s="252">
+        <v>0</v>
+      </c>
+      <c r="I5" s="252">
+        <v>0</v>
+      </c>
+      <c r="J5" s="252">
         <v>0</v>
       </c>
       <c r="K5" s="35"/>
@@ -75520,25 +76003,25 @@
       <c r="C6" s="48">
         <v>0</v>
       </c>
-      <c r="D6" s="255">
-        <v>0</v>
-      </c>
-      <c r="E6" s="255">
-        <v>0</v>
-      </c>
-      <c r="F6" s="255">
-        <v>0</v>
-      </c>
-      <c r="G6" s="255">
-        <v>0</v>
-      </c>
-      <c r="H6" s="255">
-        <v>0</v>
-      </c>
-      <c r="I6" s="255">
-        <v>0</v>
-      </c>
-      <c r="J6" s="255">
+      <c r="D6" s="252">
+        <v>0</v>
+      </c>
+      <c r="E6" s="252">
+        <v>0</v>
+      </c>
+      <c r="F6" s="252">
+        <v>0</v>
+      </c>
+      <c r="G6" s="252">
+        <v>0</v>
+      </c>
+      <c r="H6" s="252">
+        <v>0</v>
+      </c>
+      <c r="I6" s="252">
+        <v>0</v>
+      </c>
+      <c r="J6" s="252">
         <v>0</v>
       </c>
       <c r="K6" s="35"/>
@@ -75554,25 +76037,25 @@
       <c r="C7" s="48">
         <v>0</v>
       </c>
-      <c r="D7" s="255">
-        <v>0</v>
-      </c>
-      <c r="E7" s="255">
-        <v>0</v>
-      </c>
-      <c r="F7" s="255">
-        <v>0</v>
-      </c>
-      <c r="G7" s="255">
-        <v>0</v>
-      </c>
-      <c r="H7" s="255">
-        <v>0</v>
-      </c>
-      <c r="I7" s="255">
-        <v>0</v>
-      </c>
-      <c r="J7" s="255">
+      <c r="D7" s="252">
+        <v>0</v>
+      </c>
+      <c r="E7" s="252">
+        <v>0</v>
+      </c>
+      <c r="F7" s="252">
+        <v>0</v>
+      </c>
+      <c r="G7" s="252">
+        <v>0</v>
+      </c>
+      <c r="H7" s="252">
+        <v>0</v>
+      </c>
+      <c r="I7" s="252">
+        <v>0</v>
+      </c>
+      <c r="J7" s="252">
         <v>0</v>
       </c>
       <c r="K7" s="35"/>
@@ -75588,25 +76071,25 @@
       <c r="C8" s="48">
         <v>0</v>
       </c>
-      <c r="D8" s="255">
-        <v>0</v>
-      </c>
-      <c r="E8" s="255">
-        <v>0</v>
-      </c>
-      <c r="F8" s="255">
-        <v>0</v>
-      </c>
-      <c r="G8" s="255">
-        <v>0</v>
-      </c>
-      <c r="H8" s="255">
-        <v>0</v>
-      </c>
-      <c r="I8" s="255">
-        <v>0</v>
-      </c>
-      <c r="J8" s="255">
+      <c r="D8" s="252">
+        <v>0</v>
+      </c>
+      <c r="E8" s="252">
+        <v>0</v>
+      </c>
+      <c r="F8" s="252">
+        <v>0</v>
+      </c>
+      <c r="G8" s="252">
+        <v>0</v>
+      </c>
+      <c r="H8" s="252">
+        <v>0</v>
+      </c>
+      <c r="I8" s="252">
+        <v>0</v>
+      </c>
+      <c r="J8" s="252">
         <v>0</v>
       </c>
       <c r="K8" s="35"/>
@@ -75622,25 +76105,25 @@
       <c r="C9" s="48">
         <v>0</v>
       </c>
-      <c r="D9" s="255">
-        <v>0</v>
-      </c>
-      <c r="E9" s="255">
-        <v>0</v>
-      </c>
-      <c r="F9" s="255">
-        <v>0</v>
-      </c>
-      <c r="G9" s="255">
-        <v>0</v>
-      </c>
-      <c r="H9" s="255">
-        <v>0</v>
-      </c>
-      <c r="I9" s="255">
-        <v>0</v>
-      </c>
-      <c r="J9" s="255">
+      <c r="D9" s="252">
+        <v>0</v>
+      </c>
+      <c r="E9" s="252">
+        <v>0</v>
+      </c>
+      <c r="F9" s="252">
+        <v>0</v>
+      </c>
+      <c r="G9" s="252">
+        <v>0</v>
+      </c>
+      <c r="H9" s="252">
+        <v>0</v>
+      </c>
+      <c r="I9" s="252">
+        <v>0</v>
+      </c>
+      <c r="J9" s="252">
         <v>0</v>
       </c>
       <c r="K9" s="35"/>
@@ -75656,25 +76139,25 @@
       <c r="C10" s="48">
         <v>0</v>
       </c>
-      <c r="D10" s="255">
-        <v>0</v>
-      </c>
-      <c r="E10" s="255">
-        <v>0</v>
-      </c>
-      <c r="F10" s="255">
-        <v>0</v>
-      </c>
-      <c r="G10" s="255">
-        <v>0</v>
-      </c>
-      <c r="H10" s="255">
-        <v>0</v>
-      </c>
-      <c r="I10" s="255">
-        <v>0</v>
-      </c>
-      <c r="J10" s="255">
+      <c r="D10" s="252">
+        <v>0</v>
+      </c>
+      <c r="E10" s="252">
+        <v>0</v>
+      </c>
+      <c r="F10" s="252">
+        <v>0</v>
+      </c>
+      <c r="G10" s="252">
+        <v>0</v>
+      </c>
+      <c r="H10" s="252">
+        <v>0</v>
+      </c>
+      <c r="I10" s="252">
+        <v>0</v>
+      </c>
+      <c r="J10" s="252">
         <v>0</v>
       </c>
       <c r="K10" s="35"/>
@@ -75690,25 +76173,25 @@
       <c r="C11" s="48">
         <v>0</v>
       </c>
-      <c r="D11" s="255">
-        <v>0</v>
-      </c>
-      <c r="E11" s="255">
-        <v>0</v>
-      </c>
-      <c r="F11" s="255">
-        <v>0</v>
-      </c>
-      <c r="G11" s="255">
-        <v>0</v>
-      </c>
-      <c r="H11" s="255">
-        <v>0</v>
-      </c>
-      <c r="I11" s="255">
-        <v>0</v>
-      </c>
-      <c r="J11" s="255">
+      <c r="D11" s="252">
+        <v>0</v>
+      </c>
+      <c r="E11" s="252">
+        <v>0</v>
+      </c>
+      <c r="F11" s="252">
+        <v>0</v>
+      </c>
+      <c r="G11" s="252">
+        <v>0</v>
+      </c>
+      <c r="H11" s="252">
+        <v>0</v>
+      </c>
+      <c r="I11" s="252">
+        <v>0</v>
+      </c>
+      <c r="J11" s="252">
         <v>0</v>
       </c>
       <c r="K11" s="35"/>
@@ -75724,25 +76207,25 @@
       <c r="C12" s="48">
         <v>0</v>
       </c>
-      <c r="D12" s="255">
-        <v>0</v>
-      </c>
-      <c r="E12" s="255">
-        <v>0</v>
-      </c>
-      <c r="F12" s="255">
-        <v>0</v>
-      </c>
-      <c r="G12" s="255">
-        <v>0</v>
-      </c>
-      <c r="H12" s="255">
-        <v>0</v>
-      </c>
-      <c r="I12" s="255">
-        <v>0</v>
-      </c>
-      <c r="J12" s="255">
+      <c r="D12" s="252">
+        <v>0</v>
+      </c>
+      <c r="E12" s="252">
+        <v>0</v>
+      </c>
+      <c r="F12" s="252">
+        <v>0</v>
+      </c>
+      <c r="G12" s="252">
+        <v>0</v>
+      </c>
+      <c r="H12" s="252">
+        <v>0</v>
+      </c>
+      <c r="I12" s="252">
+        <v>0</v>
+      </c>
+      <c r="J12" s="252">
         <v>0</v>
       </c>
       <c r="K12" s="35"/>
@@ -75758,25 +76241,25 @@
       <c r="C13" s="48">
         <v>0</v>
       </c>
-      <c r="D13" s="255">
-        <v>0</v>
-      </c>
-      <c r="E13" s="255">
-        <v>0</v>
-      </c>
-      <c r="F13" s="255">
-        <v>0</v>
-      </c>
-      <c r="G13" s="255">
-        <v>0</v>
-      </c>
-      <c r="H13" s="255">
-        <v>0</v>
-      </c>
-      <c r="I13" s="255">
-        <v>0</v>
-      </c>
-      <c r="J13" s="255">
+      <c r="D13" s="252">
+        <v>0</v>
+      </c>
+      <c r="E13" s="252">
+        <v>0</v>
+      </c>
+      <c r="F13" s="252">
+        <v>0</v>
+      </c>
+      <c r="G13" s="252">
+        <v>0</v>
+      </c>
+      <c r="H13" s="252">
+        <v>0</v>
+      </c>
+      <c r="I13" s="252">
+        <v>0</v>
+      </c>
+      <c r="J13" s="252">
         <v>0</v>
       </c>
       <c r="K13" s="35"/>
@@ -75792,25 +76275,25 @@
       <c r="C14" s="48">
         <v>0</v>
       </c>
-      <c r="D14" s="255">
-        <v>0</v>
-      </c>
-      <c r="E14" s="255">
-        <v>0</v>
-      </c>
-      <c r="F14" s="255">
-        <v>0</v>
-      </c>
-      <c r="G14" s="255">
-        <v>0</v>
-      </c>
-      <c r="H14" s="255">
-        <v>0</v>
-      </c>
-      <c r="I14" s="255">
-        <v>0</v>
-      </c>
-      <c r="J14" s="255">
+      <c r="D14" s="252">
+        <v>0</v>
+      </c>
+      <c r="E14" s="252">
+        <v>0</v>
+      </c>
+      <c r="F14" s="252">
+        <v>0</v>
+      </c>
+      <c r="G14" s="252">
+        <v>0</v>
+      </c>
+      <c r="H14" s="252">
+        <v>0</v>
+      </c>
+      <c r="I14" s="252">
+        <v>0</v>
+      </c>
+      <c r="J14" s="252">
         <v>0</v>
       </c>
       <c r="K14" s="35"/>
@@ -75826,25 +76309,25 @@
       <c r="C15" s="48">
         <v>0</v>
       </c>
-      <c r="D15" s="255">
-        <v>0</v>
-      </c>
-      <c r="E15" s="255">
-        <v>0</v>
-      </c>
-      <c r="F15" s="255">
-        <v>0</v>
-      </c>
-      <c r="G15" s="255">
-        <v>0</v>
-      </c>
-      <c r="H15" s="255">
-        <v>0</v>
-      </c>
-      <c r="I15" s="255">
-        <v>0</v>
-      </c>
-      <c r="J15" s="255">
+      <c r="D15" s="252">
+        <v>0</v>
+      </c>
+      <c r="E15" s="252">
+        <v>0</v>
+      </c>
+      <c r="F15" s="252">
+        <v>0</v>
+      </c>
+      <c r="G15" s="252">
+        <v>0</v>
+      </c>
+      <c r="H15" s="252">
+        <v>0</v>
+      </c>
+      <c r="I15" s="252">
+        <v>0</v>
+      </c>
+      <c r="J15" s="252">
         <v>0</v>
       </c>
       <c r="K15" s="35"/>
@@ -75860,25 +76343,25 @@
       <c r="C16" s="48">
         <v>0</v>
       </c>
-      <c r="D16" s="255">
-        <v>0</v>
-      </c>
-      <c r="E16" s="255">
-        <v>0</v>
-      </c>
-      <c r="F16" s="255">
-        <v>0</v>
-      </c>
-      <c r="G16" s="255">
-        <v>0</v>
-      </c>
-      <c r="H16" s="255">
-        <v>0</v>
-      </c>
-      <c r="I16" s="255">
-        <v>0</v>
-      </c>
-      <c r="J16" s="255">
+      <c r="D16" s="252">
+        <v>0</v>
+      </c>
+      <c r="E16" s="252">
+        <v>0</v>
+      </c>
+      <c r="F16" s="252">
+        <v>0</v>
+      </c>
+      <c r="G16" s="252">
+        <v>0</v>
+      </c>
+      <c r="H16" s="252">
+        <v>0</v>
+      </c>
+      <c r="I16" s="252">
+        <v>0</v>
+      </c>
+      <c r="J16" s="252">
         <v>0</v>
       </c>
       <c r="K16" s="35"/>
@@ -75894,25 +76377,25 @@
       <c r="C17" s="48">
         <v>0</v>
       </c>
-      <c r="D17" s="255">
-        <v>0</v>
-      </c>
-      <c r="E17" s="255">
-        <v>0</v>
-      </c>
-      <c r="F17" s="255">
-        <v>0</v>
-      </c>
-      <c r="G17" s="255">
-        <v>0</v>
-      </c>
-      <c r="H17" s="255">
-        <v>0</v>
-      </c>
-      <c r="I17" s="255">
-        <v>0</v>
-      </c>
-      <c r="J17" s="255">
+      <c r="D17" s="252">
+        <v>0</v>
+      </c>
+      <c r="E17" s="252">
+        <v>0</v>
+      </c>
+      <c r="F17" s="252">
+        <v>0</v>
+      </c>
+      <c r="G17" s="252">
+        <v>0</v>
+      </c>
+      <c r="H17" s="252">
+        <v>0</v>
+      </c>
+      <c r="I17" s="252">
+        <v>0</v>
+      </c>
+      <c r="J17" s="252">
         <v>0</v>
       </c>
       <c r="K17" s="35"/>
@@ -75928,25 +76411,25 @@
       <c r="C18" s="48">
         <v>0</v>
       </c>
-      <c r="D18" s="255">
-        <v>0</v>
-      </c>
-      <c r="E18" s="255">
-        <v>0</v>
-      </c>
-      <c r="F18" s="255">
-        <v>0</v>
-      </c>
-      <c r="G18" s="255">
-        <v>0</v>
-      </c>
-      <c r="H18" s="255">
-        <v>0</v>
-      </c>
-      <c r="I18" s="255">
-        <v>0</v>
-      </c>
-      <c r="J18" s="255">
+      <c r="D18" s="252">
+        <v>0</v>
+      </c>
+      <c r="E18" s="252">
+        <v>0</v>
+      </c>
+      <c r="F18" s="252">
+        <v>0</v>
+      </c>
+      <c r="G18" s="252">
+        <v>0</v>
+      </c>
+      <c r="H18" s="252">
+        <v>0</v>
+      </c>
+      <c r="I18" s="252">
+        <v>0</v>
+      </c>
+      <c r="J18" s="252">
         <v>0</v>
       </c>
       <c r="K18" s="35"/>
@@ -75962,25 +76445,25 @@
       <c r="C19" s="48">
         <v>0</v>
       </c>
-      <c r="D19" s="255">
-        <v>0</v>
-      </c>
-      <c r="E19" s="255">
-        <v>0</v>
-      </c>
-      <c r="F19" s="255">
-        <v>0</v>
-      </c>
-      <c r="G19" s="255">
-        <v>0</v>
-      </c>
-      <c r="H19" s="255">
-        <v>0</v>
-      </c>
-      <c r="I19" s="255">
-        <v>0</v>
-      </c>
-      <c r="J19" s="255">
+      <c r="D19" s="252">
+        <v>0</v>
+      </c>
+      <c r="E19" s="252">
+        <v>0</v>
+      </c>
+      <c r="F19" s="252">
+        <v>0</v>
+      </c>
+      <c r="G19" s="252">
+        <v>0</v>
+      </c>
+      <c r="H19" s="252">
+        <v>0</v>
+      </c>
+      <c r="I19" s="252">
+        <v>0</v>
+      </c>
+      <c r="J19" s="252">
         <v>0</v>
       </c>
       <c r="K19" s="35"/>
@@ -75996,25 +76479,25 @@
       <c r="C20" s="48">
         <v>0</v>
       </c>
-      <c r="D20" s="255">
-        <v>0</v>
-      </c>
-      <c r="E20" s="255">
-        <v>0</v>
-      </c>
-      <c r="F20" s="255">
-        <v>0</v>
-      </c>
-      <c r="G20" s="255">
-        <v>0</v>
-      </c>
-      <c r="H20" s="255">
-        <v>0</v>
-      </c>
-      <c r="I20" s="255">
-        <v>0</v>
-      </c>
-      <c r="J20" s="255">
+      <c r="D20" s="252">
+        <v>0</v>
+      </c>
+      <c r="E20" s="252">
+        <v>0</v>
+      </c>
+      <c r="F20" s="252">
+        <v>0</v>
+      </c>
+      <c r="G20" s="252">
+        <v>0</v>
+      </c>
+      <c r="H20" s="252">
+        <v>0</v>
+      </c>
+      <c r="I20" s="252">
+        <v>0</v>
+      </c>
+      <c r="J20" s="252">
         <v>0</v>
       </c>
       <c r="K20" s="35"/>
@@ -76030,25 +76513,25 @@
       <c r="C21" s="48">
         <v>0</v>
       </c>
-      <c r="D21" s="255">
-        <v>0</v>
-      </c>
-      <c r="E21" s="255">
-        <v>0</v>
-      </c>
-      <c r="F21" s="255">
-        <v>0</v>
-      </c>
-      <c r="G21" s="255">
-        <v>0</v>
-      </c>
-      <c r="H21" s="255">
-        <v>0</v>
-      </c>
-      <c r="I21" s="255">
-        <v>0</v>
-      </c>
-      <c r="J21" s="255">
+      <c r="D21" s="252">
+        <v>0</v>
+      </c>
+      <c r="E21" s="252">
+        <v>0</v>
+      </c>
+      <c r="F21" s="252">
+        <v>0</v>
+      </c>
+      <c r="G21" s="252">
+        <v>0</v>
+      </c>
+      <c r="H21" s="252">
+        <v>0</v>
+      </c>
+      <c r="I21" s="252">
+        <v>0</v>
+      </c>
+      <c r="J21" s="252">
         <v>0</v>
       </c>
       <c r="K21" s="35"/>
@@ -76064,25 +76547,25 @@
       <c r="C22" s="48">
         <v>0</v>
       </c>
-      <c r="D22" s="255">
-        <v>0</v>
-      </c>
-      <c r="E22" s="255">
-        <v>0</v>
-      </c>
-      <c r="F22" s="255">
-        <v>0</v>
-      </c>
-      <c r="G22" s="255">
-        <v>0</v>
-      </c>
-      <c r="H22" s="255">
-        <v>0</v>
-      </c>
-      <c r="I22" s="255">
-        <v>0</v>
-      </c>
-      <c r="J22" s="255">
+      <c r="D22" s="252">
+        <v>0</v>
+      </c>
+      <c r="E22" s="252">
+        <v>0</v>
+      </c>
+      <c r="F22" s="252">
+        <v>0</v>
+      </c>
+      <c r="G22" s="252">
+        <v>0</v>
+      </c>
+      <c r="H22" s="252">
+        <v>0</v>
+      </c>
+      <c r="I22" s="252">
+        <v>0</v>
+      </c>
+      <c r="J22" s="252">
         <v>0</v>
       </c>
       <c r="K22" s="35"/>
@@ -76098,25 +76581,25 @@
       <c r="C23" s="48">
         <v>0</v>
       </c>
-      <c r="D23" s="255">
-        <v>0</v>
-      </c>
-      <c r="E23" s="255">
-        <v>0</v>
-      </c>
-      <c r="F23" s="255">
-        <v>0</v>
-      </c>
-      <c r="G23" s="255">
-        <v>0</v>
-      </c>
-      <c r="H23" s="255">
-        <v>0</v>
-      </c>
-      <c r="I23" s="255">
-        <v>0</v>
-      </c>
-      <c r="J23" s="255">
+      <c r="D23" s="252">
+        <v>0</v>
+      </c>
+      <c r="E23" s="252">
+        <v>0</v>
+      </c>
+      <c r="F23" s="252">
+        <v>0</v>
+      </c>
+      <c r="G23" s="252">
+        <v>0</v>
+      </c>
+      <c r="H23" s="252">
+        <v>0</v>
+      </c>
+      <c r="I23" s="252">
+        <v>0</v>
+      </c>
+      <c r="J23" s="252">
         <v>0</v>
       </c>
       <c r="K23" s="35"/>
@@ -76132,25 +76615,25 @@
       <c r="C24" s="48">
         <v>0</v>
       </c>
-      <c r="D24" s="255">
-        <v>0</v>
-      </c>
-      <c r="E24" s="255">
-        <v>0</v>
-      </c>
-      <c r="F24" s="255">
-        <v>0</v>
-      </c>
-      <c r="G24" s="255">
-        <v>0</v>
-      </c>
-      <c r="H24" s="255">
-        <v>0</v>
-      </c>
-      <c r="I24" s="255">
-        <v>0</v>
-      </c>
-      <c r="J24" s="255">
+      <c r="D24" s="252">
+        <v>0</v>
+      </c>
+      <c r="E24" s="252">
+        <v>0</v>
+      </c>
+      <c r="F24" s="252">
+        <v>0</v>
+      </c>
+      <c r="G24" s="252">
+        <v>0</v>
+      </c>
+      <c r="H24" s="252">
+        <v>0</v>
+      </c>
+      <c r="I24" s="252">
+        <v>0</v>
+      </c>
+      <c r="J24" s="252">
         <v>0</v>
       </c>
       <c r="K24" s="35"/>
@@ -76166,25 +76649,25 @@
       <c r="C25" s="48">
         <v>0</v>
       </c>
-      <c r="D25" s="255">
-        <v>0</v>
-      </c>
-      <c r="E25" s="255">
-        <v>0</v>
-      </c>
-      <c r="F25" s="255">
-        <v>0</v>
-      </c>
-      <c r="G25" s="255">
-        <v>0</v>
-      </c>
-      <c r="H25" s="255">
-        <v>0</v>
-      </c>
-      <c r="I25" s="255">
-        <v>0</v>
-      </c>
-      <c r="J25" s="255">
+      <c r="D25" s="252">
+        <v>0</v>
+      </c>
+      <c r="E25" s="252">
+        <v>0</v>
+      </c>
+      <c r="F25" s="252">
+        <v>0</v>
+      </c>
+      <c r="G25" s="252">
+        <v>0</v>
+      </c>
+      <c r="H25" s="252">
+        <v>0</v>
+      </c>
+      <c r="I25" s="252">
+        <v>0</v>
+      </c>
+      <c r="J25" s="252">
         <v>0</v>
       </c>
       <c r="K25" s="35"/>
@@ -76200,25 +76683,25 @@
       <c r="C26" s="48">
         <v>0</v>
       </c>
-      <c r="D26" s="255">
-        <v>0</v>
-      </c>
-      <c r="E26" s="255">
-        <v>0</v>
-      </c>
-      <c r="F26" s="255">
-        <v>0</v>
-      </c>
-      <c r="G26" s="255">
-        <v>0</v>
-      </c>
-      <c r="H26" s="255">
-        <v>0</v>
-      </c>
-      <c r="I26" s="255">
-        <v>0</v>
-      </c>
-      <c r="J26" s="255">
+      <c r="D26" s="252">
+        <v>0</v>
+      </c>
+      <c r="E26" s="252">
+        <v>0</v>
+      </c>
+      <c r="F26" s="252">
+        <v>0</v>
+      </c>
+      <c r="G26" s="252">
+        <v>0</v>
+      </c>
+      <c r="H26" s="252">
+        <v>0</v>
+      </c>
+      <c r="I26" s="252">
+        <v>0</v>
+      </c>
+      <c r="J26" s="252">
         <v>0</v>
       </c>
       <c r="K26" s="35"/>
@@ -76234,29 +76717,29 @@
       <c r="C27" s="48">
         <v>0</v>
       </c>
-      <c r="D27" s="255">
+      <c r="D27" s="252">
         <v>5.61</v>
       </c>
-      <c r="E27" s="255">
+      <c r="E27" s="252">
         <v>5.61</v>
       </c>
-      <c r="F27" s="255">
+      <c r="F27" s="252">
         <f>5.61+4.488</f>
         <v>10.098000000000001</v>
       </c>
-      <c r="G27" s="255">
+      <c r="G27" s="252">
         <f>5.61+4.488</f>
         <v>10.098000000000001</v>
       </c>
-      <c r="H27" s="255">
+      <c r="H27" s="252">
         <f>5.61+4.488</f>
         <v>10.098000000000001</v>
       </c>
-      <c r="I27" s="255">
+      <c r="I27" s="252">
         <f>5.61+4.488</f>
         <v>10.098000000000001</v>
       </c>
-      <c r="J27" s="255">
+      <c r="J27" s="252">
         <f>5.61+4.488</f>
         <v>10.098000000000001</v>
       </c>
@@ -76273,25 +76756,25 @@
       <c r="C28" s="48">
         <v>0</v>
       </c>
-      <c r="D28" s="255">
-        <v>0</v>
-      </c>
-      <c r="E28" s="255">
-        <v>0</v>
-      </c>
-      <c r="F28" s="255">
-        <v>0</v>
-      </c>
-      <c r="G28" s="255">
-        <v>0</v>
-      </c>
-      <c r="H28" s="255">
-        <v>0</v>
-      </c>
-      <c r="I28" s="255">
-        <v>0</v>
-      </c>
-      <c r="J28" s="255">
+      <c r="D28" s="252">
+        <v>0</v>
+      </c>
+      <c r="E28" s="252">
+        <v>0</v>
+      </c>
+      <c r="F28" s="252">
+        <v>0</v>
+      </c>
+      <c r="G28" s="252">
+        <v>0</v>
+      </c>
+      <c r="H28" s="252">
+        <v>0</v>
+      </c>
+      <c r="I28" s="252">
+        <v>0</v>
+      </c>
+      <c r="J28" s="252">
         <v>0</v>
       </c>
       <c r="K28" s="35"/>
@@ -76307,25 +76790,25 @@
       <c r="C29" s="48">
         <v>0</v>
       </c>
-      <c r="D29" s="255">
-        <v>0</v>
-      </c>
-      <c r="E29" s="255">
-        <v>0</v>
-      </c>
-      <c r="F29" s="255">
-        <v>0</v>
-      </c>
-      <c r="G29" s="255">
-        <v>0</v>
-      </c>
-      <c r="H29" s="255">
-        <v>0</v>
-      </c>
-      <c r="I29" s="255">
-        <v>0</v>
-      </c>
-      <c r="J29" s="255">
+      <c r="D29" s="252">
+        <v>0</v>
+      </c>
+      <c r="E29" s="252">
+        <v>0</v>
+      </c>
+      <c r="F29" s="252">
+        <v>0</v>
+      </c>
+      <c r="G29" s="252">
+        <v>0</v>
+      </c>
+      <c r="H29" s="252">
+        <v>0</v>
+      </c>
+      <c r="I29" s="252">
+        <v>0</v>
+      </c>
+      <c r="J29" s="252">
         <v>0</v>
       </c>
       <c r="K29" s="35"/>
@@ -76341,25 +76824,25 @@
       <c r="C30" s="48">
         <v>0</v>
       </c>
-      <c r="D30" s="255">
-        <v>0</v>
-      </c>
-      <c r="E30" s="255">
+      <c r="D30" s="252">
+        <v>0</v>
+      </c>
+      <c r="E30" s="252">
         <v>0.6</v>
       </c>
-      <c r="F30" s="255">
+      <c r="F30" s="252">
         <v>0.6</v>
       </c>
-      <c r="G30" s="255">
+      <c r="G30" s="252">
         <v>0.6</v>
       </c>
-      <c r="H30" s="255">
+      <c r="H30" s="252">
         <v>0.6</v>
       </c>
-      <c r="I30" s="255">
+      <c r="I30" s="252">
         <v>0.6</v>
       </c>
-      <c r="J30" s="255">
+      <c r="J30" s="252">
         <v>0.6</v>
       </c>
       <c r="K30" s="35"/>
@@ -76375,25 +76858,25 @@
       <c r="C31" s="48">
         <v>0</v>
       </c>
-      <c r="D31" s="255">
-        <v>0</v>
-      </c>
-      <c r="E31" s="255">
-        <v>0</v>
-      </c>
-      <c r="F31" s="255">
-        <v>0</v>
-      </c>
-      <c r="G31" s="255">
-        <v>0</v>
-      </c>
-      <c r="H31" s="255">
-        <v>0</v>
-      </c>
-      <c r="I31" s="255">
-        <v>0</v>
-      </c>
-      <c r="J31" s="255">
+      <c r="D31" s="252">
+        <v>0</v>
+      </c>
+      <c r="E31" s="252">
+        <v>0</v>
+      </c>
+      <c r="F31" s="252">
+        <v>0</v>
+      </c>
+      <c r="G31" s="252">
+        <v>0</v>
+      </c>
+      <c r="H31" s="252">
+        <v>0</v>
+      </c>
+      <c r="I31" s="252">
+        <v>0</v>
+      </c>
+      <c r="J31" s="252">
         <v>0</v>
       </c>
       <c r="K31" s="45"/>
@@ -76409,25 +76892,25 @@
       <c r="C32" s="48">
         <v>0</v>
       </c>
-      <c r="D32" s="255">
-        <v>0</v>
-      </c>
-      <c r="E32" s="255">
-        <v>0</v>
-      </c>
-      <c r="F32" s="255">
-        <v>0</v>
-      </c>
-      <c r="G32" s="255">
-        <v>0</v>
-      </c>
-      <c r="H32" s="255">
-        <v>0</v>
-      </c>
-      <c r="I32" s="255">
-        <v>0</v>
-      </c>
-      <c r="J32" s="255">
+      <c r="D32" s="252">
+        <v>0</v>
+      </c>
+      <c r="E32" s="252">
+        <v>0</v>
+      </c>
+      <c r="F32" s="252">
+        <v>0</v>
+      </c>
+      <c r="G32" s="252">
+        <v>0</v>
+      </c>
+      <c r="H32" s="252">
+        <v>0</v>
+      </c>
+      <c r="I32" s="252">
+        <v>0</v>
+      </c>
+      <c r="J32" s="252">
         <v>0</v>
       </c>
       <c r="K32" s="40"/>
@@ -76443,25 +76926,25 @@
       <c r="C33" s="48">
         <v>0</v>
       </c>
-      <c r="D33" s="255">
-        <v>0</v>
-      </c>
-      <c r="E33" s="255">
-        <v>0</v>
-      </c>
-      <c r="F33" s="255">
-        <v>0</v>
-      </c>
-      <c r="G33" s="255">
-        <v>0</v>
-      </c>
-      <c r="H33" s="255">
-        <v>0</v>
-      </c>
-      <c r="I33" s="255">
-        <v>0</v>
-      </c>
-      <c r="J33" s="255">
+      <c r="D33" s="252">
+        <v>0</v>
+      </c>
+      <c r="E33" s="252">
+        <v>0</v>
+      </c>
+      <c r="F33" s="252">
+        <v>0</v>
+      </c>
+      <c r="G33" s="252">
+        <v>0</v>
+      </c>
+      <c r="H33" s="252">
+        <v>0</v>
+      </c>
+      <c r="I33" s="252">
+        <v>0</v>
+      </c>
+      <c r="J33" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76472,25 +76955,25 @@
       <c r="C34" s="48">
         <v>0</v>
       </c>
-      <c r="D34" s="255">
-        <v>0</v>
-      </c>
-      <c r="E34" s="255">
-        <v>0</v>
-      </c>
-      <c r="F34" s="255">
-        <v>0</v>
-      </c>
-      <c r="G34" s="255">
-        <v>0</v>
-      </c>
-      <c r="H34" s="255">
-        <v>0</v>
-      </c>
-      <c r="I34" s="255">
-        <v>0</v>
-      </c>
-      <c r="J34" s="255">
+      <c r="D34" s="252">
+        <v>0</v>
+      </c>
+      <c r="E34" s="252">
+        <v>0</v>
+      </c>
+      <c r="F34" s="252">
+        <v>0</v>
+      </c>
+      <c r="G34" s="252">
+        <v>0</v>
+      </c>
+      <c r="H34" s="252">
+        <v>0</v>
+      </c>
+      <c r="I34" s="252">
+        <v>0</v>
+      </c>
+      <c r="J34" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76501,25 +76984,25 @@
       <c r="C35" s="48">
         <v>0</v>
       </c>
-      <c r="D35" s="255">
-        <v>0</v>
-      </c>
-      <c r="E35" s="255">
-        <v>0</v>
-      </c>
-      <c r="F35" s="255">
-        <v>0</v>
-      </c>
-      <c r="G35" s="255">
-        <v>0</v>
-      </c>
-      <c r="H35" s="255">
-        <v>0</v>
-      </c>
-      <c r="I35" s="255">
-        <v>0</v>
-      </c>
-      <c r="J35" s="255">
+      <c r="D35" s="252">
+        <v>0</v>
+      </c>
+      <c r="E35" s="252">
+        <v>0</v>
+      </c>
+      <c r="F35" s="252">
+        <v>0</v>
+      </c>
+      <c r="G35" s="252">
+        <v>0</v>
+      </c>
+      <c r="H35" s="252">
+        <v>0</v>
+      </c>
+      <c r="I35" s="252">
+        <v>0</v>
+      </c>
+      <c r="J35" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76530,25 +77013,25 @@
       <c r="C36" s="48">
         <v>0</v>
       </c>
-      <c r="D36" s="255">
-        <v>0</v>
-      </c>
-      <c r="E36" s="255">
-        <v>0</v>
-      </c>
-      <c r="F36" s="255">
-        <v>0</v>
-      </c>
-      <c r="G36" s="255">
-        <v>0</v>
-      </c>
-      <c r="H36" s="255">
-        <v>0</v>
-      </c>
-      <c r="I36" s="255">
-        <v>0</v>
-      </c>
-      <c r="J36" s="255">
+      <c r="D36" s="252">
+        <v>0</v>
+      </c>
+      <c r="E36" s="252">
+        <v>0</v>
+      </c>
+      <c r="F36" s="252">
+        <v>0</v>
+      </c>
+      <c r="G36" s="252">
+        <v>0</v>
+      </c>
+      <c r="H36" s="252">
+        <v>0</v>
+      </c>
+      <c r="I36" s="252">
+        <v>0</v>
+      </c>
+      <c r="J36" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76559,25 +77042,25 @@
       <c r="C37" s="48">
         <v>0</v>
       </c>
-      <c r="D37" s="255">
-        <v>0</v>
-      </c>
-      <c r="E37" s="255">
-        <v>0</v>
-      </c>
-      <c r="F37" s="255">
-        <v>0</v>
-      </c>
-      <c r="G37" s="255">
-        <v>0</v>
-      </c>
-      <c r="H37" s="255">
-        <v>0</v>
-      </c>
-      <c r="I37" s="255">
-        <v>0</v>
-      </c>
-      <c r="J37" s="255">
+      <c r="D37" s="252">
+        <v>0</v>
+      </c>
+      <c r="E37" s="252">
+        <v>0</v>
+      </c>
+      <c r="F37" s="252">
+        <v>0</v>
+      </c>
+      <c r="G37" s="252">
+        <v>0</v>
+      </c>
+      <c r="H37" s="252">
+        <v>0</v>
+      </c>
+      <c r="I37" s="252">
+        <v>0</v>
+      </c>
+      <c r="J37" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76588,25 +77071,25 @@
       <c r="C38" s="48">
         <v>0</v>
       </c>
-      <c r="D38" s="255">
-        <v>0</v>
-      </c>
-      <c r="E38" s="255">
-        <v>0</v>
-      </c>
-      <c r="F38" s="255">
-        <v>0</v>
-      </c>
-      <c r="G38" s="255">
-        <v>0</v>
-      </c>
-      <c r="H38" s="255">
-        <v>0</v>
-      </c>
-      <c r="I38" s="255">
-        <v>0</v>
-      </c>
-      <c r="J38" s="255">
+      <c r="D38" s="252">
+        <v>0</v>
+      </c>
+      <c r="E38" s="252">
+        <v>0</v>
+      </c>
+      <c r="F38" s="252">
+        <v>0</v>
+      </c>
+      <c r="G38" s="252">
+        <v>0</v>
+      </c>
+      <c r="H38" s="252">
+        <v>0</v>
+      </c>
+      <c r="I38" s="252">
+        <v>0</v>
+      </c>
+      <c r="J38" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76617,25 +77100,25 @@
       <c r="C39" s="48">
         <v>0</v>
       </c>
-      <c r="D39" s="255">
-        <v>0</v>
-      </c>
-      <c r="E39" s="255">
-        <v>0</v>
-      </c>
-      <c r="F39" s="255">
-        <v>0</v>
-      </c>
-      <c r="G39" s="255">
-        <v>0</v>
-      </c>
-      <c r="H39" s="255">
-        <v>0</v>
-      </c>
-      <c r="I39" s="255">
-        <v>0</v>
-      </c>
-      <c r="J39" s="255">
+      <c r="D39" s="252">
+        <v>0</v>
+      </c>
+      <c r="E39" s="252">
+        <v>0</v>
+      </c>
+      <c r="F39" s="252">
+        <v>0</v>
+      </c>
+      <c r="G39" s="252">
+        <v>0</v>
+      </c>
+      <c r="H39" s="252">
+        <v>0</v>
+      </c>
+      <c r="I39" s="252">
+        <v>0</v>
+      </c>
+      <c r="J39" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76646,25 +77129,25 @@
       <c r="C40" s="48">
         <v>0</v>
       </c>
-      <c r="D40" s="255">
-        <v>0</v>
-      </c>
-      <c r="E40" s="255">
-        <v>0</v>
-      </c>
-      <c r="F40" s="255">
-        <v>0</v>
-      </c>
-      <c r="G40" s="255">
-        <v>0</v>
-      </c>
-      <c r="H40" s="255">
-        <v>0</v>
-      </c>
-      <c r="I40" s="255">
-        <v>0</v>
-      </c>
-      <c r="J40" s="255">
+      <c r="D40" s="252">
+        <v>0</v>
+      </c>
+      <c r="E40" s="252">
+        <v>0</v>
+      </c>
+      <c r="F40" s="252">
+        <v>0</v>
+      </c>
+      <c r="G40" s="252">
+        <v>0</v>
+      </c>
+      <c r="H40" s="252">
+        <v>0</v>
+      </c>
+      <c r="I40" s="252">
+        <v>0</v>
+      </c>
+      <c r="J40" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76675,25 +77158,25 @@
       <c r="C41" s="48">
         <v>0</v>
       </c>
-      <c r="D41" s="255">
-        <v>0</v>
-      </c>
-      <c r="E41" s="255">
-        <v>0</v>
-      </c>
-      <c r="F41" s="255">
-        <v>0</v>
-      </c>
-      <c r="G41" s="255">
-        <v>0</v>
-      </c>
-      <c r="H41" s="255">
-        <v>0</v>
-      </c>
-      <c r="I41" s="255">
-        <v>0</v>
-      </c>
-      <c r="J41" s="255">
+      <c r="D41" s="252">
+        <v>0</v>
+      </c>
+      <c r="E41" s="252">
+        <v>0</v>
+      </c>
+      <c r="F41" s="252">
+        <v>0</v>
+      </c>
+      <c r="G41" s="252">
+        <v>0</v>
+      </c>
+      <c r="H41" s="252">
+        <v>0</v>
+      </c>
+      <c r="I41" s="252">
+        <v>0</v>
+      </c>
+      <c r="J41" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76704,25 +77187,25 @@
       <c r="C42" s="48">
         <v>0</v>
       </c>
-      <c r="D42" s="255">
-        <v>0</v>
-      </c>
-      <c r="E42" s="255">
-        <v>0</v>
-      </c>
-      <c r="F42" s="255">
-        <v>0</v>
-      </c>
-      <c r="G42" s="255">
-        <v>0</v>
-      </c>
-      <c r="H42" s="255">
-        <v>0</v>
-      </c>
-      <c r="I42" s="255">
-        <v>0</v>
-      </c>
-      <c r="J42" s="255">
+      <c r="D42" s="252">
+        <v>0</v>
+      </c>
+      <c r="E42" s="252">
+        <v>0</v>
+      </c>
+      <c r="F42" s="252">
+        <v>0</v>
+      </c>
+      <c r="G42" s="252">
+        <v>0</v>
+      </c>
+      <c r="H42" s="252">
+        <v>0</v>
+      </c>
+      <c r="I42" s="252">
+        <v>0</v>
+      </c>
+      <c r="J42" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76733,25 +77216,25 @@
       <c r="C43" s="48">
         <v>0</v>
       </c>
-      <c r="D43" s="255">
-        <v>0</v>
-      </c>
-      <c r="E43" s="255">
-        <v>0</v>
-      </c>
-      <c r="F43" s="255">
-        <v>0</v>
-      </c>
-      <c r="G43" s="255">
-        <v>0</v>
-      </c>
-      <c r="H43" s="255">
-        <v>0</v>
-      </c>
-      <c r="I43" s="255">
-        <v>0</v>
-      </c>
-      <c r="J43" s="255">
+      <c r="D43" s="252">
+        <v>0</v>
+      </c>
+      <c r="E43" s="252">
+        <v>0</v>
+      </c>
+      <c r="F43" s="252">
+        <v>0</v>
+      </c>
+      <c r="G43" s="252">
+        <v>0</v>
+      </c>
+      <c r="H43" s="252">
+        <v>0</v>
+      </c>
+      <c r="I43" s="252">
+        <v>0</v>
+      </c>
+      <c r="J43" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76762,25 +77245,25 @@
       <c r="C44" s="48">
         <v>0</v>
       </c>
-      <c r="D44" s="255">
-        <v>0</v>
-      </c>
-      <c r="E44" s="255">
-        <v>0</v>
-      </c>
-      <c r="F44" s="255">
-        <v>0</v>
-      </c>
-      <c r="G44" s="255">
-        <v>0</v>
-      </c>
-      <c r="H44" s="255">
-        <v>0</v>
-      </c>
-      <c r="I44" s="255">
-        <v>0</v>
-      </c>
-      <c r="J44" s="255">
+      <c r="D44" s="252">
+        <v>0</v>
+      </c>
+      <c r="E44" s="252">
+        <v>0</v>
+      </c>
+      <c r="F44" s="252">
+        <v>0</v>
+      </c>
+      <c r="G44" s="252">
+        <v>0</v>
+      </c>
+      <c r="H44" s="252">
+        <v>0</v>
+      </c>
+      <c r="I44" s="252">
+        <v>0</v>
+      </c>
+      <c r="J44" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76791,25 +77274,25 @@
       <c r="C45" s="48">
         <v>0</v>
       </c>
-      <c r="D45" s="255">
-        <v>0</v>
-      </c>
-      <c r="E45" s="255">
-        <v>0</v>
-      </c>
-      <c r="F45" s="255">
-        <v>0</v>
-      </c>
-      <c r="G45" s="255">
-        <v>0</v>
-      </c>
-      <c r="H45" s="255">
-        <v>0</v>
-      </c>
-      <c r="I45" s="255">
-        <v>0</v>
-      </c>
-      <c r="J45" s="255">
+      <c r="D45" s="252">
+        <v>0</v>
+      </c>
+      <c r="E45" s="252">
+        <v>0</v>
+      </c>
+      <c r="F45" s="252">
+        <v>0</v>
+      </c>
+      <c r="G45" s="252">
+        <v>0</v>
+      </c>
+      <c r="H45" s="252">
+        <v>0</v>
+      </c>
+      <c r="I45" s="252">
+        <v>0</v>
+      </c>
+      <c r="J45" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76820,25 +77303,25 @@
       <c r="C46" s="48">
         <v>0</v>
       </c>
-      <c r="D46" s="255">
-        <v>0</v>
-      </c>
-      <c r="E46" s="255">
-        <v>0</v>
-      </c>
-      <c r="F46" s="255">
-        <v>0</v>
-      </c>
-      <c r="G46" s="255">
-        <v>0</v>
-      </c>
-      <c r="H46" s="255">
-        <v>0</v>
-      </c>
-      <c r="I46" s="255">
-        <v>0</v>
-      </c>
-      <c r="J46" s="255">
+      <c r="D46" s="252">
+        <v>0</v>
+      </c>
+      <c r="E46" s="252">
+        <v>0</v>
+      </c>
+      <c r="F46" s="252">
+        <v>0</v>
+      </c>
+      <c r="G46" s="252">
+        <v>0</v>
+      </c>
+      <c r="H46" s="252">
+        <v>0</v>
+      </c>
+      <c r="I46" s="252">
+        <v>0</v>
+      </c>
+      <c r="J46" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76849,25 +77332,25 @@
       <c r="C47" s="48">
         <v>0</v>
       </c>
-      <c r="D47" s="255">
-        <v>0</v>
-      </c>
-      <c r="E47" s="255">
-        <v>0</v>
-      </c>
-      <c r="F47" s="255">
-        <v>0</v>
-      </c>
-      <c r="G47" s="255">
-        <v>0</v>
-      </c>
-      <c r="H47" s="255">
-        <v>0</v>
-      </c>
-      <c r="I47" s="255">
-        <v>0</v>
-      </c>
-      <c r="J47" s="255">
+      <c r="D47" s="252">
+        <v>0</v>
+      </c>
+      <c r="E47" s="252">
+        <v>0</v>
+      </c>
+      <c r="F47" s="252">
+        <v>0</v>
+      </c>
+      <c r="G47" s="252">
+        <v>0</v>
+      </c>
+      <c r="H47" s="252">
+        <v>0</v>
+      </c>
+      <c r="I47" s="252">
+        <v>0</v>
+      </c>
+      <c r="J47" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76878,25 +77361,25 @@
       <c r="C48" s="48">
         <v>0</v>
       </c>
-      <c r="D48" s="255">
-        <v>0</v>
-      </c>
-      <c r="E48" s="255">
-        <v>0</v>
-      </c>
-      <c r="F48" s="255">
-        <v>0</v>
-      </c>
-      <c r="G48" s="255">
-        <v>0</v>
-      </c>
-      <c r="H48" s="255">
-        <v>0</v>
-      </c>
-      <c r="I48" s="255">
-        <v>0</v>
-      </c>
-      <c r="J48" s="255">
+      <c r="D48" s="252">
+        <v>0</v>
+      </c>
+      <c r="E48" s="252">
+        <v>0</v>
+      </c>
+      <c r="F48" s="252">
+        <v>0</v>
+      </c>
+      <c r="G48" s="252">
+        <v>0</v>
+      </c>
+      <c r="H48" s="252">
+        <v>0</v>
+      </c>
+      <c r="I48" s="252">
+        <v>0</v>
+      </c>
+      <c r="J48" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76907,25 +77390,25 @@
       <c r="C49" s="48">
         <v>0</v>
       </c>
-      <c r="D49" s="255">
-        <v>0</v>
-      </c>
-      <c r="E49" s="255">
-        <v>0</v>
-      </c>
-      <c r="F49" s="255">
-        <v>0</v>
-      </c>
-      <c r="G49" s="255">
-        <v>0</v>
-      </c>
-      <c r="H49" s="255">
-        <v>0</v>
-      </c>
-      <c r="I49" s="255">
-        <v>0</v>
-      </c>
-      <c r="J49" s="255">
+      <c r="D49" s="252">
+        <v>0</v>
+      </c>
+      <c r="E49" s="252">
+        <v>0</v>
+      </c>
+      <c r="F49" s="252">
+        <v>0</v>
+      </c>
+      <c r="G49" s="252">
+        <v>0</v>
+      </c>
+      <c r="H49" s="252">
+        <v>0</v>
+      </c>
+      <c r="I49" s="252">
+        <v>0</v>
+      </c>
+      <c r="J49" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76936,25 +77419,25 @@
       <c r="C50" s="48">
         <v>0</v>
       </c>
-      <c r="D50" s="255">
-        <v>0</v>
-      </c>
-      <c r="E50" s="255">
-        <v>0</v>
-      </c>
-      <c r="F50" s="255">
-        <v>0</v>
-      </c>
-      <c r="G50" s="255">
-        <v>0</v>
-      </c>
-      <c r="H50" s="255">
-        <v>0</v>
-      </c>
-      <c r="I50" s="255">
-        <v>0</v>
-      </c>
-      <c r="J50" s="255">
+      <c r="D50" s="252">
+        <v>0</v>
+      </c>
+      <c r="E50" s="252">
+        <v>0</v>
+      </c>
+      <c r="F50" s="252">
+        <v>0</v>
+      </c>
+      <c r="G50" s="252">
+        <v>0</v>
+      </c>
+      <c r="H50" s="252">
+        <v>0</v>
+      </c>
+      <c r="I50" s="252">
+        <v>0</v>
+      </c>
+      <c r="J50" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76965,25 +77448,25 @@
       <c r="C51" s="48">
         <v>0</v>
       </c>
-      <c r="D51" s="255">
-        <v>0</v>
-      </c>
-      <c r="E51" s="255">
-        <v>0</v>
-      </c>
-      <c r="F51" s="255">
-        <v>0</v>
-      </c>
-      <c r="G51" s="255">
-        <v>0</v>
-      </c>
-      <c r="H51" s="255">
-        <v>0</v>
-      </c>
-      <c r="I51" s="255">
-        <v>0</v>
-      </c>
-      <c r="J51" s="255">
+      <c r="D51" s="252">
+        <v>0</v>
+      </c>
+      <c r="E51" s="252">
+        <v>0</v>
+      </c>
+      <c r="F51" s="252">
+        <v>0</v>
+      </c>
+      <c r="G51" s="252">
+        <v>0</v>
+      </c>
+      <c r="H51" s="252">
+        <v>0</v>
+      </c>
+      <c r="I51" s="252">
+        <v>0</v>
+      </c>
+      <c r="J51" s="252">
         <v>0</v>
       </c>
     </row>
@@ -76994,25 +77477,25 @@
       <c r="C52" s="48">
         <v>0</v>
       </c>
-      <c r="D52" s="255">
-        <v>0</v>
-      </c>
-      <c r="E52" s="255">
-        <v>0</v>
-      </c>
-      <c r="F52" s="255">
-        <v>0</v>
-      </c>
-      <c r="G52" s="255">
-        <v>0</v>
-      </c>
-      <c r="H52" s="255">
-        <v>0</v>
-      </c>
-      <c r="I52" s="255">
-        <v>0</v>
-      </c>
-      <c r="J52" s="255">
+      <c r="D52" s="252">
+        <v>0</v>
+      </c>
+      <c r="E52" s="252">
+        <v>0</v>
+      </c>
+      <c r="F52" s="252">
+        <v>0</v>
+      </c>
+      <c r="G52" s="252">
+        <v>0</v>
+      </c>
+      <c r="H52" s="252">
+        <v>0</v>
+      </c>
+      <c r="I52" s="252">
+        <v>0</v>
+      </c>
+      <c r="J52" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77023,25 +77506,25 @@
       <c r="C53" s="48">
         <v>0</v>
       </c>
-      <c r="D53" s="255">
-        <v>0</v>
-      </c>
-      <c r="E53" s="255">
-        <v>0</v>
-      </c>
-      <c r="F53" s="255">
-        <v>0</v>
-      </c>
-      <c r="G53" s="255">
-        <v>0</v>
-      </c>
-      <c r="H53" s="255">
-        <v>0</v>
-      </c>
-      <c r="I53" s="255">
-        <v>0</v>
-      </c>
-      <c r="J53" s="255">
+      <c r="D53" s="252">
+        <v>0</v>
+      </c>
+      <c r="E53" s="252">
+        <v>0</v>
+      </c>
+      <c r="F53" s="252">
+        <v>0</v>
+      </c>
+      <c r="G53" s="252">
+        <v>0</v>
+      </c>
+      <c r="H53" s="252">
+        <v>0</v>
+      </c>
+      <c r="I53" s="252">
+        <v>0</v>
+      </c>
+      <c r="J53" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77052,25 +77535,25 @@
       <c r="C54" s="48">
         <v>0</v>
       </c>
-      <c r="D54" s="255">
-        <v>0</v>
-      </c>
-      <c r="E54" s="255">
-        <v>0</v>
-      </c>
-      <c r="F54" s="255">
-        <v>0</v>
-      </c>
-      <c r="G54" s="255">
-        <v>0</v>
-      </c>
-      <c r="H54" s="255">
-        <v>0</v>
-      </c>
-      <c r="I54" s="255">
-        <v>0</v>
-      </c>
-      <c r="J54" s="255">
+      <c r="D54" s="252">
+        <v>0</v>
+      </c>
+      <c r="E54" s="252">
+        <v>0</v>
+      </c>
+      <c r="F54" s="252">
+        <v>0</v>
+      </c>
+      <c r="G54" s="252">
+        <v>0</v>
+      </c>
+      <c r="H54" s="252">
+        <v>0</v>
+      </c>
+      <c r="I54" s="252">
+        <v>0</v>
+      </c>
+      <c r="J54" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77081,25 +77564,25 @@
       <c r="C55" s="48">
         <v>0</v>
       </c>
-      <c r="D55" s="255">
-        <v>0</v>
-      </c>
-      <c r="E55" s="255">
-        <v>0</v>
-      </c>
-      <c r="F55" s="255">
-        <v>0</v>
-      </c>
-      <c r="G55" s="255">
-        <v>0</v>
-      </c>
-      <c r="H55" s="255">
-        <v>0</v>
-      </c>
-      <c r="I55" s="255">
-        <v>0</v>
-      </c>
-      <c r="J55" s="255">
+      <c r="D55" s="252">
+        <v>0</v>
+      </c>
+      <c r="E55" s="252">
+        <v>0</v>
+      </c>
+      <c r="F55" s="252">
+        <v>0</v>
+      </c>
+      <c r="G55" s="252">
+        <v>0</v>
+      </c>
+      <c r="H55" s="252">
+        <v>0</v>
+      </c>
+      <c r="I55" s="252">
+        <v>0</v>
+      </c>
+      <c r="J55" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77110,25 +77593,25 @@
       <c r="C56" s="48">
         <v>0</v>
       </c>
-      <c r="D56" s="255">
-        <v>0</v>
-      </c>
-      <c r="E56" s="255">
-        <v>0</v>
-      </c>
-      <c r="F56" s="255">
-        <v>0</v>
-      </c>
-      <c r="G56" s="255">
-        <v>0</v>
-      </c>
-      <c r="H56" s="255">
-        <v>0</v>
-      </c>
-      <c r="I56" s="255">
-        <v>0</v>
-      </c>
-      <c r="J56" s="255">
+      <c r="D56" s="252">
+        <v>0</v>
+      </c>
+      <c r="E56" s="252">
+        <v>0</v>
+      </c>
+      <c r="F56" s="252">
+        <v>0</v>
+      </c>
+      <c r="G56" s="252">
+        <v>0</v>
+      </c>
+      <c r="H56" s="252">
+        <v>0</v>
+      </c>
+      <c r="I56" s="252">
+        <v>0</v>
+      </c>
+      <c r="J56" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77139,25 +77622,25 @@
       <c r="C57" s="48">
         <v>0</v>
       </c>
-      <c r="D57" s="255">
-        <v>0</v>
-      </c>
-      <c r="E57" s="255">
-        <v>0</v>
-      </c>
-      <c r="F57" s="255">
-        <v>0</v>
-      </c>
-      <c r="G57" s="255">
-        <v>0</v>
-      </c>
-      <c r="H57" s="255">
-        <v>0</v>
-      </c>
-      <c r="I57" s="255">
-        <v>0</v>
-      </c>
-      <c r="J57" s="255">
+      <c r="D57" s="252">
+        <v>0</v>
+      </c>
+      <c r="E57" s="252">
+        <v>0</v>
+      </c>
+      <c r="F57" s="252">
+        <v>0</v>
+      </c>
+      <c r="G57" s="252">
+        <v>0</v>
+      </c>
+      <c r="H57" s="252">
+        <v>0</v>
+      </c>
+      <c r="I57" s="252">
+        <v>0</v>
+      </c>
+      <c r="J57" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77168,25 +77651,25 @@
       <c r="C58" s="48">
         <v>0</v>
       </c>
-      <c r="D58" s="255">
-        <v>0</v>
-      </c>
-      <c r="E58" s="255">
-        <v>0</v>
-      </c>
-      <c r="F58" s="255">
-        <v>0</v>
-      </c>
-      <c r="G58" s="255">
-        <v>0</v>
-      </c>
-      <c r="H58" s="255">
-        <v>0</v>
-      </c>
-      <c r="I58" s="255">
-        <v>0</v>
-      </c>
-      <c r="J58" s="255">
+      <c r="D58" s="252">
+        <v>0</v>
+      </c>
+      <c r="E58" s="252">
+        <v>0</v>
+      </c>
+      <c r="F58" s="252">
+        <v>0</v>
+      </c>
+      <c r="G58" s="252">
+        <v>0</v>
+      </c>
+      <c r="H58" s="252">
+        <v>0</v>
+      </c>
+      <c r="I58" s="252">
+        <v>0</v>
+      </c>
+      <c r="J58" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77197,25 +77680,25 @@
       <c r="C59" s="48">
         <v>0</v>
       </c>
-      <c r="D59" s="255">
-        <v>0</v>
-      </c>
-      <c r="E59" s="255">
-        <v>0</v>
-      </c>
-      <c r="F59" s="255">
-        <v>0</v>
-      </c>
-      <c r="G59" s="255">
-        <v>0</v>
-      </c>
-      <c r="H59" s="255">
-        <v>0</v>
-      </c>
-      <c r="I59" s="255">
-        <v>0</v>
-      </c>
-      <c r="J59" s="255">
+      <c r="D59" s="252">
+        <v>0</v>
+      </c>
+      <c r="E59" s="252">
+        <v>0</v>
+      </c>
+      <c r="F59" s="252">
+        <v>0</v>
+      </c>
+      <c r="G59" s="252">
+        <v>0</v>
+      </c>
+      <c r="H59" s="252">
+        <v>0</v>
+      </c>
+      <c r="I59" s="252">
+        <v>0</v>
+      </c>
+      <c r="J59" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77226,25 +77709,25 @@
       <c r="C60" s="48">
         <v>0</v>
       </c>
-      <c r="D60" s="255">
-        <v>0</v>
-      </c>
-      <c r="E60" s="255">
-        <v>0</v>
-      </c>
-      <c r="F60" s="255">
-        <v>0</v>
-      </c>
-      <c r="G60" s="255">
-        <v>0</v>
-      </c>
-      <c r="H60" s="255">
-        <v>0</v>
-      </c>
-      <c r="I60" s="255">
-        <v>0</v>
-      </c>
-      <c r="J60" s="255">
+      <c r="D60" s="252">
+        <v>0</v>
+      </c>
+      <c r="E60" s="252">
+        <v>0</v>
+      </c>
+      <c r="F60" s="252">
+        <v>0</v>
+      </c>
+      <c r="G60" s="252">
+        <v>0</v>
+      </c>
+      <c r="H60" s="252">
+        <v>0</v>
+      </c>
+      <c r="I60" s="252">
+        <v>0</v>
+      </c>
+      <c r="J60" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77255,25 +77738,25 @@
       <c r="C61" s="48">
         <v>0</v>
       </c>
-      <c r="D61" s="255">
-        <v>0</v>
-      </c>
-      <c r="E61" s="255">
-        <v>0</v>
-      </c>
-      <c r="F61" s="255">
-        <v>0</v>
-      </c>
-      <c r="G61" s="255">
-        <v>0</v>
-      </c>
-      <c r="H61" s="255">
-        <v>0</v>
-      </c>
-      <c r="I61" s="255">
-        <v>0</v>
-      </c>
-      <c r="J61" s="255">
+      <c r="D61" s="252">
+        <v>0</v>
+      </c>
+      <c r="E61" s="252">
+        <v>0</v>
+      </c>
+      <c r="F61" s="252">
+        <v>0</v>
+      </c>
+      <c r="G61" s="252">
+        <v>0</v>
+      </c>
+      <c r="H61" s="252">
+        <v>0</v>
+      </c>
+      <c r="I61" s="252">
+        <v>0</v>
+      </c>
+      <c r="J61" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77284,25 +77767,25 @@
       <c r="C62" s="48">
         <v>0</v>
       </c>
-      <c r="D62" s="255">
-        <v>0</v>
-      </c>
-      <c r="E62" s="255">
-        <v>0</v>
-      </c>
-      <c r="F62" s="255">
-        <v>0</v>
-      </c>
-      <c r="G62" s="255">
-        <v>0</v>
-      </c>
-      <c r="H62" s="255">
-        <v>0</v>
-      </c>
-      <c r="I62" s="255">
-        <v>0</v>
-      </c>
-      <c r="J62" s="255">
+      <c r="D62" s="252">
+        <v>0</v>
+      </c>
+      <c r="E62" s="252">
+        <v>0</v>
+      </c>
+      <c r="F62" s="252">
+        <v>0</v>
+      </c>
+      <c r="G62" s="252">
+        <v>0</v>
+      </c>
+      <c r="H62" s="252">
+        <v>0</v>
+      </c>
+      <c r="I62" s="252">
+        <v>0</v>
+      </c>
+      <c r="J62" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77313,25 +77796,25 @@
       <c r="C63" s="48">
         <v>0</v>
       </c>
-      <c r="D63" s="255">
-        <v>0</v>
-      </c>
-      <c r="E63" s="255">
-        <v>0</v>
-      </c>
-      <c r="F63" s="255">
-        <v>0</v>
-      </c>
-      <c r="G63" s="255">
-        <v>0</v>
-      </c>
-      <c r="H63" s="255">
-        <v>0</v>
-      </c>
-      <c r="I63" s="255">
-        <v>0</v>
-      </c>
-      <c r="J63" s="255">
+      <c r="D63" s="252">
+        <v>0</v>
+      </c>
+      <c r="E63" s="252">
+        <v>0</v>
+      </c>
+      <c r="F63" s="252">
+        <v>0</v>
+      </c>
+      <c r="G63" s="252">
+        <v>0</v>
+      </c>
+      <c r="H63" s="252">
+        <v>0</v>
+      </c>
+      <c r="I63" s="252">
+        <v>0</v>
+      </c>
+      <c r="J63" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77342,25 +77825,25 @@
       <c r="C64" s="48">
         <v>0</v>
       </c>
-      <c r="D64" s="255">
-        <v>0</v>
-      </c>
-      <c r="E64" s="255">
-        <v>0</v>
-      </c>
-      <c r="F64" s="255">
-        <v>0</v>
-      </c>
-      <c r="G64" s="255">
-        <v>0</v>
-      </c>
-      <c r="H64" s="255">
-        <v>0</v>
-      </c>
-      <c r="I64" s="255">
-        <v>0</v>
-      </c>
-      <c r="J64" s="255">
+      <c r="D64" s="252">
+        <v>0</v>
+      </c>
+      <c r="E64" s="252">
+        <v>0</v>
+      </c>
+      <c r="F64" s="252">
+        <v>0</v>
+      </c>
+      <c r="G64" s="252">
+        <v>0</v>
+      </c>
+      <c r="H64" s="252">
+        <v>0</v>
+      </c>
+      <c r="I64" s="252">
+        <v>0</v>
+      </c>
+      <c r="J64" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77371,25 +77854,25 @@
       <c r="C65" s="48">
         <v>0</v>
       </c>
-      <c r="D65" s="255">
-        <v>0</v>
-      </c>
-      <c r="E65" s="255">
-        <v>0</v>
-      </c>
-      <c r="F65" s="255">
-        <v>0</v>
-      </c>
-      <c r="G65" s="255">
-        <v>0</v>
-      </c>
-      <c r="H65" s="255">
-        <v>0</v>
-      </c>
-      <c r="I65" s="255">
-        <v>0</v>
-      </c>
-      <c r="J65" s="255">
+      <c r="D65" s="252">
+        <v>0</v>
+      </c>
+      <c r="E65" s="252">
+        <v>0</v>
+      </c>
+      <c r="F65" s="252">
+        <v>0</v>
+      </c>
+      <c r="G65" s="252">
+        <v>0</v>
+      </c>
+      <c r="H65" s="252">
+        <v>0</v>
+      </c>
+      <c r="I65" s="252">
+        <v>0</v>
+      </c>
+      <c r="J65" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77400,25 +77883,25 @@
       <c r="C66" s="48">
         <v>0</v>
       </c>
-      <c r="D66" s="255">
-        <v>0</v>
-      </c>
-      <c r="E66" s="255">
-        <v>0</v>
-      </c>
-      <c r="F66" s="255">
-        <v>0</v>
-      </c>
-      <c r="G66" s="255">
-        <v>0</v>
-      </c>
-      <c r="H66" s="255">
-        <v>0</v>
-      </c>
-      <c r="I66" s="255">
-        <v>0</v>
-      </c>
-      <c r="J66" s="255">
+      <c r="D66" s="252">
+        <v>0</v>
+      </c>
+      <c r="E66" s="252">
+        <v>0</v>
+      </c>
+      <c r="F66" s="252">
+        <v>0</v>
+      </c>
+      <c r="G66" s="252">
+        <v>0</v>
+      </c>
+      <c r="H66" s="252">
+        <v>0</v>
+      </c>
+      <c r="I66" s="252">
+        <v>0</v>
+      </c>
+      <c r="J66" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77429,25 +77912,25 @@
       <c r="C67" s="48">
         <v>0</v>
       </c>
-      <c r="D67" s="255">
-        <v>0</v>
-      </c>
-      <c r="E67" s="255">
-        <v>0</v>
-      </c>
-      <c r="F67" s="255">
-        <v>0</v>
-      </c>
-      <c r="G67" s="255">
-        <v>0</v>
-      </c>
-      <c r="H67" s="255">
-        <v>0</v>
-      </c>
-      <c r="I67" s="255">
-        <v>0</v>
-      </c>
-      <c r="J67" s="255">
+      <c r="D67" s="252">
+        <v>0</v>
+      </c>
+      <c r="E67" s="252">
+        <v>0</v>
+      </c>
+      <c r="F67" s="252">
+        <v>0</v>
+      </c>
+      <c r="G67" s="252">
+        <v>0</v>
+      </c>
+      <c r="H67" s="252">
+        <v>0</v>
+      </c>
+      <c r="I67" s="252">
+        <v>0</v>
+      </c>
+      <c r="J67" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77458,25 +77941,25 @@
       <c r="C68" s="48">
         <v>0</v>
       </c>
-      <c r="D68" s="255">
-        <v>0</v>
-      </c>
-      <c r="E68" s="255">
-        <v>0</v>
-      </c>
-      <c r="F68" s="255">
-        <v>0</v>
-      </c>
-      <c r="G68" s="255">
-        <v>0</v>
-      </c>
-      <c r="H68" s="255">
-        <v>0</v>
-      </c>
-      <c r="I68" s="255">
-        <v>0</v>
-      </c>
-      <c r="J68" s="255">
+      <c r="D68" s="252">
+        <v>0</v>
+      </c>
+      <c r="E68" s="252">
+        <v>0</v>
+      </c>
+      <c r="F68" s="252">
+        <v>0</v>
+      </c>
+      <c r="G68" s="252">
+        <v>0</v>
+      </c>
+      <c r="H68" s="252">
+        <v>0</v>
+      </c>
+      <c r="I68" s="252">
+        <v>0</v>
+      </c>
+      <c r="J68" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77487,25 +77970,25 @@
       <c r="C69" s="48">
         <v>0</v>
       </c>
-      <c r="D69" s="255">
-        <v>0</v>
-      </c>
-      <c r="E69" s="255">
-        <v>0</v>
-      </c>
-      <c r="F69" s="255">
-        <v>0</v>
-      </c>
-      <c r="G69" s="255">
-        <v>0</v>
-      </c>
-      <c r="H69" s="255">
-        <v>0</v>
-      </c>
-      <c r="I69" s="255">
-        <v>0</v>
-      </c>
-      <c r="J69" s="255">
+      <c r="D69" s="252">
+        <v>0</v>
+      </c>
+      <c r="E69" s="252">
+        <v>0</v>
+      </c>
+      <c r="F69" s="252">
+        <v>0</v>
+      </c>
+      <c r="G69" s="252">
+        <v>0</v>
+      </c>
+      <c r="H69" s="252">
+        <v>0</v>
+      </c>
+      <c r="I69" s="252">
+        <v>0</v>
+      </c>
+      <c r="J69" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77516,25 +77999,25 @@
       <c r="C70" s="48">
         <v>0</v>
       </c>
-      <c r="D70" s="255">
-        <v>0</v>
-      </c>
-      <c r="E70" s="255">
-        <v>0</v>
-      </c>
-      <c r="F70" s="255">
-        <v>0</v>
-      </c>
-      <c r="G70" s="255">
-        <v>0</v>
-      </c>
-      <c r="H70" s="255">
-        <v>0</v>
-      </c>
-      <c r="I70" s="255">
-        <v>0</v>
-      </c>
-      <c r="J70" s="255">
+      <c r="D70" s="252">
+        <v>0</v>
+      </c>
+      <c r="E70" s="252">
+        <v>0</v>
+      </c>
+      <c r="F70" s="252">
+        <v>0</v>
+      </c>
+      <c r="G70" s="252">
+        <v>0</v>
+      </c>
+      <c r="H70" s="252">
+        <v>0</v>
+      </c>
+      <c r="I70" s="252">
+        <v>0</v>
+      </c>
+      <c r="J70" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77545,25 +78028,25 @@
       <c r="C71" s="48">
         <v>0</v>
       </c>
-      <c r="D71" s="255">
-        <v>0</v>
-      </c>
-      <c r="E71" s="255">
-        <v>0</v>
-      </c>
-      <c r="F71" s="255">
-        <v>0</v>
-      </c>
-      <c r="G71" s="255">
-        <v>0</v>
-      </c>
-      <c r="H71" s="255">
-        <v>0</v>
-      </c>
-      <c r="I71" s="255">
-        <v>0</v>
-      </c>
-      <c r="J71" s="255">
+      <c r="D71" s="252">
+        <v>0</v>
+      </c>
+      <c r="E71" s="252">
+        <v>0</v>
+      </c>
+      <c r="F71" s="252">
+        <v>0</v>
+      </c>
+      <c r="G71" s="252">
+        <v>0</v>
+      </c>
+      <c r="H71" s="252">
+        <v>0</v>
+      </c>
+      <c r="I71" s="252">
+        <v>0</v>
+      </c>
+      <c r="J71" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77574,25 +78057,25 @@
       <c r="C72" s="48">
         <v>0</v>
       </c>
-      <c r="D72" s="255">
-        <v>0</v>
-      </c>
-      <c r="E72" s="255">
-        <v>0</v>
-      </c>
-      <c r="F72" s="255">
-        <v>0</v>
-      </c>
-      <c r="G72" s="255">
-        <v>0</v>
-      </c>
-      <c r="H72" s="255">
-        <v>0</v>
-      </c>
-      <c r="I72" s="255">
-        <v>0</v>
-      </c>
-      <c r="J72" s="255">
+      <c r="D72" s="252">
+        <v>0</v>
+      </c>
+      <c r="E72" s="252">
+        <v>0</v>
+      </c>
+      <c r="F72" s="252">
+        <v>0</v>
+      </c>
+      <c r="G72" s="252">
+        <v>0</v>
+      </c>
+      <c r="H72" s="252">
+        <v>0</v>
+      </c>
+      <c r="I72" s="252">
+        <v>0</v>
+      </c>
+      <c r="J72" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77603,28 +78086,28 @@
       <c r="C73" s="48">
         <v>0</v>
       </c>
-      <c r="D73" s="255">
-        <v>0</v>
-      </c>
-      <c r="E73" s="255">
-        <v>0</v>
-      </c>
-      <c r="F73" s="255">
-        <v>0</v>
-      </c>
-      <c r="G73" s="255">
+      <c r="D73" s="252">
+        <v>0</v>
+      </c>
+      <c r="E73" s="252">
+        <v>0</v>
+      </c>
+      <c r="F73" s="252">
+        <v>0</v>
+      </c>
+      <c r="G73" s="252">
         <f>274*0.1</f>
         <v>27.400000000000002</v>
       </c>
-      <c r="H73" s="255">
+      <c r="H73" s="252">
         <f>140*0.1</f>
         <v>14</v>
       </c>
-      <c r="I73" s="255">
+      <c r="I73" s="252">
         <f>70*0.1</f>
         <v>7</v>
       </c>
-      <c r="J73" s="255">
+      <c r="J73" s="252">
         <f>35*0.1</f>
         <v>3.5</v>
       </c>
@@ -77636,28 +78119,28 @@
       <c r="C74" s="48">
         <v>0</v>
       </c>
-      <c r="D74" s="255">
-        <v>0</v>
-      </c>
-      <c r="E74" s="255">
-        <v>0</v>
-      </c>
-      <c r="F74" s="255">
-        <v>0</v>
-      </c>
-      <c r="G74" s="264">
+      <c r="D74" s="252">
+        <v>0</v>
+      </c>
+      <c r="E74" s="252">
+        <v>0</v>
+      </c>
+      <c r="F74" s="252">
+        <v>0</v>
+      </c>
+      <c r="G74" s="261">
         <f>274*(1-0.108)</f>
         <v>244.40800000000002</v>
       </c>
-      <c r="H74" s="264">
+      <c r="H74" s="261">
         <f>140*(1-0.108)</f>
         <v>124.88</v>
       </c>
-      <c r="I74" s="264">
+      <c r="I74" s="261">
         <f>70*(1-0.108)</f>
         <v>62.44</v>
       </c>
-      <c r="J74" s="264">
+      <c r="J74" s="261">
         <f>35*(1-0.108)</f>
         <v>31.22</v>
       </c>
@@ -77669,25 +78152,25 @@
       <c r="C75" s="48">
         <v>0</v>
       </c>
-      <c r="D75" s="255">
-        <v>0</v>
-      </c>
-      <c r="E75" s="255">
-        <v>0</v>
-      </c>
-      <c r="F75" s="255">
-        <v>0</v>
-      </c>
-      <c r="G75" s="255">
+      <c r="D75" s="252">
+        <v>0</v>
+      </c>
+      <c r="E75" s="252">
+        <v>0</v>
+      </c>
+      <c r="F75" s="252">
+        <v>0</v>
+      </c>
+      <c r="G75" s="252">
         <v>3.02</v>
       </c>
-      <c r="H75" s="255">
+      <c r="H75" s="252">
         <v>3.02</v>
       </c>
-      <c r="I75" s="255">
+      <c r="I75" s="252">
         <v>3.02</v>
       </c>
-      <c r="J75" s="255">
+      <c r="J75" s="252">
         <v>3.02</v>
       </c>
     </row>
@@ -77698,25 +78181,25 @@
       <c r="C76" s="48">
         <v>0</v>
       </c>
-      <c r="D76" s="255">
-        <v>0</v>
-      </c>
-      <c r="E76" s="255">
-        <v>0</v>
-      </c>
-      <c r="F76" s="255">
-        <v>0</v>
-      </c>
-      <c r="G76" s="255">
-        <v>0</v>
-      </c>
-      <c r="H76" s="255">
-        <v>0</v>
-      </c>
-      <c r="I76" s="255">
-        <v>0</v>
-      </c>
-      <c r="J76" s="255">
+      <c r="D76" s="252">
+        <v>0</v>
+      </c>
+      <c r="E76" s="252">
+        <v>0</v>
+      </c>
+      <c r="F76" s="252">
+        <v>0</v>
+      </c>
+      <c r="G76" s="252">
+        <v>0</v>
+      </c>
+      <c r="H76" s="252">
+        <v>0</v>
+      </c>
+      <c r="I76" s="252">
+        <v>0</v>
+      </c>
+      <c r="J76" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77727,25 +78210,25 @@
       <c r="C77" s="48">
         <v>0</v>
       </c>
-      <c r="D77" s="255">
-        <v>0</v>
-      </c>
-      <c r="E77" s="255">
-        <v>0</v>
-      </c>
-      <c r="F77" s="255">
-        <v>0</v>
-      </c>
-      <c r="G77" s="255">
-        <v>0</v>
-      </c>
-      <c r="H77" s="255">
-        <v>0</v>
-      </c>
-      <c r="I77" s="255">
-        <v>0</v>
-      </c>
-      <c r="J77" s="255">
+      <c r="D77" s="252">
+        <v>0</v>
+      </c>
+      <c r="E77" s="252">
+        <v>0</v>
+      </c>
+      <c r="F77" s="252">
+        <v>0</v>
+      </c>
+      <c r="G77" s="252">
+        <v>0</v>
+      </c>
+      <c r="H77" s="252">
+        <v>0</v>
+      </c>
+      <c r="I77" s="252">
+        <v>0</v>
+      </c>
+      <c r="J77" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77756,31 +78239,31 @@
       <c r="C78" s="48">
         <v>0</v>
       </c>
-      <c r="D78" s="255">
+      <c r="D78" s="252">
         <f t="shared" ref="D78:J78" si="0">0.01218+0.00792</f>
         <v>2.01E-2</v>
       </c>
-      <c r="E78" s="255">
+      <c r="E78" s="252">
         <f t="shared" si="0"/>
         <v>2.01E-2</v>
       </c>
-      <c r="F78" s="255">
+      <c r="F78" s="252">
         <f t="shared" si="0"/>
         <v>2.01E-2</v>
       </c>
-      <c r="G78" s="255">
+      <c r="G78" s="252">
         <f t="shared" si="0"/>
         <v>2.01E-2</v>
       </c>
-      <c r="H78" s="255">
+      <c r="H78" s="252">
         <f t="shared" si="0"/>
         <v>2.01E-2</v>
       </c>
-      <c r="I78" s="255">
+      <c r="I78" s="252">
         <f t="shared" si="0"/>
         <v>2.01E-2</v>
       </c>
-      <c r="J78" s="255">
+      <c r="J78" s="252">
         <f t="shared" si="0"/>
         <v>2.01E-2</v>
       </c>
@@ -77792,25 +78275,25 @@
       <c r="C79" s="48">
         <v>0</v>
       </c>
-      <c r="D79" s="255">
-        <v>0</v>
-      </c>
-      <c r="E79" s="255">
-        <v>0</v>
-      </c>
-      <c r="F79" s="255">
-        <v>0</v>
-      </c>
-      <c r="G79" s="255">
-        <v>0</v>
-      </c>
-      <c r="H79" s="255">
-        <v>0</v>
-      </c>
-      <c r="I79" s="255">
-        <v>0</v>
-      </c>
-      <c r="J79" s="255">
+      <c r="D79" s="252">
+        <v>0</v>
+      </c>
+      <c r="E79" s="252">
+        <v>0</v>
+      </c>
+      <c r="F79" s="252">
+        <v>0</v>
+      </c>
+      <c r="G79" s="252">
+        <v>0</v>
+      </c>
+      <c r="H79" s="252">
+        <v>0</v>
+      </c>
+      <c r="I79" s="252">
+        <v>0</v>
+      </c>
+      <c r="J79" s="252">
         <v>0</v>
       </c>
     </row>
@@ -77821,25 +78304,25 @@
       <c r="C80" s="48">
         <v>0</v>
       </c>
-      <c r="D80" s="255">
-        <v>0</v>
-      </c>
-      <c r="E80" s="255">
+      <c r="D80" s="252">
+        <v>0</v>
+      </c>
+      <c r="E80" s="252">
         <v>6.8640000000000007E-2</v>
       </c>
-      <c r="F80" s="255">
+      <c r="F80" s="252">
         <v>6.8640000000000007E-2</v>
       </c>
-      <c r="G80" s="255">
+      <c r="G80" s="252">
         <v>6.8640000000000007E-2</v>
       </c>
-      <c r="H80" s="255">
+      <c r="H80" s="252">
         <v>6.8640000000000007E-2</v>
       </c>
-      <c r="I80" s="255">
+      <c r="I80" s="252">
         <v>6.8640000000000007E-2</v>
       </c>
-      <c r="J80" s="255">
+      <c r="J80" s="252">
         <v>6.8640000000000007E-2</v>
       </c>
     </row>
